--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -9,7 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Customer Modbus Table" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Internal Modbus Table_2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Internal Modbus Table" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2535" uniqueCount="357">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -518,12 +518,21 @@
     <t xml:space="preserve">11061 </t>
   </si>
   <si>
+    <t xml:space="preserve">Solar  R Phase Frequency</t>
+  </si>
+  <si>
     <t xml:space="preserve">11201 </t>
   </si>
   <si>
+    <t xml:space="preserve">Solar Y Phase Frequency</t>
+  </si>
+  <si>
     <t xml:space="preserve">11203</t>
   </si>
   <si>
+    <t xml:space="preserve">Solar B Phase Frequency</t>
+  </si>
+  <si>
     <t xml:space="preserve">11205 </t>
   </si>
   <si>
@@ -599,7 +608,7 @@
     <t xml:space="preserve">Ambient Temperature</t>
   </si>
   <si>
-    <t xml:space="preserve">Celcius</t>
+    <t xml:space="preserve">Celsius</t>
   </si>
   <si>
     <t xml:space="preserve">20005</t>
@@ -692,6 +701,45 @@
     <t xml:space="preserve">30027</t>
   </si>
   <si>
+    <t xml:space="preserve">Over Temperature Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under Temperature Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Over Temperature Delay Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under Temperature Delay Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG Detection Enable/Disable Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: Disabled, 1: Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fan Disable Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30039</t>
+  </si>
+  <si>
     <t xml:space="preserve">Serial Number Lower Half</t>
   </si>
   <si>
@@ -704,6 +752,12 @@
     <t xml:space="preserve">50005</t>
   </si>
   <si>
+    <t xml:space="preserve">Version Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50007</t>
+  </si>
+  <si>
     <t xml:space="preserve">READ INPUT STATUS (Function Code: 0x02)</t>
   </si>
   <si>
@@ -911,10 +965,7 @@
     <t xml:space="preserve">Load On Grid User Disabled</t>
   </si>
   <si>
-    <t xml:space="preserve">Load On Grid Disabled Due To Grid R Phase Unhelathy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
+    <t xml:space="preserve">Load On Grid Disabled Due To Grid R Phase Unhealthy</t>
   </si>
   <si>
     <t xml:space="preserve">Load On Solar User Disabled</t>
@@ -923,70 +974,10 @@
     <t xml:space="preserve">Load On Solar Disabled Due To Solar R Phase Unhealthy</t>
   </si>
   <si>
-    <t xml:space="preserve">READ COIL STATUS (Function Code: 0x01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DG Detection Disabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WRITE SINGLE COIL STATUS (Function Code: 0x05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WRITE SINGLE HOLDING REGISTERS (0x06)</t>
+    <t xml:space="preserve">WRITE MULTIPLE  HOLDING REGISTERS (0x10)</t>
   </si>
   <si>
     <t xml:space="preserve">6001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar  R Phase Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Y Phase Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar B Phase Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Celsius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Over Temperature Setting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under Temperature Setting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Over Temperature Delay Setting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under Temperature Delay Setting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DG Detection Enable/Disable Setting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0: Disabled, 1: Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fan Disable Setting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30039</t>
   </si>
   <si>
     <t xml:space="preserve">Switch Pressed</t>
@@ -1005,13 +996,27 @@
 7:  “Next“, “Decrement” &amp; “Increment” Switch Pressed</t>
   </si>
   <si>
-    <t xml:space="preserve">Version Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid Disabled Due To Grid R Phase Unhealthy</t>
+    <t xml:space="preserve">Functionally Tested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal Only. Not visible to customer. 
+If set to non-zero, indicates product was tested functionally during production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calibrated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal Only. Not visible to customer. 
+If set to non-zero, indicates product was calibrated during production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">READ COIL STATUS (Function Code: 0x01)</t>
   </si>
   <si>
     <t xml:space="preserve">Digital Input 1</t>
@@ -1089,10 +1094,13 @@
     <t xml:space="preserve">LED 8</t>
   </si>
   <si>
+    <t xml:space="preserve">WRITE SINGLE COIL STATUS (Function Code: 0x05)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Restart Controller</t>
   </si>
   <si>
-    <t xml:space="preserve">WRITE MULTIPLE  HOLDING REGISTERS (0x10)</t>
+    <t xml:space="preserve">Internal Only. Not visible to customer. </t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1110,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1154,6 +1162,13 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1275,7 +1290,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1330,6 +1345,10 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3461,7 +3480,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>75</v>
@@ -3479,7 +3498,7 @@
         <v>26</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>2</v>
@@ -3488,7 +3507,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>85</v>
+        <v>167</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>75</v>
@@ -3506,7 +3525,7 @@
         <v>26</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H74" s="7" t="n">
         <v>2</v>
@@ -3515,7 +3534,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>75</v>
@@ -3533,7 +3552,7 @@
         <v>26</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H75" s="7" t="n">
         <v>2</v>
@@ -3542,7 +3561,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>90</v>
@@ -3560,7 +3579,7 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H76" s="7" t="n">
         <v>2</v>
@@ -3569,7 +3588,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>93</v>
@@ -3587,7 +3606,7 @@
         <v>26</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H77" s="7" t="n">
         <v>2</v>
@@ -3596,7 +3615,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>96</v>
@@ -3614,7 +3633,7 @@
         <v>26</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H78" s="7" t="n">
         <v>2</v>
@@ -3623,7 +3642,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>96</v>
@@ -3641,7 +3660,7 @@
         <v>26</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H79" s="7" t="n">
         <v>2</v>
@@ -3650,7 +3669,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>90</v>
@@ -3668,7 +3687,7 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H80" s="7" t="n">
         <v>2</v>
@@ -3677,7 +3696,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>93</v>
@@ -3695,7 +3714,7 @@
         <v>26</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H81" s="7" t="n">
         <v>2</v>
@@ -3704,7 +3723,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>96</v>
@@ -3722,7 +3741,7 @@
         <v>26</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H82" s="7" t="n">
         <v>2</v>
@@ -3731,7 +3750,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>96</v>
@@ -3749,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H83" s="7" t="n">
         <v>2</v>
@@ -3758,7 +3777,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>109</v>
@@ -3776,18 +3795,18 @@
         <v>26</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H84" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>39</v>
@@ -3805,7 +3824,7 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H85" s="7" t="n">
         <v>2</v>
@@ -3814,7 +3833,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>39</v>
@@ -3832,7 +3851,7 @@
         <v>26</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H86" s="7" t="n">
         <v>2</v>
@@ -3841,10 +3860,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>25</v>
@@ -3859,7 +3878,7 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H87" s="7" t="n">
         <v>2</v>
@@ -3868,7 +3887,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>24</v>
@@ -3886,7 +3905,7 @@
         <v>26</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H88" s="7" t="n">
         <v>2</v>
@@ -3895,7 +3914,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="9" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>24</v>
@@ -3913,7 +3932,7 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H89" s="7" t="n">
         <v>2</v>
@@ -3922,7 +3941,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>24</v>
@@ -3940,7 +3959,7 @@
         <v>26</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H90" s="7" t="n">
         <v>2</v>
@@ -3949,7 +3968,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>24</v>
@@ -3967,7 +3986,7 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H91" s="7" t="n">
         <v>2</v>
@@ -3976,7 +3995,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>109</v>
@@ -3994,7 +4013,7 @@
         <v>26</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H92" s="7" t="n">
         <v>2</v>
@@ -4003,7 +4022,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>109</v>
@@ -4021,7 +4040,7 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H93" s="7" t="n">
         <v>2</v>
@@ -4030,7 +4049,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>24</v>
@@ -4048,7 +4067,7 @@
         <v>26</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H94" s="7" t="n">
         <v>2</v>
@@ -4057,7 +4076,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>24</v>
@@ -4075,7 +4094,7 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H95" s="7" t="n">
         <v>2</v>
@@ -4084,7 +4103,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>24</v>
@@ -4102,7 +4121,7 @@
         <v>26</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H96" s="7" t="n">
         <v>2</v>
@@ -4111,7 +4130,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>24</v>
@@ -4129,7 +4148,7 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>2</v>
@@ -4138,7 +4157,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>109</v>
@@ -4156,7 +4175,7 @@
         <v>26</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H98" s="7" t="n">
         <v>2</v>
@@ -4165,7 +4184,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>109</v>
@@ -4183,7 +4202,7 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>2</v>
@@ -4192,10 +4211,10 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C100" s="7" t="s">
         <v>110</v>
@@ -4210,7 +4229,7 @@
         <v>26</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H100" s="7" t="n">
         <v>2</v>
@@ -4219,10 +4238,10 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>110</v>
@@ -4237,7 +4256,7 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H101" s="7" t="n">
         <v>2</v>
@@ -4245,11 +4264,11 @@
       <c r="I101" s="7"/>
     </row>
     <row r="102" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="7" t="s">
-        <v>223</v>
+      <c r="A102" s="9" t="s">
+        <v>226</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>110</v>
@@ -4263,8 +4282,8 @@
       <c r="F102" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G102" s="7" t="s">
-        <v>224</v>
+      <c r="G102" s="10" t="s">
+        <v>227</v>
       </c>
       <c r="H102" s="7" t="n">
         <v>2</v>
@@ -4272,11 +4291,11 @@
       <c r="I102" s="7"/>
     </row>
     <row r="103" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7" t="s">
-        <v>225</v>
+      <c r="A103" s="9" t="s">
+        <v>228</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>110</v>
@@ -4290,8 +4309,8 @@
       <c r="F103" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G103" s="7" t="s">
-        <v>226</v>
+      <c r="G103" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="H103" s="7" t="n">
         <v>2</v>
@@ -4299,266 +4318,270 @@
       <c r="I103" s="7"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A104" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" s="7"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="3"/>
-      <c r="B105" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D105" s="3"/>
-      <c r="E105" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F105" s="3"/>
-      <c r="G105" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I105" s="3"/>
+      <c r="A105" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="H105" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" s="7"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-      <c r="I106" s="5"/>
+      <c r="A106" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H106" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" s="7" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G107" s="7" t="n">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>238</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I107" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G108" s="7" t="n">
-        <v>2</v>
+        <v>26</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>240</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I108" s="7"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G109" s="7" t="n">
-        <v>3</v>
+        <v>26</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I109" s="7"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>0.01</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G110" s="7" t="n">
-        <v>4</v>
+        <v>26</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I110" s="7"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E111" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G111" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H111" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I111" s="7"/>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G112" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H112" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I112" s="7"/>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G113" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H113" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I113" s="7"/>
+      <c r="A112" s="3"/>
+      <c r="B112" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112" s="3"/>
+      <c r="E112" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I112" s="3"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B113" s="5"/>
+      <c r="C113" s="5"/>
+      <c r="D113" s="5"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5"/>
+      <c r="I113" s="5"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>75</v>
@@ -4567,10 +4590,10 @@
         <v>75</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H114" s="7" t="n">
         <v>1</v>
@@ -4579,13 +4602,13 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>75</v>
@@ -4594,10 +4617,10 @@
         <v>75</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>201</v>
+        <v>2</v>
       </c>
       <c r="H115" s="7" t="n">
         <v>1</v>
@@ -4606,13 +4629,13 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>75</v>
@@ -4621,10 +4644,10 @@
         <v>75</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G116" s="7" t="n">
-        <v>202</v>
+        <v>3</v>
       </c>
       <c r="H116" s="7" t="n">
         <v>1</v>
@@ -4633,13 +4656,13 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>75</v>
@@ -4648,10 +4671,10 @@
         <v>75</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>301</v>
+        <v>4</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>1</v>
@@ -4660,13 +4683,13 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>75</v>
@@ -4675,10 +4698,10 @@
         <v>75</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>302</v>
+        <v>5</v>
       </c>
       <c r="H118" s="7" t="n">
         <v>1</v>
@@ -4687,13 +4710,13 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>75</v>
@@ -4702,10 +4725,10 @@
         <v>75</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>303</v>
+        <v>6</v>
       </c>
       <c r="H119" s="7" t="n">
         <v>1</v>
@@ -4714,13 +4737,13 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>75</v>
@@ -4729,10 +4752,10 @@
         <v>75</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>304</v>
+        <v>7</v>
       </c>
       <c r="H120" s="7" t="n">
         <v>1</v>
@@ -4741,13 +4764,13 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>75</v>
@@ -4756,10 +4779,10 @@
         <v>75</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="H121" s="7" t="n">
         <v>1</v>
@@ -4768,13 +4791,13 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>75</v>
@@ -4783,10 +4806,10 @@
         <v>75</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>306</v>
+        <v>201</v>
       </c>
       <c r="H122" s="7" t="n">
         <v>1</v>
@@ -4795,13 +4818,13 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>75</v>
@@ -4810,10 +4833,10 @@
         <v>75</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>307</v>
+        <v>202</v>
       </c>
       <c r="H123" s="7" t="n">
         <v>1</v>
@@ -4822,13 +4845,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>75</v>
@@ -4837,10 +4860,10 @@
         <v>75</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="H124" s="7" t="n">
         <v>1</v>
@@ -4849,25 +4872,25 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F125" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B125" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C125" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E125" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>230</v>
-      </c>
       <c r="G125" s="7" t="n">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="H125" s="7" t="n">
         <v>1</v>
@@ -4876,13 +4899,13 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>75</v>
@@ -4891,10 +4914,10 @@
         <v>75</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="H126" s="7" t="n">
         <v>1</v>
@@ -4903,13 +4926,13 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>75</v>
@@ -4918,10 +4941,10 @@
         <v>75</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="H127" s="7" t="n">
         <v>1</v>
@@ -4930,13 +4953,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>75</v>
@@ -4945,10 +4968,10 @@
         <v>75</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="H128" s="7" t="n">
         <v>1</v>
@@ -4957,13 +4980,13 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>75</v>
@@ -4972,10 +4995,10 @@
         <v>75</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>401</v>
+        <v>306</v>
       </c>
       <c r="H129" s="7" t="n">
         <v>1</v>
@@ -4984,13 +5007,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>75</v>
@@ -4999,10 +5022,10 @@
         <v>75</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>402</v>
+        <v>307</v>
       </c>
       <c r="H130" s="7" t="n">
         <v>1</v>
@@ -5011,13 +5034,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>75</v>
@@ -5026,10 +5049,10 @@
         <v>75</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>403</v>
+        <v>308</v>
       </c>
       <c r="H131" s="7" t="n">
         <v>1</v>
@@ -5038,13 +5061,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>75</v>
@@ -5053,10 +5076,10 @@
         <v>75</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>404</v>
+        <v>309</v>
       </c>
       <c r="H132" s="7" t="n">
         <v>1</v>
@@ -5065,13 +5088,13 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D133" s="7" t="s">
         <v>75</v>
@@ -5080,10 +5103,10 @@
         <v>75</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="H133" s="7" t="n">
         <v>1</v>
@@ -5092,13 +5115,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>75</v>
@@ -5107,10 +5130,10 @@
         <v>75</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>406</v>
+        <v>311</v>
       </c>
       <c r="H134" s="7" t="n">
         <v>1</v>
@@ -5119,13 +5142,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>75</v>
@@ -5134,10 +5157,10 @@
         <v>75</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H135" s="7" t="n">
         <v>1</v>
@@ -5146,13 +5169,13 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D136" s="7" t="s">
         <v>75</v>
@@ -5161,10 +5184,10 @@
         <v>75</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>501</v>
+        <v>401</v>
       </c>
       <c r="H136" s="7" t="n">
         <v>1</v>
@@ -5173,13 +5196,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D137" s="7" t="s">
         <v>75</v>
@@ -5188,10 +5211,10 @@
         <v>75</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>502</v>
+        <v>402</v>
       </c>
       <c r="H137" s="7" t="n">
         <v>1</v>
@@ -5200,13 +5223,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D138" s="7" t="s">
         <v>75</v>
@@ -5215,10 +5238,10 @@
         <v>75</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>503</v>
+        <v>403</v>
       </c>
       <c r="H138" s="7" t="n">
         <v>1</v>
@@ -5227,13 +5250,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>75</v>
@@ -5242,10 +5265,10 @@
         <v>75</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>504</v>
+        <v>404</v>
       </c>
       <c r="H139" s="7" t="n">
         <v>1</v>
@@ -5254,13 +5277,13 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D140" s="7" t="s">
         <v>75</v>
@@ -5269,10 +5292,10 @@
         <v>75</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>505</v>
+        <v>405</v>
       </c>
       <c r="H140" s="7" t="n">
         <v>1</v>
@@ -5281,13 +5304,13 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>75</v>
@@ -5296,10 +5319,10 @@
         <v>75</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>506</v>
+        <v>406</v>
       </c>
       <c r="H141" s="7" t="n">
         <v>1</v>
@@ -5308,13 +5331,13 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D142" s="7" t="s">
         <v>75</v>
@@ -5323,10 +5346,10 @@
         <v>75</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>507</v>
+        <v>407</v>
       </c>
       <c r="H142" s="7" t="n">
         <v>1</v>
@@ -5335,13 +5358,13 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>75</v>
@@ -5350,10 +5373,10 @@
         <v>75</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="H143" s="7" t="n">
         <v>1</v>
@@ -5362,13 +5385,13 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>75</v>
@@ -5377,10 +5400,10 @@
         <v>75</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H144" s="7" t="n">
         <v>1</v>
@@ -5389,13 +5412,13 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>75</v>
@@ -5404,10 +5427,10 @@
         <v>75</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="H145" s="7" t="n">
         <v>1</v>
@@ -5416,13 +5439,13 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>75</v>
@@ -5431,10 +5454,10 @@
         <v>75</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="H146" s="7" t="n">
         <v>1</v>
@@ -5443,13 +5466,13 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D147" s="7" t="s">
         <v>75</v>
@@ -5458,10 +5481,10 @@
         <v>75</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="H147" s="7" t="n">
         <v>1</v>
@@ -5470,13 +5493,13 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D148" s="7" t="s">
         <v>75</v>
@@ -5485,10 +5508,10 @@
         <v>75</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>601</v>
+        <v>506</v>
       </c>
       <c r="H148" s="7" t="n">
         <v>1</v>
@@ -5497,13 +5520,13 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D149" s="7" t="s">
         <v>75</v>
@@ -5512,10 +5535,10 @@
         <v>75</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>602</v>
+        <v>507</v>
       </c>
       <c r="H149" s="7" t="n">
         <v>1</v>
@@ -5524,13 +5547,13 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D150" s="7" t="s">
         <v>75</v>
@@ -5539,10 +5562,10 @@
         <v>75</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>603</v>
+        <v>508</v>
       </c>
       <c r="H150" s="7" t="n">
         <v>1</v>
@@ -5551,13 +5574,13 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D151" s="7" t="s">
         <v>75</v>
@@ -5566,10 +5589,10 @@
         <v>75</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>604</v>
+        <v>509</v>
       </c>
       <c r="H151" s="7" t="n">
         <v>1</v>
@@ -5578,13 +5601,13 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>75</v>
@@ -5593,10 +5616,10 @@
         <v>75</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>605</v>
+        <v>510</v>
       </c>
       <c r="H152" s="7" t="n">
         <v>1</v>
@@ -5605,13 +5628,13 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>75</v>
@@ -5620,10 +5643,10 @@
         <v>75</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>606</v>
+        <v>511</v>
       </c>
       <c r="H153" s="7" t="n">
         <v>1</v>
@@ -5632,13 +5655,13 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>75</v>
@@ -5647,10 +5670,10 @@
         <v>75</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>607</v>
+        <v>512</v>
       </c>
       <c r="H154" s="7" t="n">
         <v>1</v>
@@ -5659,13 +5682,13 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D155" s="7" t="s">
         <v>75</v>
@@ -5674,10 +5697,10 @@
         <v>75</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="H155" s="7" t="n">
         <v>1</v>
@@ -5686,13 +5709,13 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>75</v>
@@ -5701,10 +5724,10 @@
         <v>75</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="H156" s="7" t="n">
         <v>1</v>
@@ -5713,13 +5736,13 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D157" s="7" t="s">
         <v>75</v>
@@ -5728,10 +5751,10 @@
         <v>75</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="H157" s="7" t="n">
         <v>1</v>
@@ -5740,13 +5763,13 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D158" s="7" t="s">
         <v>75</v>
@@ -5755,10 +5778,10 @@
         <v>75</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="H158" s="7" t="n">
         <v>1</v>
@@ -5767,13 +5790,13 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D159" s="7" t="s">
         <v>75</v>
@@ -5782,10 +5805,10 @@
         <v>75</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="H159" s="7" t="n">
         <v>1</v>
@@ -5794,13 +5817,13 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D160" s="7" t="s">
         <v>75</v>
@@ -5809,10 +5832,10 @@
         <v>75</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>701</v>
+        <v>606</v>
       </c>
       <c r="H160" s="7" t="n">
         <v>1</v>
@@ -5821,13 +5844,13 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D161" s="7" t="s">
         <v>75</v>
@@ -5836,10 +5859,10 @@
         <v>75</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>702</v>
+        <v>607</v>
       </c>
       <c r="H161" s="7" t="n">
         <v>1</v>
@@ -5848,13 +5871,13 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D162" s="7" t="s">
         <v>75</v>
@@ -5863,10 +5886,10 @@
         <v>75</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>703</v>
+        <v>608</v>
       </c>
       <c r="H162" s="7" t="n">
         <v>1</v>
@@ -5875,13 +5898,13 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D163" s="7" t="s">
         <v>75</v>
@@ -5890,10 +5913,10 @@
         <v>75</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>704</v>
+        <v>609</v>
       </c>
       <c r="H163" s="7" t="n">
         <v>1</v>
@@ -5902,13 +5925,13 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D164" s="7" t="s">
         <v>75</v>
@@ -5917,10 +5940,10 @@
         <v>75</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G164" s="7" t="n">
-        <v>705</v>
+        <v>610</v>
       </c>
       <c r="H164" s="7" t="n">
         <v>1</v>
@@ -5929,13 +5952,13 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>75</v>
@@ -5944,10 +5967,10 @@
         <v>75</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G165" s="7" t="n">
-        <v>706</v>
+        <v>611</v>
       </c>
       <c r="H165" s="7" t="n">
         <v>1</v>
@@ -5956,13 +5979,13 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D166" s="7" t="s">
         <v>75</v>
@@ -5971,10 +5994,10 @@
         <v>75</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G166" s="7" t="n">
-        <v>707</v>
+        <v>612</v>
       </c>
       <c r="H166" s="7" t="n">
         <v>1</v>
@@ -5983,13 +6006,13 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D167" s="7" t="s">
         <v>75</v>
@@ -5998,10 +6021,10 @@
         <v>75</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G167" s="7" t="n">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="H167" s="7" t="n">
         <v>1</v>
@@ -6010,13 +6033,13 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D168" s="7" t="s">
         <v>75</v>
@@ -6025,10 +6048,10 @@
         <v>75</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G168" s="7" t="n">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="H168" s="7" t="n">
         <v>1</v>
@@ -6037,13 +6060,13 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D169" s="7" t="s">
         <v>75</v>
@@ -6052,10 +6075,10 @@
         <v>75</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G169" s="7" t="n">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="H169" s="7" t="n">
         <v>1</v>
@@ -6064,13 +6087,13 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D170" s="7" t="s">
         <v>75</v>
@@ -6079,10 +6102,10 @@
         <v>75</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G170" s="7" t="n">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="H170" s="7" t="n">
         <v>1</v>
@@ -6091,13 +6114,13 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D171" s="7" t="s">
         <v>75</v>
@@ -6106,10 +6129,10 @@
         <v>75</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G171" s="7" t="n">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="H171" s="7" t="n">
         <v>1</v>
@@ -6118,28 +6141,40 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B172" s="7"/>
-      <c r="C172" s="7"/>
-      <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
+        <v>306</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>248</v>
+      </c>
       <c r="G172" s="7" t="n">
-        <v>801</v>
-      </c>
-      <c r="H172" s="7"/>
+        <v>706</v>
+      </c>
+      <c r="H172" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="I172" s="7"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>297</v>
+        <v>75</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D173" s="7" t="s">
         <v>75</v>
@@ -6148,10 +6183,10 @@
         <v>75</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G173" s="7" t="n">
-        <v>802</v>
+        <v>707</v>
       </c>
       <c r="H173" s="7" t="n">
         <v>1</v>
@@ -6160,13 +6195,13 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D174" s="7" t="s">
         <v>75</v>
@@ -6175,289 +6210,327 @@
         <v>75</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G174" s="7" t="n">
+        <v>708</v>
+      </c>
+      <c r="H174" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" s="7"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A175" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G175" s="7" t="n">
+        <v>709</v>
+      </c>
+      <c r="H175" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" s="7"/>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G176" s="7" t="n">
+        <v>710</v>
+      </c>
+      <c r="H176" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I176" s="7"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A177" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G177" s="7" t="n">
+        <v>711</v>
+      </c>
+      <c r="H177" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I177" s="7"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G178" s="7" t="n">
+        <v>712</v>
+      </c>
+      <c r="H178" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" s="7"/>
+    </row>
+    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A179" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G179" s="7" t="n">
+        <v>801</v>
+      </c>
+      <c r="H179" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" s="7"/>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G180" s="7" t="n">
+        <v>802</v>
+      </c>
+      <c r="H180" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I180" s="7"/>
+    </row>
+    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A181" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F181" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G181" s="7" t="n">
         <v>803</v>
       </c>
-      <c r="H174" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I174" s="7"/>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B175" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C175" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D175" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E175" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F175" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G175" s="7" t="n">
+      <c r="H181" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" s="7"/>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G182" s="7" t="n">
         <v>804</v>
       </c>
-      <c r="H175" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I175" s="7"/>
-    </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="3" t="s">
+      <c r="H182" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" s="7"/>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A183" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B183" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C183" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D176" s="3" t="s">
+      <c r="D183" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E176" s="4" t="s">
+      <c r="E183" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F176" s="3" t="s">
+      <c r="F183" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G176" s="4" t="s">
+      <c r="G183" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H176" s="4" t="s">
+      <c r="H183" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I176" s="3" t="s">
+      <c r="I183" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="3"/>
-      <c r="B177" s="4" t="s">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="3"/>
+      <c r="B184" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C177" s="4" t="s">
+      <c r="C184" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D177" s="3"/>
-      <c r="E177" s="4" t="s">
+      <c r="D184" s="3"/>
+      <c r="E184" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F177" s="3"/>
-      <c r="G177" s="4" t="s">
+      <c r="F184" s="3"/>
+      <c r="G184" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H177" s="4" t="s">
+      <c r="H184" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I177" s="3"/>
-    </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="B178" s="5"/>
-      <c r="C178" s="5"/>
-      <c r="D178" s="5"/>
-      <c r="E178" s="5"/>
-      <c r="F178" s="5"/>
-      <c r="G178" s="5"/>
-      <c r="H178" s="5"/>
-      <c r="I178" s="5"/>
-    </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B179" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C179" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D179" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E179" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F179" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G179" s="7" t="n">
-        <v>2001</v>
-      </c>
-      <c r="H179" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I179" s="7"/>
-    </row>
-    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B180" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E180" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G180" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H180" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I180" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="3"/>
-      <c r="B181" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D181" s="3"/>
-      <c r="E181" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F181" s="3"/>
-      <c r="G181" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H181" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I181" s="3"/>
-    </row>
-    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B182" s="5"/>
-      <c r="C182" s="5"/>
-      <c r="D182" s="5"/>
-      <c r="E182" s="5"/>
-      <c r="F182" s="5"/>
-      <c r="G182" s="5"/>
-      <c r="H182" s="5"/>
-      <c r="I182" s="5"/>
-    </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B183" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C183" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D183" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E183" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F183" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G183" s="7" t="n">
-        <v>2001</v>
-      </c>
-      <c r="H183" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I183" s="7"/>
-    </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E184" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G184" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H184" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I184" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="3"/>
-      <c r="B185" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D185" s="3"/>
-      <c r="E185" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F185" s="3"/>
-      <c r="G185" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H185" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I185" s="3"/>
-    </row>
-    <row r="186" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B186" s="5"/>
-      <c r="C186" s="5"/>
-      <c r="D186" s="5"/>
-      <c r="E186" s="5"/>
-      <c r="F186" s="5"/>
-      <c r="G186" s="5"/>
-      <c r="H186" s="5"/>
-      <c r="I186" s="5"/>
+      <c r="I184" s="3"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A185" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B185" s="5"/>
+      <c r="C185" s="5"/>
+      <c r="D185" s="5"/>
+      <c r="E185" s="5"/>
+      <c r="F185" s="5"/>
+      <c r="G185" s="5"/>
+      <c r="H185" s="5"/>
+      <c r="I185" s="5"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D186" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E186" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G186" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="H186" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I186" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="9" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="B187" s="7" t="s">
         <v>109</v>
@@ -6475,21 +6548,21 @@
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>304</v>
+        <v>188</v>
       </c>
       <c r="H187" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="9" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C188" s="7" t="s">
         <v>110</v>
@@ -6504,18 +6577,16 @@
         <v>26</v>
       </c>
       <c r="G188" s="10" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="H188" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I188" s="7" t="s">
-        <v>186</v>
-      </c>
+      <c r="I188" s="7"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="9" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>24</v>
@@ -6533,7 +6604,7 @@
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H189" s="7" t="n">
         <v>2</v>
@@ -6542,7 +6613,7 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="9" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
         <v>24</v>
@@ -6560,7 +6631,7 @@
         <v>26</v>
       </c>
       <c r="G190" s="10" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H190" s="7" t="n">
         <v>2</v>
@@ -6569,7 +6640,7 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="9" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B191" s="7" t="s">
         <v>24</v>
@@ -6587,7 +6658,7 @@
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H191" s="7" t="n">
         <v>2</v>
@@ -6596,10 +6667,10 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="9" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C192" s="7" t="s">
         <v>110</v>
@@ -6614,7 +6685,7 @@
         <v>26</v>
       </c>
       <c r="G192" s="10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H192" s="7" t="n">
         <v>2</v>
@@ -6623,7 +6694,7 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="9" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B193" s="7" t="s">
         <v>109</v>
@@ -6641,7 +6712,7 @@
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H193" s="7" t="n">
         <v>2</v>
@@ -6650,10 +6721,10 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="9" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C194" s="7" t="s">
         <v>110</v>
@@ -6668,7 +6739,7 @@
         <v>26</v>
       </c>
       <c r="G194" s="10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H194" s="7" t="n">
         <v>2</v>
@@ -6677,7 +6748,7 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="9" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B195" s="7" t="s">
         <v>24</v>
@@ -6695,7 +6766,7 @@
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H195" s="7" t="n">
         <v>2</v>
@@ -6704,7 +6775,7 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="9" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B196" s="7" t="s">
         <v>24</v>
@@ -6722,7 +6793,7 @@
         <v>26</v>
       </c>
       <c r="G196" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="H196" s="7" t="n">
         <v>2</v>
@@ -6731,7 +6802,7 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="9" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B197" s="7" t="s">
         <v>24</v>
@@ -6749,7 +6820,7 @@
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="H197" s="7" t="n">
         <v>2</v>
@@ -6758,10 +6829,10 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="9" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>110</v>
@@ -6776,7 +6847,7 @@
         <v>26</v>
       </c>
       <c r="G198" s="10" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H198" s="7" t="n">
         <v>2</v>
@@ -6785,7 +6856,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="9" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B199" s="7" t="s">
         <v>109</v>
@@ -6803,7 +6874,7 @@
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H199" s="7" t="n">
         <v>2</v>
@@ -6812,10 +6883,10 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="9" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="C200" s="7" t="s">
         <v>110</v>
@@ -6830,7 +6901,7 @@
         <v>26</v>
       </c>
       <c r="G200" s="10" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H200" s="7" t="n">
         <v>2</v>
@@ -6839,10 +6910,10 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="9" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C201" s="7" t="s">
         <v>110</v>
@@ -6857,7 +6928,7 @@
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H201" s="7" t="n">
         <v>2</v>
@@ -6866,10 +6937,10 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="9" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="C202" s="7" t="s">
         <v>110</v>
@@ -6884,13 +6955,200 @@
         <v>26</v>
       </c>
       <c r="G202" s="10" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H202" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I202" s="7"/>
     </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D203" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E203" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G203" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H203" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I203" s="7"/>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D204" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E204" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G204" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H204" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I204" s="7"/>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D205" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E205" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G205" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="H205" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I205" s="7"/>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D206" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E206" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G206" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H206" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I206" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D207" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E207" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G207" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="H207" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I207" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1048485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -6936,32 +7194,22 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="15">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="F104:F105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="A106:I106"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="D176:D177"/>
-    <mergeCell ref="F176:F177"/>
-    <mergeCell ref="I176:I177"/>
-    <mergeCell ref="A178:I178"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="D180:D181"/>
-    <mergeCell ref="F180:F181"/>
-    <mergeCell ref="I180:I181"/>
-    <mergeCell ref="A182:I182"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="F184:F185"/>
-    <mergeCell ref="I184:I185"/>
-    <mergeCell ref="A186:I186"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="D111:D112"/>
+    <mergeCell ref="F111:F112"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="A113:I113"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="D183:D184"/>
+    <mergeCell ref="F183:F184"/>
+    <mergeCell ref="I183:I184"/>
+    <mergeCell ref="A185:I185"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6978,7 +7226,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1048576"/>
+  <dimension ref="A1:I259"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.94"/>
@@ -8858,7 +9106,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>305</v>
+        <v>165</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>75</v>
@@ -8876,7 +9124,7 @@
         <v>26</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>2</v>
@@ -8885,7 +9133,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>306</v>
+        <v>167</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>75</v>
@@ -8903,7 +9151,7 @@
         <v>26</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H74" s="7" t="n">
         <v>2</v>
@@ -8912,7 +9160,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>307</v>
+        <v>169</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>75</v>
@@ -8930,7 +9178,7 @@
         <v>26</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H75" s="7" t="n">
         <v>2</v>
@@ -8939,7 +9187,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>90</v>
@@ -8957,7 +9205,7 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H76" s="7" t="n">
         <v>2</v>
@@ -8966,7 +9214,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>93</v>
@@ -8984,7 +9232,7 @@
         <v>26</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H77" s="7" t="n">
         <v>2</v>
@@ -8993,7 +9241,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>96</v>
@@ -9011,7 +9259,7 @@
         <v>26</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H78" s="7" t="n">
         <v>2</v>
@@ -9020,7 +9268,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>96</v>
@@ -9038,7 +9286,7 @@
         <v>26</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H79" s="7" t="n">
         <v>2</v>
@@ -9047,7 +9295,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>90</v>
@@ -9065,7 +9313,7 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H80" s="7" t="n">
         <v>2</v>
@@ -9074,7 +9322,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>93</v>
@@ -9092,7 +9340,7 @@
         <v>26</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H81" s="7" t="n">
         <v>2</v>
@@ -9101,7 +9349,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>96</v>
@@ -9119,7 +9367,7 @@
         <v>26</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H82" s="7" t="n">
         <v>2</v>
@@ -9128,7 +9376,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>96</v>
@@ -9146,7 +9394,7 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H83" s="7" t="n">
         <v>2</v>
@@ -9155,7 +9403,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>109</v>
@@ -9173,18 +9421,18 @@
         <v>26</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H84" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>39</v>
@@ -9202,7 +9450,7 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H85" s="7" t="n">
         <v>2</v>
@@ -9211,7 +9459,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>39</v>
@@ -9229,7 +9477,7 @@
         <v>26</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H86" s="7" t="n">
         <v>2</v>
@@ -9238,10 +9486,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>308</v>
+        <v>195</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>25</v>
@@ -9256,7 +9504,7 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H87" s="7" t="n">
         <v>2</v>
@@ -9265,7 +9513,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>24</v>
@@ -9283,7 +9531,7 @@
         <v>26</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H88" s="7" t="n">
         <v>2</v>
@@ -9292,7 +9540,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="9" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>24</v>
@@ -9310,7 +9558,7 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H89" s="7" t="n">
         <v>2</v>
@@ -9319,7 +9567,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>24</v>
@@ -9337,7 +9585,7 @@
         <v>26</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H90" s="7" t="n">
         <v>2</v>
@@ -9346,7 +9594,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>24</v>
@@ -9364,7 +9612,7 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H91" s="7" t="n">
         <v>2</v>
@@ -9373,7 +9621,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>109</v>
@@ -9391,7 +9639,7 @@
         <v>26</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H92" s="7" t="n">
         <v>2</v>
@@ -9400,7 +9648,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>109</v>
@@ -9418,7 +9666,7 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H93" s="7" t="n">
         <v>2</v>
@@ -9427,7 +9675,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>24</v>
@@ -9445,7 +9693,7 @@
         <v>26</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H94" s="7" t="n">
         <v>2</v>
@@ -9454,7 +9702,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>24</v>
@@ -9472,7 +9720,7 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H95" s="7" t="n">
         <v>2</v>
@@ -9481,7 +9729,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>24</v>
@@ -9499,7 +9747,7 @@
         <v>26</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H96" s="7" t="n">
         <v>2</v>
@@ -9508,7 +9756,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>24</v>
@@ -9526,7 +9774,7 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>2</v>
@@ -9535,7 +9783,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>109</v>
@@ -9553,7 +9801,7 @@
         <v>26</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H98" s="7" t="n">
         <v>2</v>
@@ -9562,7 +9810,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>109</v>
@@ -9580,7 +9828,7 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>2</v>
@@ -9589,10 +9837,10 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C100" s="7" t="s">
         <v>110</v>
@@ -9607,7 +9855,7 @@
         <v>26</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H100" s="7" t="n">
         <v>2</v>
@@ -9616,10 +9864,10 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>110</v>
@@ -9634,7 +9882,7 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H101" s="7" t="n">
         <v>2</v>
@@ -9643,10 +9891,10 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="9" t="s">
-        <v>309</v>
+        <v>226</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>308</v>
+        <v>195</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>110</v>
@@ -9661,7 +9909,7 @@
         <v>26</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>310</v>
+        <v>227</v>
       </c>
       <c r="H102" s="7" t="n">
         <v>2</v>
@@ -9670,10 +9918,10 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="9" t="s">
-        <v>311</v>
+        <v>228</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>308</v>
+        <v>195</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>110</v>
@@ -9688,7 +9936,7 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>312</v>
+        <v>229</v>
       </c>
       <c r="H103" s="7" t="n">
         <v>2</v>
@@ -9697,7 +9945,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="9" t="s">
-        <v>313</v>
+        <v>230</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>109</v>
@@ -9715,7 +9963,7 @@
         <v>26</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>314</v>
+        <v>231</v>
       </c>
       <c r="H104" s="7" t="n">
         <v>2</v>
@@ -9724,7 +9972,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="9" t="s">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>109</v>
@@ -9742,7 +9990,7 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>316</v>
+        <v>233</v>
       </c>
       <c r="H105" s="7" t="n">
         <v>2</v>
@@ -9751,7 +9999,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>317</v>
+        <v>234</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>75</v>
@@ -9769,18 +10017,18 @@
         <v>26</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>318</v>
+        <v>235</v>
       </c>
       <c r="H106" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>319</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>320</v>
+        <v>237</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>75</v>
@@ -9798,18 +10046,18 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>321</v>
+        <v>238</v>
       </c>
       <c r="H107" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>319</v>
+        <v>236</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="86.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="11" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>75</v>
@@ -9827,18 +10075,18 @@
         <v>26</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H108" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>75</v>
@@ -9856,7 +10104,7 @@
         <v>26</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>2</v>
@@ -9865,7 +10113,7 @@
     </row>
     <row r="110" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>75</v>
@@ -9883,7 +10131,7 @@
         <v>26</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="H110" s="7" t="n">
         <v>2</v>
@@ -9892,7 +10140,7 @@
     </row>
     <row r="111" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>325</v>
+        <v>243</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>75</v>
@@ -9910,139 +10158,143 @@
         <v>26</v>
       </c>
       <c r="G111" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="7"/>
+    </row>
+    <row r="112" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="B112" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D112" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G112" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D113" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G113" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="H111" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I111" s="7"/>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="3" t="s">
+      <c r="H113" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B114" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C114" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D114" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E112" s="4" t="s">
+      <c r="E114" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F114" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G112" s="4" t="s">
+      <c r="G114" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H112" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I112" s="3" t="s">
+      <c r="I114" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="3"/>
-      <c r="B113" s="4" t="s">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="3"/>
+      <c r="B115" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C115" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D113" s="3"/>
-      <c r="E113" s="4" t="s">
+      <c r="D115" s="3"/>
+      <c r="E115" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="4" t="s">
+      <c r="F115" s="3"/>
+      <c r="G115" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H113" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I113" s="3"/>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5"/>
-      <c r="I114" s="5"/>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G115" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H115" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I115" s="7"/>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B116" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G116" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H116" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I116" s="7"/>
+      <c r="I115" s="3"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="5"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="5"/>
+      <c r="I116" s="5"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>75</v>
@@ -10051,10 +10303,10 @@
         <v>75</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>1</v>
@@ -10063,13 +10315,13 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>75</v>
@@ -10078,10 +10330,10 @@
         <v>75</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H118" s="7" t="n">
         <v>1</v>
@@ -10090,13 +10342,13 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>75</v>
@@ -10105,10 +10357,10 @@
         <v>75</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H119" s="7" t="n">
         <v>1</v>
@@ -10117,13 +10369,13 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>75</v>
@@ -10132,10 +10384,10 @@
         <v>75</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H120" s="7" t="n">
         <v>1</v>
@@ -10144,13 +10396,13 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>75</v>
@@ -10159,10 +10411,10 @@
         <v>75</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H121" s="7" t="n">
         <v>1</v>
@@ -10171,13 +10423,13 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>75</v>
@@ -10186,10 +10438,10 @@
         <v>75</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H122" s="7" t="n">
         <v>1</v>
@@ -10198,13 +10450,13 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>75</v>
@@ -10213,10 +10465,10 @@
         <v>75</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="H123" s="7" t="n">
         <v>1</v>
@@ -10225,13 +10477,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>75</v>
@@ -10240,10 +10492,10 @@
         <v>75</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>202</v>
+        <v>8</v>
       </c>
       <c r="H124" s="7" t="n">
         <v>1</v>
@@ -10252,13 +10504,13 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>75</v>
@@ -10267,10 +10519,10 @@
         <v>75</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="H125" s="7" t="n">
         <v>1</v>
@@ -10279,13 +10531,13 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>75</v>
@@ -10294,10 +10546,10 @@
         <v>75</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>302</v>
+        <v>202</v>
       </c>
       <c r="H126" s="7" t="n">
         <v>1</v>
@@ -10306,13 +10558,13 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>75</v>
@@ -10321,10 +10573,10 @@
         <v>75</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H127" s="7" t="n">
         <v>1</v>
@@ -10333,13 +10585,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>75</v>
@@ -10348,10 +10600,10 @@
         <v>75</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H128" s="7" t="n">
         <v>1</v>
@@ -10360,13 +10612,13 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>75</v>
@@ -10375,10 +10627,10 @@
         <v>75</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H129" s="7" t="n">
         <v>1</v>
@@ -10387,13 +10639,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>75</v>
@@ -10402,10 +10654,10 @@
         <v>75</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H130" s="7" t="n">
         <v>1</v>
@@ -10414,13 +10666,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>75</v>
@@ -10429,10 +10681,10 @@
         <v>75</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H131" s="7" t="n">
         <v>1</v>
@@ -10441,13 +10693,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>75</v>
@@ -10456,10 +10708,10 @@
         <v>75</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H132" s="7" t="n">
         <v>1</v>
@@ -10468,25 +10720,25 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F133" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B133" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E133" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>230</v>
-      </c>
       <c r="G133" s="7" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H133" s="7" t="n">
         <v>1</v>
@@ -10495,13 +10747,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>75</v>
@@ -10510,10 +10762,10 @@
         <v>75</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H134" s="7" t="n">
         <v>1</v>
@@ -10522,13 +10774,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>75</v>
@@ -10537,10 +10789,10 @@
         <v>75</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H135" s="7" t="n">
         <v>1</v>
@@ -10549,13 +10801,13 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D136" s="7" t="s">
         <v>75</v>
@@ -10564,10 +10816,10 @@
         <v>75</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H136" s="7" t="n">
         <v>1</v>
@@ -10576,13 +10828,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D137" s="7" t="s">
         <v>75</v>
@@ -10591,10 +10843,10 @@
         <v>75</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>401</v>
+        <v>311</v>
       </c>
       <c r="H137" s="7" t="n">
         <v>1</v>
@@ -10603,13 +10855,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D138" s="7" t="s">
         <v>75</v>
@@ -10618,10 +10870,10 @@
         <v>75</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="H138" s="7" t="n">
         <v>1</v>
@@ -10630,13 +10882,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>75</v>
@@ -10645,10 +10897,10 @@
         <v>75</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H139" s="7" t="n">
         <v>1</v>
@@ -10657,13 +10909,13 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D140" s="7" t="s">
         <v>75</v>
@@ -10672,10 +10924,10 @@
         <v>75</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H140" s="7" t="n">
         <v>1</v>
@@ -10684,13 +10936,13 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>75</v>
@@ -10699,10 +10951,10 @@
         <v>75</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H141" s="7" t="n">
         <v>1</v>
@@ -10711,13 +10963,13 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D142" s="7" t="s">
         <v>75</v>
@@ -10726,10 +10978,10 @@
         <v>75</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H142" s="7" t="n">
         <v>1</v>
@@ -10738,13 +10990,13 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>75</v>
@@ -10753,10 +11005,10 @@
         <v>75</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H143" s="7" t="n">
         <v>1</v>
@@ -10765,13 +11017,13 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>75</v>
@@ -10780,10 +11032,10 @@
         <v>75</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>501</v>
+        <v>406</v>
       </c>
       <c r="H144" s="7" t="n">
         <v>1</v>
@@ -10792,13 +11044,13 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>75</v>
@@ -10807,10 +11059,10 @@
         <v>75</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>502</v>
+        <v>407</v>
       </c>
       <c r="H145" s="7" t="n">
         <v>1</v>
@@ -10819,13 +11071,13 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>75</v>
@@ -10834,10 +11086,10 @@
         <v>75</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H146" s="7" t="n">
         <v>1</v>
@@ -10846,13 +11098,13 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D147" s="7" t="s">
         <v>75</v>
@@ -10861,10 +11113,10 @@
         <v>75</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H147" s="7" t="n">
         <v>1</v>
@@ -10873,13 +11125,13 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D148" s="7" t="s">
         <v>75</v>
@@ -10888,10 +11140,10 @@
         <v>75</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H148" s="7" t="n">
         <v>1</v>
@@ -10900,13 +11152,13 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D149" s="7" t="s">
         <v>75</v>
@@ -10915,10 +11167,10 @@
         <v>75</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H149" s="7" t="n">
         <v>1</v>
@@ -10927,13 +11179,13 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D150" s="7" t="s">
         <v>75</v>
@@ -10942,10 +11194,10 @@
         <v>75</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H150" s="7" t="n">
         <v>1</v>
@@ -10954,13 +11206,13 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D151" s="7" t="s">
         <v>75</v>
@@ -10969,10 +11221,10 @@
         <v>75</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H151" s="7" t="n">
         <v>1</v>
@@ -10981,13 +11233,13 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>75</v>
@@ -10996,10 +11248,10 @@
         <v>75</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H152" s="7" t="n">
         <v>1</v>
@@ -11008,13 +11260,13 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>75</v>
@@ -11023,10 +11275,10 @@
         <v>75</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H153" s="7" t="n">
         <v>1</v>
@@ -11035,13 +11287,13 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>75</v>
@@ -11050,10 +11302,10 @@
         <v>75</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H154" s="7" t="n">
         <v>1</v>
@@ -11062,13 +11314,13 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D155" s="7" t="s">
         <v>75</v>
@@ -11077,10 +11329,10 @@
         <v>75</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H155" s="7" t="n">
         <v>1</v>
@@ -11089,13 +11341,13 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>75</v>
@@ -11104,10 +11356,10 @@
         <v>75</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>601</v>
+        <v>511</v>
       </c>
       <c r="H156" s="7" t="n">
         <v>1</v>
@@ -11116,13 +11368,13 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D157" s="7" t="s">
         <v>75</v>
@@ -11131,10 +11383,10 @@
         <v>75</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>602</v>
+        <v>512</v>
       </c>
       <c r="H157" s="7" t="n">
         <v>1</v>
@@ -11143,13 +11395,13 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D158" s="7" t="s">
         <v>75</v>
@@ -11158,10 +11410,10 @@
         <v>75</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H158" s="7" t="n">
         <v>1</v>
@@ -11170,13 +11422,13 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D159" s="7" t="s">
         <v>75</v>
@@ -11185,10 +11437,10 @@
         <v>75</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H159" s="7" t="n">
         <v>1</v>
@@ -11197,13 +11449,13 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D160" s="7" t="s">
         <v>75</v>
@@ -11212,10 +11464,10 @@
         <v>75</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H160" s="7" t="n">
         <v>1</v>
@@ -11224,13 +11476,13 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D161" s="7" t="s">
         <v>75</v>
@@ -11239,10 +11491,10 @@
         <v>75</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H161" s="7" t="n">
         <v>1</v>
@@ -11251,13 +11503,13 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D162" s="7" t="s">
         <v>75</v>
@@ -11266,10 +11518,10 @@
         <v>75</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H162" s="7" t="n">
         <v>1</v>
@@ -11278,13 +11530,13 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D163" s="7" t="s">
         <v>75</v>
@@ -11293,10 +11545,10 @@
         <v>75</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H163" s="7" t="n">
         <v>1</v>
@@ -11305,13 +11557,13 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D164" s="7" t="s">
         <v>75</v>
@@ -11320,10 +11572,10 @@
         <v>75</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G164" s="7" t="n">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H164" s="7" t="n">
         <v>1</v>
@@ -11332,13 +11584,13 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>75</v>
@@ -11347,10 +11599,10 @@
         <v>75</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G165" s="7" t="n">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H165" s="7" t="n">
         <v>1</v>
@@ -11359,13 +11611,13 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D166" s="7" t="s">
         <v>75</v>
@@ -11374,10 +11626,10 @@
         <v>75</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G166" s="7" t="n">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H166" s="7" t="n">
         <v>1</v>
@@ -11386,13 +11638,13 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D167" s="7" t="s">
         <v>75</v>
@@ -11401,10 +11653,10 @@
         <v>75</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G167" s="7" t="n">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H167" s="7" t="n">
         <v>1</v>
@@ -11413,13 +11665,13 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D168" s="7" t="s">
         <v>75</v>
@@ -11428,10 +11680,10 @@
         <v>75</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G168" s="7" t="n">
-        <v>701</v>
+        <v>611</v>
       </c>
       <c r="H168" s="7" t="n">
         <v>1</v>
@@ -11440,13 +11692,13 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D169" s="7" t="s">
         <v>75</v>
@@ -11455,10 +11707,10 @@
         <v>75</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G169" s="7" t="n">
-        <v>702</v>
+        <v>612</v>
       </c>
       <c r="H169" s="7" t="n">
         <v>1</v>
@@ -11467,13 +11719,13 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D170" s="7" t="s">
         <v>75</v>
@@ -11482,10 +11734,10 @@
         <v>75</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G170" s="7" t="n">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="H170" s="7" t="n">
         <v>1</v>
@@ -11494,13 +11746,13 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D171" s="7" t="s">
         <v>75</v>
@@ -11509,10 +11761,10 @@
         <v>75</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G171" s="7" t="n">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H171" s="7" t="n">
         <v>1</v>
@@ -11521,13 +11773,13 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D172" s="7" t="s">
         <v>75</v>
@@ -11536,10 +11788,10 @@
         <v>75</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G172" s="7" t="n">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H172" s="7" t="n">
         <v>1</v>
@@ -11548,13 +11800,13 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D173" s="7" t="s">
         <v>75</v>
@@ -11563,10 +11815,10 @@
         <v>75</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G173" s="7" t="n">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H173" s="7" t="n">
         <v>1</v>
@@ -11575,13 +11827,13 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D174" s="7" t="s">
         <v>75</v>
@@ -11590,10 +11842,10 @@
         <v>75</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G174" s="7" t="n">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H174" s="7" t="n">
         <v>1</v>
@@ -11602,13 +11854,13 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D175" s="7" t="s">
         <v>75</v>
@@ -11617,10 +11869,10 @@
         <v>75</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G175" s="7" t="n">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H175" s="7" t="n">
         <v>1</v>
@@ -11629,13 +11881,13 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D176" s="7" t="s">
         <v>75</v>
@@ -11644,10 +11896,10 @@
         <v>75</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G176" s="7" t="n">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H176" s="7" t="n">
         <v>1</v>
@@ -11656,13 +11908,13 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D177" s="7" t="s">
         <v>75</v>
@@ -11671,10 +11923,10 @@
         <v>75</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G177" s="7" t="n">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H177" s="7" t="n">
         <v>1</v>
@@ -11683,13 +11935,13 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D178" s="7" t="s">
         <v>75</v>
@@ -11698,10 +11950,10 @@
         <v>75</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G178" s="7" t="n">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H178" s="7" t="n">
         <v>1</v>
@@ -11710,13 +11962,13 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D179" s="7" t="s">
         <v>75</v>
@@ -11725,10 +11977,10 @@
         <v>75</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G179" s="7" t="n">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H179" s="7" t="n">
         <v>1</v>
@@ -11737,13 +11989,13 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D180" s="7" t="s">
         <v>75</v>
@@ -11752,10 +12004,10 @@
         <v>75</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G180" s="7" t="n">
-        <v>801</v>
+        <v>711</v>
       </c>
       <c r="H180" s="7" t="n">
         <v>1</v>
@@ -11764,13 +12016,13 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="B181" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D181" s="7" t="s">
         <v>75</v>
@@ -11779,10 +12031,10 @@
         <v>75</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G181" s="7" t="n">
-        <v>802</v>
+        <v>712</v>
       </c>
       <c r="H181" s="7" t="n">
         <v>1</v>
@@ -11791,13 +12043,13 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="B182" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D182" s="7" t="s">
         <v>75</v>
@@ -11806,10 +12058,10 @@
         <v>75</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G182" s="7" t="n">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="H182" s="7" t="n">
         <v>1</v>
@@ -11818,13 +12070,13 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D183" s="7" t="s">
         <v>75</v>
@@ -11833,146 +12085,142 @@
         <v>75</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G183" s="7" t="n">
+        <v>802</v>
+      </c>
+      <c r="H183" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I183" s="7"/>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G184" s="7" t="n">
+        <v>803</v>
+      </c>
+      <c r="H184" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I184" s="7"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G185" s="7" t="n">
         <v>804</v>
       </c>
-      <c r="H183" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I183" s="7"/>
-    </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="3" t="s">
+      <c r="H185" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" s="7"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A186" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="B186" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C184" s="4" t="s">
+      <c r="C186" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D184" s="3" t="s">
+      <c r="D186" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E184" s="4" t="s">
+      <c r="E186" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F184" s="3" t="s">
+      <c r="F186" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G184" s="4" t="s">
+      <c r="G186" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H184" s="4" t="s">
+      <c r="H186" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I184" s="3" t="s">
+      <c r="I186" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="3"/>
-      <c r="B185" s="4" t="s">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="3"/>
+      <c r="B187" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C185" s="4" t="s">
+      <c r="C187" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D185" s="3"/>
-      <c r="E185" s="4" t="s">
+      <c r="D187" s="3"/>
+      <c r="E187" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F185" s="3"/>
-      <c r="G185" s="4" t="s">
+      <c r="F187" s="3"/>
+      <c r="G187" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H185" s="4" t="s">
+      <c r="H187" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I185" s="3"/>
-    </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="B186" s="5"/>
-      <c r="C186" s="5"/>
-      <c r="D186" s="5"/>
-      <c r="E186" s="5"/>
-      <c r="F186" s="5"/>
-      <c r="G186" s="5"/>
-      <c r="H186" s="5"/>
-      <c r="I186" s="5"/>
-    </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="12" t="s">
+      <c r="I187" s="3"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A188" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="B187" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C187" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D187" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E187" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F187" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="G187" s="12" t="n">
-        <v>20001</v>
-      </c>
-      <c r="H187" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I187" s="12" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="B188" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C188" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D188" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E188" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F188" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="G188" s="12" t="n">
-        <v>20002</v>
-      </c>
-      <c r="H188" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I188" s="12" t="s">
-        <v>330</v>
-      </c>
+      <c r="B188" s="5"/>
+      <c r="C188" s="5"/>
+      <c r="D188" s="5"/>
+      <c r="E188" s="5"/>
+      <c r="F188" s="5"/>
+      <c r="G188" s="5"/>
+      <c r="H188" s="5"/>
+      <c r="I188" s="5"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="12" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D189" s="12" t="s">
         <v>75</v>
@@ -11981,27 +12229,27 @@
         <v>75</v>
       </c>
       <c r="F189" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>20003</v>
+        <v>20001</v>
       </c>
       <c r="H189" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D190" s="12" t="s">
         <v>75</v>
@@ -12010,27 +12258,27 @@
         <v>75</v>
       </c>
       <c r="F190" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>20004</v>
+        <v>20002</v>
       </c>
       <c r="H190" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D191" s="12" t="s">
         <v>75</v>
@@ -12039,27 +12287,27 @@
         <v>75</v>
       </c>
       <c r="F191" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>20005</v>
+        <v>20003</v>
       </c>
       <c r="H191" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D192" s="12" t="s">
         <v>75</v>
@@ -12068,27 +12316,27 @@
         <v>75</v>
       </c>
       <c r="F192" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>20006</v>
+        <v>20004</v>
       </c>
       <c r="H192" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B193" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D193" s="12" t="s">
         <v>75</v>
@@ -12097,27 +12345,27 @@
         <v>75</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>20007</v>
+        <v>20005</v>
       </c>
       <c r="H193" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D194" s="12" t="s">
         <v>75</v>
@@ -12126,27 +12374,27 @@
         <v>75</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>20008</v>
+        <v>20006</v>
       </c>
       <c r="H194" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D195" s="12" t="s">
         <v>75</v>
@@ -12155,27 +12403,27 @@
         <v>75</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>30001</v>
+        <v>20007</v>
       </c>
       <c r="H195" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D196" s="12" t="s">
         <v>75</v>
@@ -12184,27 +12432,27 @@
         <v>75</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>30002</v>
+        <v>20008</v>
       </c>
       <c r="H196" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D197" s="12" t="s">
         <v>75</v>
@@ -12213,27 +12461,27 @@
         <v>75</v>
       </c>
       <c r="F197" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>30003</v>
+        <v>30001</v>
       </c>
       <c r="H197" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D198" s="12" t="s">
         <v>75</v>
@@ -12242,27 +12490,27 @@
         <v>75</v>
       </c>
       <c r="F198" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>30004</v>
+        <v>30002</v>
       </c>
       <c r="H198" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B199" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D199" s="12" t="s">
         <v>75</v>
@@ -12271,27 +12519,27 @@
         <v>75</v>
       </c>
       <c r="F199" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>30005</v>
+        <v>30003</v>
       </c>
       <c r="H199" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D200" s="12" t="s">
         <v>75</v>
@@ -12300,27 +12548,27 @@
         <v>75</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>30006</v>
+        <v>30004</v>
       </c>
       <c r="H200" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D201" s="12" t="s">
         <v>75</v>
@@ -12329,27 +12577,27 @@
         <v>75</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>40001</v>
+        <v>30005</v>
       </c>
       <c r="H201" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D202" s="12" t="s">
         <v>75</v>
@@ -12358,27 +12606,27 @@
         <v>75</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>60001</v>
+        <v>30006</v>
       </c>
       <c r="H202" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D203" s="12" t="s">
         <v>75</v>
@@ -12387,27 +12635,27 @@
         <v>75</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>60002</v>
+        <v>40001</v>
       </c>
       <c r="H203" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D204" s="12" t="s">
         <v>75</v>
@@ -12416,27 +12664,27 @@
         <v>75</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>60003</v>
+        <v>60001</v>
       </c>
       <c r="H204" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D205" s="12" t="s">
         <v>75</v>
@@ -12445,27 +12693,27 @@
         <v>75</v>
       </c>
       <c r="F205" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>60004</v>
+        <v>60002</v>
       </c>
       <c r="H205" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B206" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D206" s="12" t="s">
         <v>75</v>
@@ -12474,27 +12722,27 @@
         <v>75</v>
       </c>
       <c r="F206" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G206" s="12" t="n">
-        <v>60005</v>
+        <v>60003</v>
       </c>
       <c r="H206" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D207" s="12" t="s">
         <v>75</v>
@@ -12503,27 +12751,27 @@
         <v>75</v>
       </c>
       <c r="F207" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G207" s="12" t="n">
-        <v>60006</v>
+        <v>60004</v>
       </c>
       <c r="H207" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D208" s="12" t="s">
         <v>75</v>
@@ -12532,177 +12780,177 @@
         <v>75</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>60007</v>
+        <v>60005</v>
       </c>
       <c r="H208" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B209" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D209" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E209" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F209" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="G209" s="12" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H209" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I209" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B209" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C209" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D209" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E209" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F209" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="G209" s="12" t="n">
+      <c r="B210" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E210" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F210" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="G210" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H210" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I210" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D211" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E211" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F211" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="G211" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H209" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I209" s="12" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A210" s="3" t="s">
+      <c r="H211" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A212" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="B212" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C210" s="4" t="s">
+      <c r="C212" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D210" s="3" t="s">
+      <c r="D212" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E210" s="4" t="s">
+      <c r="E212" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F210" s="3" t="s">
+      <c r="F212" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G210" s="4" t="s">
+      <c r="G212" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H210" s="4" t="s">
+      <c r="H212" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I210" s="3" t="s">
+      <c r="I212" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="3"/>
-      <c r="B211" s="4" t="s">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="3"/>
+      <c r="B213" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C211" s="4" t="s">
+      <c r="C213" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D211" s="3"/>
-      <c r="E211" s="4" t="s">
+      <c r="D213" s="3"/>
+      <c r="E213" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F211" s="3"/>
-      <c r="G211" s="4" t="s">
+      <c r="F213" s="3"/>
+      <c r="G213" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H211" s="4" t="s">
+      <c r="H213" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I211" s="3"/>
-    </row>
-    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B212" s="5"/>
-      <c r="C212" s="5"/>
-      <c r="D212" s="5"/>
-      <c r="E212" s="5"/>
-      <c r="F212" s="5"/>
-      <c r="G212" s="5"/>
-      <c r="H212" s="5"/>
-      <c r="I212" s="5"/>
-    </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="B213" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C213" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D213" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E213" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F213" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="G213" s="12" t="n">
-        <v>30001</v>
-      </c>
-      <c r="H213" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I213" s="12" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="B214" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C214" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D214" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E214" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F214" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="G214" s="12" t="n">
-        <v>30002</v>
-      </c>
-      <c r="H214" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I214" s="12" t="s">
-        <v>330</v>
-      </c>
+      <c r="I213" s="3"/>
+    </row>
+    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A214" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B214" s="5"/>
+      <c r="C214" s="5"/>
+      <c r="D214" s="5"/>
+      <c r="E214" s="5"/>
+      <c r="F214" s="5"/>
+      <c r="G214" s="5"/>
+      <c r="H214" s="5"/>
+      <c r="I214" s="5"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B215" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D215" s="12" t="s">
         <v>75</v>
@@ -12711,27 +12959,27 @@
         <v>75</v>
       </c>
       <c r="F215" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G215" s="12" t="n">
-        <v>30003</v>
+        <v>30001</v>
       </c>
       <c r="H215" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I215" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B216" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D216" s="12" t="s">
         <v>75</v>
@@ -12740,27 +12988,27 @@
         <v>75</v>
       </c>
       <c r="F216" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G216" s="12" t="n">
-        <v>30004</v>
+        <v>30002</v>
       </c>
       <c r="H216" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I216" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B217" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D217" s="12" t="s">
         <v>75</v>
@@ -12769,27 +13017,27 @@
         <v>75</v>
       </c>
       <c r="F217" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G217" s="12" t="n">
-        <v>30005</v>
+        <v>30003</v>
       </c>
       <c r="H217" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I217" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B218" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D218" s="12" t="s">
         <v>75</v>
@@ -12798,27 +13046,27 @@
         <v>75</v>
       </c>
       <c r="F218" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G218" s="12" t="n">
-        <v>30006</v>
+        <v>30004</v>
       </c>
       <c r="H218" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I218" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B219" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D219" s="12" t="s">
         <v>75</v>
@@ -12827,27 +13075,27 @@
         <v>75</v>
       </c>
       <c r="F219" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G219" s="12" t="n">
-        <v>40001</v>
+        <v>30005</v>
       </c>
       <c r="H219" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I219" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="12" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B220" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D220" s="12" t="s">
         <v>75</v>
@@ -12856,16 +13104,16 @@
         <v>75</v>
       </c>
       <c r="F220" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G220" s="12" t="n">
-        <v>45001</v>
+        <v>30006</v>
       </c>
       <c r="H220" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I220" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12876,7 +13124,7 @@
         <v>75</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D221" s="12" t="s">
         <v>75</v>
@@ -12885,27 +13133,27 @@
         <v>75</v>
       </c>
       <c r="F221" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G221" s="12" t="n">
-        <v>60001</v>
+        <v>40001</v>
       </c>
       <c r="H221" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I221" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="12" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B222" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D222" s="12" t="s">
         <v>75</v>
@@ -12914,27 +13162,27 @@
         <v>75</v>
       </c>
       <c r="F222" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G222" s="12" t="n">
-        <v>60002</v>
+        <v>45001</v>
       </c>
       <c r="H222" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B223" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D223" s="12" t="s">
         <v>75</v>
@@ -12943,27 +13191,27 @@
         <v>75</v>
       </c>
       <c r="F223" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G223" s="12" t="n">
-        <v>60003</v>
+        <v>60001</v>
       </c>
       <c r="H223" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I223" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B224" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D224" s="12" t="s">
         <v>75</v>
@@ -12972,27 +13220,27 @@
         <v>75</v>
       </c>
       <c r="F224" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G224" s="12" t="n">
-        <v>60004</v>
+        <v>60002</v>
       </c>
       <c r="H224" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I224" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B225" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C225" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D225" s="12" t="s">
         <v>75</v>
@@ -13001,27 +13249,27 @@
         <v>75</v>
       </c>
       <c r="F225" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G225" s="12" t="n">
-        <v>60005</v>
+        <v>60003</v>
       </c>
       <c r="H225" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I225" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B226" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C226" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D226" s="12" t="s">
         <v>75</v>
@@ -13030,27 +13278,27 @@
         <v>75</v>
       </c>
       <c r="F226" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G226" s="12" t="n">
-        <v>60006</v>
+        <v>60004</v>
       </c>
       <c r="H226" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I226" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B227" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C227" s="12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D227" s="12" t="s">
         <v>75</v>
@@ -13059,174 +13307,174 @@
         <v>75</v>
       </c>
       <c r="F227" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G227" s="12" t="n">
-        <v>60007</v>
+        <v>60005</v>
       </c>
       <c r="H227" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I227" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B228" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D228" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E228" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F228" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="G228" s="12" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H228" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B228" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C228" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D228" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E228" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F228" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="G228" s="12" t="n">
+      <c r="B229" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D229" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E229" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F229" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="G229" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H229" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B230" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D230" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E230" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F230" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="G230" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H228" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I228" s="12" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A229" s="3" t="s">
+      <c r="H230" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A231" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B229" s="4" t="s">
+      <c r="B231" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C229" s="4" t="s">
+      <c r="C231" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D229" s="3" t="s">
+      <c r="D231" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E229" s="4" t="s">
+      <c r="E231" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F229" s="3" t="s">
+      <c r="F231" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G229" s="4" t="s">
+      <c r="G231" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H229" s="4" t="s">
+      <c r="H231" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I229" s="3" t="s">
+      <c r="I231" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="3"/>
-      <c r="B230" s="4" t="s">
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="3"/>
+      <c r="B232" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C230" s="4" t="s">
+      <c r="C232" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D230" s="3"/>
-      <c r="E230" s="4" t="s">
+      <c r="D232" s="3"/>
+      <c r="E232" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F230" s="3"/>
-      <c r="G230" s="4" t="s">
+      <c r="F232" s="3"/>
+      <c r="G232" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H230" s="4" t="s">
+      <c r="H232" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I230" s="3"/>
-    </row>
-    <row r="231" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="B231" s="5"/>
-      <c r="C231" s="5"/>
-      <c r="D231" s="5"/>
-      <c r="E231" s="5"/>
-      <c r="F231" s="5"/>
-      <c r="G231" s="5"/>
-      <c r="H231" s="5"/>
-      <c r="I231" s="5"/>
-    </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B232" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C232" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D232" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E232" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F232" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G232" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="H232" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I232" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B233" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C233" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D233" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E233" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F233" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G233" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="H233" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I233" s="7" t="s">
-        <v>186</v>
-      </c>
+      <c r="I232" s="3"/>
+    </row>
+    <row r="233" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A233" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B233" s="5"/>
+      <c r="C233" s="5"/>
+      <c r="D233" s="5"/>
+      <c r="E233" s="5"/>
+      <c r="F233" s="5"/>
+      <c r="G233" s="5"/>
+      <c r="H233" s="5"/>
+      <c r="I233" s="5"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="9" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C234" s="7" t="s">
         <v>110</v>
@@ -13241,19 +13489,21 @@
         <v>26</v>
       </c>
       <c r="G234" s="10" t="s">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="H234" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I234" s="7"/>
+      <c r="I234" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="9" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C235" s="7" t="s">
         <v>110</v>
@@ -13268,16 +13518,18 @@
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="H235" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I235" s="7"/>
+      <c r="I235" s="7" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B236" s="7" t="s">
         <v>24</v>
@@ -13295,7 +13547,7 @@
         <v>26</v>
       </c>
       <c r="G236" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H236" s="7" t="n">
         <v>2</v>
@@ -13304,7 +13556,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B237" s="7" t="s">
         <v>24</v>
@@ -13322,7 +13574,7 @@
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H237" s="7" t="n">
         <v>2</v>
@@ -13331,10 +13583,10 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B238" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C238" s="7" t="s">
         <v>110</v>
@@ -13349,7 +13601,7 @@
         <v>26</v>
       </c>
       <c r="G238" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H238" s="7" t="n">
         <v>2</v>
@@ -13358,10 +13610,10 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B239" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C239" s="7" t="s">
         <v>110</v>
@@ -13376,7 +13628,7 @@
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H239" s="7" t="n">
         <v>2</v>
@@ -13385,10 +13637,10 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C240" s="7" t="s">
         <v>110</v>
@@ -13403,7 +13655,7 @@
         <v>26</v>
       </c>
       <c r="G240" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H240" s="7" t="n">
         <v>2</v>
@@ -13412,10 +13664,10 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C241" s="7" t="s">
         <v>110</v>
@@ -13430,7 +13682,7 @@
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H241" s="7" t="n">
         <v>2</v>
@@ -13439,7 +13691,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B242" s="7" t="s">
         <v>24</v>
@@ -13457,7 +13709,7 @@
         <v>26</v>
       </c>
       <c r="G242" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H242" s="7" t="n">
         <v>2</v>
@@ -13466,7 +13718,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B243" s="7" t="s">
         <v>24</v>
@@ -13484,7 +13736,7 @@
         <v>26</v>
       </c>
       <c r="G243" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H243" s="7" t="n">
         <v>2</v>
@@ -13493,10 +13745,10 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C244" s="7" t="s">
         <v>110</v>
@@ -13511,7 +13763,7 @@
         <v>26</v>
       </c>
       <c r="G244" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H244" s="7" t="n">
         <v>2</v>
@@ -13520,10 +13772,10 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C245" s="7" t="s">
         <v>110</v>
@@ -13538,7 +13790,7 @@
         <v>26</v>
       </c>
       <c r="G245" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H245" s="7" t="n">
         <v>2</v>
@@ -13547,10 +13799,10 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>219</v>
+        <v>109</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>110</v>
@@ -13565,7 +13817,7 @@
         <v>26</v>
       </c>
       <c r="G246" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H246" s="7" t="n">
         <v>2</v>
@@ -13574,10 +13826,10 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B247" s="7" t="s">
-        <v>219</v>
+        <v>109</v>
       </c>
       <c r="C247" s="7" t="s">
         <v>110</v>
@@ -13592,7 +13844,7 @@
         <v>26</v>
       </c>
       <c r="G247" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H247" s="7" t="n">
         <v>2</v>
@@ -13601,10 +13853,10 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>309</v>
+        <v>221</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>308</v>
+        <v>222</v>
       </c>
       <c r="C248" s="7" t="s">
         <v>110</v>
@@ -13619,7 +13871,7 @@
         <v>26</v>
       </c>
       <c r="G248" s="10" t="s">
-        <v>310</v>
+        <v>223</v>
       </c>
       <c r="H248" s="7" t="n">
         <v>2</v>
@@ -13628,10 +13880,10 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>311</v>
+        <v>224</v>
       </c>
       <c r="B249" s="7" t="s">
-        <v>308</v>
+        <v>222</v>
       </c>
       <c r="C249" s="7" t="s">
         <v>110</v>
@@ -13646,7 +13898,7 @@
         <v>26</v>
       </c>
       <c r="G249" s="10" t="s">
-        <v>312</v>
+        <v>225</v>
       </c>
       <c r="H249" s="7" t="n">
         <v>2</v>
@@ -13655,10 +13907,10 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="C250" s="7" t="s">
         <v>110</v>
@@ -13673,7 +13925,7 @@
         <v>26</v>
       </c>
       <c r="G250" s="10" t="s">
-        <v>314</v>
+        <v>227</v>
       </c>
       <c r="H250" s="7" t="n">
         <v>2</v>
@@ -13682,10 +13934,10 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>315</v>
+        <v>228</v>
       </c>
       <c r="B251" s="7" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="C251" s="7" t="s">
         <v>110</v>
@@ -13700,7 +13952,7 @@
         <v>26</v>
       </c>
       <c r="G251" s="10" t="s">
-        <v>316</v>
+        <v>229</v>
       </c>
       <c r="H251" s="7" t="n">
         <v>2</v>
@@ -13708,11 +13960,11 @@
       <c r="I251" s="7"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="7" t="s">
-        <v>317</v>
+      <c r="A252" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C252" s="7" t="s">
         <v>110</v>
@@ -13727,21 +13979,19 @@
         <v>26</v>
       </c>
       <c r="G252" s="10" t="s">
-        <v>314</v>
+        <v>231</v>
       </c>
       <c r="H252" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I252" s="7" t="s">
-        <v>319</v>
-      </c>
+      <c r="I252" s="7"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="7" t="s">
-        <v>320</v>
+      <c r="A253" s="9" t="s">
+        <v>232</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C253" s="7" t="s">
         <v>110</v>
@@ -13756,70 +14006,187 @@
         <v>26</v>
       </c>
       <c r="G253" s="10" t="s">
-        <v>321</v>
+        <v>233</v>
       </c>
       <c r="H253" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I253" s="7" t="s">
-        <v>319</v>
-      </c>
+      <c r="I253" s="7"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="B254" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C254" s="12" t="s">
+      <c r="A254" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B254" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C254" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D254" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E254" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F254" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G254" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="H254" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I254" s="12"/>
+      <c r="D254" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E254" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G254" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H254" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I254" s="7" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B255" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C255" s="12" t="s">
+      <c r="A255" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B255" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C255" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D255" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E255" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F255" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G255" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="H255" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I255" s="12"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D255" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E255" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F255" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G255" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="H255" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B256" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C256" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D256" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E256" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G256" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="H256" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I256" s="14" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B257" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C257" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D257" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E257" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F257" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G257" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="H257" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I257" s="14" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="B258" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C258" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D258" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E258" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F258" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G258" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="H258" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I258" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="B259" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C259" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D259" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E259" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F259" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G259" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="H259" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I259" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="A6:A7"/>
@@ -13827,26 +14194,26 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="D112:D113"/>
-    <mergeCell ref="F112:F113"/>
-    <mergeCell ref="I112:I113"/>
-    <mergeCell ref="A114:I114"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="F184:F185"/>
-    <mergeCell ref="I184:I185"/>
-    <mergeCell ref="A186:I186"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="F210:F211"/>
-    <mergeCell ref="I210:I211"/>
-    <mergeCell ref="A212:I212"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="D229:D230"/>
-    <mergeCell ref="F229:F230"/>
-    <mergeCell ref="I229:I230"/>
-    <mergeCell ref="A231:I231"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="F114:F115"/>
+    <mergeCell ref="I114:I115"/>
+    <mergeCell ref="A116:I116"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A188:I188"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="F212:F213"/>
+    <mergeCell ref="I212:I213"/>
+    <mergeCell ref="A214:I214"/>
+    <mergeCell ref="A231:A232"/>
+    <mergeCell ref="D231:D232"/>
+    <mergeCell ref="F231:F232"/>
+    <mergeCell ref="I231:I232"/>
+    <mergeCell ref="A233:I233"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2535" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="365">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -1016,6 +1016,66 @@
 If set to non-zero, indicates product was calibrated during production</t>
   </si>
   <si>
+    <t xml:space="preserve">Calibration State</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50013</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Internal Only. Not visible to customer. 
+Indicates the state machine of calibration
+0: Calibration Not Initiated. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 20A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. Set Fan 1 Current and Fan 2 current to 0.1A each. And then s</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">et Advance Calibration Flag.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+16,17,18,19: High Point Calibration In Progress
+20: High Point Calibration Done. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 4A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
+21,22,23: Mid Point Calibration In Progress
+24: Mid Point Calibration Done. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 0.4A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
+25,26,27: Low Point Calibration In Progress
+127: Calibration Completed Successfully
+126: Error occured during calibration. Please restart controller</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">READ COIL STATUS (Function Code: 0x01)</t>
   </si>
   <si>
@@ -1097,10 +1157,90 @@
     <t xml:space="preserve">WRITE SINGLE COIL STATUS (Function Code: 0x05)</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Internal Only. Not visible to customer.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Only writtable when test mode enabled.</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Restart Controller</t>
   </si>
   <si>
-    <t xml:space="preserve">Internal Only. Not visible to customer. </t>
+    <t xml:space="preserve">Internal Only. Not visible to customer. 
+Only writtable when test mode enabled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal Only. Not visible to customer. 
+If set to non-zero, indicates product was tested functionally during production. Only writtable when test mode enabled.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Internal Only. Not visible to customer. 
+If set to non-zero, indicates product was calibrated during production. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Only writtable when test mode enabled.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Advance Calibration State</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Internal Only. Not visible to customer. 
+If set to non-zero, it advances the calibration state machine when it is waiting for external input. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Only writtable when test mode enabled.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -7226,7 +7366,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I259"/>
+  <dimension ref="A1:I261"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.94"/>
@@ -10223,99 +10363,101 @@
         <v>327</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="3" t="s">
+    <row r="114" customFormat="false" ht="236.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D114" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" s="12" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B115" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C115" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D115" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="E115" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="F115" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="G115" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H114" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I114" s="3" t="s">
+      <c r="I115" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="3"/>
-      <c r="B115" s="4" t="s">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="3"/>
+      <c r="B116" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C116" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D115" s="3"/>
-      <c r="E115" s="4" t="s">
+      <c r="D116" s="3"/>
+      <c r="E116" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="4" t="s">
+      <c r="F116" s="3"/>
+      <c r="G116" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H115" s="4" t="s">
+      <c r="H116" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I115" s="3"/>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="5" t="s">
+      <c r="I116" s="3"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5"/>
-      <c r="I116" s="5"/>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G117" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H117" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I117" s="7"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="5"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>75</v>
@@ -10333,7 +10475,7 @@
         <v>248</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H118" s="7" t="n">
         <v>1</v>
@@ -10342,7 +10484,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>75</v>
@@ -10360,7 +10502,7 @@
         <v>248</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H119" s="7" t="n">
         <v>1</v>
@@ -10369,7 +10511,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>75</v>
@@ -10387,7 +10529,7 @@
         <v>248</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H120" s="7" t="n">
         <v>1</v>
@@ -10396,7 +10538,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>75</v>
@@ -10414,7 +10556,7 @@
         <v>248</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H121" s="7" t="n">
         <v>1</v>
@@ -10423,7 +10565,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>75</v>
@@ -10441,7 +10583,7 @@
         <v>248</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H122" s="7" t="n">
         <v>1</v>
@@ -10450,7 +10592,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>75</v>
@@ -10468,7 +10610,7 @@
         <v>248</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H123" s="7" t="n">
         <v>1</v>
@@ -10477,7 +10619,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>75</v>
@@ -10495,7 +10637,7 @@
         <v>248</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H124" s="7" t="n">
         <v>1</v>
@@ -10504,7 +10646,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>75</v>
@@ -10522,7 +10664,7 @@
         <v>248</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>201</v>
+        <v>8</v>
       </c>
       <c r="H125" s="7" t="n">
         <v>1</v>
@@ -10531,7 +10673,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>75</v>
@@ -10549,7 +10691,7 @@
         <v>248</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H126" s="7" t="n">
         <v>1</v>
@@ -10558,7 +10700,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>75</v>
@@ -10576,7 +10718,7 @@
         <v>248</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="H127" s="7" t="n">
         <v>1</v>
@@ -10585,7 +10727,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>75</v>
@@ -10603,7 +10745,7 @@
         <v>248</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H128" s="7" t="n">
         <v>1</v>
@@ -10612,7 +10754,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>75</v>
@@ -10630,7 +10772,7 @@
         <v>248</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H129" s="7" t="n">
         <v>1</v>
@@ -10639,7 +10781,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>75</v>
@@ -10657,7 +10799,7 @@
         <v>248</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H130" s="7" t="n">
         <v>1</v>
@@ -10666,7 +10808,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>75</v>
@@ -10684,7 +10826,7 @@
         <v>248</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H131" s="7" t="n">
         <v>1</v>
@@ -10693,7 +10835,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>75</v>
@@ -10711,7 +10853,7 @@
         <v>248</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H132" s="7" t="n">
         <v>1</v>
@@ -10720,7 +10862,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>75</v>
@@ -10738,7 +10880,7 @@
         <v>248</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H133" s="7" t="n">
         <v>1</v>
@@ -10747,7 +10889,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>75</v>
@@ -10765,7 +10907,7 @@
         <v>248</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H134" s="7" t="n">
         <v>1</v>
@@ -10774,7 +10916,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>75</v>
@@ -10792,7 +10934,7 @@
         <v>248</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H135" s="7" t="n">
         <v>1</v>
@@ -10801,7 +10943,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>75</v>
@@ -10819,7 +10961,7 @@
         <v>248</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H136" s="7" t="n">
         <v>1</v>
@@ -10828,7 +10970,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>75</v>
@@ -10846,7 +10988,7 @@
         <v>248</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H137" s="7" t="n">
         <v>1</v>
@@ -10855,7 +10997,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>75</v>
@@ -10873,7 +11015,7 @@
         <v>248</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H138" s="7" t="n">
         <v>1</v>
@@ -10882,7 +11024,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>75</v>
@@ -10900,7 +11042,7 @@
         <v>248</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>401</v>
+        <v>312</v>
       </c>
       <c r="H139" s="7" t="n">
         <v>1</v>
@@ -10909,7 +11051,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>75</v>
@@ -10927,7 +11069,7 @@
         <v>248</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H140" s="7" t="n">
         <v>1</v>
@@ -10936,7 +11078,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>75</v>
@@ -10954,7 +11096,7 @@
         <v>248</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H141" s="7" t="n">
         <v>1</v>
@@ -10963,7 +11105,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>75</v>
@@ -10981,7 +11123,7 @@
         <v>248</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H142" s="7" t="n">
         <v>1</v>
@@ -10990,7 +11132,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>75</v>
@@ -11008,7 +11150,7 @@
         <v>248</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H143" s="7" t="n">
         <v>1</v>
@@ -11017,7 +11159,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
@@ -11035,7 +11177,7 @@
         <v>248</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H144" s="7" t="n">
         <v>1</v>
@@ -11044,7 +11186,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
@@ -11062,7 +11204,7 @@
         <v>248</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H145" s="7" t="n">
         <v>1</v>
@@ -11071,7 +11213,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
@@ -11089,7 +11231,7 @@
         <v>248</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>501</v>
+        <v>407</v>
       </c>
       <c r="H146" s="7" t="n">
         <v>1</v>
@@ -11098,7 +11240,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
@@ -11116,7 +11258,7 @@
         <v>248</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H147" s="7" t="n">
         <v>1</v>
@@ -11125,7 +11267,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
@@ -11143,7 +11285,7 @@
         <v>248</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H148" s="7" t="n">
         <v>1</v>
@@ -11152,7 +11294,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
@@ -11170,7 +11312,7 @@
         <v>248</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H149" s="7" t="n">
         <v>1</v>
@@ -11179,7 +11321,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
@@ -11197,7 +11339,7 @@
         <v>248</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H150" s="7" t="n">
         <v>1</v>
@@ -11206,7 +11348,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
@@ -11224,7 +11366,7 @@
         <v>248</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H151" s="7" t="n">
         <v>1</v>
@@ -11233,7 +11375,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
@@ -11251,7 +11393,7 @@
         <v>248</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H152" s="7" t="n">
         <v>1</v>
@@ -11260,7 +11402,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
@@ -11278,7 +11420,7 @@
         <v>248</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H153" s="7" t="n">
         <v>1</v>
@@ -11287,7 +11429,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
@@ -11305,7 +11447,7 @@
         <v>248</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H154" s="7" t="n">
         <v>1</v>
@@ -11314,7 +11456,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
@@ -11332,7 +11474,7 @@
         <v>248</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H155" s="7" t="n">
         <v>1</v>
@@ -11341,7 +11483,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
@@ -11359,7 +11501,7 @@
         <v>248</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H156" s="7" t="n">
         <v>1</v>
@@ -11368,7 +11510,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
@@ -11386,7 +11528,7 @@
         <v>248</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H157" s="7" t="n">
         <v>1</v>
@@ -11395,7 +11537,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
@@ -11413,7 +11555,7 @@
         <v>248</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>601</v>
+        <v>512</v>
       </c>
       <c r="H158" s="7" t="n">
         <v>1</v>
@@ -11422,7 +11564,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
@@ -11440,7 +11582,7 @@
         <v>248</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H159" s="7" t="n">
         <v>1</v>
@@ -11449,7 +11591,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
@@ -11467,7 +11609,7 @@
         <v>248</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H160" s="7" t="n">
         <v>1</v>
@@ -11476,7 +11618,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
@@ -11494,7 +11636,7 @@
         <v>248</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H161" s="7" t="n">
         <v>1</v>
@@ -11503,7 +11645,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
@@ -11521,7 +11663,7 @@
         <v>248</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H162" s="7" t="n">
         <v>1</v>
@@ -11530,7 +11672,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
@@ -11548,7 +11690,7 @@
         <v>248</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H163" s="7" t="n">
         <v>1</v>
@@ -11557,7 +11699,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
@@ -11575,7 +11717,7 @@
         <v>248</v>
       </c>
       <c r="G164" s="7" t="n">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H164" s="7" t="n">
         <v>1</v>
@@ -11584,7 +11726,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
@@ -11602,7 +11744,7 @@
         <v>248</v>
       </c>
       <c r="G165" s="7" t="n">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H165" s="7" t="n">
         <v>1</v>
@@ -11611,7 +11753,7 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
@@ -11629,7 +11771,7 @@
         <v>248</v>
       </c>
       <c r="G166" s="7" t="n">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H166" s="7" t="n">
         <v>1</v>
@@ -11638,7 +11780,7 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>75</v>
@@ -11656,7 +11798,7 @@
         <v>248</v>
       </c>
       <c r="G167" s="7" t="n">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H167" s="7" t="n">
         <v>1</v>
@@ -11665,7 +11807,7 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>75</v>
@@ -11683,7 +11825,7 @@
         <v>248</v>
       </c>
       <c r="G168" s="7" t="n">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H168" s="7" t="n">
         <v>1</v>
@@ -11692,7 +11834,7 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>75</v>
@@ -11710,7 +11852,7 @@
         <v>248</v>
       </c>
       <c r="G169" s="7" t="n">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H169" s="7" t="n">
         <v>1</v>
@@ -11719,7 +11861,7 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>75</v>
@@ -11737,7 +11879,7 @@
         <v>248</v>
       </c>
       <c r="G170" s="7" t="n">
-        <v>701</v>
+        <v>612</v>
       </c>
       <c r="H170" s="7" t="n">
         <v>1</v>
@@ -11746,7 +11888,7 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>75</v>
@@ -11764,7 +11906,7 @@
         <v>248</v>
       </c>
       <c r="G171" s="7" t="n">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H171" s="7" t="n">
         <v>1</v>
@@ -11773,7 +11915,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>75</v>
@@ -11791,7 +11933,7 @@
         <v>248</v>
       </c>
       <c r="G172" s="7" t="n">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H172" s="7" t="n">
         <v>1</v>
@@ -11800,7 +11942,7 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>75</v>
@@ -11818,7 +11960,7 @@
         <v>248</v>
       </c>
       <c r="G173" s="7" t="n">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H173" s="7" t="n">
         <v>1</v>
@@ -11827,7 +11969,7 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>75</v>
@@ -11845,7 +11987,7 @@
         <v>248</v>
       </c>
       <c r="G174" s="7" t="n">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H174" s="7" t="n">
         <v>1</v>
@@ -11854,7 +11996,7 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>75</v>
@@ -11872,7 +12014,7 @@
         <v>248</v>
       </c>
       <c r="G175" s="7" t="n">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H175" s="7" t="n">
         <v>1</v>
@@ -11881,7 +12023,7 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>75</v>
@@ -11899,7 +12041,7 @@
         <v>248</v>
       </c>
       <c r="G176" s="7" t="n">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H176" s="7" t="n">
         <v>1</v>
@@ -11908,7 +12050,7 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>75</v>
@@ -11926,7 +12068,7 @@
         <v>248</v>
       </c>
       <c r="G177" s="7" t="n">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H177" s="7" t="n">
         <v>1</v>
@@ -11935,7 +12077,7 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>75</v>
@@ -11953,7 +12095,7 @@
         <v>248</v>
       </c>
       <c r="G178" s="7" t="n">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H178" s="7" t="n">
         <v>1</v>
@@ -11962,7 +12104,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>75</v>
@@ -11980,7 +12122,7 @@
         <v>248</v>
       </c>
       <c r="G179" s="7" t="n">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H179" s="7" t="n">
         <v>1</v>
@@ -11989,7 +12131,7 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>75</v>
@@ -12007,7 +12149,7 @@
         <v>248</v>
       </c>
       <c r="G180" s="7" t="n">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H180" s="7" t="n">
         <v>1</v>
@@ -12016,7 +12158,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B181" s="7" t="s">
         <v>75</v>
@@ -12034,7 +12176,7 @@
         <v>248</v>
       </c>
       <c r="G181" s="7" t="n">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H181" s="7" t="n">
         <v>1</v>
@@ -12043,7 +12185,7 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B182" s="7" t="s">
         <v>75</v>
@@ -12061,7 +12203,7 @@
         <v>248</v>
       </c>
       <c r="G182" s="7" t="n">
-        <v>801</v>
+        <v>712</v>
       </c>
       <c r="H182" s="7" t="n">
         <v>1</v>
@@ -12070,7 +12212,7 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>75</v>
@@ -12088,7 +12230,7 @@
         <v>248</v>
       </c>
       <c r="G183" s="7" t="n">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H183" s="7" t="n">
         <v>1</v>
@@ -12097,7 +12239,7 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B184" s="7" t="s">
         <v>75</v>
@@ -12115,7 +12257,7 @@
         <v>248</v>
       </c>
       <c r="G184" s="7" t="n">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H184" s="7" t="n">
         <v>1</v>
@@ -12124,7 +12266,7 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B185" s="7" t="s">
         <v>75</v>
@@ -12142,104 +12284,102 @@
         <v>248</v>
       </c>
       <c r="G185" s="7" t="n">
+        <v>803</v>
+      </c>
+      <c r="H185" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" s="7"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G186" s="7" t="n">
         <v>804</v>
       </c>
-      <c r="H185" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I185" s="7"/>
-    </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="3" t="s">
+      <c r="H186" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I186" s="7"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A187" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="B187" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C186" s="4" t="s">
+      <c r="C187" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D186" s="3" t="s">
+      <c r="D187" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E186" s="4" t="s">
+      <c r="E187" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F186" s="3" t="s">
+      <c r="F187" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G186" s="4" t="s">
+      <c r="G187" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H186" s="4" t="s">
+      <c r="H187" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I186" s="3" t="s">
+      <c r="I187" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="3"/>
-      <c r="B187" s="4" t="s">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="3"/>
+      <c r="B188" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C187" s="4" t="s">
+      <c r="C188" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D187" s="3"/>
-      <c r="E187" s="4" t="s">
+      <c r="D188" s="3"/>
+      <c r="E188" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F187" s="3"/>
-      <c r="G187" s="4" t="s">
+      <c r="F188" s="3"/>
+      <c r="G188" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H187" s="4" t="s">
+      <c r="H188" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I187" s="3"/>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B188" s="5"/>
-      <c r="C188" s="5"/>
-      <c r="D188" s="5"/>
-      <c r="E188" s="5"/>
-      <c r="F188" s="5"/>
-      <c r="G188" s="5"/>
-      <c r="H188" s="5"/>
-      <c r="I188" s="5"/>
-    </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="B189" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C189" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D189" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E189" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F189" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G189" s="12" t="n">
-        <v>20001</v>
-      </c>
-      <c r="H189" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I189" s="12" t="s">
+      <c r="I188" s="3"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A189" s="5" t="s">
         <v>331</v>
       </c>
+      <c r="B189" s="5"/>
+      <c r="C189" s="5"/>
+      <c r="D189" s="5"/>
+      <c r="E189" s="5"/>
+      <c r="F189" s="5"/>
+      <c r="G189" s="5"/>
+      <c r="H189" s="5"/>
+      <c r="I189" s="5"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="12" t="s">
@@ -12258,79 +12398,79 @@
         <v>75</v>
       </c>
       <c r="F190" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>20002</v>
+        <v>20001</v>
       </c>
       <c r="H190" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D191" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E191" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F191" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B191" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C191" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D191" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E191" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F191" s="12" t="s">
-        <v>330</v>
-      </c>
       <c r="G191" s="12" t="n">
-        <v>20003</v>
+        <v>20002</v>
       </c>
       <c r="H191" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B192" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D192" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E192" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F192" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>20003</v>
+      </c>
+      <c r="H192" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I192" s="12" t="s">
         <v>334</v>
-      </c>
-      <c r="B192" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C192" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D192" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E192" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F192" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G192" s="12" t="n">
-        <v>20004</v>
-      </c>
-      <c r="H192" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I192" s="12" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B193" s="12" t="s">
         <v>75</v>
@@ -12345,21 +12485,21 @@
         <v>75</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>20005</v>
+        <v>20004</v>
       </c>
       <c r="H193" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>75</v>
@@ -12374,21 +12514,21 @@
         <v>75</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>20006</v>
+        <v>20005</v>
       </c>
       <c r="H194" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>75</v>
@@ -12403,21 +12543,21 @@
         <v>75</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>20007</v>
+        <v>20006</v>
       </c>
       <c r="H195" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>75</v>
@@ -12432,21 +12572,21 @@
         <v>75</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>20008</v>
+        <v>20007</v>
       </c>
       <c r="H196" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>75</v>
@@ -12461,21 +12601,21 @@
         <v>75</v>
       </c>
       <c r="F197" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>30001</v>
+        <v>20008</v>
       </c>
       <c r="H197" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>75</v>
@@ -12490,21 +12630,21 @@
         <v>75</v>
       </c>
       <c r="F198" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="H198" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B199" s="12" t="s">
         <v>75</v>
@@ -12519,21 +12659,21 @@
         <v>75</v>
       </c>
       <c r="F199" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="H199" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>75</v>
@@ -12548,21 +12688,21 @@
         <v>75</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="H200" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>75</v>
@@ -12577,21 +12717,21 @@
         <v>75</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>30005</v>
+        <v>30004</v>
       </c>
       <c r="H201" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>75</v>
@@ -12606,21 +12746,21 @@
         <v>75</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>30006</v>
+        <v>30005</v>
       </c>
       <c r="H202" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>75</v>
@@ -12635,21 +12775,21 @@
         <v>75</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>40001</v>
+        <v>30006</v>
       </c>
       <c r="H203" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>75</v>
@@ -12664,21 +12804,21 @@
         <v>75</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>60001</v>
+        <v>40001</v>
       </c>
       <c r="H204" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>75</v>
@@ -12693,21 +12833,21 @@
         <v>75</v>
       </c>
       <c r="F205" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="H205" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B206" s="12" t="s">
         <v>75</v>
@@ -12722,21 +12862,21 @@
         <v>75</v>
       </c>
       <c r="F206" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G206" s="12" t="n">
-        <v>60003</v>
+        <v>60002</v>
       </c>
       <c r="H206" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>75</v>
@@ -12751,21 +12891,21 @@
         <v>75</v>
       </c>
       <c r="F207" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G207" s="12" t="n">
-        <v>60004</v>
+        <v>60003</v>
       </c>
       <c r="H207" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>75</v>
@@ -12780,21 +12920,21 @@
         <v>75</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>60005</v>
+        <v>60004</v>
       </c>
       <c r="H208" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>75</v>
@@ -12809,21 +12949,21 @@
         <v>75</v>
       </c>
       <c r="F209" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>60006</v>
+        <v>60005</v>
       </c>
       <c r="H209" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>75</v>
@@ -12838,669 +12978,669 @@
         <v>75</v>
       </c>
       <c r="F210" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G210" s="12" t="n">
-        <v>60007</v>
+        <v>60006</v>
       </c>
       <c r="H210" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D211" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E211" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F211" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G211" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H211" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" s="12" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B212" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E212" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F212" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G212" s="12" t="n">
+        <v>60008</v>
+      </c>
+      <c r="H212" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I212" s="12" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A213" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G213" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H213" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="3"/>
+      <c r="B214" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D214" s="3"/>
+      <c r="E214" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F214" s="3"/>
+      <c r="G214" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I214" s="3"/>
+    </row>
+    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A215" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B215" s="5"/>
+      <c r="C215" s="5"/>
+      <c r="D215" s="5"/>
+      <c r="E215" s="5"/>
+      <c r="F215" s="5"/>
+      <c r="G215" s="5"/>
+      <c r="H215" s="5"/>
+      <c r="I215" s="5"/>
+    </row>
+    <row r="216" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B216" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E216" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F216" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G216" s="12" t="n">
+        <v>30001</v>
+      </c>
+      <c r="H216" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E217" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F217" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G217" s="12" t="n">
+        <v>30002</v>
+      </c>
+      <c r="H217" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B218" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D218" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E218" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F218" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G218" s="12" t="n">
+        <v>30003</v>
+      </c>
+      <c r="H218" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B219" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D219" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E219" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F219" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G219" s="12" t="n">
+        <v>30004</v>
+      </c>
+      <c r="H219" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B220" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D220" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E220" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F220" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G220" s="12" t="n">
+        <v>30005</v>
+      </c>
+      <c r="H220" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I220" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D221" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E221" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F221" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G221" s="12" t="n">
+        <v>30006</v>
+      </c>
+      <c r="H221" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B222" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D222" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E222" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F222" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G222" s="12" t="n">
+        <v>40001</v>
+      </c>
+      <c r="H222" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I222" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E223" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G223" s="12" t="n">
+        <v>45001</v>
+      </c>
+      <c r="H223" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B224" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D224" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E224" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F224" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G224" s="12" t="n">
+        <v>60001</v>
+      </c>
+      <c r="H224" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B225" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D225" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E225" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F225" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G225" s="12" t="n">
+        <v>60002</v>
+      </c>
+      <c r="H225" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I225" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B226" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D226" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E226" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F226" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G226" s="12" t="n">
+        <v>60003</v>
+      </c>
+      <c r="H226" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="B227" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E227" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F227" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G227" s="12" t="n">
+        <v>60004</v>
+      </c>
+      <c r="H227" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I227" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="B211" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C211" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D211" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E211" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F211" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G211" s="12" t="n">
+      <c r="B228" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D228" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E228" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F228" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G228" s="12" t="n">
+        <v>60005</v>
+      </c>
+      <c r="H228" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B229" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D229" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E229" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F229" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G229" s="12" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H229" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B230" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D230" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E230" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F230" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G230" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H230" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B231" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D231" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E231" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F231" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G231" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H211" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I211" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="s">
+      <c r="H231" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A232" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B232" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C232" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D212" s="3" t="s">
+      <c r="D232" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E212" s="4" t="s">
+      <c r="E232" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F212" s="3" t="s">
+      <c r="F232" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G212" s="4" t="s">
+      <c r="G232" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H212" s="4" t="s">
+      <c r="H232" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I212" s="3" t="s">
+      <c r="I232" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="3"/>
-      <c r="B213" s="4" t="s">
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="3"/>
+      <c r="B233" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C213" s="4" t="s">
+      <c r="C233" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D213" s="3"/>
-      <c r="E213" s="4" t="s">
+      <c r="D233" s="3"/>
+      <c r="E233" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F213" s="3"/>
-      <c r="G213" s="4" t="s">
+      <c r="F233" s="3"/>
+      <c r="G233" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H213" s="4" t="s">
+      <c r="H233" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I213" s="3"/>
-    </row>
-    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="B214" s="5"/>
-      <c r="C214" s="5"/>
-      <c r="D214" s="5"/>
-      <c r="E214" s="5"/>
-      <c r="F214" s="5"/>
-      <c r="G214" s="5"/>
-      <c r="H214" s="5"/>
-      <c r="I214" s="5"/>
-    </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="B215" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C215" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D215" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E215" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F215" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G215" s="12" t="n">
-        <v>30001</v>
-      </c>
-      <c r="H215" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I215" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="B216" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C216" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D216" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E216" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F216" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G216" s="12" t="n">
-        <v>30002</v>
-      </c>
-      <c r="H216" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I216" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="B217" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C217" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D217" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E217" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F217" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G217" s="12" t="n">
-        <v>30003</v>
-      </c>
-      <c r="H217" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I217" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="B218" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C218" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D218" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E218" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F218" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G218" s="12" t="n">
-        <v>30004</v>
-      </c>
-      <c r="H218" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I218" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="B219" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C219" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D219" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E219" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F219" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G219" s="12" t="n">
-        <v>30005</v>
-      </c>
-      <c r="H219" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I219" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="B220" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C220" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D220" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E220" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F220" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G220" s="12" t="n">
-        <v>30006</v>
-      </c>
-      <c r="H220" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I220" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="B221" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C221" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D221" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E221" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F221" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G221" s="12" t="n">
-        <v>40001</v>
-      </c>
-      <c r="H221" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I221" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="B222" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C222" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D222" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E222" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F222" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G222" s="12" t="n">
-        <v>45001</v>
-      </c>
-      <c r="H222" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I222" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B223" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C223" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D223" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E223" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F223" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G223" s="12" t="n">
-        <v>60001</v>
-      </c>
-      <c r="H223" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I223" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="B224" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C224" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D224" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E224" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F224" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G224" s="12" t="n">
-        <v>60002</v>
-      </c>
-      <c r="H224" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I224" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="B225" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C225" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D225" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E225" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F225" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G225" s="12" t="n">
-        <v>60003</v>
-      </c>
-      <c r="H225" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I225" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="B226" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C226" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D226" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E226" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F226" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G226" s="12" t="n">
-        <v>60004</v>
-      </c>
-      <c r="H226" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I226" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="B227" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C227" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D227" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E227" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F227" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G227" s="12" t="n">
-        <v>60005</v>
-      </c>
-      <c r="H227" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I227" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="B228" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C228" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D228" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E228" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F228" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G228" s="12" t="n">
-        <v>60006</v>
-      </c>
-      <c r="H228" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I228" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="B229" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C229" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D229" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E229" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F229" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G229" s="12" t="n">
-        <v>60007</v>
-      </c>
-      <c r="H229" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I229" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="B230" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C230" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D230" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E230" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F230" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="G230" s="12" t="n">
-        <v>60008</v>
-      </c>
-      <c r="H230" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I230" s="12" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B231" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C231" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E231" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F231" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G231" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H231" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I231" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="3"/>
-      <c r="B232" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C232" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D232" s="3"/>
-      <c r="E232" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F232" s="3"/>
-      <c r="G232" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H232" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I232" s="3"/>
-    </row>
-    <row r="233" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="5" t="s">
+      <c r="I233" s="3"/>
+    </row>
+    <row r="234" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A234" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B233" s="5"/>
-      <c r="C233" s="5"/>
-      <c r="D233" s="5"/>
-      <c r="E233" s="5"/>
-      <c r="F233" s="5"/>
-      <c r="G233" s="5"/>
-      <c r="H233" s="5"/>
-      <c r="I233" s="5"/>
-    </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B234" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C234" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D234" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E234" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F234" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G234" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="H234" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I234" s="7" t="s">
-        <v>112</v>
-      </c>
+      <c r="B234" s="5"/>
+      <c r="C234" s="5"/>
+      <c r="D234" s="5"/>
+      <c r="E234" s="5"/>
+      <c r="F234" s="5"/>
+      <c r="G234" s="5"/>
+      <c r="H234" s="5"/>
+      <c r="I234" s="5"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="9" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="B235" s="7" t="s">
         <v>109</v>
@@ -13518,21 +13658,21 @@
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>188</v>
+        <v>318</v>
       </c>
       <c r="H235" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I235" s="7" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="9" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C236" s="7" t="s">
         <v>110</v>
@@ -13547,16 +13687,18 @@
         <v>26</v>
       </c>
       <c r="G236" s="10" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="H236" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I236" s="7"/>
+      <c r="I236" s="7" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B237" s="7" t="s">
         <v>24</v>
@@ -13574,7 +13716,7 @@
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H237" s="7" t="n">
         <v>2</v>
@@ -13583,7 +13725,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B238" s="7" t="s">
         <v>24</v>
@@ -13601,7 +13743,7 @@
         <v>26</v>
       </c>
       <c r="G238" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H238" s="7" t="n">
         <v>2</v>
@@ -13610,7 +13752,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B239" s="7" t="s">
         <v>24</v>
@@ -13628,7 +13770,7 @@
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H239" s="7" t="n">
         <v>2</v>
@@ -13637,10 +13779,10 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C240" s="7" t="s">
         <v>110</v>
@@ -13655,7 +13797,7 @@
         <v>26</v>
       </c>
       <c r="G240" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H240" s="7" t="n">
         <v>2</v>
@@ -13664,7 +13806,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B241" s="7" t="s">
         <v>109</v>
@@ -13682,7 +13824,7 @@
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H241" s="7" t="n">
         <v>2</v>
@@ -13691,10 +13833,10 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C242" s="7" t="s">
         <v>110</v>
@@ -13709,7 +13851,7 @@
         <v>26</v>
       </c>
       <c r="G242" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H242" s="7" t="n">
         <v>2</v>
@@ -13718,7 +13860,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B243" s="7" t="s">
         <v>24</v>
@@ -13736,7 +13878,7 @@
         <v>26</v>
       </c>
       <c r="G243" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H243" s="7" t="n">
         <v>2</v>
@@ -13745,7 +13887,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>24</v>
@@ -13763,7 +13905,7 @@
         <v>26</v>
       </c>
       <c r="G244" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H244" s="7" t="n">
         <v>2</v>
@@ -13772,7 +13914,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B245" s="7" t="s">
         <v>24</v>
@@ -13790,7 +13932,7 @@
         <v>26</v>
       </c>
       <c r="G245" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H245" s="7" t="n">
         <v>2</v>
@@ -13799,10 +13941,10 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>110</v>
@@ -13817,7 +13959,7 @@
         <v>26</v>
       </c>
       <c r="G246" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H246" s="7" t="n">
         <v>2</v>
@@ -13826,7 +13968,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B247" s="7" t="s">
         <v>109</v>
@@ -13844,7 +13986,7 @@
         <v>26</v>
       </c>
       <c r="G247" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H247" s="7" t="n">
         <v>2</v>
@@ -13853,10 +13995,10 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>222</v>
+        <v>109</v>
       </c>
       <c r="C248" s="7" t="s">
         <v>110</v>
@@ -13871,7 +14013,7 @@
         <v>26</v>
       </c>
       <c r="G248" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H248" s="7" t="n">
         <v>2</v>
@@ -13880,7 +14022,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B249" s="7" t="s">
         <v>222</v>
@@ -13898,7 +14040,7 @@
         <v>26</v>
       </c>
       <c r="G249" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H249" s="7" t="n">
         <v>2</v>
@@ -13907,10 +14049,10 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C250" s="7" t="s">
         <v>110</v>
@@ -13925,7 +14067,7 @@
         <v>26</v>
       </c>
       <c r="G250" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H250" s="7" t="n">
         <v>2</v>
@@ -13934,7 +14076,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B251" s="7" t="s">
         <v>195</v>
@@ -13952,7 +14094,7 @@
         <v>26</v>
       </c>
       <c r="G251" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H251" s="7" t="n">
         <v>2</v>
@@ -13961,10 +14103,10 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="C252" s="7" t="s">
         <v>110</v>
@@ -13979,7 +14121,7 @@
         <v>26</v>
       </c>
       <c r="G252" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H252" s="7" t="n">
         <v>2</v>
@@ -13988,7 +14130,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B253" s="7" t="s">
         <v>109</v>
@@ -14006,7 +14148,7 @@
         <v>26</v>
       </c>
       <c r="G253" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H253" s="7" t="n">
         <v>2</v>
@@ -14014,11 +14156,11 @@
       <c r="I253" s="7"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="7" t="s">
-        <v>234</v>
+      <c r="A254" s="9" t="s">
+        <v>232</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C254" s="7" t="s">
         <v>110</v>
@@ -14033,18 +14175,16 @@
         <v>26</v>
       </c>
       <c r="G254" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H254" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I254" s="7" t="s">
-        <v>236</v>
-      </c>
+      <c r="I254" s="7"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>75</v>
@@ -14062,7 +14202,7 @@
         <v>26</v>
       </c>
       <c r="G255" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H255" s="7" t="n">
         <v>2</v>
@@ -14072,37 +14212,37 @@
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="12" t="s">
+      <c r="A256" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B256" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C256" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D256" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E256" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G256" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="H256" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I256" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="12" t="s">
         <v>239</v>
-      </c>
-      <c r="B256" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C256" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D256" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E256" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F256" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G256" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="H256" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I256" s="14" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="12" t="s">
-        <v>241</v>
       </c>
       <c r="B257" s="12" t="s">
         <v>75</v>
@@ -14120,18 +14260,18 @@
         <v>26</v>
       </c>
       <c r="G257" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H257" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I257" s="14" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="258" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="11" t="s">
-        <v>322</v>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="12" t="s">
+        <v>241</v>
       </c>
       <c r="B258" s="12" t="s">
         <v>75</v>
@@ -14148,19 +14288,19 @@
       <c r="F258" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G258" s="13" t="s">
-        <v>323</v>
+      <c r="G258" s="12" t="s">
+        <v>242</v>
       </c>
       <c r="H258" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I258" s="12" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="259" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I258" s="14" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B259" s="12" t="s">
         <v>75</v>
@@ -14178,13 +14318,71 @@
         <v>26</v>
       </c>
       <c r="G259" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="H259" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I259" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="B260" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C260" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D260" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E260" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G260" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="H259" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I259" s="12" t="s">
-        <v>327</v>
+      <c r="H260" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I260" s="12" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B261" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C261" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D261" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E261" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F261" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G261" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="H261" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I261" s="12" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -14194,26 +14392,26 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="F114:F115"/>
-    <mergeCell ref="I114:I115"/>
-    <mergeCell ref="A116:I116"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A188:I188"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="F212:F213"/>
-    <mergeCell ref="I212:I213"/>
-    <mergeCell ref="A214:I214"/>
-    <mergeCell ref="A231:A232"/>
-    <mergeCell ref="D231:D232"/>
-    <mergeCell ref="F231:F232"/>
-    <mergeCell ref="I231:I232"/>
-    <mergeCell ref="A233:I233"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="D115:D116"/>
+    <mergeCell ref="F115:F116"/>
+    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="A117:I117"/>
+    <mergeCell ref="A187:A188"/>
+    <mergeCell ref="D187:D188"/>
+    <mergeCell ref="F187:F188"/>
+    <mergeCell ref="I187:I188"/>
+    <mergeCell ref="A189:I189"/>
+    <mergeCell ref="A213:A214"/>
+    <mergeCell ref="D213:D214"/>
+    <mergeCell ref="F213:F214"/>
+    <mergeCell ref="I213:I214"/>
+    <mergeCell ref="A215:I215"/>
+    <mergeCell ref="A232:A233"/>
+    <mergeCell ref="D232:D233"/>
+    <mergeCell ref="F232:F233"/>
+    <mergeCell ref="I232:I233"/>
+    <mergeCell ref="A234:I234"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="366">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -1157,35 +1157,21 @@
     <t xml:space="preserve">WRITE SINGLE COIL STATUS (Function Code: 0x05)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Internal Only. Not visible to customer.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">Only writtable when test mode enabled.</t>
-    </r>
+    <t xml:space="preserve">Internal Only. Not visible to customer.
+Only settable when test mode enabled</t>
   </si>
   <si>
     <t xml:space="preserve">Restart Controller</t>
   </si>
   <si>
     <t xml:space="preserve">Internal Only. Not visible to customer. 
-Only writtable when test mode enabled.</t>
+Only writtable when test mode enabled.
+Only writtable together with Serial Number Upper Half</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal Only. Not visible to customer. 
+Only writtable when test mode enabled.
+Only writtable together with Serial Number Lower Half</t>
   </si>
   <si>
     <t xml:space="preserve">Internal Only. Not visible to customer. 
@@ -13285,7 +13271,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="12" t="s">
         <v>348</v>
       </c>
@@ -13311,7 +13297,7 @@
         <v>1</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14240,7 +14226,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="12" t="s">
         <v>239</v>
       </c>
@@ -14269,7 +14255,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="12" t="s">
         <v>241</v>
       </c>
@@ -14295,7 +14281,7 @@
         <v>2</v>
       </c>
       <c r="I258" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14324,7 +14310,7 @@
         <v>2</v>
       </c>
       <c r="I259" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14353,12 +14339,12 @@
         <v>2</v>
       </c>
       <c r="I260" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B261" s="12" t="s">
         <v>75</v>
@@ -14382,7 +14368,7 @@
         <v>2</v>
       </c>
       <c r="I261" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="367">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -1074,6 +1074,9 @@
 127: Calibration Completed Successfully
 126: Error occured during calibration. Please restart controller</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Grid Contactor &amp; Solar Neutral Earth Contactor Coil</t>
   </si>
   <si>
     <t xml:space="preserve">READ COIL STATUS (Function Code: 0x01)</t>
@@ -7352,7 +7355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I261"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.94"/>
@@ -11145,7 +11148,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
@@ -11172,7 +11175,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
@@ -11199,7 +11202,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
@@ -11217,7 +11220,7 @@
         <v>248</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>407</v>
+        <v>501</v>
       </c>
       <c r="H146" s="7" t="n">
         <v>1</v>
@@ -11226,7 +11229,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
@@ -11244,7 +11247,7 @@
         <v>248</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H147" s="7" t="n">
         <v>1</v>
@@ -11253,7 +11256,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
@@ -11271,7 +11274,7 @@
         <v>248</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H148" s="7" t="n">
         <v>1</v>
@@ -11280,7 +11283,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
@@ -11298,7 +11301,7 @@
         <v>248</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H149" s="7" t="n">
         <v>1</v>
@@ -11307,7 +11310,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
@@ -11325,7 +11328,7 @@
         <v>248</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H150" s="7" t="n">
         <v>1</v>
@@ -11334,7 +11337,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
@@ -11352,7 +11355,7 @@
         <v>248</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H151" s="7" t="n">
         <v>1</v>
@@ -11361,7 +11364,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
@@ -11379,7 +11382,7 @@
         <v>248</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H152" s="7" t="n">
         <v>1</v>
@@ -11388,7 +11391,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
@@ -11406,7 +11409,7 @@
         <v>248</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H153" s="7" t="n">
         <v>1</v>
@@ -11415,7 +11418,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
@@ -11433,7 +11436,7 @@
         <v>248</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H154" s="7" t="n">
         <v>1</v>
@@ -11442,7 +11445,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
@@ -11460,7 +11463,7 @@
         <v>248</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H155" s="7" t="n">
         <v>1</v>
@@ -11469,7 +11472,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
@@ -11487,7 +11490,7 @@
         <v>248</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H156" s="7" t="n">
         <v>1</v>
@@ -11496,7 +11499,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
@@ -11514,7 +11517,7 @@
         <v>248</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H157" s="7" t="n">
         <v>1</v>
@@ -11523,7 +11526,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
@@ -11541,7 +11544,7 @@
         <v>248</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>512</v>
+        <v>601</v>
       </c>
       <c r="H158" s="7" t="n">
         <v>1</v>
@@ -11550,7 +11553,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
@@ -11568,7 +11571,7 @@
         <v>248</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H159" s="7" t="n">
         <v>1</v>
@@ -11577,7 +11580,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
@@ -11595,7 +11598,7 @@
         <v>248</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H160" s="7" t="n">
         <v>1</v>
@@ -11604,7 +11607,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
@@ -11622,7 +11625,7 @@
         <v>248</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H161" s="7" t="n">
         <v>1</v>
@@ -11631,7 +11634,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
@@ -11649,7 +11652,7 @@
         <v>248</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H162" s="7" t="n">
         <v>1</v>
@@ -11658,7 +11661,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
@@ -11676,7 +11679,7 @@
         <v>248</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H163" s="7" t="n">
         <v>1</v>
@@ -11685,7 +11688,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
@@ -11703,7 +11706,7 @@
         <v>248</v>
       </c>
       <c r="G164" s="7" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H164" s="7" t="n">
         <v>1</v>
@@ -11712,7 +11715,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
@@ -11730,7 +11733,7 @@
         <v>248</v>
       </c>
       <c r="G165" s="7" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H165" s="7" t="n">
         <v>1</v>
@@ -11739,7 +11742,7 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
@@ -11757,7 +11760,7 @@
         <v>248</v>
       </c>
       <c r="G166" s="7" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H166" s="7" t="n">
         <v>1</v>
@@ -11766,7 +11769,7 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>75</v>
@@ -11784,7 +11787,7 @@
         <v>248</v>
       </c>
       <c r="G167" s="7" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H167" s="7" t="n">
         <v>1</v>
@@ -11793,7 +11796,7 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>75</v>
@@ -11811,7 +11814,7 @@
         <v>248</v>
       </c>
       <c r="G168" s="7" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H168" s="7" t="n">
         <v>1</v>
@@ -11820,7 +11823,7 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>75</v>
@@ -11838,7 +11841,7 @@
         <v>248</v>
       </c>
       <c r="G169" s="7" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H169" s="7" t="n">
         <v>1</v>
@@ -11847,7 +11850,7 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>75</v>
@@ -11865,7 +11868,7 @@
         <v>248</v>
       </c>
       <c r="G170" s="7" t="n">
-        <v>612</v>
+        <v>701</v>
       </c>
       <c r="H170" s="7" t="n">
         <v>1</v>
@@ -11874,7 +11877,7 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>75</v>
@@ -11892,7 +11895,7 @@
         <v>248</v>
       </c>
       <c r="G171" s="7" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H171" s="7" t="n">
         <v>1</v>
@@ -11901,7 +11904,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>75</v>
@@ -11919,7 +11922,7 @@
         <v>248</v>
       </c>
       <c r="G172" s="7" t="n">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H172" s="7" t="n">
         <v>1</v>
@@ -11928,7 +11931,7 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>75</v>
@@ -11946,7 +11949,7 @@
         <v>248</v>
       </c>
       <c r="G173" s="7" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H173" s="7" t="n">
         <v>1</v>
@@ -11955,7 +11958,7 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>75</v>
@@ -11973,7 +11976,7 @@
         <v>248</v>
       </c>
       <c r="G174" s="7" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H174" s="7" t="n">
         <v>1</v>
@@ -11982,7 +11985,7 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>75</v>
@@ -12000,7 +12003,7 @@
         <v>248</v>
       </c>
       <c r="G175" s="7" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H175" s="7" t="n">
         <v>1</v>
@@ -12009,7 +12012,7 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>75</v>
@@ -12027,7 +12030,7 @@
         <v>248</v>
       </c>
       <c r="G176" s="7" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H176" s="7" t="n">
         <v>1</v>
@@ -12036,7 +12039,7 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>75</v>
@@ -12054,7 +12057,7 @@
         <v>248</v>
       </c>
       <c r="G177" s="7" t="n">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H177" s="7" t="n">
         <v>1</v>
@@ -12063,7 +12066,7 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>75</v>
@@ -12081,7 +12084,7 @@
         <v>248</v>
       </c>
       <c r="G178" s="7" t="n">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H178" s="7" t="n">
         <v>1</v>
@@ -12090,7 +12093,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>75</v>
@@ -12108,7 +12111,7 @@
         <v>248</v>
       </c>
       <c r="G179" s="7" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H179" s="7" t="n">
         <v>1</v>
@@ -12117,7 +12120,7 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>75</v>
@@ -12135,7 +12138,7 @@
         <v>248</v>
       </c>
       <c r="G180" s="7" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H180" s="7" t="n">
         <v>1</v>
@@ -12144,7 +12147,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B181" s="7" t="s">
         <v>75</v>
@@ -12162,7 +12165,7 @@
         <v>248</v>
       </c>
       <c r="G181" s="7" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H181" s="7" t="n">
         <v>1</v>
@@ -12171,7 +12174,7 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B182" s="7" t="s">
         <v>75</v>
@@ -12189,7 +12192,7 @@
         <v>248</v>
       </c>
       <c r="G182" s="7" t="n">
-        <v>712</v>
+        <v>801</v>
       </c>
       <c r="H182" s="7" t="n">
         <v>1</v>
@@ -12198,7 +12201,7 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>75</v>
@@ -12216,7 +12219,7 @@
         <v>248</v>
       </c>
       <c r="G183" s="7" t="n">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H183" s="7" t="n">
         <v>1</v>
@@ -12225,7 +12228,7 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B184" s="7" t="s">
         <v>75</v>
@@ -12243,7 +12246,7 @@
         <v>248</v>
       </c>
       <c r="G184" s="7" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H184" s="7" t="n">
         <v>1</v>
@@ -12252,7 +12255,7 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B185" s="7" t="s">
         <v>75</v>
@@ -12270,106 +12273,108 @@
         <v>248</v>
       </c>
       <c r="G185" s="7" t="n">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H185" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I185" s="7"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D186" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E186" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F186" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G186" s="7" t="n">
-        <v>804</v>
-      </c>
-      <c r="H186" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I186" s="7"/>
-    </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="3" t="s">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A186" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="B186" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I186" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="3"/>
       <c r="B187" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D187" s="3"/>
       <c r="E187" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F187" s="3"/>
       <c r="G187" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I187" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="3"/>
-      <c r="B188" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D188" s="3"/>
-      <c r="E188" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F188" s="3"/>
-      <c r="G188" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H188" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I188" s="3"/>
-    </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="B189" s="5"/>
-      <c r="C189" s="5"/>
-      <c r="D189" s="5"/>
-      <c r="E189" s="5"/>
-      <c r="F189" s="5"/>
-      <c r="G189" s="5"/>
-      <c r="H189" s="5"/>
-      <c r="I189" s="5"/>
+      <c r="I187" s="3"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A188" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B188" s="5"/>
+      <c r="C188" s="5"/>
+      <c r="D188" s="5"/>
+      <c r="E188" s="5"/>
+      <c r="F188" s="5"/>
+      <c r="G188" s="5"/>
+      <c r="H188" s="5"/>
+      <c r="I188" s="5"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D189" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E189" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F189" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>20001</v>
+      </c>
+      <c r="H189" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I189" s="12" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="12" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>75</v>
@@ -12384,50 +12389,50 @@
         <v>75</v>
       </c>
       <c r="F190" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>20001</v>
+        <v>20002</v>
       </c>
       <c r="H190" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D191" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E191" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F191" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>20003</v>
+      </c>
+      <c r="H191" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" s="12" t="s">
         <v>335</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C191" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D191" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E191" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F191" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="G191" s="12" t="n">
-        <v>20002</v>
-      </c>
-      <c r="H191" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I191" s="12" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>75</v>
@@ -12442,21 +12447,21 @@
         <v>75</v>
       </c>
       <c r="F192" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>20003</v>
+        <v>20004</v>
       </c>
       <c r="H192" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B193" s="12" t="s">
         <v>75</v>
@@ -12471,21 +12476,21 @@
         <v>75</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>20004</v>
+        <v>20005</v>
       </c>
       <c r="H193" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>75</v>
@@ -12500,21 +12505,21 @@
         <v>75</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>20005</v>
+        <v>20006</v>
       </c>
       <c r="H194" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>75</v>
@@ -12529,21 +12534,21 @@
         <v>75</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>20006</v>
+        <v>20007</v>
       </c>
       <c r="H195" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>75</v>
@@ -12558,21 +12563,21 @@
         <v>75</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>20007</v>
+        <v>20008</v>
       </c>
       <c r="H196" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>75</v>
@@ -12587,21 +12592,21 @@
         <v>75</v>
       </c>
       <c r="F197" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>20008</v>
+        <v>30001</v>
       </c>
       <c r="H197" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>75</v>
@@ -12616,21 +12621,21 @@
         <v>75</v>
       </c>
       <c r="F198" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="H198" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B199" s="12" t="s">
         <v>75</v>
@@ -12645,21 +12650,21 @@
         <v>75</v>
       </c>
       <c r="F199" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>30002</v>
+        <v>30003</v>
       </c>
       <c r="H199" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>75</v>
@@ -12674,21 +12679,21 @@
         <v>75</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>30003</v>
+        <v>30004</v>
       </c>
       <c r="H200" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>75</v>
@@ -12703,21 +12708,21 @@
         <v>75</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>30004</v>
+        <v>30005</v>
       </c>
       <c r="H201" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>75</v>
@@ -12732,21 +12737,21 @@
         <v>75</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>30005</v>
+        <v>30006</v>
       </c>
       <c r="H202" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>75</v>
@@ -12761,21 +12766,21 @@
         <v>75</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>30006</v>
+        <v>40001</v>
       </c>
       <c r="H203" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>75</v>
@@ -12790,21 +12795,21 @@
         <v>75</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>40001</v>
+        <v>60001</v>
       </c>
       <c r="H204" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>75</v>
@@ -12819,21 +12824,21 @@
         <v>75</v>
       </c>
       <c r="F205" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>60001</v>
+        <v>60002</v>
       </c>
       <c r="H205" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B206" s="12" t="s">
         <v>75</v>
@@ -12848,21 +12853,21 @@
         <v>75</v>
       </c>
       <c r="F206" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G206" s="12" t="n">
-        <v>60002</v>
+        <v>60003</v>
       </c>
       <c r="H206" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>75</v>
@@ -12877,21 +12882,21 @@
         <v>75</v>
       </c>
       <c r="F207" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G207" s="12" t="n">
-        <v>60003</v>
+        <v>60004</v>
       </c>
       <c r="H207" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>75</v>
@@ -12906,21 +12911,21 @@
         <v>75</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>60004</v>
+        <v>60005</v>
       </c>
       <c r="H208" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>75</v>
@@ -12935,21 +12940,21 @@
         <v>75</v>
       </c>
       <c r="F209" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>60005</v>
+        <v>60006</v>
       </c>
       <c r="H209" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="12" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>75</v>
@@ -12964,21 +12969,21 @@
         <v>75</v>
       </c>
       <c r="F210" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G210" s="12" t="n">
-        <v>60006</v>
+        <v>60007</v>
       </c>
       <c r="H210" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>75</v>
@@ -12993,113 +12998,113 @@
         <v>75</v>
       </c>
       <c r="F211" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G211" s="12" t="n">
-        <v>60007</v>
+        <v>60008</v>
       </c>
       <c r="H211" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I211" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A212" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="3"/>
+      <c r="B213" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D213" s="3"/>
+      <c r="E213" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F213" s="3"/>
+      <c r="G213" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H213" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I213" s="3"/>
+    </row>
+    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A214" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B214" s="5"/>
+      <c r="C214" s="5"/>
+      <c r="D214" s="5"/>
+      <c r="E214" s="5"/>
+      <c r="F214" s="5"/>
+      <c r="G214" s="5"/>
+      <c r="H214" s="5"/>
+      <c r="I214" s="5"/>
+    </row>
+    <row r="215" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B215" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E215" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F215" s="12" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="B212" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C212" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D212" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E212" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F212" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="G212" s="12" t="n">
-        <v>60008</v>
-      </c>
-      <c r="H212" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I212" s="12" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A213" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B213" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C213" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E213" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F213" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G213" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H213" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I213" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="3"/>
-      <c r="B214" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C214" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D214" s="3"/>
-      <c r="E214" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F214" s="3"/>
-      <c r="G214" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H214" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I214" s="3"/>
-    </row>
-    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="B215" s="5"/>
-      <c r="C215" s="5"/>
-      <c r="D215" s="5"/>
-      <c r="E215" s="5"/>
-      <c r="F215" s="5"/>
-      <c r="G215" s="5"/>
-      <c r="H215" s="5"/>
-      <c r="I215" s="5"/>
+      <c r="G215" s="12" t="n">
+        <v>30001</v>
+      </c>
+      <c r="H215" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="12" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="216" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B216" s="12" t="s">
         <v>75</v>
@@ -13114,21 +13119,21 @@
         <v>75</v>
       </c>
       <c r="F216" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G216" s="12" t="n">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="H216" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I216" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B217" s="12" t="s">
         <v>75</v>
@@ -13143,21 +13148,21 @@
         <v>75</v>
       </c>
       <c r="F217" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G217" s="12" t="n">
-        <v>30002</v>
+        <v>30003</v>
       </c>
       <c r="H217" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I217" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B218" s="12" t="s">
         <v>75</v>
@@ -13172,21 +13177,21 @@
         <v>75</v>
       </c>
       <c r="F218" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G218" s="12" t="n">
-        <v>30003</v>
+        <v>30004</v>
       </c>
       <c r="H218" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I218" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B219" s="12" t="s">
         <v>75</v>
@@ -13201,21 +13206,21 @@
         <v>75</v>
       </c>
       <c r="F219" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G219" s="12" t="n">
-        <v>30004</v>
+        <v>30005</v>
       </c>
       <c r="H219" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I219" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B220" s="12" t="s">
         <v>75</v>
@@ -13230,21 +13235,21 @@
         <v>75</v>
       </c>
       <c r="F220" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G220" s="12" t="n">
-        <v>30005</v>
+        <v>30006</v>
       </c>
       <c r="H220" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I220" s="12" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B221" s="12" t="s">
         <v>75</v>
@@ -13259,21 +13264,21 @@
         <v>75</v>
       </c>
       <c r="F221" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G221" s="12" t="n">
-        <v>30006</v>
+        <v>40001</v>
       </c>
       <c r="H221" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I221" s="12" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B222" s="12" t="s">
         <v>75</v>
@@ -13288,50 +13293,50 @@
         <v>75</v>
       </c>
       <c r="F222" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G222" s="12" t="n">
-        <v>40001</v>
+        <v>45001</v>
       </c>
       <c r="H222" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E223" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="G223" s="12" t="n">
+        <v>60001</v>
+      </c>
+      <c r="H223" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" s="12" t="s">
         <v>359</v>
-      </c>
-      <c r="B223" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C223" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D223" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E223" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F223" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="G223" s="12" t="n">
-        <v>45001</v>
-      </c>
-      <c r="H223" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I223" s="12" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B224" s="12" t="s">
         <v>75</v>
@@ -13346,21 +13351,21 @@
         <v>75</v>
       </c>
       <c r="F224" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G224" s="12" t="n">
-        <v>60001</v>
+        <v>60002</v>
       </c>
       <c r="H224" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I224" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B225" s="12" t="s">
         <v>75</v>
@@ -13375,21 +13380,21 @@
         <v>75</v>
       </c>
       <c r="F225" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G225" s="12" t="n">
-        <v>60002</v>
+        <v>60003</v>
       </c>
       <c r="H225" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I225" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B226" s="12" t="s">
         <v>75</v>
@@ -13404,21 +13409,21 @@
         <v>75</v>
       </c>
       <c r="F226" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G226" s="12" t="n">
-        <v>60003</v>
+        <v>60004</v>
       </c>
       <c r="H226" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I226" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B227" s="12" t="s">
         <v>75</v>
@@ -13433,21 +13438,21 @@
         <v>75</v>
       </c>
       <c r="F227" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G227" s="12" t="n">
-        <v>60004</v>
+        <v>60005</v>
       </c>
       <c r="H227" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I227" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B228" s="12" t="s">
         <v>75</v>
@@ -13462,21 +13467,21 @@
         <v>75</v>
       </c>
       <c r="F228" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G228" s="12" t="n">
-        <v>60005</v>
+        <v>60006</v>
       </c>
       <c r="H228" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I228" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="12" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B229" s="12" t="s">
         <v>75</v>
@@ -13491,21 +13496,21 @@
         <v>75</v>
       </c>
       <c r="F229" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G229" s="12" t="n">
-        <v>60006</v>
+        <v>60007</v>
       </c>
       <c r="H229" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I229" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B230" s="12" t="s">
         <v>75</v>
@@ -13520,113 +13525,113 @@
         <v>75</v>
       </c>
       <c r="F230" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G230" s="12" t="n">
-        <v>60007</v>
+        <v>60008</v>
       </c>
       <c r="H230" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I230" s="12" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="B231" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C231" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D231" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E231" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F231" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="G231" s="12" t="n">
-        <v>60008</v>
-      </c>
-      <c r="H231" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I231" s="12" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A232" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A231" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="B231" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G231" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H231" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="3"/>
       <c r="B232" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D232" s="3"/>
       <c r="E232" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F232" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F232" s="3"/>
       <c r="G232" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I232" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="3"/>
-      <c r="B233" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C233" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D233" s="3"/>
-      <c r="E233" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F233" s="3"/>
-      <c r="G233" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H233" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I233" s="3"/>
-    </row>
-    <row r="234" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A234" s="5" t="s">
+      <c r="I232" s="3"/>
+    </row>
+    <row r="233" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A233" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B234" s="5"/>
-      <c r="C234" s="5"/>
-      <c r="D234" s="5"/>
-      <c r="E234" s="5"/>
-      <c r="F234" s="5"/>
-      <c r="G234" s="5"/>
-      <c r="H234" s="5"/>
-      <c r="I234" s="5"/>
+      <c r="B233" s="5"/>
+      <c r="C233" s="5"/>
+      <c r="D233" s="5"/>
+      <c r="E233" s="5"/>
+      <c r="F233" s="5"/>
+      <c r="G233" s="5"/>
+      <c r="H233" s="5"/>
+      <c r="I233" s="5"/>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B234" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D234" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E234" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G234" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="H234" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I234" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="9" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="B235" s="7" t="s">
         <v>109</v>
@@ -13644,21 +13649,21 @@
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="H235" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I235" s="7" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="9" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C236" s="7" t="s">
         <v>110</v>
@@ -13673,18 +13678,16 @@
         <v>26</v>
       </c>
       <c r="G236" s="10" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H236" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I236" s="7" t="s">
-        <v>189</v>
-      </c>
+      <c r="I236" s="7"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B237" s="7" t="s">
         <v>24</v>
@@ -13702,7 +13705,7 @@
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H237" s="7" t="n">
         <v>2</v>
@@ -13711,7 +13714,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B238" s="7" t="s">
         <v>24</v>
@@ -13729,7 +13732,7 @@
         <v>26</v>
       </c>
       <c r="G238" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H238" s="7" t="n">
         <v>2</v>
@@ -13738,7 +13741,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B239" s="7" t="s">
         <v>24</v>
@@ -13756,7 +13759,7 @@
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H239" s="7" t="n">
         <v>2</v>
@@ -13765,10 +13768,10 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C240" s="7" t="s">
         <v>110</v>
@@ -13783,7 +13786,7 @@
         <v>26</v>
       </c>
       <c r="G240" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H240" s="7" t="n">
         <v>2</v>
@@ -13792,7 +13795,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B241" s="7" t="s">
         <v>109</v>
@@ -13810,7 +13813,7 @@
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H241" s="7" t="n">
         <v>2</v>
@@ -13819,10 +13822,10 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C242" s="7" t="s">
         <v>110</v>
@@ -13837,7 +13840,7 @@
         <v>26</v>
       </c>
       <c r="G242" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H242" s="7" t="n">
         <v>2</v>
@@ -13846,7 +13849,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B243" s="7" t="s">
         <v>24</v>
@@ -13864,7 +13867,7 @@
         <v>26</v>
       </c>
       <c r="G243" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H243" s="7" t="n">
         <v>2</v>
@@ -13873,7 +13876,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>24</v>
@@ -13891,7 +13894,7 @@
         <v>26</v>
       </c>
       <c r="G244" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H244" s="7" t="n">
         <v>2</v>
@@ -13900,7 +13903,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B245" s="7" t="s">
         <v>24</v>
@@ -13918,7 +13921,7 @@
         <v>26</v>
       </c>
       <c r="G245" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H245" s="7" t="n">
         <v>2</v>
@@ -13927,10 +13930,10 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>110</v>
@@ -13945,7 +13948,7 @@
         <v>26</v>
       </c>
       <c r="G246" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H246" s="7" t="n">
         <v>2</v>
@@ -13954,7 +13957,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B247" s="7" t="s">
         <v>109</v>
@@ -13972,7 +13975,7 @@
         <v>26</v>
       </c>
       <c r="G247" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H247" s="7" t="n">
         <v>2</v>
@@ -13981,10 +13984,10 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="C248" s="7" t="s">
         <v>110</v>
@@ -13999,7 +14002,7 @@
         <v>26</v>
       </c>
       <c r="G248" s="10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H248" s="7" t="n">
         <v>2</v>
@@ -14008,7 +14011,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B249" s="7" t="s">
         <v>222</v>
@@ -14026,7 +14029,7 @@
         <v>26</v>
       </c>
       <c r="G249" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H249" s="7" t="n">
         <v>2</v>
@@ -14035,10 +14038,10 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="C250" s="7" t="s">
         <v>110</v>
@@ -14053,7 +14056,7 @@
         <v>26</v>
       </c>
       <c r="G250" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H250" s="7" t="n">
         <v>2</v>
@@ -14062,7 +14065,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B251" s="7" t="s">
         <v>195</v>
@@ -14080,7 +14083,7 @@
         <v>26</v>
       </c>
       <c r="G251" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H251" s="7" t="n">
         <v>2</v>
@@ -14089,10 +14092,10 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="C252" s="7" t="s">
         <v>110</v>
@@ -14107,7 +14110,7 @@
         <v>26</v>
       </c>
       <c r="G252" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H252" s="7" t="n">
         <v>2</v>
@@ -14116,7 +14119,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B253" s="7" t="s">
         <v>109</v>
@@ -14134,7 +14137,7 @@
         <v>26</v>
       </c>
       <c r="G253" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H253" s="7" t="n">
         <v>2</v>
@@ -14142,11 +14145,11 @@
       <c r="I253" s="7"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="9" t="s">
-        <v>232</v>
+      <c r="A254" s="7" t="s">
+        <v>234</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="C254" s="7" t="s">
         <v>110</v>
@@ -14161,16 +14164,18 @@
         <v>26</v>
       </c>
       <c r="G254" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H254" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I254" s="7"/>
+      <c r="I254" s="7" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>75</v>
@@ -14188,7 +14193,7 @@
         <v>26</v>
       </c>
       <c r="G255" s="10" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H255" s="7" t="n">
         <v>2</v>
@@ -14197,38 +14202,38 @@
         <v>236</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B256" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C256" s="7" t="s">
+    <row r="256" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B256" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C256" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D256" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E256" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F256" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G256" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H256" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I256" s="7" t="s">
-        <v>236</v>
+      <c r="D256" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E256" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G256" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="H256" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I256" s="14" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B257" s="12" t="s">
         <v>75</v>
@@ -14246,18 +14251,18 @@
         <v>26</v>
       </c>
       <c r="G257" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H257" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I257" s="14" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="258" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="12" t="s">
-        <v>241</v>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="11" t="s">
+        <v>322</v>
       </c>
       <c r="B258" s="12" t="s">
         <v>75</v>
@@ -14274,19 +14279,19 @@
       <c r="F258" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G258" s="12" t="s">
-        <v>242</v>
+      <c r="G258" s="13" t="s">
+        <v>323</v>
       </c>
       <c r="H258" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I258" s="14" t="s">
-        <v>361</v>
+      <c r="I258" s="12" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B259" s="12" t="s">
         <v>75</v>
@@ -14304,18 +14309,18 @@
         <v>26</v>
       </c>
       <c r="G259" s="13" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H259" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I259" s="12" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="11" t="s">
-        <v>325</v>
+        <v>365</v>
       </c>
       <c r="B260" s="12" t="s">
         <v>75</v>
@@ -14333,44 +14338,16 @@
         <v>26</v>
       </c>
       <c r="G260" s="13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H260" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I260" s="12" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="B261" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C261" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D261" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E261" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F261" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G261" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="H261" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I261" s="12" t="s">
-        <v>365</v>
-      </c>
-    </row>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="A6:A7"/>
@@ -14383,21 +14360,21 @@
     <mergeCell ref="F115:F116"/>
     <mergeCell ref="I115:I116"/>
     <mergeCell ref="A117:I117"/>
-    <mergeCell ref="A187:A188"/>
-    <mergeCell ref="D187:D188"/>
-    <mergeCell ref="F187:F188"/>
-    <mergeCell ref="I187:I188"/>
-    <mergeCell ref="A189:I189"/>
-    <mergeCell ref="A213:A214"/>
-    <mergeCell ref="D213:D214"/>
-    <mergeCell ref="F213:F214"/>
-    <mergeCell ref="I213:I214"/>
-    <mergeCell ref="A215:I215"/>
-    <mergeCell ref="A232:A233"/>
-    <mergeCell ref="D232:D233"/>
-    <mergeCell ref="F232:F233"/>
-    <mergeCell ref="I232:I233"/>
-    <mergeCell ref="A234:I234"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A188:I188"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="F212:F213"/>
+    <mergeCell ref="I212:I213"/>
+    <mergeCell ref="A214:I214"/>
+    <mergeCell ref="A231:A232"/>
+    <mergeCell ref="D231:D232"/>
+    <mergeCell ref="F231:F232"/>
+    <mergeCell ref="I231:I232"/>
+    <mergeCell ref="A233:I233"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -1022,58 +1022,16 @@
     <t xml:space="preserve">50013</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Internal Only. Not visible to customer. 
+    <t xml:space="preserve">Internal Only. Not visible to customer. 
 Indicates the state machine of calibration
-0: Calibration Not Initiated. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 20A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. Set Fan 1 Current and Fan 2 current to 0.1A each. And then s</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">et Advance Calibration Flag.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-16,17,18,19: High Point Calibration In Progress
-20: High Point Calibration Done. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 4A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
-21,22,23: Mid Point Calibration In Progress
-24: Mid Point Calibration Done. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 0.4A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
-25,26,27: Low Point Calibration In Progress
+0: Calibration Not Initiated. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 20A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. Set Fan 1 Current and Fan 2 current to 0.1A each. And then set Advance Calibration Flag.
+17,18,19,20: High Point Calibration In Progress
+21: High Point Calibration Done. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 4A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
+22,23,24: Mid Point Calibration In Progress
+25: Mid Point Calibration Done. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 0.4A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
+26,27,28: Low Point Calibration In Progress
 127: Calibration Completed Successfully
 126: Error occured during calibration. Please restart controller</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Load On Grid Contactor &amp; Solar Neutral Earth Contactor Coil</t>
@@ -1181,55 +1139,15 @@
 If set to non-zero, indicates product was tested functionally during production. Only writtable when test mode enabled.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Internal Only. Not visible to customer. 
-If set to non-zero, indicates product was calibrated during production. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">Only writtable when test mode enabled.</t>
-    </r>
+    <t xml:space="preserve">Internal Only. Not visible to customer. 
+If set to non-zero, indicates product was calibrated during production. Only writtable when test mode enabled.</t>
   </si>
   <si>
     <t xml:space="preserve">Advance Calibration State</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Internal Only. Not visible to customer. 
-If set to non-zero, it advances the calibration state machine when it is waiting for external input. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">Only writtable when test mode enabled.</t>
-    </r>
+    <t xml:space="preserve">Internal Only. Not visible to customer. 
+If set to non-zero, it advances the calibration state machine when it is waiting for external input. Only writtable when test mode enabled.</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1157,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1291,13 +1209,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1419,7 +1330,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1474,10 +1385,6 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -13073,7 +12980,7 @@
       <c r="H214" s="5"/>
       <c r="I214" s="5"/>
     </row>
-    <row r="215" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="12" t="s">
         <v>343</v>
       </c>
@@ -13102,7 +13009,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="12" t="s">
         <v>344</v>
       </c>
@@ -13131,7 +13038,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="12" t="s">
         <v>345</v>
       </c>
@@ -13160,7 +13067,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="12" t="s">
         <v>346</v>
       </c>
@@ -13189,7 +13096,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="12" t="s">
         <v>347</v>
       </c>
@@ -13218,7 +13125,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="12" t="s">
         <v>348</v>
       </c>
@@ -13276,7 +13183,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="12" t="s">
         <v>360</v>
       </c>
@@ -13305,7 +13212,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="12" t="s">
         <v>350</v>
       </c>
@@ -13334,7 +13241,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="12" t="s">
         <v>351</v>
       </c>
@@ -13363,7 +13270,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="12" t="s">
         <v>352</v>
       </c>
@@ -13392,7 +13299,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="12" t="s">
         <v>353</v>
       </c>
@@ -13421,7 +13328,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="12" t="s">
         <v>354</v>
       </c>
@@ -13450,7 +13357,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="12" t="s">
         <v>355</v>
       </c>
@@ -13479,7 +13386,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="12" t="s">
         <v>356</v>
       </c>
@@ -13508,7 +13415,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="12" t="s">
         <v>357</v>
       </c>
@@ -14202,7 +14109,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="12" t="s">
         <v>239</v>
       </c>
@@ -14227,11 +14134,11 @@
       <c r="H256" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I256" s="14" t="s">
+      <c r="I256" s="12" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="12" t="s">
         <v>241</v>
       </c>
@@ -14256,7 +14163,7 @@
       <c r="H257" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I257" s="14" t="s">
+      <c r="I257" s="12" t="s">
         <v>362</v>
       </c>
     </row>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -1136,11 +1136,11 @@
   </si>
   <si>
     <t xml:space="preserve">Internal Only. Not visible to customer. 
-If set to non-zero, indicates product was tested functionally during production. Only writtable when test mode enabled.</t>
+If set to non-zero, indicates product was tested functionally during production. Only writtable when test mode enabled. Suggested to write the Unix Timestamp for the time when the product was functionally tested.</t>
   </si>
   <si>
     <t xml:space="preserve">Internal Only. Not visible to customer. 
-If set to non-zero, indicates product was calibrated during production. Only writtable when test mode enabled.</t>
+If set to non-zero, indicates product was calibrated during production. Only writtable when test mode enabled. Suggested to write Unix Epoch Timestamp of the time when calibration took place</t>
   </si>
   <si>
     <t xml:space="preserve">Advance Calibration State</t>
@@ -14167,7 +14167,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="11" t="s">
         <v>322</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="11" t="s">
         <v>325</v>
       </c>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="375">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -978,6 +978,15 @@
   </si>
   <si>
     <t xml:space="preserve">6001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG Detection Disable Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: OFF (DG Detection Enabled), 1: ON (DG Detection Disabled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: OFF (Fans Enabled), 1: ON (Fans Disabled)</t>
   </si>
   <si>
     <t xml:space="preserve">Switch Pressed</t>
@@ -1034,7 +1043,22 @@
 126: Error occured during calibration. Please restart controller</t>
   </si>
   <si>
-    <t xml:space="preserve">Load On Grid Contactor &amp; Solar Neutral Earth Contactor Coil</t>
+    <t xml:space="preserve">Grid R Phase Contactor Coil Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Y Phase Contactor Coil Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B Phase Contactor Coil Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Solar Contactor Coil Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Grid Contactor &amp; Solar Neutral Earth Contactor Coil Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fans Output</t>
   </si>
   <si>
     <t xml:space="preserve">READ COIL STATUS (Function Code: 0x01)</t>
@@ -10035,7 +10059,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>234</v>
+        <v>319</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>75</v>
@@ -10059,7 +10083,7 @@
         <v>2</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>236</v>
+        <v>320</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10088,12 +10112,12 @@
         <v>2</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>236</v>
+        <v>321</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="86.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="11" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>75</v>
@@ -10111,13 +10135,13 @@
         <v>26</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H108" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10203,7 +10227,7 @@
     </row>
     <row r="112" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B112" s="12" t="s">
         <v>75</v>
@@ -10221,18 +10245,18 @@
         <v>26</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H112" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="11" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B113" s="12" t="s">
         <v>75</v>
@@ -10250,18 +10274,18 @@
         <v>26</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H113" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="236.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="11" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B114" s="12" t="s">
         <v>75</v>
@@ -10279,13 +10303,13 @@
         <v>26</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H114" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I114" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10947,7 +10971,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>75</v>
@@ -10974,7 +10998,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>75</v>
@@ -11001,7 +11025,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>75</v>
@@ -11028,7 +11052,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>273</v>
+        <v>337</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>75</v>
@@ -11055,7 +11079,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
@@ -11082,7 +11106,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>276</v>
+        <v>339</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
@@ -12239,7 +12263,7 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="5" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -12252,7 +12276,7 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="12" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>75</v>
@@ -12267,7 +12291,7 @@
         <v>75</v>
       </c>
       <c r="F189" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G189" s="12" t="n">
         <v>20001</v>
@@ -12276,12 +12300,12 @@
         <v>1</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="12" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>75</v>
@@ -12296,7 +12320,7 @@
         <v>75</v>
       </c>
       <c r="F190" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G190" s="12" t="n">
         <v>20002</v>
@@ -12305,12 +12329,12 @@
         <v>1</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="12" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>75</v>
@@ -12325,7 +12349,7 @@
         <v>75</v>
       </c>
       <c r="F191" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G191" s="12" t="n">
         <v>20003</v>
@@ -12334,12 +12358,12 @@
         <v>1</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="12" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>75</v>
@@ -12354,7 +12378,7 @@
         <v>75</v>
       </c>
       <c r="F192" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G192" s="12" t="n">
         <v>20004</v>
@@ -12363,12 +12387,12 @@
         <v>1</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="12" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B193" s="12" t="s">
         <v>75</v>
@@ -12383,7 +12407,7 @@
         <v>75</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G193" s="12" t="n">
         <v>20005</v>
@@ -12392,12 +12416,12 @@
         <v>1</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="12" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>75</v>
@@ -12412,7 +12436,7 @@
         <v>75</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G194" s="12" t="n">
         <v>20006</v>
@@ -12421,12 +12445,12 @@
         <v>1</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="12" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>75</v>
@@ -12441,7 +12465,7 @@
         <v>75</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G195" s="12" t="n">
         <v>20007</v>
@@ -12450,27 +12474,27 @@
         <v>1</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D196" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E196" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F196" s="12" t="s">
         <v>342</v>
-      </c>
-      <c r="B196" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C196" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D196" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E196" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F196" s="12" t="s">
-        <v>334</v>
       </c>
       <c r="G196" s="12" t="n">
         <v>20008</v>
@@ -12479,12 +12503,12 @@
         <v>1</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="12" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>75</v>
@@ -12499,7 +12523,7 @@
         <v>75</v>
       </c>
       <c r="F197" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G197" s="12" t="n">
         <v>30001</v>
@@ -12508,12 +12532,12 @@
         <v>1</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="12" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>75</v>
@@ -12528,7 +12552,7 @@
         <v>75</v>
       </c>
       <c r="F198" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G198" s="12" t="n">
         <v>30002</v>
@@ -12537,12 +12561,12 @@
         <v>1</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="12" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B199" s="12" t="s">
         <v>75</v>
@@ -12557,7 +12581,7 @@
         <v>75</v>
       </c>
       <c r="F199" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G199" s="12" t="n">
         <v>30003</v>
@@ -12566,12 +12590,12 @@
         <v>1</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="12" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>75</v>
@@ -12586,7 +12610,7 @@
         <v>75</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G200" s="12" t="n">
         <v>30004</v>
@@ -12595,12 +12619,12 @@
         <v>1</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>75</v>
@@ -12615,7 +12639,7 @@
         <v>75</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G201" s="12" t="n">
         <v>30005</v>
@@ -12624,12 +12648,12 @@
         <v>1</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="12" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>75</v>
@@ -12644,7 +12668,7 @@
         <v>75</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G202" s="12" t="n">
         <v>30006</v>
@@ -12653,12 +12677,12 @@
         <v>1</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="12" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>75</v>
@@ -12673,7 +12697,7 @@
         <v>75</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G203" s="12" t="n">
         <v>40001</v>
@@ -12682,12 +12706,12 @@
         <v>1</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="12" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>75</v>
@@ -12702,7 +12726,7 @@
         <v>75</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G204" s="12" t="n">
         <v>60001</v>
@@ -12711,12 +12735,12 @@
         <v>1</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="12" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>75</v>
@@ -12731,7 +12755,7 @@
         <v>75</v>
       </c>
       <c r="F205" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G205" s="12" t="n">
         <v>60002</v>
@@ -12740,12 +12764,12 @@
         <v>1</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="12" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B206" s="12" t="s">
         <v>75</v>
@@ -12760,7 +12784,7 @@
         <v>75</v>
       </c>
       <c r="F206" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G206" s="12" t="n">
         <v>60003</v>
@@ -12769,12 +12793,12 @@
         <v>1</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="12" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>75</v>
@@ -12789,7 +12813,7 @@
         <v>75</v>
       </c>
       <c r="F207" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G207" s="12" t="n">
         <v>60004</v>
@@ -12798,12 +12822,12 @@
         <v>1</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>75</v>
@@ -12818,7 +12842,7 @@
         <v>75</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G208" s="12" t="n">
         <v>60005</v>
@@ -12827,12 +12851,12 @@
         <v>1</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>75</v>
@@ -12847,7 +12871,7 @@
         <v>75</v>
       </c>
       <c r="F209" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G209" s="12" t="n">
         <v>60006</v>
@@ -12856,12 +12880,12 @@
         <v>1</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="12" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>75</v>
@@ -12876,7 +12900,7 @@
         <v>75</v>
       </c>
       <c r="F210" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G210" s="12" t="n">
         <v>60007</v>
@@ -12885,12 +12909,12 @@
         <v>1</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="12" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>75</v>
@@ -12905,7 +12929,7 @@
         <v>75</v>
       </c>
       <c r="F211" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G211" s="12" t="n">
         <v>60008</v>
@@ -12914,7 +12938,7 @@
         <v>1</v>
       </c>
       <c r="I211" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12969,7 +12993,7 @@
     </row>
     <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="5" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -12982,7 +13006,7 @@
     </row>
     <row r="215" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="12" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B215" s="12" t="s">
         <v>75</v>
@@ -12997,7 +13021,7 @@
         <v>75</v>
       </c>
       <c r="F215" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G215" s="12" t="n">
         <v>30001</v>
@@ -13006,12 +13030,12 @@
         <v>1</v>
       </c>
       <c r="I215" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="12" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B216" s="12" t="s">
         <v>75</v>
@@ -13026,7 +13050,7 @@
         <v>75</v>
       </c>
       <c r="F216" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G216" s="12" t="n">
         <v>30002</v>
@@ -13035,12 +13059,12 @@
         <v>1</v>
       </c>
       <c r="I216" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="12" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B217" s="12" t="s">
         <v>75</v>
@@ -13055,7 +13079,7 @@
         <v>75</v>
       </c>
       <c r="F217" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G217" s="12" t="n">
         <v>30003</v>
@@ -13064,12 +13088,12 @@
         <v>1</v>
       </c>
       <c r="I217" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="12" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B218" s="12" t="s">
         <v>75</v>
@@ -13084,7 +13108,7 @@
         <v>75</v>
       </c>
       <c r="F218" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G218" s="12" t="n">
         <v>30004</v>
@@ -13093,12 +13117,12 @@
         <v>1</v>
       </c>
       <c r="I218" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="12" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B219" s="12" t="s">
         <v>75</v>
@@ -13113,7 +13137,7 @@
         <v>75</v>
       </c>
       <c r="F219" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G219" s="12" t="n">
         <v>30005</v>
@@ -13122,12 +13146,12 @@
         <v>1</v>
       </c>
       <c r="I219" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="12" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B220" s="12" t="s">
         <v>75</v>
@@ -13142,7 +13166,7 @@
         <v>75</v>
       </c>
       <c r="F220" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G220" s="12" t="n">
         <v>30006</v>
@@ -13151,12 +13175,12 @@
         <v>1</v>
       </c>
       <c r="I220" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="12" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B221" s="12" t="s">
         <v>75</v>
@@ -13171,7 +13195,7 @@
         <v>75</v>
       </c>
       <c r="F221" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G221" s="12" t="n">
         <v>40001</v>
@@ -13180,12 +13204,12 @@
         <v>1</v>
       </c>
       <c r="I221" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="12" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B222" s="12" t="s">
         <v>75</v>
@@ -13200,7 +13224,7 @@
         <v>75</v>
       </c>
       <c r="F222" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G222" s="12" t="n">
         <v>45001</v>
@@ -13209,12 +13233,12 @@
         <v>1</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="12" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B223" s="12" t="s">
         <v>75</v>
@@ -13229,7 +13253,7 @@
         <v>75</v>
       </c>
       <c r="F223" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G223" s="12" t="n">
         <v>60001</v>
@@ -13238,12 +13262,12 @@
         <v>1</v>
       </c>
       <c r="I223" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="12" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B224" s="12" t="s">
         <v>75</v>
@@ -13258,7 +13282,7 @@
         <v>75</v>
       </c>
       <c r="F224" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G224" s="12" t="n">
         <v>60002</v>
@@ -13267,12 +13291,12 @@
         <v>1</v>
       </c>
       <c r="I224" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="12" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B225" s="12" t="s">
         <v>75</v>
@@ -13287,7 +13311,7 @@
         <v>75</v>
       </c>
       <c r="F225" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G225" s="12" t="n">
         <v>60003</v>
@@ -13296,12 +13320,12 @@
         <v>1</v>
       </c>
       <c r="I225" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="12" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B226" s="12" t="s">
         <v>75</v>
@@ -13316,7 +13340,7 @@
         <v>75</v>
       </c>
       <c r="F226" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G226" s="12" t="n">
         <v>60004</v>
@@ -13325,12 +13349,12 @@
         <v>1</v>
       </c>
       <c r="I226" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="12" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B227" s="12" t="s">
         <v>75</v>
@@ -13345,7 +13369,7 @@
         <v>75</v>
       </c>
       <c r="F227" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G227" s="12" t="n">
         <v>60005</v>
@@ -13354,12 +13378,12 @@
         <v>1</v>
       </c>
       <c r="I227" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="12" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B228" s="12" t="s">
         <v>75</v>
@@ -13374,7 +13398,7 @@
         <v>75</v>
       </c>
       <c r="F228" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G228" s="12" t="n">
         <v>60006</v>
@@ -13383,12 +13407,12 @@
         <v>1</v>
       </c>
       <c r="I228" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="12" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B229" s="12" t="s">
         <v>75</v>
@@ -13403,7 +13427,7 @@
         <v>75</v>
       </c>
       <c r="F229" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G229" s="12" t="n">
         <v>60007</v>
@@ -13412,12 +13436,12 @@
         <v>1</v>
       </c>
       <c r="I229" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="12" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B230" s="12" t="s">
         <v>75</v>
@@ -13432,7 +13456,7 @@
         <v>75</v>
       </c>
       <c r="F230" s="12" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G230" s="12" t="n">
         <v>60008</v>
@@ -13441,7 +13465,7 @@
         <v>1</v>
       </c>
       <c r="I230" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14077,7 +14101,7 @@
         <v>2</v>
       </c>
       <c r="I254" s="7" t="s">
-        <v>236</v>
+        <v>320</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14106,7 +14130,7 @@
         <v>2</v>
       </c>
       <c r="I255" s="7" t="s">
-        <v>236</v>
+        <v>321</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14135,7 +14159,7 @@
         <v>2</v>
       </c>
       <c r="I256" s="12" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14164,12 +14188,12 @@
         <v>2</v>
       </c>
       <c r="I257" s="12" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B258" s="12" t="s">
         <v>75</v>
@@ -14187,18 +14211,18 @@
         <v>26</v>
       </c>
       <c r="G258" s="13" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H258" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I258" s="12" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="11" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B259" s="12" t="s">
         <v>75</v>
@@ -14216,18 +14240,18 @@
         <v>26</v>
       </c>
       <c r="G259" s="13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H259" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I259" s="12" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="11" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B260" s="12" t="s">
         <v>75</v>
@@ -14245,13 +14269,13 @@
         <v>26</v>
       </c>
       <c r="G260" s="13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H260" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I260" s="12" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="384">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -1059,6 +1059,33 @@
   </si>
   <si>
     <t xml:space="preserve">Fans Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Grid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Grid  As User Disabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Grid As Grid R Phase Unhealthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Grid As Solar Contactors On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Solar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Solar As User Disabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Solar As Solar R Phase Unhealthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Solar As Grid Contactors On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Solar As DG Running</t>
   </si>
   <si>
     <t xml:space="preserve">READ COIL STATUS (Function Code: 0x01)</t>
@@ -7286,7 +7313,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1048576"/>
+  <dimension ref="A1:I265"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.94"/>
@@ -12105,7 +12132,7 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="B182" s="7" t="s">
         <v>75</v>
@@ -12132,7 +12159,7 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>75</v>
@@ -12159,7 +12186,7 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="B184" s="7" t="s">
         <v>75</v>
@@ -12186,7 +12213,7 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="B185" s="7" t="s">
         <v>75</v>
@@ -12211,217 +12238,207 @@
       </c>
       <c r="I185" s="7"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="3" t="s">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G186" s="7" t="n">
+        <v>805</v>
+      </c>
+      <c r="H186" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I186" s="7"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G187" s="7" t="n">
+        <v>806</v>
+      </c>
+      <c r="H187" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I187" s="7"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G188" s="7" t="n">
+        <v>807</v>
+      </c>
+      <c r="H188" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I188" s="7"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F189" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G189" s="7" t="n">
+        <v>808</v>
+      </c>
+      <c r="H189" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I189" s="7"/>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G190" s="7" t="n">
+        <v>809</v>
+      </c>
+      <c r="H190" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" s="7"/>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A191" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="B191" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C186" s="4" t="s">
+      <c r="C191" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D186" s="3" t="s">
+      <c r="D191" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E186" s="4" t="s">
+      <c r="E191" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F186" s="3" t="s">
+      <c r="F191" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G186" s="4" t="s">
+      <c r="G191" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H186" s="4" t="s">
+      <c r="H191" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I186" s="3" t="s">
+      <c r="I191" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="3"/>
-      <c r="B187" s="4" t="s">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="3"/>
+      <c r="B192" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C187" s="4" t="s">
+      <c r="C192" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D187" s="3"/>
-      <c r="E187" s="4" t="s">
+      <c r="D192" s="3"/>
+      <c r="E192" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F187" s="3"/>
-      <c r="G187" s="4" t="s">
+      <c r="F192" s="3"/>
+      <c r="G192" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H187" s="4" t="s">
+      <c r="H192" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I187" s="3"/>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="B188" s="5"/>
-      <c r="C188" s="5"/>
-      <c r="D188" s="5"/>
-      <c r="E188" s="5"/>
-      <c r="F188" s="5"/>
-      <c r="G188" s="5"/>
-      <c r="H188" s="5"/>
-      <c r="I188" s="5"/>
-    </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="B189" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C189" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D189" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E189" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F189" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G189" s="12" t="n">
-        <v>20001</v>
-      </c>
-      <c r="H189" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I189" s="12" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="B190" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C190" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E190" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F190" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G190" s="12" t="n">
-        <v>20002</v>
-      </c>
-      <c r="H190" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I190" s="12" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C191" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D191" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E191" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F191" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G191" s="12" t="n">
-        <v>20003</v>
-      </c>
-      <c r="H191" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I191" s="12" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B192" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C192" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D192" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E192" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F192" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G192" s="12" t="n">
-        <v>20004</v>
-      </c>
-      <c r="H192" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I192" s="12" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="B193" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C193" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D193" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E193" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F193" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G193" s="12" t="n">
-        <v>20005</v>
-      </c>
-      <c r="H193" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I193" s="12" t="s">
-        <v>343</v>
-      </c>
+      <c r="I192" s="3"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B193" s="5"/>
+      <c r="C193" s="5"/>
+      <c r="D193" s="5"/>
+      <c r="E193" s="5"/>
+      <c r="F193" s="5"/>
+      <c r="G193" s="5"/>
+      <c r="H193" s="5"/>
+      <c r="I193" s="5"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>75</v>
@@ -12436,21 +12453,21 @@
         <v>75</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>20006</v>
+        <v>20001</v>
       </c>
       <c r="H194" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="12" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>75</v>
@@ -12465,21 +12482,21 @@
         <v>75</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>20007</v>
+        <v>20002</v>
       </c>
       <c r="H195" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="12" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>75</v>
@@ -12494,79 +12511,79 @@
         <v>75</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>20008</v>
+        <v>20003</v>
       </c>
       <c r="H196" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D197" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E197" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F197" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="B197" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C197" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D197" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E197" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F197" s="12" t="s">
-        <v>342</v>
-      </c>
       <c r="G197" s="12" t="n">
-        <v>30001</v>
+        <v>20004</v>
       </c>
       <c r="H197" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B198" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D198" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E198" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F198" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G198" s="12" t="n">
+        <v>20005</v>
+      </c>
+      <c r="H198" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I198" s="12" t="s">
         <v>352</v>
-      </c>
-      <c r="B198" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C198" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D198" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E198" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F198" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G198" s="12" t="n">
-        <v>30002</v>
-      </c>
-      <c r="H198" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I198" s="12" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="12" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B199" s="12" t="s">
         <v>75</v>
@@ -12581,21 +12598,21 @@
         <v>75</v>
       </c>
       <c r="F199" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>30003</v>
+        <v>20006</v>
       </c>
       <c r="H199" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="12" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>75</v>
@@ -12610,21 +12627,21 @@
         <v>75</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>30004</v>
+        <v>20007</v>
       </c>
       <c r="H200" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>75</v>
@@ -12639,21 +12656,21 @@
         <v>75</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>30005</v>
+        <v>20008</v>
       </c>
       <c r="H201" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="12" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>75</v>
@@ -12668,21 +12685,21 @@
         <v>75</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>30006</v>
+        <v>30001</v>
       </c>
       <c r="H202" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="12" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>75</v>
@@ -12697,21 +12714,21 @@
         <v>75</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>40001</v>
+        <v>30002</v>
       </c>
       <c r="H203" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="12" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>75</v>
@@ -12726,21 +12743,21 @@
         <v>75</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>60001</v>
+        <v>30003</v>
       </c>
       <c r="H204" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>75</v>
@@ -12755,21 +12772,21 @@
         <v>75</v>
       </c>
       <c r="F205" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>60002</v>
+        <v>30004</v>
       </c>
       <c r="H205" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="12" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B206" s="12" t="s">
         <v>75</v>
@@ -12784,21 +12801,21 @@
         <v>75</v>
       </c>
       <c r="F206" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G206" s="12" t="n">
-        <v>60003</v>
+        <v>30005</v>
       </c>
       <c r="H206" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="12" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>75</v>
@@ -12813,21 +12830,21 @@
         <v>75</v>
       </c>
       <c r="F207" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G207" s="12" t="n">
-        <v>60004</v>
+        <v>30006</v>
       </c>
       <c r="H207" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>75</v>
@@ -12842,21 +12859,21 @@
         <v>75</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>60005</v>
+        <v>40001</v>
       </c>
       <c r="H208" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>75</v>
@@ -12871,21 +12888,21 @@
         <v>75</v>
       </c>
       <c r="F209" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>60006</v>
+        <v>60001</v>
       </c>
       <c r="H209" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="12" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>75</v>
@@ -12900,21 +12917,21 @@
         <v>75</v>
       </c>
       <c r="F210" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G210" s="12" t="n">
-        <v>60007</v>
+        <v>60002</v>
       </c>
       <c r="H210" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="12" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>75</v>
@@ -12929,229 +12946,229 @@
         <v>75</v>
       </c>
       <c r="F211" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G211" s="12" t="n">
+        <v>60003</v>
+      </c>
+      <c r="H211" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B212" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E212" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F212" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G212" s="12" t="n">
+        <v>60004</v>
+      </c>
+      <c r="H212" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I212" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E213" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F213" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G213" s="12" t="n">
+        <v>60005</v>
+      </c>
+      <c r="H213" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E214" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F214" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G214" s="12" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H214" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B215" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E215" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F215" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G215" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H215" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B216" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E216" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F216" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G216" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H211" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I211" s="12" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="s">
+      <c r="H216" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A217" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B217" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C217" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D212" s="3" t="s">
+      <c r="D217" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E212" s="4" t="s">
+      <c r="E217" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F212" s="3" t="s">
+      <c r="F217" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G212" s="4" t="s">
+      <c r="G217" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H212" s="4" t="s">
+      <c r="H217" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I212" s="3" t="s">
+      <c r="I217" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="3"/>
-      <c r="B213" s="4" t="s">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="3"/>
+      <c r="B218" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C213" s="4" t="s">
+      <c r="C218" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D213" s="3"/>
-      <c r="E213" s="4" t="s">
+      <c r="D218" s="3"/>
+      <c r="E218" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F213" s="3"/>
-      <c r="G213" s="4" t="s">
+      <c r="F218" s="3"/>
+      <c r="G218" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H213" s="4" t="s">
+      <c r="H218" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I213" s="3"/>
-    </row>
-    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="B214" s="5"/>
-      <c r="C214" s="5"/>
-      <c r="D214" s="5"/>
-      <c r="E214" s="5"/>
-      <c r="F214" s="5"/>
-      <c r="G214" s="5"/>
-      <c r="H214" s="5"/>
-      <c r="I214" s="5"/>
-    </row>
-    <row r="215" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="B215" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C215" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D215" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E215" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F215" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G215" s="12" t="n">
-        <v>30001</v>
-      </c>
-      <c r="H215" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I215" s="12" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="B216" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C216" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D216" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E216" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F216" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G216" s="12" t="n">
-        <v>30002</v>
-      </c>
-      <c r="H216" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I216" s="12" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="B217" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C217" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D217" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E217" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F217" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G217" s="12" t="n">
-        <v>30003</v>
-      </c>
-      <c r="H217" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I217" s="12" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="B218" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C218" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D218" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E218" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F218" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G218" s="12" t="n">
-        <v>30004</v>
-      </c>
-      <c r="H218" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I218" s="12" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="B219" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C219" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D219" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E219" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F219" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="G219" s="12" t="n">
-        <v>30005</v>
-      </c>
-      <c r="H219" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I219" s="12" t="s">
-        <v>367</v>
-      </c>
+      <c r="I218" s="3"/>
+    </row>
+    <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A219" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B219" s="5"/>
+      <c r="C219" s="5"/>
+      <c r="D219" s="5"/>
+      <c r="E219" s="5"/>
+      <c r="F219" s="5"/>
+      <c r="G219" s="5"/>
+      <c r="H219" s="5"/>
+      <c r="I219" s="5"/>
     </row>
     <row r="220" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="12" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B220" s="12" t="s">
         <v>75</v>
@@ -13166,21 +13183,21 @@
         <v>75</v>
       </c>
       <c r="F220" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G220" s="12" t="n">
-        <v>30006</v>
+        <v>30001</v>
       </c>
       <c r="H220" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I220" s="12" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="12" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B221" s="12" t="s">
         <v>75</v>
@@ -13195,21 +13212,21 @@
         <v>75</v>
       </c>
       <c r="F221" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G221" s="12" t="n">
-        <v>40001</v>
+        <v>30002</v>
       </c>
       <c r="H221" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I221" s="12" t="s">
-        <v>343</v>
+        <v>376</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="12" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B222" s="12" t="s">
         <v>75</v>
@@ -13224,21 +13241,21 @@
         <v>75</v>
       </c>
       <c r="F222" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G222" s="12" t="n">
-        <v>45001</v>
+        <v>30003</v>
       </c>
       <c r="H222" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="12" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B223" s="12" t="s">
         <v>75</v>
@@ -13253,21 +13270,21 @@
         <v>75</v>
       </c>
       <c r="F223" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G223" s="12" t="n">
-        <v>60001</v>
+        <v>30004</v>
       </c>
       <c r="H223" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I223" s="12" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="12" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B224" s="12" t="s">
         <v>75</v>
@@ -13282,21 +13299,21 @@
         <v>75</v>
       </c>
       <c r="F224" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G224" s="12" t="n">
-        <v>60002</v>
+        <v>30005</v>
       </c>
       <c r="H224" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I224" s="12" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="12" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B225" s="12" t="s">
         <v>75</v>
@@ -13311,21 +13328,21 @@
         <v>75</v>
       </c>
       <c r="F225" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G225" s="12" t="n">
-        <v>60003</v>
+        <v>30006</v>
       </c>
       <c r="H225" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I225" s="12" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="226" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="12" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B226" s="12" t="s">
         <v>75</v>
@@ -13340,21 +13357,21 @@
         <v>75</v>
       </c>
       <c r="F226" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G226" s="12" t="n">
-        <v>60004</v>
+        <v>40001</v>
       </c>
       <c r="H226" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I226" s="12" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="12" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="B227" s="12" t="s">
         <v>75</v>
@@ -13369,21 +13386,21 @@
         <v>75</v>
       </c>
       <c r="F227" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G227" s="12" t="n">
-        <v>60005</v>
+        <v>45001</v>
       </c>
       <c r="H227" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I227" s="12" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="12" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B228" s="12" t="s">
         <v>75</v>
@@ -13398,21 +13415,21 @@
         <v>75</v>
       </c>
       <c r="F228" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G228" s="12" t="n">
-        <v>60006</v>
+        <v>60001</v>
       </c>
       <c r="H228" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I228" s="12" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="12" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B229" s="12" t="s">
         <v>75</v>
@@ -13427,21 +13444,21 @@
         <v>75</v>
       </c>
       <c r="F229" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G229" s="12" t="n">
-        <v>60007</v>
+        <v>60002</v>
       </c>
       <c r="H229" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I229" s="12" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="12" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B230" s="12" t="s">
         <v>75</v>
@@ -13456,226 +13473,232 @@
         <v>75</v>
       </c>
       <c r="F230" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G230" s="12" t="n">
+        <v>60003</v>
+      </c>
+      <c r="H230" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B231" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D231" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E231" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F231" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G231" s="12" t="n">
+        <v>60004</v>
+      </c>
+      <c r="H231" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B232" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D232" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E232" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F232" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G232" s="12" t="n">
+        <v>60005</v>
+      </c>
+      <c r="H232" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I232" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B233" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D233" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E233" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F233" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G233" s="12" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H233" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B234" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D234" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E234" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F234" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G234" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H234" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I234" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B235" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C235" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D235" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E235" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F235" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G235" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H230" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I230" s="12" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="3" t="s">
+      <c r="H235" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I235" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A236" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B231" s="4" t="s">
+      <c r="B236" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C231" s="4" t="s">
+      <c r="C236" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D231" s="3" t="s">
+      <c r="D236" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E231" s="4" t="s">
+      <c r="E236" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F231" s="3" t="s">
+      <c r="F236" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G231" s="4" t="s">
+      <c r="G236" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H231" s="4" t="s">
+      <c r="H236" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I231" s="3" t="s">
+      <c r="I236" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="3"/>
-      <c r="B232" s="4" t="s">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="3"/>
+      <c r="B237" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C232" s="4" t="s">
+      <c r="C237" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D232" s="3"/>
-      <c r="E232" s="4" t="s">
+      <c r="D237" s="3"/>
+      <c r="E237" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F232" s="3"/>
-      <c r="G232" s="4" t="s">
+      <c r="F237" s="3"/>
+      <c r="G237" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H232" s="4" t="s">
+      <c r="H237" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I232" s="3"/>
-    </row>
-    <row r="233" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="5" t="s">
+      <c r="I237" s="3"/>
+    </row>
+    <row r="238" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A238" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B233" s="5"/>
-      <c r="C233" s="5"/>
-      <c r="D233" s="5"/>
-      <c r="E233" s="5"/>
-      <c r="F233" s="5"/>
-      <c r="G233" s="5"/>
-      <c r="H233" s="5"/>
-      <c r="I233" s="5"/>
-    </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B234" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C234" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D234" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E234" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F234" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G234" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="H234" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I234" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="B235" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C235" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D235" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E235" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F235" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G235" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H235" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I235" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B236" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C236" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D236" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E236" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F236" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G236" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="H236" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I236" s="7"/>
-    </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B237" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C237" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D237" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E237" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F237" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G237" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H237" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I237" s="7"/>
-    </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B238" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C238" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D238" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E238" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F238" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G238" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="H238" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I238" s="7"/>
+      <c r="B238" s="5"/>
+      <c r="C238" s="5"/>
+      <c r="D238" s="5"/>
+      <c r="E238" s="5"/>
+      <c r="F238" s="5"/>
+      <c r="G238" s="5"/>
+      <c r="H238" s="5"/>
+      <c r="I238" s="5"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="9" t="s">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="B239" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C239" s="7" t="s">
         <v>110</v>
@@ -13690,16 +13713,18 @@
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>204</v>
+        <v>318</v>
       </c>
       <c r="H239" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I239" s="7"/>
+      <c r="I239" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="9" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="B240" s="7" t="s">
         <v>109</v>
@@ -13717,19 +13742,21 @@
         <v>26</v>
       </c>
       <c r="G240" s="10" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="H240" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I240" s="7"/>
+      <c r="I240" s="7" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="9" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C241" s="7" t="s">
         <v>110</v>
@@ -13744,7 +13771,7 @@
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="H241" s="7" t="n">
         <v>2</v>
@@ -13753,7 +13780,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="9" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B242" s="7" t="s">
         <v>24</v>
@@ -13771,7 +13798,7 @@
         <v>26</v>
       </c>
       <c r="G242" s="10" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H242" s="7" t="n">
         <v>2</v>
@@ -13780,7 +13807,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B243" s="7" t="s">
         <v>24</v>
@@ -13798,7 +13825,7 @@
         <v>26</v>
       </c>
       <c r="G243" s="10" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="H243" s="7" t="n">
         <v>2</v>
@@ -13807,7 +13834,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="9" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>24</v>
@@ -13825,7 +13852,7 @@
         <v>26</v>
       </c>
       <c r="G244" s="10" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="H244" s="7" t="n">
         <v>2</v>
@@ -13834,10 +13861,10 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="9" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C245" s="7" t="s">
         <v>110</v>
@@ -13852,7 +13879,7 @@
         <v>26</v>
       </c>
       <c r="G245" s="10" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="H245" s="7" t="n">
         <v>2</v>
@@ -13861,7 +13888,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="9" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B246" s="7" t="s">
         <v>109</v>
@@ -13879,7 +13906,7 @@
         <v>26</v>
       </c>
       <c r="G246" s="10" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="H246" s="7" t="n">
         <v>2</v>
@@ -13888,10 +13915,10 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B247" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C247" s="7" t="s">
         <v>110</v>
@@ -13906,7 +13933,7 @@
         <v>26</v>
       </c>
       <c r="G247" s="10" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="H247" s="7" t="n">
         <v>2</v>
@@ -13915,10 +13942,10 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>222</v>
+        <v>24</v>
       </c>
       <c r="C248" s="7" t="s">
         <v>110</v>
@@ -13933,7 +13960,7 @@
         <v>26</v>
       </c>
       <c r="G248" s="10" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="H248" s="7" t="n">
         <v>2</v>
@@ -13942,10 +13969,10 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B249" s="7" t="s">
-        <v>222</v>
+        <v>24</v>
       </c>
       <c r="C249" s="7" t="s">
         <v>110</v>
@@ -13960,7 +13987,7 @@
         <v>26</v>
       </c>
       <c r="G249" s="10" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="H249" s="7" t="n">
         <v>2</v>
@@ -13969,10 +13996,10 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="C250" s="7" t="s">
         <v>110</v>
@@ -13987,7 +14014,7 @@
         <v>26</v>
       </c>
       <c r="G250" s="10" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="H250" s="7" t="n">
         <v>2</v>
@@ -13996,10 +14023,10 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="B251" s="7" t="s">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="C251" s="7" t="s">
         <v>110</v>
@@ -14014,7 +14041,7 @@
         <v>26</v>
       </c>
       <c r="G251" s="10" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="H251" s="7" t="n">
         <v>2</v>
@@ -14023,7 +14050,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B252" s="7" t="s">
         <v>109</v>
@@ -14041,7 +14068,7 @@
         <v>26</v>
       </c>
       <c r="G252" s="10" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="H252" s="7" t="n">
         <v>2</v>
@@ -14050,10 +14077,10 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="C253" s="7" t="s">
         <v>110</v>
@@ -14068,7 +14095,7 @@
         <v>26</v>
       </c>
       <c r="G253" s="10" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="H253" s="7" t="n">
         <v>2</v>
@@ -14076,11 +14103,11 @@
       <c r="I253" s="7"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="7" t="s">
-        <v>234</v>
+      <c r="A254" s="9" t="s">
+        <v>224</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="C254" s="7" t="s">
         <v>110</v>
@@ -14095,21 +14122,19 @@
         <v>26</v>
       </c>
       <c r="G254" s="10" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="H254" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I254" s="7" t="s">
-        <v>320</v>
-      </c>
+      <c r="I254" s="7"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="7" t="s">
-        <v>237</v>
+      <c r="A255" s="9" t="s">
+        <v>226</v>
       </c>
       <c r="B255" s="7" t="s">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="C255" s="7" t="s">
         <v>110</v>
@@ -14124,161 +14149,297 @@
         <v>26</v>
       </c>
       <c r="G255" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="H255" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" s="7"/>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B256" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C256" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D256" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E256" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G256" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H256" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I256" s="7"/>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B257" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C257" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D257" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E257" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F257" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G257" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H257" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I257" s="7"/>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B258" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C258" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D258" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E258" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F258" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G258" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="H258" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I258" s="7"/>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B259" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C259" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D259" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E259" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F259" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G259" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H259" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I259" s="7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B260" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C260" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D260" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E260" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G260" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="H255" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I255" s="7" t="s">
+      <c r="H260" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I260" s="7" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="12" t="s">
+    <row r="261" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B256" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C256" s="12" t="s">
+      <c r="B261" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C261" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D256" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E256" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F256" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G256" s="12" t="s">
+      <c r="D261" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E261" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F261" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G261" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="H256" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I256" s="12" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="12" t="s">
+      <c r="H261" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I261" s="12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B257" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C257" s="12" t="s">
+      <c r="B262" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C262" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D257" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E257" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F257" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G257" s="12" t="s">
+      <c r="D262" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E262" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F262" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G262" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="H257" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I257" s="12" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="258" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="11" t="s">
+      <c r="H262" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I262" s="12" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="B258" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C258" s="12" t="s">
+      <c r="B263" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C263" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D258" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E258" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F258" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G258" s="13" t="s">
+      <c r="D263" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E263" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F263" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G263" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="H258" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I258" s="12" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="259" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="11" t="s">
+      <c r="H263" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I263" s="12" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="B259" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C259" s="12" t="s">
+      <c r="B264" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C264" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D259" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E259" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F259" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G259" s="13" t="s">
+      <c r="D264" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E264" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F264" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G264" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="H259" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I259" s="12" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="B260" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C260" s="12" t="s">
+      <c r="H264" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I264" s="12" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="B265" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C265" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D260" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E260" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F260" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G260" s="13" t="s">
+      <c r="D265" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E265" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F265" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G265" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="H260" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I260" s="12" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="H265" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I265" s="12" t="s">
+        <v>383</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="A6:A7"/>
@@ -14291,21 +14452,21 @@
     <mergeCell ref="F115:F116"/>
     <mergeCell ref="I115:I116"/>
     <mergeCell ref="A117:I117"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A188:I188"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="F212:F213"/>
-    <mergeCell ref="I212:I213"/>
-    <mergeCell ref="A214:I214"/>
-    <mergeCell ref="A231:A232"/>
-    <mergeCell ref="D231:D232"/>
-    <mergeCell ref="F231:F232"/>
-    <mergeCell ref="I231:I232"/>
-    <mergeCell ref="A233:I233"/>
+    <mergeCell ref="A191:A192"/>
+    <mergeCell ref="D191:D192"/>
+    <mergeCell ref="F191:F192"/>
+    <mergeCell ref="I191:I192"/>
+    <mergeCell ref="A193:I193"/>
+    <mergeCell ref="A217:A218"/>
+    <mergeCell ref="D217:D218"/>
+    <mergeCell ref="F217:F218"/>
+    <mergeCell ref="I217:I218"/>
+    <mergeCell ref="A219:I219"/>
+    <mergeCell ref="A236:A237"/>
+    <mergeCell ref="D236:D237"/>
+    <mergeCell ref="F236:F237"/>
+    <mergeCell ref="I236:I237"/>
+    <mergeCell ref="A238:I238"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="384">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -7313,7 +7313,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I265"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.94"/>
@@ -11160,7 +11160,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
@@ -11178,7 +11178,7 @@
         <v>248</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>501</v>
+        <v>601</v>
       </c>
       <c r="H146" s="7" t="n">
         <v>1</v>
@@ -11187,7 +11187,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
@@ -11205,7 +11205,7 @@
         <v>248</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>502</v>
+        <v>602</v>
       </c>
       <c r="H147" s="7" t="n">
         <v>1</v>
@@ -11214,7 +11214,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
@@ -11232,7 +11232,7 @@
         <v>248</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>503</v>
+        <v>603</v>
       </c>
       <c r="H148" s="7" t="n">
         <v>1</v>
@@ -11241,7 +11241,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
@@ -11259,7 +11259,7 @@
         <v>248</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>504</v>
+        <v>604</v>
       </c>
       <c r="H149" s="7" t="n">
         <v>1</v>
@@ -11268,7 +11268,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
@@ -11286,7 +11286,7 @@
         <v>248</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>505</v>
+        <v>605</v>
       </c>
       <c r="H150" s="7" t="n">
         <v>1</v>
@@ -11295,7 +11295,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
@@ -11313,7 +11313,7 @@
         <v>248</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>506</v>
+        <v>606</v>
       </c>
       <c r="H151" s="7" t="n">
         <v>1</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
@@ -11340,7 +11340,7 @@
         <v>248</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>507</v>
+        <v>607</v>
       </c>
       <c r="H152" s="7" t="n">
         <v>1</v>
@@ -11349,7 +11349,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
@@ -11367,7 +11367,7 @@
         <v>248</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>508</v>
+        <v>608</v>
       </c>
       <c r="H153" s="7" t="n">
         <v>1</v>
@@ -11376,7 +11376,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
@@ -11394,7 +11394,7 @@
         <v>248</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>509</v>
+        <v>609</v>
       </c>
       <c r="H154" s="7" t="n">
         <v>1</v>
@@ -11403,7 +11403,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
@@ -11421,7 +11421,7 @@
         <v>248</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>510</v>
+        <v>610</v>
       </c>
       <c r="H155" s="7" t="n">
         <v>1</v>
@@ -11430,7 +11430,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
@@ -11448,7 +11448,7 @@
         <v>248</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>511</v>
+        <v>611</v>
       </c>
       <c r="H156" s="7" t="n">
         <v>1</v>
@@ -11457,7 +11457,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
@@ -11475,7 +11475,7 @@
         <v>248</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>512</v>
+        <v>612</v>
       </c>
       <c r="H157" s="7" t="n">
         <v>1</v>
@@ -11484,7 +11484,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
@@ -11502,7 +11502,7 @@
         <v>248</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>601</v>
+        <v>801</v>
       </c>
       <c r="H158" s="7" t="n">
         <v>1</v>
@@ -11511,7 +11511,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
@@ -11529,7 +11529,7 @@
         <v>248</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>602</v>
+        <v>802</v>
       </c>
       <c r="H159" s="7" t="n">
         <v>1</v>
@@ -11538,7 +11538,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>291</v>
+        <v>342</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
@@ -11556,7 +11556,7 @@
         <v>248</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>603</v>
+        <v>803</v>
       </c>
       <c r="H160" s="7" t="n">
         <v>1</v>
@@ -11565,7 +11565,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>292</v>
+        <v>343</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
@@ -11583,7 +11583,7 @@
         <v>248</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>604</v>
+        <v>804</v>
       </c>
       <c r="H161" s="7" t="n">
         <v>1</v>
@@ -11592,7 +11592,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
@@ -11610,7 +11610,7 @@
         <v>248</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>605</v>
+        <v>805</v>
       </c>
       <c r="H162" s="7" t="n">
         <v>1</v>
@@ -11619,7 +11619,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>294</v>
+        <v>345</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
@@ -11637,7 +11637,7 @@
         <v>248</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>606</v>
+        <v>806</v>
       </c>
       <c r="H163" s="7" t="n">
         <v>1</v>
@@ -11646,7 +11646,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
@@ -11664,7 +11664,7 @@
         <v>248</v>
       </c>
       <c r="G164" s="7" t="n">
-        <v>607</v>
+        <v>807</v>
       </c>
       <c r="H164" s="7" t="n">
         <v>1</v>
@@ -11673,7 +11673,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>296</v>
+        <v>347</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
@@ -11691,7 +11691,7 @@
         <v>248</v>
       </c>
       <c r="G165" s="7" t="n">
-        <v>608</v>
+        <v>808</v>
       </c>
       <c r="H165" s="7" t="n">
         <v>1</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>297</v>
+        <v>348</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
@@ -11718,785 +11718,809 @@
         <v>248</v>
       </c>
       <c r="G166" s="7" t="n">
-        <v>609</v>
+        <v>809</v>
       </c>
       <c r="H166" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I166" s="7"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C167" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D167" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E167" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F167" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G167" s="7" t="n">
-        <v>610</v>
-      </c>
-      <c r="H167" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I167" s="7"/>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C168" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D168" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E168" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F168" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G168" s="7" t="n">
-        <v>611</v>
-      </c>
-      <c r="H168" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I168" s="7"/>
-    </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B169" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C169" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D169" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E169" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F169" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G169" s="7" t="n">
-        <v>612</v>
-      </c>
-      <c r="H169" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I169" s="7"/>
+      <c r="A168" s="3"/>
+      <c r="B168" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D168" s="3"/>
+      <c r="E168" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F168" s="3"/>
+      <c r="G168" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I168" s="3"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B169" s="5"/>
+      <c r="C169" s="5"/>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="5"/>
+      <c r="G169" s="5"/>
+      <c r="H169" s="5"/>
+      <c r="I169" s="5"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C170" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D170" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E170" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F170" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G170" s="7" t="n">
-        <v>701</v>
-      </c>
-      <c r="H170" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I170" s="7"/>
+      <c r="A170" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F170" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>20001</v>
+      </c>
+      <c r="H170" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B171" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C171" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D171" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E171" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F171" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G171" s="7" t="n">
-        <v>702</v>
-      </c>
-      <c r="H171" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I171" s="7"/>
+      <c r="A171" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E171" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>20002</v>
+      </c>
+      <c r="H171" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="B172" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C172" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D172" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E172" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F172" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G172" s="7" t="n">
-        <v>703</v>
-      </c>
-      <c r="H172" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I172" s="7"/>
+      <c r="A172" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F172" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>20003</v>
+      </c>
+      <c r="H172" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I172" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="B173" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C173" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D173" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E173" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F173" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G173" s="7" t="n">
-        <v>704</v>
-      </c>
-      <c r="H173" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I173" s="7"/>
+      <c r="A173" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E173" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F173" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>20004</v>
+      </c>
+      <c r="H173" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C174" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E174" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F174" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G174" s="7" t="n">
-        <v>705</v>
-      </c>
-      <c r="H174" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I174" s="7"/>
+      <c r="A174" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F174" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>20005</v>
+      </c>
+      <c r="H174" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="B175" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C175" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D175" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E175" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F175" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G175" s="7" t="n">
-        <v>706</v>
-      </c>
-      <c r="H175" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I175" s="7"/>
+      <c r="A175" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E175" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F175" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>20006</v>
+      </c>
+      <c r="H175" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B176" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C176" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D176" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E176" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F176" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G176" s="7" t="n">
-        <v>707</v>
-      </c>
-      <c r="H176" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I176" s="7"/>
+      <c r="A176" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E176" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F176" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>20007</v>
+      </c>
+      <c r="H176" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I176" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B177" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C177" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D177" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E177" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F177" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G177" s="7" t="n">
-        <v>708</v>
-      </c>
-      <c r="H177" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I177" s="7"/>
+      <c r="A177" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E177" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>20008</v>
+      </c>
+      <c r="H177" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I177" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C178" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D178" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E178" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G178" s="7" t="n">
-        <v>709</v>
-      </c>
-      <c r="H178" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I178" s="7"/>
+      <c r="A178" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D178" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E178" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>30001</v>
+      </c>
+      <c r="H178" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="B179" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C179" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D179" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E179" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F179" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G179" s="7" t="n">
-        <v>710</v>
-      </c>
-      <c r="H179" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I179" s="7"/>
+      <c r="A179" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B179" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D179" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E179" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F179" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>30002</v>
+      </c>
+      <c r="H179" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="B180" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C180" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D180" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E180" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F180" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G180" s="7" t="n">
-        <v>711</v>
-      </c>
-      <c r="H180" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I180" s="7"/>
+      <c r="A180" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B180" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C180" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D180" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E180" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F180" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>30003</v>
+      </c>
+      <c r="H180" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I180" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B181" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C181" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D181" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E181" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F181" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G181" s="7" t="n">
-        <v>712</v>
-      </c>
-      <c r="H181" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I181" s="7"/>
+      <c r="A181" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D181" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E181" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>30004</v>
+      </c>
+      <c r="H181" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C182" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D182" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E182" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F182" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G182" s="7" t="n">
-        <v>801</v>
-      </c>
-      <c r="H182" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I182" s="7"/>
+      <c r="A182" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="B182" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D182" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E182" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F182" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>30005</v>
+      </c>
+      <c r="H182" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B183" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C183" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D183" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E183" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F183" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G183" s="7" t="n">
-        <v>802</v>
-      </c>
-      <c r="H183" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I183" s="7"/>
+      <c r="A183" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E183" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F183" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>30006</v>
+      </c>
+      <c r="H183" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I183" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C184" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D184" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E184" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F184" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G184" s="7" t="n">
-        <v>803</v>
-      </c>
-      <c r="H184" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I184" s="7"/>
+      <c r="A184" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E184" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F184" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>40001</v>
+      </c>
+      <c r="H184" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I184" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="B185" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C185" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D185" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E185" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F185" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G185" s="7" t="n">
-        <v>804</v>
-      </c>
-      <c r="H185" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I185" s="7"/>
+      <c r="A185" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E185" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F185" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>60001</v>
+      </c>
+      <c r="H185" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D186" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E186" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F186" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G186" s="7" t="n">
-        <v>805</v>
-      </c>
-      <c r="H186" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I186" s="7"/>
+      <c r="A186" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B186" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D186" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E186" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F186" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>60002</v>
+      </c>
+      <c r="H186" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I186" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="B187" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C187" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D187" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E187" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F187" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G187" s="7" t="n">
-        <v>806</v>
-      </c>
-      <c r="H187" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I187" s="7"/>
+      <c r="A187" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B187" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E187" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F187" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>60003</v>
+      </c>
+      <c r="H187" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I187" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C188" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D188" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E188" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F188" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G188" s="7" t="n">
-        <v>807</v>
-      </c>
-      <c r="H188" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I188" s="7"/>
+      <c r="A188" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D188" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E188" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F188" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>60004</v>
+      </c>
+      <c r="H188" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I188" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="B189" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C189" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D189" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E189" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F189" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G189" s="7" t="n">
-        <v>808</v>
-      </c>
-      <c r="H189" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I189" s="7"/>
+      <c r="A189" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D189" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E189" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F189" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>60005</v>
+      </c>
+      <c r="H189" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I189" s="12" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D190" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E190" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G190" s="7" t="n">
-        <v>809</v>
-      </c>
-      <c r="H190" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I190" s="7"/>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="3" t="s">
+      <c r="A190" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D190" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E190" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F190" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H190" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D191" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E191" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F191" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H191" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B192" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D192" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E192" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F192" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>60008</v>
+      </c>
+      <c r="H192" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I192" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B191" s="4" t="s">
+      <c r="B193" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C191" s="4" t="s">
+      <c r="C193" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D191" s="3" t="s">
+      <c r="D193" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E191" s="4" t="s">
+      <c r="E193" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F191" s="3" t="s">
+      <c r="F193" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G191" s="4" t="s">
+      <c r="G193" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H191" s="4" t="s">
+      <c r="H193" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I191" s="3" t="s">
+      <c r="I193" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="3"/>
-      <c r="B192" s="4" t="s">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="3"/>
+      <c r="B194" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C192" s="4" t="s">
+      <c r="C194" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D192" s="3"/>
-      <c r="E192" s="4" t="s">
+      <c r="D194" s="3"/>
+      <c r="E194" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F192" s="3"/>
-      <c r="G192" s="4" t="s">
+      <c r="F194" s="3"/>
+      <c r="G194" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H192" s="4" t="s">
+      <c r="H194" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I192" s="3"/>
-    </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="B193" s="5"/>
-      <c r="C193" s="5"/>
-      <c r="D193" s="5"/>
-      <c r="E193" s="5"/>
-      <c r="F193" s="5"/>
-      <c r="G193" s="5"/>
-      <c r="H193" s="5"/>
-      <c r="I193" s="5"/>
-    </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="B194" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C194" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D194" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E194" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F194" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G194" s="12" t="n">
-        <v>20001</v>
-      </c>
-      <c r="H194" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I194" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="B195" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C195" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D195" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E195" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F195" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G195" s="12" t="n">
-        <v>20002</v>
-      </c>
-      <c r="H195" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I195" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I194" s="3"/>
+    </row>
+    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B195" s="5"/>
+      <c r="C195" s="5"/>
+      <c r="D195" s="5"/>
+      <c r="E195" s="5"/>
+      <c r="F195" s="5"/>
+      <c r="G195" s="5"/>
+      <c r="H195" s="5"/>
+      <c r="I195" s="5"/>
+    </row>
+    <row r="196" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="12" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>75</v>
@@ -12514,18 +12538,18 @@
         <v>351</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>20003</v>
+        <v>30001</v>
       </c>
       <c r="H196" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="12" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>75</v>
@@ -12543,18 +12567,18 @@
         <v>351</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>20004</v>
+        <v>30002</v>
       </c>
       <c r="H197" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="12" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>75</v>
@@ -12572,18 +12596,18 @@
         <v>351</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>20005</v>
+        <v>30003</v>
       </c>
       <c r="H198" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="12" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B199" s="12" t="s">
         <v>75</v>
@@ -12601,18 +12625,18 @@
         <v>351</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>20006</v>
+        <v>30004</v>
       </c>
       <c r="H199" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="12" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>75</v>
@@ -12630,18 +12654,18 @@
         <v>351</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>20007</v>
+        <v>30005</v>
       </c>
       <c r="H200" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>75</v>
@@ -12659,18 +12683,18 @@
         <v>351</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>20008</v>
+        <v>30006</v>
       </c>
       <c r="H201" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="12" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>75</v>
@@ -12688,7 +12712,7 @@
         <v>351</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>30001</v>
+        <v>40001</v>
       </c>
       <c r="H202" s="12" t="n">
         <v>1</v>
@@ -12697,9 +12721,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="12" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>75</v>
@@ -12717,18 +12741,18 @@
         <v>351</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>30002</v>
+        <v>45001</v>
       </c>
       <c r="H203" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="12" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>75</v>
@@ -12746,18 +12770,18 @@
         <v>351</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>30003</v>
+        <v>60001</v>
       </c>
       <c r="H204" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="12" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>75</v>
@@ -12775,18 +12799,18 @@
         <v>351</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>30004</v>
+        <v>60002</v>
       </c>
       <c r="H205" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="12" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B206" s="12" t="s">
         <v>75</v>
@@ -12804,18 +12828,18 @@
         <v>351</v>
       </c>
       <c r="G206" s="12" t="n">
-        <v>30005</v>
+        <v>60003</v>
       </c>
       <c r="H206" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="12" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>75</v>
@@ -12833,18 +12857,18 @@
         <v>351</v>
       </c>
       <c r="G207" s="12" t="n">
-        <v>30006</v>
+        <v>60004</v>
       </c>
       <c r="H207" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>75</v>
@@ -12862,18 +12886,18 @@
         <v>351</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>40001</v>
+        <v>60005</v>
       </c>
       <c r="H208" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>75</v>
@@ -12891,18 +12915,18 @@
         <v>351</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>60001</v>
+        <v>60006</v>
       </c>
       <c r="H209" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>75</v>
@@ -12920,18 +12944,18 @@
         <v>351</v>
       </c>
       <c r="G210" s="12" t="n">
-        <v>60002</v>
+        <v>60007</v>
       </c>
       <c r="H210" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="12" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>75</v>
@@ -12949,1497 +12973,849 @@
         <v>351</v>
       </c>
       <c r="G211" s="12" t="n">
-        <v>60003</v>
+        <v>60008</v>
       </c>
       <c r="H211" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I211" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="B212" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C212" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D212" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E212" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F212" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G212" s="12" t="n">
-        <v>60004</v>
-      </c>
-      <c r="H212" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I212" s="12" t="s">
-        <v>352</v>
+        <v>376</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A212" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="B213" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C213" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D213" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E213" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F213" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G213" s="12" t="n">
-        <v>60005</v>
-      </c>
-      <c r="H213" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I213" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="B214" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C214" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D214" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E214" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F214" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G214" s="12" t="n">
-        <v>60006</v>
-      </c>
-      <c r="H214" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I214" s="12" t="s">
-        <v>352</v>
-      </c>
+      <c r="A213" s="3"/>
+      <c r="B213" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D213" s="3"/>
+      <c r="E213" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F213" s="3"/>
+      <c r="G213" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H213" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I213" s="3"/>
+    </row>
+    <row r="214" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A214" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B214" s="5"/>
+      <c r="C214" s="5"/>
+      <c r="D214" s="5"/>
+      <c r="E214" s="5"/>
+      <c r="F214" s="5"/>
+      <c r="G214" s="5"/>
+      <c r="H214" s="5"/>
+      <c r="I214" s="5"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="B215" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C215" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D215" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E215" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F215" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G215" s="12" t="n">
-        <v>60007</v>
-      </c>
-      <c r="H215" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I215" s="12" t="s">
-        <v>352</v>
+      <c r="A215" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D215" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E215" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F215" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G215" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="H215" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I215" s="7" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="B216" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C216" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D216" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E216" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F216" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G216" s="12" t="n">
-        <v>60008</v>
-      </c>
-      <c r="H216" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I216" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E217" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F217" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G217" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H217" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I217" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A216" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B216" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D216" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E216" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F216" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G216" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H216" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I216" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D217" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E217" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G217" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H217" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I217" s="7"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="3"/>
-      <c r="B218" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D218" s="3"/>
-      <c r="E218" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F218" s="3"/>
-      <c r="G218" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H218" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I218" s="3"/>
-    </row>
-    <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="B219" s="5"/>
-      <c r="C219" s="5"/>
-      <c r="D219" s="5"/>
-      <c r="E219" s="5"/>
-      <c r="F219" s="5"/>
-      <c r="G219" s="5"/>
-      <c r="H219" s="5"/>
-      <c r="I219" s="5"/>
-    </row>
-    <row r="220" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="B220" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C220" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D220" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E220" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F220" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G220" s="12" t="n">
-        <v>30001</v>
-      </c>
-      <c r="H220" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I220" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="B221" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C221" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D221" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E221" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F221" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G221" s="12" t="n">
-        <v>30002</v>
-      </c>
-      <c r="H221" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I221" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="B222" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C222" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D222" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E222" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F222" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G222" s="12" t="n">
-        <v>30003</v>
-      </c>
-      <c r="H222" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I222" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="B223" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C223" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D223" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E223" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F223" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G223" s="12" t="n">
-        <v>30004</v>
-      </c>
-      <c r="H223" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I223" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="B224" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C224" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D224" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E224" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F224" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G224" s="12" t="n">
-        <v>30005</v>
-      </c>
-      <c r="H224" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I224" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="225" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B225" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C225" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D225" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E225" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F225" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G225" s="12" t="n">
-        <v>30006</v>
-      </c>
-      <c r="H225" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I225" s="12" t="s">
-        <v>376</v>
-      </c>
+      <c r="A218" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C218" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D218" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E218" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G218" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H218" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I218" s="7"/>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D219" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E219" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G219" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H219" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I219" s="7"/>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D220" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E220" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G220" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="H220" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I220" s="7"/>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D221" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E221" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G221" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H221" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I221" s="7"/>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D222" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E222" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G222" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H222" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I222" s="7"/>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D223" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E223" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F223" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G223" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H223" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I223" s="7"/>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D224" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E224" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F224" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G224" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="H224" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I224" s="7"/>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D225" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E225" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G225" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="H225" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I225" s="7"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="B226" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C226" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D226" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E226" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F226" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G226" s="12" t="n">
-        <v>40001</v>
-      </c>
-      <c r="H226" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I226" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="227" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="B227" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C227" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D227" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E227" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F227" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G227" s="12" t="n">
-        <v>45001</v>
-      </c>
-      <c r="H227" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I227" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="228" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="B228" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C228" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D228" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E228" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F228" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G228" s="12" t="n">
-        <v>60001</v>
-      </c>
-      <c r="H228" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I228" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="B229" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C229" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D229" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E229" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F229" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G229" s="12" t="n">
-        <v>60002</v>
-      </c>
-      <c r="H229" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I229" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="230" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="B230" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C230" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D230" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E230" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F230" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G230" s="12" t="n">
-        <v>60003</v>
-      </c>
-      <c r="H230" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I230" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="B231" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C231" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D231" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E231" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F231" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G231" s="12" t="n">
-        <v>60004</v>
-      </c>
-      <c r="H231" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I231" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="B232" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C232" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D232" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E232" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F232" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G232" s="12" t="n">
-        <v>60005</v>
-      </c>
-      <c r="H232" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I232" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="B233" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C233" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D233" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E233" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F233" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G233" s="12" t="n">
-        <v>60006</v>
-      </c>
-      <c r="H233" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I233" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="B234" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C234" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D234" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E234" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F234" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G234" s="12" t="n">
-        <v>60007</v>
-      </c>
-      <c r="H234" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I234" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="235" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="B235" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C235" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D235" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E235" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F235" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G235" s="12" t="n">
-        <v>60008</v>
-      </c>
-      <c r="H235" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I235" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A236" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B236" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E236" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F236" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G236" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H236" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I236" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="3"/>
-      <c r="B237" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D237" s="3"/>
-      <c r="E237" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F237" s="3"/>
-      <c r="G237" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H237" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I237" s="3"/>
-    </row>
-    <row r="238" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A238" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B238" s="5"/>
-      <c r="C238" s="5"/>
-      <c r="D238" s="5"/>
-      <c r="E238" s="5"/>
-      <c r="F238" s="5"/>
-      <c r="G238" s="5"/>
-      <c r="H238" s="5"/>
-      <c r="I238" s="5"/>
-    </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B239" s="7" t="s">
+      <c r="A226" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D226" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E226" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G226" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="H226" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I226" s="7"/>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B227" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C239" s="7" t="s">
+      <c r="C227" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D239" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E239" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F239" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G239" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="H239" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I239" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="B240" s="7" t="s">
+      <c r="D227" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E227" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G227" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H227" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I227" s="7"/>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B228" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C240" s="7" t="s">
+      <c r="C228" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D240" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E240" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F240" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G240" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H240" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I240" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B241" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C241" s="7" t="s">
+      <c r="D228" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E228" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G228" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="H228" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I228" s="7"/>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C229" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D241" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E241" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F241" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G241" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="H241" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I241" s="7"/>
-    </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B242" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C242" s="7" t="s">
+      <c r="D229" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E229" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G229" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H229" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I229" s="7"/>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C230" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D242" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E242" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F242" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G242" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H242" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I242" s="7"/>
-    </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B243" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C243" s="7" t="s">
+      <c r="D230" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E230" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G230" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H230" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I230" s="7"/>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C231" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D243" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E243" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F243" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G243" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="H243" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I243" s="7"/>
-    </row>
-    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B244" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C244" s="7" t="s">
+      <c r="D231" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E231" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F231" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G231" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="H231" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I231" s="7"/>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C232" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D244" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E244" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F244" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G244" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="H244" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I244" s="7"/>
-    </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="B245" s="7" t="s">
+      <c r="D232" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E232" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G232" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H232" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I232" s="7"/>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B233" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C245" s="7" t="s">
+      <c r="C233" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D245" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E245" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F245" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G245" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="H245" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I245" s="7"/>
-    </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B246" s="7" t="s">
+      <c r="D233" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E233" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F233" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G233" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H233" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I233" s="7"/>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B234" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C246" s="7" t="s">
+      <c r="C234" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D246" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E246" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F246" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G246" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="H246" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I246" s="7"/>
-    </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B247" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C247" s="7" t="s">
+      <c r="D234" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E234" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G234" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="H234" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I234" s="7"/>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B235" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C235" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D247" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E247" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F247" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G247" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="H247" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I247" s="7"/>
-    </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B248" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C248" s="7" t="s">
+      <c r="D235" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E235" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F235" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G235" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H235" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I235" s="7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C236" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D248" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E248" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F248" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G248" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="H248" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I248" s="7"/>
-    </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B249" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C249" s="7" t="s">
+      <c r="D236" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E236" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F236" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G236" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="H236" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I236" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B237" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C237" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D249" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E249" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F249" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G249" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="H249" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I249" s="7"/>
-    </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="B250" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C250" s="7" t="s">
+      <c r="D237" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E237" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F237" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G237" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="H237" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I237" s="12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B238" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C238" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D250" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E250" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F250" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G250" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="H250" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I250" s="7"/>
-    </row>
-    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="B251" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C251" s="7" t="s">
+      <c r="D238" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E238" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F238" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G238" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="H238" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I238" s="12" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="B239" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C239" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D251" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E251" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F251" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G251" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="H251" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I251" s="7"/>
-    </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B252" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C252" s="7" t="s">
+      <c r="D239" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E239" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G239" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="H239" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I239" s="12" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="B240" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C240" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D252" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E252" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F252" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G252" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="H252" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I252" s="7"/>
-    </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="B253" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C253" s="7" t="s">
+      <c r="D240" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E240" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G240" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="H240" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I240" s="12" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="B241" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C241" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D253" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E253" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F253" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G253" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H253" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I253" s="7"/>
-    </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="B254" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C254" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D254" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E254" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F254" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G254" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="H254" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I254" s="7"/>
-    </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="B255" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C255" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D255" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E255" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F255" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G255" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="H255" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I255" s="7"/>
-    </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="B256" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C256" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D256" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E256" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F256" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G256" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="H256" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I256" s="7"/>
-    </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B257" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C257" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D257" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E257" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F257" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G257" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="H257" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I257" s="7"/>
-    </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="B258" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C258" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D258" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E258" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F258" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G258" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="H258" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I258" s="7"/>
-    </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B259" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C259" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D259" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E259" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F259" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G259" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="H259" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I259" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B260" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C260" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D260" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E260" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F260" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G260" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H260" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I260" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B261" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C261" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D261" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E261" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F261" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G261" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="H261" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I261" s="12" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="B262" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C262" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D262" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E262" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F262" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G262" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="H262" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I262" s="12" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="263" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="B263" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C263" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D263" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E263" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F263" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G263" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="H263" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I263" s="12" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="264" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="B264" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C264" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D264" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E264" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F264" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G264" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="H264" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I264" s="12" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="265" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="B265" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C265" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D265" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E265" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F265" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G265" s="13" t="s">
+      <c r="D241" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E241" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G241" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="H265" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I265" s="12" t="s">
+      <c r="H241" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I241" s="12" t="s">
         <v>383</v>
       </c>
     </row>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="A6:A7"/>
@@ -14452,21 +13828,21 @@
     <mergeCell ref="F115:F116"/>
     <mergeCell ref="I115:I116"/>
     <mergeCell ref="A117:I117"/>
-    <mergeCell ref="A191:A192"/>
-    <mergeCell ref="D191:D192"/>
-    <mergeCell ref="F191:F192"/>
-    <mergeCell ref="I191:I192"/>
-    <mergeCell ref="A193:I193"/>
-    <mergeCell ref="A217:A218"/>
-    <mergeCell ref="D217:D218"/>
-    <mergeCell ref="F217:F218"/>
-    <mergeCell ref="I217:I218"/>
-    <mergeCell ref="A219:I219"/>
-    <mergeCell ref="A236:A237"/>
-    <mergeCell ref="D236:D237"/>
-    <mergeCell ref="F236:F237"/>
-    <mergeCell ref="I236:I237"/>
-    <mergeCell ref="A238:I238"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="I167:I168"/>
+    <mergeCell ref="A169:I169"/>
+    <mergeCell ref="A193:A194"/>
+    <mergeCell ref="D193:D194"/>
+    <mergeCell ref="F193:F194"/>
+    <mergeCell ref="I193:I194"/>
+    <mergeCell ref="A195:I195"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="F212:F213"/>
+    <mergeCell ref="I212:I213"/>
+    <mergeCell ref="A214:I214"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="352">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -725,268 +725,217 @@
     <t xml:space="preserve">30035</t>
   </si>
   <si>
+    <t xml:space="preserve">DG Detection Disable Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: OFF (DG Detection Enabled), 1: ON (DG Detection Disabled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fan Disable Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: OFF (Fans Enabled), 1: ON (Fans Disabled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serial Number Lower Half</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serial Number Upper Half</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">READ INPUT STATUS (Function Code: 0x02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Phase 1 Contactor On Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input Status </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Phase 2 Contactor On Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Phase 3 Contactor On Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Solar Contactor On Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Grid  Contactor On Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar Neutral Earth Contactor On Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG Off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC Aux Power Available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC Aux Power Available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid R Phase Under Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid R Phase Over Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Y Phase Under Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Y Phase Over Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B Phase Under Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B Phase Over Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar R Phase Under Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar R Phase Over Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar Y Phase Under Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar Y Phase Over Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar B Phase Under Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar B Phase Over Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid R Phase Contactor Coil Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Y Phase Contactor Coil Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B Phase Contactor Coil Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Solar Contactor Coil Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Grid Contactor &amp; Solar Neutral Earth Contactor Coil Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fans Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid R Phase Contactor Stuck Open Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid R Phase Contactor Stuck Closed Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Y Phase Contactor Stuck Open Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Y Phase Contactor Stuck Closed Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B Phase Contactor Stuck Open Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B Phase Contactor Stuck Closed Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Solar Contactor Stuck Open Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Solar Contactor Stuck Closed Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Grid Contactor Stuck Open Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Grid Contactor Stuck Closed Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar Neutral Earth Contactor Stuck Open Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar Neutral Earth Contactor Stuck Closed Error Suspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Grid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Grid  As User Disabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Grid As Grid R Phase Unhealthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Grid As Solar Contactors On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load On Solar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Solar As User Disabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Solar As Solar R Phase Unhealthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Solar As Grid Contactors On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load Not On Solar As DG Running</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fan 1 Short Circuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fan 1 Open Circuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fan 2 Short Circuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fan 2 Open Circuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WRITE MULTIPLE  HOLDING REGISTERS (0x10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6001</t>
+  </si>
+  <si>
     <t xml:space="preserve">DG Detection Enable/Disable Setting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0: Disabled, 1: Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fan Disable Setting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serial Number Lower Half</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serial Number Upper Half</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">READ INPUT STATUS (Function Code: 0x02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Phase 1 Contactor On Feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input Status </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Phase 2 Contactor On Feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Phase 3 Contactor On Feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar Contactor On Feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid  Contactor On Feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Neutral Earth Contactor On Feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DG Off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC Aux Power Available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC Aux Power Available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid R Phase Under Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid R Phase Over Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Under Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Over Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Under Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Over Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar R Phase Under Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar R Phase Over Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Y Phase Under Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Y Phase Over Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar B Phase Under Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar B Phase Over Voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid R Phase Contactor Coil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Contactor Coil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Contactor Coil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar Contactor Coil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid Contactor Coil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Neutral Earth Contactor Coil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid R Phase Voltage without Current Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Voltage without Current Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Voltage without Current Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid R Phase Current without Voltage Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Current without Voltage Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Current without Voltage Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar R Phase Voltage without Current Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Y Phase Voltage without Current Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar B Phase Voltage without Current Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar R Phase Current without Voltage Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Y Phase Current without Voltage Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar B Phase Current without Voltage Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid R Phase Contactor Stuck Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Contactor Stuck Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Contactor Stuck Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar Contactor Stuck Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid Contactor Stuck Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Neutral Earth Contactor Stuck Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid R Phase Contactor Stuck Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Contactor Stuck Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Contactor Stuck Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar Contactor Stuck Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid Contactor Stuck Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Neutral Earth Contactor Stuck Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid R Phase Contactor Feedback Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Contactor Feedback Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Contactor Feedback Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar Contactor Feedback Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid Contactor Feedback Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Neutral Earth Contactor Feedback Open Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid R Phase Contactor Feedback Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Contactor Feedback Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Contactor Feedback Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar Contactor Feedback Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid Contactor Feedback Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Neutral Earth Contactor Feedback Closed Error Suspected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid User Disabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid Disabled Due To Grid R Phase Unhealthy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar User Disabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar Disabled Due To Solar R Phase Unhealthy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WRITE MULTIPLE  HOLDING REGISTERS (0x10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DG Detection Disable Setting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0: OFF (DG Detection Enabled), 1: ON (DG Detection Disabled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0: OFF (Fans Enabled), 1: ON (Fans Disabled)</t>
   </si>
   <si>
     <t xml:space="preserve">Switch Pressed</t>
@@ -1041,51 +990,6 @@
 26,27,28: Low Point Calibration In Progress
 127: Calibration Completed Successfully
 126: Error occured during calibration. Please restart controller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid R Phase Contactor Coil Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Contactor Coil Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Contactor Coil Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar Contactor Coil Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid Contactor &amp; Solar Neutral Earth Contactor Coil Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fans Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load Not On Grid  As User Disabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load Not On Grid As Grid R Phase Unhealthy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load Not On Grid As Solar Contactors On</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load Not On Solar As User Disabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load Not On Solar As Solar R Phase Unhealthy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load Not On Solar As Grid Contactors On</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load Not On Solar As DG Running</t>
   </si>
   <si>
     <t xml:space="preserve">READ COIL STATUS (Function Code: 0x01)</t>
@@ -4350,7 +4254,7 @@
       </c>
       <c r="I101" s="7"/>
     </row>
-    <row r="102" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="9" t="s">
         <v>226</v>
       </c>
@@ -4377,7 +4281,7 @@
       </c>
       <c r="I102" s="7"/>
     </row>
-    <row r="103" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="9" t="s">
         <v>228</v>
       </c>
@@ -4404,7 +4308,7 @@
       </c>
       <c r="I103" s="7"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="9" t="s">
         <v>230</v>
       </c>
@@ -4458,7 +4362,7 @@
       </c>
       <c r="I105" s="7"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
         <v>234</v>
       </c>
@@ -4513,12 +4417,12 @@
         <v>2</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>75</v>
@@ -4536,16 +4440,16 @@
         <v>26</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H108" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I108" s="7"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>75</v>
@@ -4563,16 +4467,16 @@
         <v>26</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I109" s="7"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>75</v>
@@ -4590,7 +4494,7 @@
         <v>26</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H110" s="7" t="n">
         <v>2</v>
@@ -4649,7 +4553,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -4662,13 +4566,13 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>75</v>
@@ -4677,7 +4581,7 @@
         <v>75</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>1</v>
@@ -4689,22 +4593,22 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F115" s="7" t="s">
         <v>249</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>248</v>
       </c>
       <c r="G115" s="7" t="n">
         <v>2</v>
@@ -4716,13 +4620,13 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>75</v>
@@ -4731,7 +4635,7 @@
         <v>75</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>3</v>
@@ -4743,13 +4647,13 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>75</v>
@@ -4758,7 +4662,7 @@
         <v>75</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G117" s="7" t="n">
         <v>4</v>
@@ -4770,13 +4674,13 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>75</v>
@@ -4785,7 +4689,7 @@
         <v>75</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>5</v>
@@ -4797,13 +4701,13 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>75</v>
@@ -4812,7 +4716,7 @@
         <v>75</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G119" s="7" t="n">
         <v>6</v>
@@ -4824,13 +4728,13 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>75</v>
@@ -4839,7 +4743,7 @@
         <v>75</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>7</v>
@@ -4851,13 +4755,13 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>75</v>
@@ -4866,7 +4770,7 @@
         <v>75</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>8</v>
@@ -4878,13 +4782,13 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>75</v>
@@ -4893,7 +4797,7 @@
         <v>75</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>201</v>
@@ -4905,13 +4809,13 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>75</v>
@@ -4920,7 +4824,7 @@
         <v>75</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>202</v>
@@ -4932,13 +4836,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>75</v>
@@ -4947,7 +4851,7 @@
         <v>75</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>301</v>
@@ -4959,13 +4863,13 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>75</v>
@@ -4974,7 +4878,7 @@
         <v>75</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>302</v>
@@ -4986,13 +4890,13 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>75</v>
@@ -5001,7 +4905,7 @@
         <v>75</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>303</v>
@@ -5013,13 +4917,13 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>75</v>
@@ -5028,7 +4932,7 @@
         <v>75</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>304</v>
@@ -5040,13 +4944,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>75</v>
@@ -5055,7 +4959,7 @@
         <v>75</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>305</v>
@@ -5067,13 +4971,13 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>75</v>
@@ -5082,7 +4986,7 @@
         <v>75</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>306</v>
@@ -5094,13 +4998,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>75</v>
@@ -5109,7 +5013,7 @@
         <v>75</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G130" s="7" t="n">
         <v>307</v>
@@ -5121,13 +5025,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>75</v>
@@ -5136,7 +5040,7 @@
         <v>75</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G131" s="7" t="n">
         <v>308</v>
@@ -5148,13 +5052,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>75</v>
@@ -5163,7 +5067,7 @@
         <v>75</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>309</v>
@@ -5175,13 +5079,13 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D133" s="7" t="s">
         <v>75</v>
@@ -5190,7 +5094,7 @@
         <v>75</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G133" s="7" t="n">
         <v>310</v>
@@ -5202,13 +5106,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>75</v>
@@ -5217,7 +5121,7 @@
         <v>75</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>311</v>
@@ -5229,13 +5133,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>75</v>
@@ -5244,7 +5148,7 @@
         <v>75</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G135" s="7" t="n">
         <v>312</v>
@@ -5256,13 +5160,13 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D136" s="7" t="s">
         <v>75</v>
@@ -5271,7 +5175,7 @@
         <v>75</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>401</v>
@@ -5283,13 +5187,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D137" s="7" t="s">
         <v>75</v>
@@ -5298,7 +5202,7 @@
         <v>75</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G137" s="7" t="n">
         <v>402</v>
@@ -5310,13 +5214,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D138" s="7" t="s">
         <v>75</v>
@@ -5325,7 +5229,7 @@
         <v>75</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>403</v>
@@ -5337,13 +5241,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>75</v>
@@ -5352,7 +5256,7 @@
         <v>75</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G139" s="7" t="n">
         <v>404</v>
@@ -5364,13 +5268,13 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D140" s="7" t="s">
         <v>75</v>
@@ -5379,7 +5283,7 @@
         <v>75</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>405</v>
@@ -5391,13 +5295,13 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>75</v>
@@ -5406,7 +5310,7 @@
         <v>75</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G141" s="7" t="n">
         <v>406</v>
@@ -5418,13 +5322,13 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D142" s="7" t="s">
         <v>75</v>
@@ -5433,10 +5337,10 @@
         <v>75</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>407</v>
+        <v>601</v>
       </c>
       <c r="H142" s="7" t="n">
         <v>1</v>
@@ -5445,13 +5349,13 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>75</v>
@@ -5460,10 +5364,10 @@
         <v>75</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>501</v>
+        <v>602</v>
       </c>
       <c r="H143" s="7" t="n">
         <v>1</v>
@@ -5472,13 +5376,13 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>75</v>
@@ -5487,10 +5391,10 @@
         <v>75</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>502</v>
+        <v>603</v>
       </c>
       <c r="H144" s="7" t="n">
         <v>1</v>
@@ -5499,13 +5403,13 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>75</v>
@@ -5514,10 +5418,10 @@
         <v>75</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>503</v>
+        <v>604</v>
       </c>
       <c r="H145" s="7" t="n">
         <v>1</v>
@@ -5526,13 +5430,13 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>75</v>
@@ -5541,10 +5445,10 @@
         <v>75</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>504</v>
+        <v>605</v>
       </c>
       <c r="H146" s="7" t="n">
         <v>1</v>
@@ -5553,13 +5457,13 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D147" s="7" t="s">
         <v>75</v>
@@ -5568,10 +5472,10 @@
         <v>75</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>505</v>
+        <v>606</v>
       </c>
       <c r="H147" s="7" t="n">
         <v>1</v>
@@ -5580,13 +5484,13 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D148" s="7" t="s">
         <v>75</v>
@@ -5595,10 +5499,10 @@
         <v>75</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>506</v>
+        <v>607</v>
       </c>
       <c r="H148" s="7" t="n">
         <v>1</v>
@@ -5607,13 +5511,13 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D149" s="7" t="s">
         <v>75</v>
@@ -5622,10 +5526,10 @@
         <v>75</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>507</v>
+        <v>608</v>
       </c>
       <c r="H149" s="7" t="n">
         <v>1</v>
@@ -5634,13 +5538,13 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D150" s="7" t="s">
         <v>75</v>
@@ -5649,10 +5553,10 @@
         <v>75</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>508</v>
+        <v>609</v>
       </c>
       <c r="H150" s="7" t="n">
         <v>1</v>
@@ -5661,13 +5565,13 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D151" s="7" t="s">
         <v>75</v>
@@ -5676,10 +5580,10 @@
         <v>75</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>509</v>
+        <v>610</v>
       </c>
       <c r="H151" s="7" t="n">
         <v>1</v>
@@ -5688,13 +5592,13 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>75</v>
@@ -5703,10 +5607,10 @@
         <v>75</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>510</v>
+        <v>611</v>
       </c>
       <c r="H152" s="7" t="n">
         <v>1</v>
@@ -5715,13 +5619,13 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>75</v>
@@ -5730,10 +5634,10 @@
         <v>75</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>511</v>
+        <v>612</v>
       </c>
       <c r="H153" s="7" t="n">
         <v>1</v>
@@ -5742,13 +5646,13 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>75</v>
@@ -5757,10 +5661,10 @@
         <v>75</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>512</v>
+        <v>801</v>
       </c>
       <c r="H154" s="7" t="n">
         <v>1</v>
@@ -5769,13 +5673,13 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D155" s="7" t="s">
         <v>75</v>
@@ -5784,10 +5688,10 @@
         <v>75</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>601</v>
+        <v>802</v>
       </c>
       <c r="H155" s="7" t="n">
         <v>1</v>
@@ -5796,13 +5700,13 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>75</v>
@@ -5811,10 +5715,10 @@
         <v>75</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>602</v>
+        <v>803</v>
       </c>
       <c r="H156" s="7" t="n">
         <v>1</v>
@@ -5823,13 +5727,13 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D157" s="7" t="s">
         <v>75</v>
@@ -5838,10 +5742,10 @@
         <v>75</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>603</v>
+        <v>804</v>
       </c>
       <c r="H157" s="7" t="n">
         <v>1</v>
@@ -5850,13 +5754,13 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D158" s="7" t="s">
         <v>75</v>
@@ -5865,10 +5769,10 @@
         <v>75</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>604</v>
+        <v>805</v>
       </c>
       <c r="H158" s="7" t="n">
         <v>1</v>
@@ -5877,13 +5781,13 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D159" s="7" t="s">
         <v>75</v>
@@ -5892,10 +5796,10 @@
         <v>75</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>605</v>
+        <v>806</v>
       </c>
       <c r="H159" s="7" t="n">
         <v>1</v>
@@ -5904,13 +5808,13 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D160" s="7" t="s">
         <v>75</v>
@@ -5919,10 +5823,10 @@
         <v>75</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>606</v>
+        <v>807</v>
       </c>
       <c r="H160" s="7" t="n">
         <v>1</v>
@@ -5931,13 +5835,13 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D161" s="7" t="s">
         <v>75</v>
@@ -5946,10 +5850,10 @@
         <v>75</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>607</v>
+        <v>808</v>
       </c>
       <c r="H161" s="7" t="n">
         <v>1</v>
@@ -5958,13 +5862,13 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D162" s="7" t="s">
         <v>75</v>
@@ -5973,10 +5877,10 @@
         <v>75</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>608</v>
+        <v>809</v>
       </c>
       <c r="H162" s="7" t="n">
         <v>1</v>
@@ -5985,13 +5889,13 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D163" s="7" t="s">
         <v>75</v>
@@ -6000,10 +5904,10 @@
         <v>75</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>609</v>
+        <v>901</v>
       </c>
       <c r="H163" s="7" t="n">
         <v>1</v>
@@ -6012,13 +5916,13 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D164" s="7" t="s">
         <v>75</v>
@@ -6027,10 +5931,10 @@
         <v>75</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G164" s="7" t="n">
-        <v>610</v>
+        <v>902</v>
       </c>
       <c r="H164" s="7" t="n">
         <v>1</v>
@@ -6039,13 +5943,13 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>75</v>
@@ -6054,10 +5958,10 @@
         <v>75</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G165" s="7" t="n">
-        <v>611</v>
+        <v>903</v>
       </c>
       <c r="H165" s="7" t="n">
         <v>1</v>
@@ -6066,13 +5970,13 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D166" s="7" t="s">
         <v>75</v>
@@ -6081,517 +5985,521 @@
         <v>75</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G166" s="7" t="n">
-        <v>612</v>
+        <v>904</v>
       </c>
       <c r="H166" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I166" s="7"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C167" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D167" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E167" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F167" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G167" s="7" t="n">
-        <v>701</v>
-      </c>
-      <c r="H167" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I167" s="7"/>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="7" t="s">
+      <c r="A168" s="3"/>
+      <c r="B168" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D168" s="3"/>
+      <c r="E168" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F168" s="3"/>
+      <c r="G168" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I168" s="3"/>
+    </row>
+    <row r="169" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B168" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C168" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D168" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E168" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F168" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G168" s="7" t="n">
-        <v>702</v>
-      </c>
-      <c r="H168" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I168" s="7"/>
-    </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="7" t="s">
+      <c r="B169" s="5"/>
+      <c r="C169" s="5"/>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="5"/>
+      <c r="G169" s="5"/>
+      <c r="H169" s="5"/>
+      <c r="I169" s="5"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D170" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G170" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B169" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C169" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D169" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E169" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F169" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G169" s="7" t="n">
-        <v>703</v>
-      </c>
-      <c r="H169" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I169" s="7"/>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C170" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D170" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E170" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F170" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G170" s="7" t="n">
-        <v>704</v>
-      </c>
       <c r="H170" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I170" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="I170" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="7" t="s">
-        <v>305</v>
+      <c r="A171" s="9" t="s">
+        <v>187</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D171" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E171" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D171" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E171" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G171" s="7" t="n">
-        <v>705</v>
+        <v>26</v>
+      </c>
+      <c r="G171" s="10" t="s">
+        <v>188</v>
       </c>
       <c r="H171" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I171" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="I171" s="7" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="7" t="s">
-        <v>306</v>
+      <c r="A172" s="9" t="s">
+        <v>197</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D172" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E172" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D172" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E172" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G172" s="7" t="n">
-        <v>706</v>
+        <v>26</v>
+      </c>
+      <c r="G172" s="10" t="s">
+        <v>198</v>
       </c>
       <c r="H172" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I172" s="7"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="7" t="s">
-        <v>307</v>
+      <c r="A173" s="9" t="s">
+        <v>199</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D173" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E173" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D173" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E173" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G173" s="7" t="n">
-        <v>707</v>
+        <v>26</v>
+      </c>
+      <c r="G173" s="10" t="s">
+        <v>200</v>
       </c>
       <c r="H173" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I173" s="7"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="7" t="s">
-        <v>308</v>
+      <c r="A174" s="9" t="s">
+        <v>201</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E174" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D174" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E174" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G174" s="7" t="n">
-        <v>708</v>
+        <v>26</v>
+      </c>
+      <c r="G174" s="10" t="s">
+        <v>202</v>
       </c>
       <c r="H174" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I174" s="7"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="7" t="s">
-        <v>309</v>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="9" t="s">
+        <v>203</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D175" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E175" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D175" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E175" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G175" s="7" t="n">
-        <v>709</v>
+        <v>26</v>
+      </c>
+      <c r="G175" s="10" t="s">
+        <v>204</v>
       </c>
       <c r="H175" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I175" s="7"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="7" t="s">
-        <v>310</v>
+      <c r="A176" s="9" t="s">
+        <v>205</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D176" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E176" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D176" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E176" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G176" s="7" t="n">
-        <v>710</v>
+        <v>26</v>
+      </c>
+      <c r="G176" s="10" t="s">
+        <v>206</v>
       </c>
       <c r="H176" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I176" s="7"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="7" t="s">
-        <v>311</v>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D177" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E177" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D177" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E177" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G177" s="7" t="n">
-        <v>711</v>
+        <v>26</v>
+      </c>
+      <c r="G177" s="10" t="s">
+        <v>208</v>
       </c>
       <c r="H177" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I177" s="7"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="7" t="s">
-        <v>312</v>
+      <c r="A178" s="9" t="s">
+        <v>209</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D178" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E178" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D178" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E178" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G178" s="7" t="n">
-        <v>712</v>
+        <v>26</v>
+      </c>
+      <c r="G178" s="10" t="s">
+        <v>210</v>
       </c>
       <c r="H178" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I178" s="7"/>
     </row>
-    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="7" t="s">
-        <v>313</v>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="9" t="s">
+        <v>211</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D179" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E179" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D179" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E179" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G179" s="7" t="n">
-        <v>801</v>
+        <v>26</v>
+      </c>
+      <c r="G179" s="10" t="s">
+        <v>212</v>
       </c>
       <c r="H179" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I179" s="7"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="7" t="s">
-        <v>314</v>
+      <c r="A180" s="9" t="s">
+        <v>213</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D180" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E180" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D180" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E180" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G180" s="7" t="n">
-        <v>802</v>
+        <v>26</v>
+      </c>
+      <c r="G180" s="10" t="s">
+        <v>214</v>
       </c>
       <c r="H180" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I180" s="7"/>
     </row>
-    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="7" t="s">
-        <v>315</v>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D181" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E181" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D181" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E181" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G181" s="7" t="n">
-        <v>803</v>
+        <v>26</v>
+      </c>
+      <c r="G181" s="10" t="s">
+        <v>216</v>
       </c>
       <c r="H181" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I181" s="7"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="7" t="s">
-        <v>316</v>
+      <c r="A182" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D182" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E182" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
+      </c>
+      <c r="D182" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E182" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G182" s="7" t="n">
-        <v>804</v>
+        <v>26</v>
+      </c>
+      <c r="G182" s="10" t="s">
+        <v>218</v>
       </c>
       <c r="H182" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I182" s="7"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D183" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E183" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F183" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G183" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H183" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I183" s="3" t="s">
-        <v>16</v>
-      </c>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D183" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E183" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G183" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="H183" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I183" s="7"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="3"/>
-      <c r="B184" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D184" s="3"/>
-      <c r="E184" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F184" s="3"/>
-      <c r="G184" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H184" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I184" s="3"/>
-    </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B185" s="5"/>
-      <c r="C185" s="5"/>
-      <c r="D185" s="5"/>
-      <c r="E185" s="5"/>
-      <c r="F185" s="5"/>
-      <c r="G185" s="5"/>
-      <c r="H185" s="5"/>
-      <c r="I185" s="5"/>
+      <c r="A184" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D184" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E184" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G184" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H184" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I184" s="7"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D185" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E185" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G185" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H185" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I185" s="7"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="9" t="s">
-        <v>108</v>
+        <v>226</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="C186" s="7" t="s">
         <v>110</v>
@@ -6606,21 +6514,19 @@
         <v>26</v>
       </c>
       <c r="G186" s="10" t="s">
-        <v>318</v>
+        <v>227</v>
       </c>
       <c r="H186" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I186" s="7" t="s">
-        <v>112</v>
-      </c>
+      <c r="I186" s="7"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="9" t="s">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="C187" s="7" t="s">
         <v>110</v>
@@ -6635,21 +6541,19 @@
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="H187" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I187" s="7" t="s">
-        <v>189</v>
-      </c>
+      <c r="I187" s="7"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="9" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C188" s="7" t="s">
         <v>110</v>
@@ -6664,7 +6568,7 @@
         <v>26</v>
       </c>
       <c r="G188" s="10" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="H188" s="7" t="n">
         <v>2</v>
@@ -6673,10 +6577,10 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="9" t="s">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C189" s="7" t="s">
         <v>110</v>
@@ -6691,7 +6595,7 @@
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="H189" s="7" t="n">
         <v>2</v>
@@ -6699,11 +6603,11 @@
       <c r="I189" s="7"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="9" t="s">
-        <v>201</v>
+      <c r="A190" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="C190" s="7" t="s">
         <v>110</v>
@@ -6718,19 +6622,21 @@
         <v>26</v>
       </c>
       <c r="G190" s="10" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="H190" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I190" s="7"/>
+      <c r="I190" s="7" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="9" t="s">
-        <v>203</v>
+      <c r="A191" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="C191" s="7" t="s">
         <v>110</v>
@@ -6745,491 +6651,15 @@
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="H191" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I191" s="7"/>
-    </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C192" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D192" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E192" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F192" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G192" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="H192" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I192" s="7"/>
-    </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B193" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C193" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D193" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E193" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F193" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G193" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="H193" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I193" s="7"/>
-    </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C194" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D194" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E194" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F194" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G194" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="H194" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I194" s="7"/>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B195" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C195" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D195" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E195" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G195" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="H195" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I195" s="7"/>
-    </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B196" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C196" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D196" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E196" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G196" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="H196" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I196" s="7"/>
-    </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="B197" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C197" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D197" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E197" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G197" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="H197" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I197" s="7"/>
-    </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="B198" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C198" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D198" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E198" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G198" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="H198" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I198" s="7"/>
-    </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B199" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C199" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D199" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E199" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G199" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="H199" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I199" s="7"/>
-    </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="B200" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C200" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D200" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E200" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F200" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G200" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H200" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I200" s="7"/>
-    </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="B201" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C201" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D201" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E201" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F201" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G201" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="H201" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I201" s="7"/>
-    </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="B202" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C202" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D202" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E202" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F202" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G202" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="H202" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I202" s="7"/>
-    </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="B203" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C203" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D203" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E203" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F203" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G203" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="H203" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I203" s="7"/>
-    </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C204" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D204" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E204" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F204" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G204" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="H204" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I204" s="7"/>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="B205" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C205" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D205" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E205" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F205" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G205" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="H205" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I205" s="7"/>
-    </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B206" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C206" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D206" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E206" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F206" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G206" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="H206" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I206" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B207" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C207" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D207" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E207" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F207" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G207" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H207" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I207" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="1048485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="I191" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
     <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -7292,11 +6722,11 @@
     <mergeCell ref="F111:F112"/>
     <mergeCell ref="I111:I112"/>
     <mergeCell ref="A113:I113"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="D183:D184"/>
-    <mergeCell ref="F183:F184"/>
-    <mergeCell ref="I183:I184"/>
-    <mergeCell ref="A185:I185"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="I167:I168"/>
+    <mergeCell ref="A169:I169"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10086,7 +9516,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>319</v>
+        <v>234</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>75</v>
@@ -10110,7 +9540,7 @@
         <v>2</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>320</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10139,12 +9569,12 @@
         <v>2</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>321</v>
+        <v>239</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="86.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="11" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>75</v>
@@ -10162,18 +9592,18 @@
         <v>26</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="H108" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>75</v>
@@ -10191,7 +9621,7 @@
         <v>26</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>2</v>
@@ -10200,7 +9630,7 @@
     </row>
     <row r="110" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>75</v>
@@ -10218,7 +9648,7 @@
         <v>26</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H110" s="7" t="n">
         <v>2</v>
@@ -10227,7 +9657,7 @@
     </row>
     <row r="111" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>75</v>
@@ -10245,7 +9675,7 @@
         <v>26</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H111" s="7" t="n">
         <v>2</v>
@@ -10254,7 +9684,7 @@
     </row>
     <row r="112" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="11" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="B112" s="12" t="s">
         <v>75</v>
@@ -10272,18 +9702,18 @@
         <v>26</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="H112" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="11" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="B113" s="12" t="s">
         <v>75</v>
@@ -10301,18 +9731,18 @@
         <v>26</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="H113" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="236.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="11" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="B114" s="12" t="s">
         <v>75</v>
@@ -10330,13 +9760,13 @@
         <v>26</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="H114" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I114" s="12" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10391,7 +9821,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -10404,13 +9834,13 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>75</v>
@@ -10419,7 +9849,7 @@
         <v>75</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>1</v>
@@ -10431,22 +9861,22 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F119" s="7" t="s">
         <v>249</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>248</v>
       </c>
       <c r="G119" s="7" t="n">
         <v>2</v>
@@ -10458,13 +9888,13 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>75</v>
@@ -10473,7 +9903,7 @@
         <v>75</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>3</v>
@@ -10485,13 +9915,13 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>75</v>
@@ -10500,7 +9930,7 @@
         <v>75</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>4</v>
@@ -10512,13 +9942,13 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>75</v>
@@ -10527,7 +9957,7 @@
         <v>75</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>5</v>
@@ -10539,13 +9969,13 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>75</v>
@@ -10554,7 +9984,7 @@
         <v>75</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>6</v>
@@ -10566,13 +9996,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>75</v>
@@ -10581,7 +10011,7 @@
         <v>75</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>7</v>
@@ -10593,13 +10023,13 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>75</v>
@@ -10608,7 +10038,7 @@
         <v>75</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>8</v>
@@ -10620,13 +10050,13 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>75</v>
@@ -10635,7 +10065,7 @@
         <v>75</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>201</v>
@@ -10647,13 +10077,13 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>75</v>
@@ -10662,7 +10092,7 @@
         <v>75</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>202</v>
@@ -10674,13 +10104,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>75</v>
@@ -10689,7 +10119,7 @@
         <v>75</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>301</v>
@@ -10701,13 +10131,13 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>75</v>
@@ -10716,7 +10146,7 @@
         <v>75</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>302</v>
@@ -10728,13 +10158,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>75</v>
@@ -10743,7 +10173,7 @@
         <v>75</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G130" s="7" t="n">
         <v>303</v>
@@ -10755,13 +10185,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>75</v>
@@ -10770,7 +10200,7 @@
         <v>75</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G131" s="7" t="n">
         <v>304</v>
@@ -10782,13 +10212,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>75</v>
@@ -10797,7 +10227,7 @@
         <v>75</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>305</v>
@@ -10809,13 +10239,13 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D133" s="7" t="s">
         <v>75</v>
@@ -10824,7 +10254,7 @@
         <v>75</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G133" s="7" t="n">
         <v>306</v>
@@ -10836,13 +10266,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>75</v>
@@ -10851,7 +10281,7 @@
         <v>75</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>307</v>
@@ -10863,13 +10293,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>75</v>
@@ -10878,7 +10308,7 @@
         <v>75</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G135" s="7" t="n">
         <v>308</v>
@@ -10890,13 +10320,13 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D136" s="7" t="s">
         <v>75</v>
@@ -10905,7 +10335,7 @@
         <v>75</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>309</v>
@@ -10917,13 +10347,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D137" s="7" t="s">
         <v>75</v>
@@ -10932,7 +10362,7 @@
         <v>75</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G137" s="7" t="n">
         <v>310</v>
@@ -10944,13 +10374,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D138" s="7" t="s">
         <v>75</v>
@@ -10959,7 +10389,7 @@
         <v>75</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>311</v>
@@ -10971,13 +10401,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>75</v>
@@ -10986,7 +10416,7 @@
         <v>75</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G139" s="7" t="n">
         <v>312</v>
@@ -10998,13 +10428,13 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>334</v>
+        <v>271</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D140" s="7" t="s">
         <v>75</v>
@@ -11013,7 +10443,7 @@
         <v>75</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>401</v>
@@ -11025,13 +10455,13 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>335</v>
+        <v>272</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>75</v>
@@ -11040,7 +10470,7 @@
         <v>75</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G141" s="7" t="n">
         <v>402</v>
@@ -11052,13 +10482,13 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>336</v>
+        <v>273</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D142" s="7" t="s">
         <v>75</v>
@@ -11067,7 +10497,7 @@
         <v>75</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G142" s="7" t="n">
         <v>403</v>
@@ -11079,13 +10509,13 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>337</v>
+        <v>274</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>75</v>
@@ -11094,7 +10524,7 @@
         <v>75</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G143" s="7" t="n">
         <v>404</v>
@@ -11106,13 +10536,13 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>338</v>
+        <v>275</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>75</v>
@@ -11121,7 +10551,7 @@
         <v>75</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G144" s="7" t="n">
         <v>405</v>
@@ -11133,13 +10563,13 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>339</v>
+        <v>276</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>75</v>
@@ -11148,7 +10578,7 @@
         <v>75</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G145" s="7" t="n">
         <v>406</v>
@@ -11160,13 +10590,13 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>75</v>
@@ -11175,7 +10605,7 @@
         <v>75</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>601</v>
@@ -11187,13 +10617,13 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D147" s="7" t="s">
         <v>75</v>
@@ -11202,7 +10632,7 @@
         <v>75</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G147" s="7" t="n">
         <v>602</v>
@@ -11214,13 +10644,13 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D148" s="7" t="s">
         <v>75</v>
@@ -11229,7 +10659,7 @@
         <v>75</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>603</v>
@@ -11241,13 +10671,13 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D149" s="7" t="s">
         <v>75</v>
@@ -11256,7 +10686,7 @@
         <v>75</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G149" s="7" t="n">
         <v>604</v>
@@ -11268,13 +10698,13 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D150" s="7" t="s">
         <v>75</v>
@@ -11283,7 +10713,7 @@
         <v>75</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G150" s="7" t="n">
         <v>605</v>
@@ -11295,13 +10725,13 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D151" s="7" t="s">
         <v>75</v>
@@ -11310,7 +10740,7 @@
         <v>75</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G151" s="7" t="n">
         <v>606</v>
@@ -11322,13 +10752,13 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>75</v>
@@ -11337,7 +10767,7 @@
         <v>75</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G152" s="7" t="n">
         <v>607</v>
@@ -11349,13 +10779,13 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>75</v>
@@ -11364,7 +10794,7 @@
         <v>75</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G153" s="7" t="n">
         <v>608</v>
@@ -11376,13 +10806,13 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>75</v>
@@ -11391,7 +10821,7 @@
         <v>75</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>609</v>
@@ -11403,13 +10833,13 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D155" s="7" t="s">
         <v>75</v>
@@ -11418,7 +10848,7 @@
         <v>75</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G155" s="7" t="n">
         <v>610</v>
@@ -11430,13 +10860,13 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>75</v>
@@ -11445,7 +10875,7 @@
         <v>75</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>611</v>
@@ -11457,13 +10887,13 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D157" s="7" t="s">
         <v>75</v>
@@ -11472,7 +10902,7 @@
         <v>75</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G157" s="7" t="n">
         <v>612</v>
@@ -11484,13 +10914,13 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>340</v>
+        <v>289</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D158" s="7" t="s">
         <v>75</v>
@@ -11499,7 +10929,7 @@
         <v>75</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>801</v>
@@ -11511,13 +10941,13 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>341</v>
+        <v>290</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D159" s="7" t="s">
         <v>75</v>
@@ -11526,7 +10956,7 @@
         <v>75</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G159" s="7" t="n">
         <v>802</v>
@@ -11538,13 +10968,13 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>342</v>
+        <v>291</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D160" s="7" t="s">
         <v>75</v>
@@ -11553,7 +10983,7 @@
         <v>75</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>803</v>
@@ -11565,13 +10995,13 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>343</v>
+        <v>292</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D161" s="7" t="s">
         <v>75</v>
@@ -11580,7 +11010,7 @@
         <v>75</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G161" s="7" t="n">
         <v>804</v>
@@ -11592,13 +11022,13 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D162" s="7" t="s">
         <v>75</v>
@@ -11607,7 +11037,7 @@
         <v>75</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>805</v>
@@ -11619,13 +11049,13 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D163" s="7" t="s">
         <v>75</v>
@@ -11634,7 +11064,7 @@
         <v>75</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G163" s="7" t="n">
         <v>806</v>
@@ -11646,13 +11076,13 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>346</v>
+        <v>295</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D164" s="7" t="s">
         <v>75</v>
@@ -11661,7 +11091,7 @@
         <v>75</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G164" s="7" t="n">
         <v>807</v>
@@ -11673,13 +11103,13 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>347</v>
+        <v>296</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>75</v>
@@ -11688,7 +11118,7 @@
         <v>75</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G165" s="7" t="n">
         <v>808</v>
@@ -11700,13 +11130,13 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D166" s="7" t="s">
         <v>75</v>
@@ -11715,7 +11145,7 @@
         <v>75</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G166" s="7" t="n">
         <v>809</v>
@@ -11725,194 +11155,186 @@
       </c>
       <c r="I166" s="7"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="3" t="s">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F167" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G167" s="7" t="n">
+        <v>901</v>
+      </c>
+      <c r="H167" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" s="7"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G168" s="7" t="n">
+        <v>902</v>
+      </c>
+      <c r="H168" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" s="7"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G169" s="7" t="n">
+        <v>903</v>
+      </c>
+      <c r="H169" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" s="7"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G170" s="7" t="n">
+        <v>904</v>
+      </c>
+      <c r="H170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="7"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A171" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B171" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C171" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D167" s="3" t="s">
+      <c r="D171" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E167" s="4" t="s">
+      <c r="E171" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F167" s="3" t="s">
+      <c r="F171" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G167" s="4" t="s">
+      <c r="G171" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H167" s="4" t="s">
+      <c r="H171" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I167" s="3" t="s">
+      <c r="I171" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="3"/>
-      <c r="B168" s="4" t="s">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="3"/>
+      <c r="B172" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C172" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D168" s="3"/>
-      <c r="E168" s="4" t="s">
+      <c r="D172" s="3"/>
+      <c r="E172" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F168" s="3"/>
-      <c r="G168" s="4" t="s">
+      <c r="F172" s="3"/>
+      <c r="G172" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H168" s="4" t="s">
+      <c r="H172" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I168" s="3"/>
-    </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="B169" s="5"/>
-      <c r="C169" s="5"/>
-      <c r="D169" s="5"/>
-      <c r="E169" s="5"/>
-      <c r="F169" s="5"/>
-      <c r="G169" s="5"/>
-      <c r="H169" s="5"/>
-      <c r="I169" s="5"/>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="B170" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C170" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D170" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E170" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F170" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G170" s="12" t="n">
-        <v>20001</v>
-      </c>
-      <c r="H170" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I170" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="B171" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C171" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D171" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E171" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F171" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G171" s="12" t="n">
-        <v>20002</v>
-      </c>
-      <c r="H171" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I171" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="B172" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C172" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D172" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E172" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F172" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G172" s="12" t="n">
-        <v>20003</v>
-      </c>
-      <c r="H172" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I172" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="B173" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C173" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D173" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E173" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F173" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G173" s="12" t="n">
-        <v>20004</v>
-      </c>
-      <c r="H173" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I173" s="12" t="s">
-        <v>352</v>
-      </c>
+      <c r="I172" s="3"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A173" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B173" s="5"/>
+      <c r="C173" s="5"/>
+      <c r="D173" s="5"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="5"/>
+      <c r="G173" s="5"/>
+      <c r="H173" s="5"/>
+      <c r="I173" s="5"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="12" t="s">
-        <v>356</v>
+        <v>318</v>
       </c>
       <c r="B174" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D174" s="12" t="s">
         <v>75</v>
@@ -11921,27 +11343,27 @@
         <v>75</v>
       </c>
       <c r="F174" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>20005</v>
+        <v>20001</v>
       </c>
       <c r="H174" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I174" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="12" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="B175" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D175" s="12" t="s">
         <v>75</v>
@@ -11950,27 +11372,27 @@
         <v>75</v>
       </c>
       <c r="F175" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>20006</v>
+        <v>20002</v>
       </c>
       <c r="H175" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I175" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="12" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="B176" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D176" s="12" t="s">
         <v>75</v>
@@ -11979,27 +11401,27 @@
         <v>75</v>
       </c>
       <c r="F176" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>20007</v>
+        <v>20003</v>
       </c>
       <c r="H176" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I176" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="12" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="B177" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D177" s="12" t="s">
         <v>75</v>
@@ -12008,27 +11430,27 @@
         <v>75</v>
       </c>
       <c r="F177" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>20008</v>
+        <v>20004</v>
       </c>
       <c r="H177" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I177" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="12" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="B178" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D178" s="12" t="s">
         <v>75</v>
@@ -12037,27 +11459,27 @@
         <v>75</v>
       </c>
       <c r="F178" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>30001</v>
+        <v>20005</v>
       </c>
       <c r="H178" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I178" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="12" t="s">
-        <v>361</v>
+        <v>325</v>
       </c>
       <c r="B179" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D179" s="12" t="s">
         <v>75</v>
@@ -12066,27 +11488,27 @@
         <v>75</v>
       </c>
       <c r="F179" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>30002</v>
+        <v>20006</v>
       </c>
       <c r="H179" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I179" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="12" t="s">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="B180" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D180" s="12" t="s">
         <v>75</v>
@@ -12095,27 +11517,27 @@
         <v>75</v>
       </c>
       <c r="F180" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>30003</v>
+        <v>20007</v>
       </c>
       <c r="H180" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I180" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="12" t="s">
-        <v>363</v>
+        <v>327</v>
       </c>
       <c r="B181" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D181" s="12" t="s">
         <v>75</v>
@@ -12124,27 +11546,27 @@
         <v>75</v>
       </c>
       <c r="F181" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>30004</v>
+        <v>20008</v>
       </c>
       <c r="H181" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I181" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="12" t="s">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="B182" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D182" s="12" t="s">
         <v>75</v>
@@ -12153,27 +11575,27 @@
         <v>75</v>
       </c>
       <c r="F182" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>30005</v>
+        <v>30001</v>
       </c>
       <c r="H182" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I182" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="12" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="B183" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D183" s="12" t="s">
         <v>75</v>
@@ -12182,27 +11604,27 @@
         <v>75</v>
       </c>
       <c r="F183" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>30006</v>
+        <v>30002</v>
       </c>
       <c r="H183" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I183" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="12" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="B184" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D184" s="12" t="s">
         <v>75</v>
@@ -12211,27 +11633,27 @@
         <v>75</v>
       </c>
       <c r="F184" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>40001</v>
+        <v>30003</v>
       </c>
       <c r="H184" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I184" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="12" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="B185" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D185" s="12" t="s">
         <v>75</v>
@@ -12240,27 +11662,27 @@
         <v>75</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>60001</v>
+        <v>30004</v>
       </c>
       <c r="H185" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I185" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="12" t="s">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="B186" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D186" s="12" t="s">
         <v>75</v>
@@ -12269,27 +11691,27 @@
         <v>75</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>60002</v>
+        <v>30005</v>
       </c>
       <c r="H186" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I186" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="12" t="s">
-        <v>369</v>
+        <v>333</v>
       </c>
       <c r="B187" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D187" s="12" t="s">
         <v>75</v>
@@ -12298,27 +11720,27 @@
         <v>75</v>
       </c>
       <c r="F187" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>60003</v>
+        <v>30006</v>
       </c>
       <c r="H187" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I187" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="12" t="s">
-        <v>370</v>
+        <v>334</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D188" s="12" t="s">
         <v>75</v>
@@ -12327,27 +11749,27 @@
         <v>75</v>
       </c>
       <c r="F188" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>60004</v>
+        <v>40001</v>
       </c>
       <c r="H188" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="12" t="s">
-        <v>371</v>
+        <v>335</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D189" s="12" t="s">
         <v>75</v>
@@ -12356,27 +11778,27 @@
         <v>75</v>
       </c>
       <c r="F189" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>60005</v>
+        <v>60001</v>
       </c>
       <c r="H189" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="12" t="s">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D190" s="12" t="s">
         <v>75</v>
@@ -12385,27 +11807,27 @@
         <v>75</v>
       </c>
       <c r="F190" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>60006</v>
+        <v>60002</v>
       </c>
       <c r="H190" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="12" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D191" s="12" t="s">
         <v>75</v>
@@ -12414,27 +11836,27 @@
         <v>75</v>
       </c>
       <c r="F191" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>60007</v>
+        <v>60003</v>
       </c>
       <c r="H191" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="12" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D192" s="12" t="s">
         <v>75</v>
@@ -12443,206 +11865,206 @@
         <v>75</v>
       </c>
       <c r="F192" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G192" s="12" t="n">
+        <v>60004</v>
+      </c>
+      <c r="H192" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I192" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C193" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D193" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E193" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F193" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>60005</v>
+      </c>
+      <c r="H193" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I193" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C194" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D194" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E194" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F194" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H194" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B195" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D195" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E195" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F195" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="G195" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H195" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I195" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D196" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E196" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F196" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="G196" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H192" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I192" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="3" t="s">
+      <c r="H196" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A197" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B193" s="4" t="s">
+      <c r="B197" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C193" s="4" t="s">
+      <c r="C197" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D193" s="3" t="s">
+      <c r="D197" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E193" s="4" t="s">
+      <c r="E197" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F193" s="3" t="s">
+      <c r="F197" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G193" s="4" t="s">
+      <c r="G197" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H193" s="4" t="s">
+      <c r="H197" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I193" s="3" t="s">
+      <c r="I197" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="3"/>
-      <c r="B194" s="4" t="s">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="3"/>
+      <c r="B198" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C194" s="4" t="s">
+      <c r="C198" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D194" s="3"/>
-      <c r="E194" s="4" t="s">
+      <c r="D198" s="3"/>
+      <c r="E198" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F194" s="3"/>
-      <c r="G194" s="4" t="s">
+      <c r="F198" s="3"/>
+      <c r="G198" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H194" s="4" t="s">
+      <c r="H198" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I194" s="3"/>
-    </row>
-    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="B195" s="5"/>
-      <c r="C195" s="5"/>
-      <c r="D195" s="5"/>
-      <c r="E195" s="5"/>
-      <c r="F195" s="5"/>
-      <c r="G195" s="5"/>
-      <c r="H195" s="5"/>
-      <c r="I195" s="5"/>
-    </row>
-    <row r="196" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="B196" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C196" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D196" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E196" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F196" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G196" s="12" t="n">
-        <v>30001</v>
-      </c>
-      <c r="H196" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I196" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="197" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="B197" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C197" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D197" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E197" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F197" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G197" s="12" t="n">
-        <v>30002</v>
-      </c>
-      <c r="H197" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I197" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="B198" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C198" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D198" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E198" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F198" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G198" s="12" t="n">
-        <v>30003</v>
-      </c>
-      <c r="H198" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I198" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="B199" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C199" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D199" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E199" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F199" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G199" s="12" t="n">
-        <v>30004</v>
-      </c>
-      <c r="H199" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I199" s="12" t="s">
-        <v>376</v>
-      </c>
+      <c r="I198" s="3"/>
+    </row>
+    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B199" s="5"/>
+      <c r="C199" s="5"/>
+      <c r="D199" s="5"/>
+      <c r="E199" s="5"/>
+      <c r="F199" s="5"/>
+      <c r="G199" s="5"/>
+      <c r="H199" s="5"/>
+      <c r="I199" s="5"/>
     </row>
     <row r="200" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="12" t="s">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D200" s="12" t="s">
         <v>75</v>
@@ -12651,27 +12073,27 @@
         <v>75</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>30005</v>
+        <v>30001</v>
       </c>
       <c r="H200" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D201" s="12" t="s">
         <v>75</v>
@@ -12680,27 +12102,27 @@
         <v>75</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>30006</v>
+        <v>30002</v>
       </c>
       <c r="H201" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="12" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D202" s="12" t="s">
         <v>75</v>
@@ -12709,27 +12131,27 @@
         <v>75</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>40001</v>
+        <v>30003</v>
       </c>
       <c r="H202" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="12" t="s">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D203" s="12" t="s">
         <v>75</v>
@@ -12738,27 +12160,27 @@
         <v>75</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>45001</v>
+        <v>30004</v>
       </c>
       <c r="H203" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="12" t="s">
-        <v>367</v>
+        <v>332</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D204" s="12" t="s">
         <v>75</v>
@@ -12767,27 +12189,27 @@
         <v>75</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>60001</v>
+        <v>30005</v>
       </c>
       <c r="H204" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="12" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D205" s="12" t="s">
         <v>75</v>
@@ -12796,27 +12218,27 @@
         <v>75</v>
       </c>
       <c r="F205" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>60002</v>
+        <v>30006</v>
       </c>
       <c r="H205" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="12" t="s">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="B206" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D206" s="12" t="s">
         <v>75</v>
@@ -12825,27 +12247,27 @@
         <v>75</v>
       </c>
       <c r="F206" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G206" s="12" t="n">
-        <v>60003</v>
+        <v>40001</v>
       </c>
       <c r="H206" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>376</v>
+        <v>320</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="12" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D207" s="12" t="s">
         <v>75</v>
@@ -12854,27 +12276,27 @@
         <v>75</v>
       </c>
       <c r="F207" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G207" s="12" t="n">
-        <v>60004</v>
+        <v>45001</v>
       </c>
       <c r="H207" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
-        <v>371</v>
+        <v>335</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D208" s="12" t="s">
         <v>75</v>
@@ -12883,27 +12305,27 @@
         <v>75</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>60005</v>
+        <v>60001</v>
       </c>
       <c r="H208" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D209" s="12" t="s">
         <v>75</v>
@@ -12912,27 +12334,27 @@
         <v>75</v>
       </c>
       <c r="F209" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>60006</v>
+        <v>60002</v>
       </c>
       <c r="H209" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="12" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D210" s="12" t="s">
         <v>75</v>
@@ -12941,27 +12363,27 @@
         <v>75</v>
       </c>
       <c r="F210" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G210" s="12" t="n">
-        <v>60007</v>
+        <v>60003</v>
       </c>
       <c r="H210" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="12" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D211" s="12" t="s">
         <v>75</v>
@@ -12970,199 +12392,203 @@
         <v>75</v>
       </c>
       <c r="F211" s="12" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="G211" s="12" t="n">
+        <v>60004</v>
+      </c>
+      <c r="H211" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" s="12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B212" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E212" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F212" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="G212" s="12" t="n">
+        <v>60005</v>
+      </c>
+      <c r="H212" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I212" s="12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E213" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F213" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="G213" s="12" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H213" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" s="12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E214" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F214" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="G214" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H214" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" s="12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B215" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E215" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F215" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="G215" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H211" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I211" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="s">
+      <c r="H215" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A216" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B216" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C216" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D212" s="3" t="s">
+      <c r="D216" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E212" s="4" t="s">
+      <c r="E216" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F212" s="3" t="s">
+      <c r="F216" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G212" s="4" t="s">
+      <c r="G216" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H212" s="4" t="s">
+      <c r="H216" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I212" s="3" t="s">
+      <c r="I216" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="3"/>
-      <c r="B213" s="4" t="s">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="3"/>
+      <c r="B217" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C213" s="4" t="s">
+      <c r="C217" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D213" s="3"/>
-      <c r="E213" s="4" t="s">
+      <c r="D217" s="3"/>
+      <c r="E217" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F213" s="3"/>
-      <c r="G213" s="4" t="s">
+      <c r="F217" s="3"/>
+      <c r="G217" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H213" s="4" t="s">
+      <c r="H217" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I213" s="3"/>
-    </row>
-    <row r="214" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B214" s="5"/>
-      <c r="C214" s="5"/>
-      <c r="D214" s="5"/>
-      <c r="E214" s="5"/>
-      <c r="F214" s="5"/>
-      <c r="G214" s="5"/>
-      <c r="H214" s="5"/>
-      <c r="I214" s="5"/>
-    </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B215" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C215" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D215" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E215" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F215" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G215" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="H215" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I215" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="B216" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C216" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D216" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E216" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F216" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G216" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H216" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I216" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B217" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C217" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D217" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E217" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F217" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G217" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="H217" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I217" s="7"/>
-    </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B218" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C218" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D218" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E218" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F218" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G218" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H218" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I218" s="7"/>
+      <c r="I217" s="3"/>
+    </row>
+    <row r="218" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A218" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B218" s="5"/>
+      <c r="C218" s="5"/>
+      <c r="D218" s="5"/>
+      <c r="E218" s="5"/>
+      <c r="F218" s="5"/>
+      <c r="G218" s="5"/>
+      <c r="H218" s="5"/>
+      <c r="I218" s="5"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="9" t="s">
-        <v>201</v>
+        <v>108</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C219" s="7" t="s">
         <v>110</v>
@@ -13177,19 +12603,21 @@
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="H219" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I219" s="7"/>
+      <c r="I219" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="9" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C220" s="7" t="s">
         <v>110</v>
@@ -13204,19 +12632,21 @@
         <v>26</v>
       </c>
       <c r="G220" s="10" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="H220" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I220" s="7"/>
+      <c r="I220" s="7" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="9" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C221" s="7" t="s">
         <v>110</v>
@@ -13231,7 +12661,7 @@
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="H221" s="7" t="n">
         <v>2</v>
@@ -13240,10 +12670,10 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="9" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C222" s="7" t="s">
         <v>110</v>
@@ -13258,7 +12688,7 @@
         <v>26</v>
       </c>
       <c r="G222" s="10" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="H222" s="7" t="n">
         <v>2</v>
@@ -13267,7 +12697,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="9" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B223" s="7" t="s">
         <v>24</v>
@@ -13285,7 +12715,7 @@
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="H223" s="7" t="n">
         <v>2</v>
@@ -13294,7 +12724,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="9" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B224" s="7" t="s">
         <v>24</v>
@@ -13312,7 +12742,7 @@
         <v>26</v>
       </c>
       <c r="G224" s="10" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="H224" s="7" t="n">
         <v>2</v>
@@ -13321,10 +12751,10 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="9" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C225" s="7" t="s">
         <v>110</v>
@@ -13339,7 +12769,7 @@
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H225" s="7" t="n">
         <v>2</v>
@@ -13348,10 +12778,10 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="9" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C226" s="7" t="s">
         <v>110</v>
@@ -13366,7 +12796,7 @@
         <v>26</v>
       </c>
       <c r="G226" s="10" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="H226" s="7" t="n">
         <v>2</v>
@@ -13375,10 +12805,10 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C227" s="7" t="s">
         <v>110</v>
@@ -13393,7 +12823,7 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="H227" s="7" t="n">
         <v>2</v>
@@ -13402,10 +12832,10 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="9" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C228" s="7" t="s">
         <v>110</v>
@@ -13420,7 +12850,7 @@
         <v>26</v>
       </c>
       <c r="G228" s="10" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="H228" s="7" t="n">
         <v>2</v>
@@ -13429,10 +12859,10 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="9" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>222</v>
+        <v>24</v>
       </c>
       <c r="C229" s="7" t="s">
         <v>110</v>
@@ -13447,7 +12877,7 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="H229" s="7" t="n">
         <v>2</v>
@@ -13456,10 +12886,10 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="9" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>222</v>
+        <v>24</v>
       </c>
       <c r="C230" s="7" t="s">
         <v>110</v>
@@ -13474,7 +12904,7 @@
         <v>26</v>
       </c>
       <c r="G230" s="10" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="H230" s="7" t="n">
         <v>2</v>
@@ -13483,10 +12913,10 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="C231" s="7" t="s">
         <v>110</v>
@@ -13501,7 +12931,7 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="H231" s="7" t="n">
         <v>2</v>
@@ -13510,10 +12940,10 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="9" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="C232" s="7" t="s">
         <v>110</v>
@@ -13528,7 +12958,7 @@
         <v>26</v>
       </c>
       <c r="G232" s="10" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="H232" s="7" t="n">
         <v>2</v>
@@ -13537,10 +12967,10 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="9" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="C233" s="7" t="s">
         <v>110</v>
@@ -13555,7 +12985,7 @@
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="H233" s="7" t="n">
         <v>2</v>
@@ -13564,10 +12994,10 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="9" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="C234" s="7" t="s">
         <v>110</v>
@@ -13582,7 +13012,7 @@
         <v>26</v>
       </c>
       <c r="G234" s="10" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H234" s="7" t="n">
         <v>2</v>
@@ -13590,11 +13020,11 @@
       <c r="I234" s="7"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="7" t="s">
-        <v>234</v>
+      <c r="A235" s="9" t="s">
+        <v>226</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="C235" s="7" t="s">
         <v>110</v>
@@ -13609,21 +13039,19 @@
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="H235" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I235" s="7" t="s">
-        <v>320</v>
-      </c>
+      <c r="I235" s="7"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="7" t="s">
-        <v>237</v>
+      <c r="A236" s="9" t="s">
+        <v>228</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="C236" s="7" t="s">
         <v>110</v>
@@ -13638,134 +13066,128 @@
         <v>26</v>
       </c>
       <c r="G236" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H236" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I236" s="7"/>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D237" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E237" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F237" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G237" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H237" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I237" s="7"/>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B238" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D238" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E238" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F238" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G238" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="H238" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I238" s="7"/>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D239" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E239" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G239" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H239" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I239" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B240" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C240" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D240" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E240" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G240" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="H236" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I236" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="237" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="12" t="s">
+      <c r="H240" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I240" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B237" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C237" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D237" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E237" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F237" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G237" s="12" t="s">
+    </row>
+    <row r="241" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="12" t="s">
         <v>240</v>
-      </c>
-      <c r="H237" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I237" s="12" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="238" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="B238" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C238" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D238" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E238" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F238" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G238" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="H238" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I238" s="12" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="B239" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C239" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D239" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E239" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F239" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G239" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="H239" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I239" s="12" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="240" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="B240" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C240" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D240" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E240" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F240" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G240" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="H240" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I240" s="12" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="11" t="s">
-        <v>382</v>
       </c>
       <c r="B241" s="12" t="s">
         <v>75</v>
@@ -13782,20 +13204,132 @@
       <c r="F241" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G241" s="13" t="s">
-        <v>332</v>
+      <c r="G241" s="12" t="s">
+        <v>241</v>
       </c>
       <c r="H241" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I241" s="12" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B242" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C242" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D242" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E242" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F242" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G242" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="H242" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I242" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B243" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C243" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D243" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E243" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F243" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G243" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="H243" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I243" s="12" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B244" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C244" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D244" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E244" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G244" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="H244" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I244" s="12" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="B245" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D245" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E245" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F245" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G245" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="H245" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I245" s="12" t="s">
+        <v>351</v>
+      </c>
+    </row>
     <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -13828,21 +13362,21 @@
     <mergeCell ref="F115:F116"/>
     <mergeCell ref="I115:I116"/>
     <mergeCell ref="A117:I117"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="I167:I168"/>
-    <mergeCell ref="A169:I169"/>
-    <mergeCell ref="A193:A194"/>
-    <mergeCell ref="D193:D194"/>
-    <mergeCell ref="F193:F194"/>
-    <mergeCell ref="I193:I194"/>
-    <mergeCell ref="A195:I195"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="F212:F213"/>
-    <mergeCell ref="I212:I213"/>
-    <mergeCell ref="A214:I214"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="D171:D172"/>
+    <mergeCell ref="F171:F172"/>
+    <mergeCell ref="I171:I172"/>
+    <mergeCell ref="A173:I173"/>
+    <mergeCell ref="A197:A198"/>
+    <mergeCell ref="D197:D198"/>
+    <mergeCell ref="F197:F198"/>
+    <mergeCell ref="I197:I198"/>
+    <mergeCell ref="A199:I199"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="D216:D217"/>
+    <mergeCell ref="F216:F217"/>
+    <mergeCell ref="I216:I217"/>
+    <mergeCell ref="A218:I218"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Modbus Table" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Internal Modbus Table" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="EMS Testing Firmware" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2438" uniqueCount="384">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -1104,6 +1105,102 @@
     <t xml:space="preserve">Internal Only. Not visible to customer. 
 If set to non-zero, it advances the calibration state machine when it is waiting for external input. Only writtable when test mode enabled.</t>
   </si>
+  <si>
+    <t xml:space="preserve">EMS (Energy Management System)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel Test Firmware V1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS485 Port of EMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">READ MULTIPLE HOLDING REGISTERS (Function Code: 0x03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature Sensor 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature sensor #1 reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature Sensor 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature sensor #2 reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery Voltage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48VDC Battery voltage (Analog Input 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAN Connectivity Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: Disconnected, 1: Connected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: Inactive, 1: Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTES (Panel Test Firmware Behaviour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. EMS Serial parameters are (baud rate: 9600, parity: No parity, stop bits: 1, slave ID: 1). These are same as the default modbus parameters for SOCO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. The customer Modbus master connects to the  RS-485 port 1 of the EMS. The EMS in turn talks to SOCO over its RS-485 port 2. Only the port 1 is exposed externally for panel testing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. EMS routes incoming requests on a per-address basis: holding registers in the 65001-65016 range listed above are answered locally by the EMS (panel test firmware). Every other request - regardless of function code (0x01 Read Coils, 0x02 Read Discrete Inputs, 0x03 Read Holding Registers outside 65001-65016, 0x05 Write Single Coil, 0x06 Write Single Holding Register, 0x10 Write Multiple Holding Registers, etc.) - is forwarded transparently to SOCO and the SOCO response is relayed back to the master.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. The EMS-local register block (65001-65016) was chosen to sit above the highest SOCO Modbus address currently in use while still fitting inside the Modbus 16-bit address space (maximum 1-based address = 65536, since the on-the-wire address field is 2 bytes). This leaves clear separation from SOCO and still keeps every byte of every frame within the standard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. All EMS-local entries are exposed only via Function Code 0x03 (Read Multiple Holding Registers). Writes to 65001-65016 will be rejected with Modbus exception 0x02 (Illegal Data Address).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Float values use IEEE-754 32-bit, transmitted high-word first (big-endian word order), matching the SOCO convention. The two Modbus registers must be read together in a single request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Boolean values (Digital Input 1-4, LAN Connectivity Status) are encoded as 32-bit unsigned integers in the same 2-register format. Only the LSB carries information: 0 = inactive/disconnected, 1 = active/connected. All other bits are reserved and read as 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. The Digital Inputs reflect the raw electrical state of the EMS DI pins after debouncing; their mapping to panel signals is defined by the panel wiring drawing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. The 'LAN Connectivity Status' bit is set when the Ethernet PHY reports link-up AND a valid IPv4 address has been acquired (static or DHCP). It is cleared on link-down or IP loss.</t>
+  </si>
 </sst>
 </file>
 
@@ -1112,7 +1209,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1161,6 +1258,28 @@
     <font>
       <b val="true"/>
       <sz val="8"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1285,7 +1404,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1340,6 +1459,30 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1592,7 +1735,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.15"/>
@@ -12056,7 +12199,7 @@
       <c r="H199" s="5"/>
       <c r="I199" s="5"/>
     </row>
-    <row r="200" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="12" t="s">
         <v>328</v>
       </c>
@@ -12085,7 +12228,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
         <v>329</v>
       </c>
@@ -12114,7 +12257,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="12" t="s">
         <v>330</v>
       </c>
@@ -12143,7 +12286,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="12" t="s">
         <v>331</v>
       </c>
@@ -12172,7 +12315,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="12" t="s">
         <v>332</v>
       </c>
@@ -12201,7 +12344,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="12" t="s">
         <v>333</v>
       </c>
@@ -12259,7 +12402,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="12" t="s">
         <v>345</v>
       </c>
@@ -12288,7 +12431,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
         <v>335</v>
       </c>
@@ -12317,7 +12460,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
         <v>336</v>
       </c>
@@ -12346,7 +12489,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="12" t="s">
         <v>337</v>
       </c>
@@ -12375,7 +12518,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="12" t="s">
         <v>338</v>
       </c>
@@ -12404,7 +12547,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="12" t="s">
         <v>339</v>
       </c>
@@ -12433,7 +12576,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="12" t="s">
         <v>340</v>
       </c>
@@ -12462,7 +12605,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="12" t="s">
         <v>341</v>
       </c>
@@ -12491,7 +12634,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="12" t="s">
         <v>342</v>
       </c>
@@ -13185,7 +13328,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="12" t="s">
         <v>240</v>
       </c>
@@ -13214,7 +13357,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="12" t="s">
         <v>242</v>
       </c>
@@ -13243,7 +13386,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="45.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="11" t="s">
         <v>308</v>
       </c>
@@ -13272,7 +13415,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="47.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="36.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="11" t="s">
         <v>311</v>
       </c>
@@ -13301,7 +13444,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="11" t="s">
         <v>350</v>
       </c>
@@ -13386,4 +13529,516 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40.86"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A29:I29"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Modbus Table" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2438" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2450" uniqueCount="387">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -991,6 +991,16 @@
 26,27,28: Low Point Calibration In Progress
 127: Calibration Completed Successfully
 126: Error occured during calibration. Please restart controller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scratch Pad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal Only. Not visible to customer. 
+Used to store a temporarily value. Resets when SOCO restarts on POR.</t>
   </si>
   <si>
     <t xml:space="preserve">READ COIL STATUS (Function Code: 0x01)</t>
@@ -1404,7 +1414,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1461,27 +1471,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9912,99 +9914,101 @@
         <v>316</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="3" t="s">
+    <row r="115" customFormat="false" ht="36.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B116" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C116" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D116" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E115" s="4" t="s">
+      <c r="E116" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F116" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="G116" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H115" s="4" t="s">
+      <c r="H116" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I115" s="3" t="s">
+      <c r="I116" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="3"/>
-      <c r="B116" s="4" t="s">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="3"/>
+      <c r="B117" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C117" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D116" s="3"/>
-      <c r="E116" s="4" t="s">
+      <c r="D117" s="3"/>
+      <c r="E117" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F116" s="3"/>
-      <c r="G116" s="4" t="s">
+      <c r="F117" s="3"/>
+      <c r="G117" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H116" s="4" t="s">
+      <c r="H117" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I116" s="3"/>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="5" t="s">
+      <c r="I117" s="3"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5"/>
-      <c r="I117" s="5"/>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="G118" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H118" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I118" s="7"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="5"/>
+      <c r="E118" s="5"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
+      <c r="I118" s="5"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>75</v>
@@ -10022,7 +10026,7 @@
         <v>249</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H119" s="7" t="n">
         <v>1</v>
@@ -10031,7 +10035,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>75</v>
@@ -10049,7 +10053,7 @@
         <v>249</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H120" s="7" t="n">
         <v>1</v>
@@ -10058,7 +10062,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>75</v>
@@ -10076,7 +10080,7 @@
         <v>249</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H121" s="7" t="n">
         <v>1</v>
@@ -10085,7 +10089,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>75</v>
@@ -10103,7 +10107,7 @@
         <v>249</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H122" s="7" t="n">
         <v>1</v>
@@ -10112,7 +10116,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>75</v>
@@ -10130,7 +10134,7 @@
         <v>249</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H123" s="7" t="n">
         <v>1</v>
@@ -10139,7 +10143,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>75</v>
@@ -10157,7 +10161,7 @@
         <v>249</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H124" s="7" t="n">
         <v>1</v>
@@ -10166,7 +10170,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>75</v>
@@ -10184,7 +10188,7 @@
         <v>249</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H125" s="7" t="n">
         <v>1</v>
@@ -10193,7 +10197,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>75</v>
@@ -10211,7 +10215,7 @@
         <v>249</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>201</v>
+        <v>8</v>
       </c>
       <c r="H126" s="7" t="n">
         <v>1</v>
@@ -10220,7 +10224,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>75</v>
@@ -10238,7 +10242,7 @@
         <v>249</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H127" s="7" t="n">
         <v>1</v>
@@ -10247,7 +10251,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>75</v>
@@ -10265,7 +10269,7 @@
         <v>249</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="H128" s="7" t="n">
         <v>1</v>
@@ -10274,7 +10278,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>75</v>
@@ -10292,7 +10296,7 @@
         <v>249</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H129" s="7" t="n">
         <v>1</v>
@@ -10301,7 +10305,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>75</v>
@@ -10319,7 +10323,7 @@
         <v>249</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H130" s="7" t="n">
         <v>1</v>
@@ -10328,7 +10332,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>75</v>
@@ -10346,7 +10350,7 @@
         <v>249</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H131" s="7" t="n">
         <v>1</v>
@@ -10355,7 +10359,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>75</v>
@@ -10373,7 +10377,7 @@
         <v>249</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H132" s="7" t="n">
         <v>1</v>
@@ -10382,7 +10386,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>75</v>
@@ -10400,7 +10404,7 @@
         <v>249</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H133" s="7" t="n">
         <v>1</v>
@@ -10409,7 +10413,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>75</v>
@@ -10427,7 +10431,7 @@
         <v>249</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H134" s="7" t="n">
         <v>1</v>
@@ -10436,7 +10440,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>75</v>
@@ -10454,7 +10458,7 @@
         <v>249</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H135" s="7" t="n">
         <v>1</v>
@@ -10463,7 +10467,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>75</v>
@@ -10481,7 +10485,7 @@
         <v>249</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H136" s="7" t="n">
         <v>1</v>
@@ -10490,7 +10494,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>75</v>
@@ -10508,7 +10512,7 @@
         <v>249</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H137" s="7" t="n">
         <v>1</v>
@@ -10517,7 +10521,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>75</v>
@@ -10535,7 +10539,7 @@
         <v>249</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H138" s="7" t="n">
         <v>1</v>
@@ -10544,7 +10548,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>75</v>
@@ -10562,7 +10566,7 @@
         <v>249</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H139" s="7" t="n">
         <v>1</v>
@@ -10571,7 +10575,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>75</v>
@@ -10589,7 +10593,7 @@
         <v>249</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>401</v>
+        <v>312</v>
       </c>
       <c r="H140" s="7" t="n">
         <v>1</v>
@@ -10598,7 +10602,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>75</v>
@@ -10616,7 +10620,7 @@
         <v>249</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H141" s="7" t="n">
         <v>1</v>
@@ -10625,7 +10629,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>75</v>
@@ -10643,7 +10647,7 @@
         <v>249</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H142" s="7" t="n">
         <v>1</v>
@@ -10652,7 +10656,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>75</v>
@@ -10670,7 +10674,7 @@
         <v>249</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H143" s="7" t="n">
         <v>1</v>
@@ -10679,7 +10683,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
@@ -10697,7 +10701,7 @@
         <v>249</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H144" s="7" t="n">
         <v>1</v>
@@ -10706,7 +10710,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
@@ -10724,7 +10728,7 @@
         <v>249</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H145" s="7" t="n">
         <v>1</v>
@@ -10733,7 +10737,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
@@ -10751,7 +10755,7 @@
         <v>249</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>601</v>
+        <v>406</v>
       </c>
       <c r="H146" s="7" t="n">
         <v>1</v>
@@ -10760,7 +10764,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
@@ -10778,7 +10782,7 @@
         <v>249</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H147" s="7" t="n">
         <v>1</v>
@@ -10787,7 +10791,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
@@ -10805,7 +10809,7 @@
         <v>249</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H148" s="7" t="n">
         <v>1</v>
@@ -10814,7 +10818,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
@@ -10832,7 +10836,7 @@
         <v>249</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H149" s="7" t="n">
         <v>1</v>
@@ -10841,7 +10845,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
@@ -10859,7 +10863,7 @@
         <v>249</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H150" s="7" t="n">
         <v>1</v>
@@ -10868,7 +10872,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
@@ -10886,7 +10890,7 @@
         <v>249</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H151" s="7" t="n">
         <v>1</v>
@@ -10895,7 +10899,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
@@ -10913,7 +10917,7 @@
         <v>249</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H152" s="7" t="n">
         <v>1</v>
@@ -10922,7 +10926,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
@@ -10940,7 +10944,7 @@
         <v>249</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H153" s="7" t="n">
         <v>1</v>
@@ -10949,7 +10953,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
@@ -10967,7 +10971,7 @@
         <v>249</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H154" s="7" t="n">
         <v>1</v>
@@ -10976,7 +10980,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
@@ -10994,7 +10998,7 @@
         <v>249</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H155" s="7" t="n">
         <v>1</v>
@@ -11003,7 +11007,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
@@ -11021,7 +11025,7 @@
         <v>249</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H156" s="7" t="n">
         <v>1</v>
@@ -11030,7 +11034,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
@@ -11048,7 +11052,7 @@
         <v>249</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H157" s="7" t="n">
         <v>1</v>
@@ -11057,7 +11061,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
@@ -11075,7 +11079,7 @@
         <v>249</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>801</v>
+        <v>612</v>
       </c>
       <c r="H158" s="7" t="n">
         <v>1</v>
@@ -11084,7 +11088,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
@@ -11102,7 +11106,7 @@
         <v>249</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H159" s="7" t="n">
         <v>1</v>
@@ -11111,7 +11115,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
@@ -11129,7 +11133,7 @@
         <v>249</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H160" s="7" t="n">
         <v>1</v>
@@ -11138,7 +11142,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
@@ -11156,7 +11160,7 @@
         <v>249</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H161" s="7" t="n">
         <v>1</v>
@@ -11165,7 +11169,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
@@ -11183,7 +11187,7 @@
         <v>249</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H162" s="7" t="n">
         <v>1</v>
@@ -11192,7 +11196,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
@@ -11210,7 +11214,7 @@
         <v>249</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H163" s="7" t="n">
         <v>1</v>
@@ -11219,7 +11223,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
@@ -11237,7 +11241,7 @@
         <v>249</v>
       </c>
       <c r="G164" s="7" t="n">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H164" s="7" t="n">
         <v>1</v>
@@ -11246,7 +11250,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
@@ -11264,7 +11268,7 @@
         <v>249</v>
       </c>
       <c r="G165" s="7" t="n">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H165" s="7" t="n">
         <v>1</v>
@@ -11273,7 +11277,7 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
@@ -11291,7 +11295,7 @@
         <v>249</v>
       </c>
       <c r="G166" s="7" t="n">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H166" s="7" t="n">
         <v>1</v>
@@ -11300,7 +11304,7 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>75</v>
@@ -11318,7 +11322,7 @@
         <v>249</v>
       </c>
       <c r="G167" s="7" t="n">
-        <v>901</v>
+        <v>809</v>
       </c>
       <c r="H167" s="7" t="n">
         <v>1</v>
@@ -11327,7 +11331,7 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>75</v>
@@ -11345,7 +11349,7 @@
         <v>249</v>
       </c>
       <c r="G168" s="7" t="n">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H168" s="7" t="n">
         <v>1</v>
@@ -11354,7 +11358,7 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>75</v>
@@ -11372,7 +11376,7 @@
         <v>249</v>
       </c>
       <c r="G169" s="7" t="n">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H169" s="7" t="n">
         <v>1</v>
@@ -11381,7 +11385,7 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>75</v>
@@ -11399,104 +11403,102 @@
         <v>249</v>
       </c>
       <c r="G170" s="7" t="n">
+        <v>903</v>
+      </c>
+      <c r="H170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="7"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F171" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G171" s="7" t="n">
         <v>904</v>
       </c>
-      <c r="H170" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I170" s="7"/>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="3" t="s">
+      <c r="H171" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" s="7"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B172" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C171" s="4" t="s">
+      <c r="C172" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D171" s="3" t="s">
+      <c r="D172" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E171" s="4" t="s">
+      <c r="E172" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F171" s="3" t="s">
+      <c r="F172" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G171" s="4" t="s">
+      <c r="G172" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H171" s="4" t="s">
+      <c r="H172" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I171" s="3" t="s">
+      <c r="I172" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="3"/>
-      <c r="B172" s="4" t="s">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="3"/>
+      <c r="B173" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C172" s="4" t="s">
+      <c r="C173" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D172" s="3"/>
-      <c r="E172" s="4" t="s">
+      <c r="D173" s="3"/>
+      <c r="E173" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F172" s="3"/>
-      <c r="G172" s="4" t="s">
+      <c r="F173" s="3"/>
+      <c r="G173" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H172" s="4" t="s">
+      <c r="H173" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I172" s="3"/>
-    </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B173" s="5"/>
-      <c r="C173" s="5"/>
-      <c r="D173" s="5"/>
-      <c r="E173" s="5"/>
-      <c r="F173" s="5"/>
-      <c r="G173" s="5"/>
-      <c r="H173" s="5"/>
-      <c r="I173" s="5"/>
-    </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="B174" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C174" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D174" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E174" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F174" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="G174" s="12" t="n">
-        <v>20001</v>
-      </c>
-      <c r="H174" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I174" s="12" t="s">
+      <c r="I173" s="3"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A174" s="5" t="s">
         <v>320</v>
       </c>
+      <c r="B174" s="5"/>
+      <c r="C174" s="5"/>
+      <c r="D174" s="5"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="5"/>
+      <c r="G174" s="5"/>
+      <c r="H174" s="5"/>
+      <c r="I174" s="5"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="12" t="s">
@@ -11515,79 +11517,79 @@
         <v>75</v>
       </c>
       <c r="F175" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>20002</v>
+        <v>20001</v>
       </c>
       <c r="H175" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I175" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E176" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F176" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="B176" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C176" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E176" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F176" s="12" t="s">
-        <v>319</v>
-      </c>
       <c r="G176" s="12" t="n">
-        <v>20003</v>
+        <v>20002</v>
       </c>
       <c r="H176" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I176" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E177" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>20003</v>
+      </c>
+      <c r="H177" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I177" s="12" t="s">
         <v>323</v>
-      </c>
-      <c r="B177" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C177" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D177" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E177" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F177" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="G177" s="12" t="n">
-        <v>20004</v>
-      </c>
-      <c r="H177" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I177" s="12" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B178" s="12" t="s">
         <v>75</v>
@@ -11602,21 +11604,21 @@
         <v>75</v>
       </c>
       <c r="F178" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>20005</v>
+        <v>20004</v>
       </c>
       <c r="H178" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I178" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B179" s="12" t="s">
         <v>75</v>
@@ -11631,21 +11633,21 @@
         <v>75</v>
       </c>
       <c r="F179" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>20006</v>
+        <v>20005</v>
       </c>
       <c r="H179" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I179" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="12" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B180" s="12" t="s">
         <v>75</v>
@@ -11660,21 +11662,21 @@
         <v>75</v>
       </c>
       <c r="F180" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>20007</v>
+        <v>20006</v>
       </c>
       <c r="H180" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I180" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="12" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B181" s="12" t="s">
         <v>75</v>
@@ -11689,21 +11691,21 @@
         <v>75</v>
       </c>
       <c r="F181" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>20008</v>
+        <v>20007</v>
       </c>
       <c r="H181" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I181" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="12" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B182" s="12" t="s">
         <v>75</v>
@@ -11718,21 +11720,21 @@
         <v>75</v>
       </c>
       <c r="F182" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>30001</v>
+        <v>20008</v>
       </c>
       <c r="H182" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I182" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B183" s="12" t="s">
         <v>75</v>
@@ -11747,21 +11749,21 @@
         <v>75</v>
       </c>
       <c r="F183" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="H183" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I183" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="12" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B184" s="12" t="s">
         <v>75</v>
@@ -11776,21 +11778,21 @@
         <v>75</v>
       </c>
       <c r="F184" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="H184" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I184" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B185" s="12" t="s">
         <v>75</v>
@@ -11805,21 +11807,21 @@
         <v>75</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="H185" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I185" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B186" s="12" t="s">
         <v>75</v>
@@ -11834,21 +11836,21 @@
         <v>75</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>30005</v>
+        <v>30004</v>
       </c>
       <c r="H186" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I186" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B187" s="12" t="s">
         <v>75</v>
@@ -11863,21 +11865,21 @@
         <v>75</v>
       </c>
       <c r="F187" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>30006</v>
+        <v>30005</v>
       </c>
       <c r="H187" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I187" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>75</v>
@@ -11892,21 +11894,21 @@
         <v>75</v>
       </c>
       <c r="F188" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>40001</v>
+        <v>30006</v>
       </c>
       <c r="H188" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>75</v>
@@ -11921,21 +11923,21 @@
         <v>75</v>
       </c>
       <c r="F189" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>60001</v>
+        <v>40001</v>
       </c>
       <c r="H189" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>75</v>
@@ -11950,21 +11952,21 @@
         <v>75</v>
       </c>
       <c r="F190" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="H190" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>75</v>
@@ -11979,21 +11981,21 @@
         <v>75</v>
       </c>
       <c r="F191" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>60003</v>
+        <v>60002</v>
       </c>
       <c r="H191" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>75</v>
@@ -12008,21 +12010,21 @@
         <v>75</v>
       </c>
       <c r="F192" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>60004</v>
+        <v>60003</v>
       </c>
       <c r="H192" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B193" s="12" t="s">
         <v>75</v>
@@ -12037,21 +12039,21 @@
         <v>75</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>60005</v>
+        <v>60004</v>
       </c>
       <c r="H193" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>75</v>
@@ -12066,21 +12068,21 @@
         <v>75</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>60006</v>
+        <v>60005</v>
       </c>
       <c r="H194" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>75</v>
@@ -12095,21 +12097,21 @@
         <v>75</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>60007</v>
+        <v>60006</v>
       </c>
       <c r="H195" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>75</v>
@@ -12124,113 +12126,113 @@
         <v>75</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G196" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H196" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" s="12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D197" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E197" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F197" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="G197" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H196" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I196" s="12" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="3" t="s">
+      <c r="H197" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A198" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B198" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C197" s="4" t="s">
+      <c r="C198" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D197" s="3" t="s">
+      <c r="D198" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E197" s="4" t="s">
+      <c r="E198" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F197" s="3" t="s">
+      <c r="F198" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G197" s="4" t="s">
+      <c r="G198" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H197" s="4" t="s">
+      <c r="H198" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I197" s="3" t="s">
+      <c r="I198" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="3"/>
-      <c r="B198" s="4" t="s">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="3"/>
+      <c r="B199" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C198" s="4" t="s">
+      <c r="C199" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D198" s="3"/>
-      <c r="E198" s="4" t="s">
+      <c r="D199" s="3"/>
+      <c r="E199" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F198" s="3"/>
-      <c r="G198" s="4" t="s">
+      <c r="F199" s="3"/>
+      <c r="G199" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H198" s="4" t="s">
+      <c r="H199" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I198" s="3"/>
-    </row>
-    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B199" s="5"/>
-      <c r="C199" s="5"/>
-      <c r="D199" s="5"/>
-      <c r="E199" s="5"/>
-      <c r="F199" s="5"/>
-      <c r="G199" s="5"/>
-      <c r="H199" s="5"/>
-      <c r="I199" s="5"/>
-    </row>
-    <row r="200" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="B200" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C200" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D200" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E200" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F200" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="G200" s="12" t="n">
-        <v>30001</v>
-      </c>
-      <c r="H200" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I200" s="12" t="s">
-        <v>344</v>
-      </c>
+      <c r="I199" s="3"/>
+    </row>
+    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A200" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B200" s="5"/>
+      <c r="C200" s="5"/>
+      <c r="D200" s="5"/>
+      <c r="E200" s="5"/>
+      <c r="F200" s="5"/>
+      <c r="G200" s="5"/>
+      <c r="H200" s="5"/>
+      <c r="I200" s="5"/>
     </row>
     <row r="201" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>75</v>
@@ -12245,21 +12247,21 @@
         <v>75</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="H201" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="12" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>75</v>
@@ -12274,21 +12276,21 @@
         <v>75</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="H202" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>75</v>
@@ -12303,21 +12305,21 @@
         <v>75</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="H203" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>75</v>
@@ -12332,21 +12334,21 @@
         <v>75</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>30005</v>
+        <v>30004</v>
       </c>
       <c r="H204" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>75</v>
@@ -12361,79 +12363,79 @@
         <v>75</v>
       </c>
       <c r="F205" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G205" s="12" t="n">
+        <v>30005</v>
+      </c>
+      <c r="H205" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B206" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D206" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E206" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F206" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="G206" s="12" t="n">
         <v>30006</v>
       </c>
-      <c r="H205" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I205" s="12" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="B206" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C206" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D206" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E206" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F206" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="G206" s="12" t="n">
+      <c r="H206" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D207" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E207" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F207" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="G207" s="12" t="n">
         <v>40001</v>
       </c>
-      <c r="H206" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I206" s="12" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="B207" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C207" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D207" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E207" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F207" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="G207" s="12" t="n">
-        <v>45001</v>
-      </c>
       <c r="H207" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>75</v>
@@ -12448,21 +12450,21 @@
         <v>75</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>60001</v>
+        <v>45001</v>
       </c>
       <c r="H208" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>75</v>
@@ -12477,21 +12479,21 @@
         <v>75</v>
       </c>
       <c r="F209" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="H209" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>75</v>
@@ -12506,21 +12508,21 @@
         <v>75</v>
       </c>
       <c r="F210" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G210" s="12" t="n">
-        <v>60003</v>
+        <v>60002</v>
       </c>
       <c r="H210" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>75</v>
@@ -12535,21 +12537,21 @@
         <v>75</v>
       </c>
       <c r="F211" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G211" s="12" t="n">
-        <v>60004</v>
+        <v>60003</v>
       </c>
       <c r="H211" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I211" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B212" s="12" t="s">
         <v>75</v>
@@ -12564,21 +12566,21 @@
         <v>75</v>
       </c>
       <c r="F212" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G212" s="12" t="n">
-        <v>60005</v>
+        <v>60004</v>
       </c>
       <c r="H212" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B213" s="12" t="s">
         <v>75</v>
@@ -12593,21 +12595,21 @@
         <v>75</v>
       </c>
       <c r="F213" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G213" s="12" t="n">
-        <v>60006</v>
+        <v>60005</v>
       </c>
       <c r="H213" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I213" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B214" s="12" t="s">
         <v>75</v>
@@ -12622,21 +12624,21 @@
         <v>75</v>
       </c>
       <c r="F214" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G214" s="12" t="n">
-        <v>60007</v>
+        <v>60006</v>
       </c>
       <c r="H214" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I214" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B215" s="12" t="s">
         <v>75</v>
@@ -12651,113 +12653,113 @@
         <v>75</v>
       </c>
       <c r="F215" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G215" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H215" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B216" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E216" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F216" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="G216" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H215" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I215" s="12" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A216" s="3" t="s">
+      <c r="H216" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A217" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B216" s="4" t="s">
+      <c r="B217" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C216" s="4" t="s">
+      <c r="C217" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D216" s="3" t="s">
+      <c r="D217" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E216" s="4" t="s">
+      <c r="E217" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F216" s="3" t="s">
+      <c r="F217" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G216" s="4" t="s">
+      <c r="G217" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H216" s="4" t="s">
+      <c r="H217" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I216" s="3" t="s">
+      <c r="I217" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="3"/>
-      <c r="B217" s="4" t="s">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="3"/>
+      <c r="B218" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C217" s="4" t="s">
+      <c r="C218" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D217" s="3"/>
-      <c r="E217" s="4" t="s">
+      <c r="D218" s="3"/>
+      <c r="E218" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F217" s="3"/>
-      <c r="G217" s="4" t="s">
+      <c r="F218" s="3"/>
+      <c r="G218" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H217" s="4" t="s">
+      <c r="H218" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I217" s="3"/>
-    </row>
-    <row r="218" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A218" s="5" t="s">
+      <c r="I218" s="3"/>
+    </row>
+    <row r="219" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A219" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B218" s="5"/>
-      <c r="C218" s="5"/>
-      <c r="D218" s="5"/>
-      <c r="E218" s="5"/>
-      <c r="F218" s="5"/>
-      <c r="G218" s="5"/>
-      <c r="H218" s="5"/>
-      <c r="I218" s="5"/>
-    </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B219" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C219" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D219" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E219" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F219" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G219" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="H219" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I219" s="7" t="s">
-        <v>112</v>
-      </c>
+      <c r="B219" s="5"/>
+      <c r="C219" s="5"/>
+      <c r="D219" s="5"/>
+      <c r="E219" s="5"/>
+      <c r="F219" s="5"/>
+      <c r="G219" s="5"/>
+      <c r="H219" s="5"/>
+      <c r="I219" s="5"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="9" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="B220" s="7" t="s">
         <v>109</v>
@@ -12775,21 +12777,21 @@
         <v>26</v>
       </c>
       <c r="G220" s="10" t="s">
-        <v>188</v>
+        <v>303</v>
       </c>
       <c r="H220" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I220" s="7" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="9" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C221" s="7" t="s">
         <v>110</v>
@@ -12804,16 +12806,18 @@
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="H221" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I221" s="7"/>
+      <c r="I221" s="7" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>24</v>
@@ -12831,7 +12835,7 @@
         <v>26</v>
       </c>
       <c r="G222" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H222" s="7" t="n">
         <v>2</v>
@@ -12840,7 +12844,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B223" s="7" t="s">
         <v>24</v>
@@ -12858,7 +12862,7 @@
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H223" s="7" t="n">
         <v>2</v>
@@ -12867,7 +12871,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B224" s="7" t="s">
         <v>24</v>
@@ -12885,7 +12889,7 @@
         <v>26</v>
       </c>
       <c r="G224" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H224" s="7" t="n">
         <v>2</v>
@@ -12894,10 +12898,10 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C225" s="7" t="s">
         <v>110</v>
@@ -12912,7 +12916,7 @@
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H225" s="7" t="n">
         <v>2</v>
@@ -12921,7 +12925,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B226" s="7" t="s">
         <v>109</v>
@@ -12939,7 +12943,7 @@
         <v>26</v>
       </c>
       <c r="G226" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H226" s="7" t="n">
         <v>2</v>
@@ -12948,10 +12952,10 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C227" s="7" t="s">
         <v>110</v>
@@ -12966,7 +12970,7 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H227" s="7" t="n">
         <v>2</v>
@@ -12975,7 +12979,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B228" s="7" t="s">
         <v>24</v>
@@ -12993,7 +12997,7 @@
         <v>26</v>
       </c>
       <c r="G228" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H228" s="7" t="n">
         <v>2</v>
@@ -13002,7 +13006,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B229" s="7" t="s">
         <v>24</v>
@@ -13020,7 +13024,7 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H229" s="7" t="n">
         <v>2</v>
@@ -13029,7 +13033,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B230" s="7" t="s">
         <v>24</v>
@@ -13047,7 +13051,7 @@
         <v>26</v>
       </c>
       <c r="G230" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H230" s="7" t="n">
         <v>2</v>
@@ -13056,10 +13060,10 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C231" s="7" t="s">
         <v>110</v>
@@ -13074,7 +13078,7 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H231" s="7" t="n">
         <v>2</v>
@@ -13083,7 +13087,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B232" s="7" t="s">
         <v>109</v>
@@ -13101,7 +13105,7 @@
         <v>26</v>
       </c>
       <c r="G232" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H232" s="7" t="n">
         <v>2</v>
@@ -13110,10 +13114,10 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>222</v>
+        <v>109</v>
       </c>
       <c r="C233" s="7" t="s">
         <v>110</v>
@@ -13128,7 +13132,7 @@
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H233" s="7" t="n">
         <v>2</v>
@@ -13137,7 +13141,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B234" s="7" t="s">
         <v>222</v>
@@ -13155,7 +13159,7 @@
         <v>26</v>
       </c>
       <c r="G234" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H234" s="7" t="n">
         <v>2</v>
@@ -13164,10 +13168,10 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C235" s="7" t="s">
         <v>110</v>
@@ -13182,7 +13186,7 @@
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H235" s="7" t="n">
         <v>2</v>
@@ -13191,7 +13195,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B236" s="7" t="s">
         <v>195</v>
@@ -13209,7 +13213,7 @@
         <v>26</v>
       </c>
       <c r="G236" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H236" s="7" t="n">
         <v>2</v>
@@ -13218,10 +13222,10 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="C237" s="7" t="s">
         <v>110</v>
@@ -13236,7 +13240,7 @@
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H237" s="7" t="n">
         <v>2</v>
@@ -13245,7 +13249,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B238" s="7" t="s">
         <v>109</v>
@@ -13263,7 +13267,7 @@
         <v>26</v>
       </c>
       <c r="G238" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H238" s="7" t="n">
         <v>2</v>
@@ -13271,11 +13275,11 @@
       <c r="I238" s="7"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="7" t="s">
-        <v>304</v>
+      <c r="A239" s="9" t="s">
+        <v>232</v>
       </c>
       <c r="B239" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C239" s="7" t="s">
         <v>110</v>
@@ -13290,18 +13294,16 @@
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H239" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I239" s="7" t="s">
-        <v>236</v>
-      </c>
+      <c r="I239" s="7"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="7" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="B240" s="7" t="s">
         <v>75</v>
@@ -13319,47 +13321,47 @@
         <v>26</v>
       </c>
       <c r="G240" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H240" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I240" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B241" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C241" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D241" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E241" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G241" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="H240" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I240" s="7" t="s">
+      <c r="H241" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I241" s="7" t="s">
         <v>239</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="B241" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C241" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D241" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E241" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F241" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G241" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="H241" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I241" s="12" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B242" s="12" t="s">
         <v>75</v>
@@ -13377,18 +13379,18 @@
         <v>26</v>
       </c>
       <c r="G242" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H242" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I242" s="12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="45.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="11" t="s">
-        <v>308</v>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="12" t="s">
+        <v>242</v>
       </c>
       <c r="B243" s="12" t="s">
         <v>75</v>
@@ -13405,19 +13407,19 @@
       <c r="F243" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G243" s="13" t="s">
-        <v>309</v>
+      <c r="G243" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="H243" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I243" s="12" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="244" customFormat="false" ht="36.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="45.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B244" s="12" t="s">
         <v>75</v>
@@ -13435,18 +13437,18 @@
         <v>26</v>
       </c>
       <c r="G244" s="13" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H244" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I244" s="12" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="245" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="36.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="11" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
       <c r="B245" s="12" t="s">
         <v>75</v>
@@ -13464,16 +13466,73 @@
         <v>26</v>
       </c>
       <c r="G245" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="H245" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I245" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="B246" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C246" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D246" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E246" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F246" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G246" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="H245" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I245" s="12" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="H246" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I246" s="12" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="28.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C247" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D247" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E247" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F247" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G247" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="H247" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I247" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
     <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -13500,26 +13559,26 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="D115:D116"/>
-    <mergeCell ref="F115:F116"/>
-    <mergeCell ref="I115:I116"/>
-    <mergeCell ref="A117:I117"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="D171:D172"/>
-    <mergeCell ref="F171:F172"/>
-    <mergeCell ref="I171:I172"/>
-    <mergeCell ref="A173:I173"/>
-    <mergeCell ref="A197:A198"/>
-    <mergeCell ref="D197:D198"/>
-    <mergeCell ref="F197:F198"/>
-    <mergeCell ref="I197:I198"/>
-    <mergeCell ref="A199:I199"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="D216:D217"/>
-    <mergeCell ref="F216:F217"/>
-    <mergeCell ref="I216:I217"/>
-    <mergeCell ref="A218:I218"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="F116:F117"/>
+    <mergeCell ref="I116:I117"/>
+    <mergeCell ref="A118:I118"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="D172:D173"/>
+    <mergeCell ref="F172:F173"/>
+    <mergeCell ref="I172:I173"/>
+    <mergeCell ref="A174:I174"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="D198:D199"/>
+    <mergeCell ref="F198:F199"/>
+    <mergeCell ref="I198:I199"/>
+    <mergeCell ref="A200:I200"/>
+    <mergeCell ref="A217:A218"/>
+    <mergeCell ref="D217:D218"/>
+    <mergeCell ref="F217:F218"/>
+    <mergeCell ref="I217:I218"/>
+    <mergeCell ref="A219:I219"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13539,15 +13598,15 @@
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="40.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13555,7 +13614,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13563,7 +13622,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13584,436 +13643,436 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16" t="s">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16" t="s">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="16"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
+      <c r="A9" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>357</v>
-      </c>
-      <c r="B10" s="18" t="s">
+      <c r="A10" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>359</v>
+      <c r="C10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="B11" s="18" t="s">
+      <c r="A11" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>362</v>
+      <c r="C11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>365</v>
+      <c r="C12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="18" t="s">
+      <c r="A13" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>368</v>
+      <c r="D13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="18" t="s">
+      <c r="A14" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>370</v>
+      <c r="D14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="18" t="s">
+      <c r="A15" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>370</v>
+      <c r="D15" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>322</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="18" t="s">
+      <c r="A16" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>370</v>
+      <c r="D16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="18" t="s">
+      <c r="A17" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="18" t="s">
+      <c r="D17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="H17" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>374</v>
-      </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
+      <c r="A20" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
+      <c r="A21" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
+      <c r="A22" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
+      <c r="A23" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
+      <c r="A24" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
+      <c r="A25" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
+      <c r="A26" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>381</v>
-      </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
+      <c r="A27" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>382</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
+      <c r="A28" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
+      <c r="A29" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2450" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2498" uniqueCount="397">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -937,6 +937,15 @@
   </si>
   <si>
     <t xml:space="preserve">DG Detection Enable/Disable Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firmware Upgrade Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: No Firmware Upgrade Ongoing/Firmware Upgrade completed, 1:Firmware Uploading Ongoing, 2: Firmware Updating Ongoing, 127: Error Occured</t>
   </si>
   <si>
     <t xml:space="preserve">Switch Pressed</t>
@@ -1003,6 +1012,24 @@
 Used to store a temporarily value. Resets when SOCO restarts on POR.</t>
   </si>
   <si>
+    <t xml:space="preserve">Grid R Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Y Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar R Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar Y Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar B Phase Loss</t>
+  </si>
+  <si>
     <t xml:space="preserve">READ COIL STATUS (Function Code: 0x01)</t>
   </si>
   <si>
@@ -1089,6 +1116,9 @@
   </si>
   <si>
     <t xml:space="preserve">Restart Controller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: No Action, 1:Signals start of Firmware Uploading, 2: Signals end of Firmware Uploading</t>
   </si>
   <si>
     <t xml:space="preserve">Internal Only. Not visible to customer. 
@@ -9717,65 +9747,67 @@
         <v>239</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="86.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="11" t="s">
+    <row r="108" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B108" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C108" s="12" t="s">
+      <c r="B108" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C108" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D108" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E108" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" s="13" t="s">
+      <c r="D108" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="H108" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I108" s="12" t="s">
+      <c r="H108" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" s="7" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C109" s="7" t="s">
+    <row r="109" customFormat="false" ht="86.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C109" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D109" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E109" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="H109" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I109" s="7"/>
+      <c r="D109" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G109" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" s="12" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>75</v>
@@ -9793,7 +9825,7 @@
         <v>26</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H110" s="7" t="n">
         <v>2</v>
@@ -9802,7 +9834,7 @@
     </row>
     <row r="111" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>75</v>
@@ -9814,47 +9846,45 @@
         <v>4</v>
       </c>
       <c r="E111" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="7"/>
+    </row>
+    <row r="112" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E112" s="7" t="n">
         <v>0.01</v>
       </c>
-      <c r="F111" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G111" s="7" t="s">
+      <c r="F112" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G112" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="H111" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I111" s="7"/>
-    </row>
-    <row r="112" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="B112" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C112" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D112" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E112" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G112" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="H112" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I112" s="12" t="s">
-        <v>310</v>
-      </c>
+      <c r="H112" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" s="7"/>
     </row>
     <row r="113" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="11" t="s">
@@ -9885,7 +9915,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="236.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="11" t="s">
         <v>314</v>
       </c>
@@ -9914,7 +9944,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="36.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="236.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="11" t="s">
         <v>317</v>
       </c>
@@ -9943,99 +9973,101 @@
         <v>319</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="3" t="s">
+    <row r="116" customFormat="false" ht="36.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D116" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G116" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="H116" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B117" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C117" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D117" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="E117" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F117" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="G117" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H116" s="4" t="s">
+      <c r="H117" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I116" s="3" t="s">
+      <c r="I117" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="3"/>
-      <c r="B117" s="4" t="s">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="3"/>
+      <c r="B118" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C118" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D117" s="3"/>
-      <c r="E117" s="4" t="s">
+      <c r="D118" s="3"/>
+      <c r="E118" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="4" t="s">
+      <c r="F118" s="3"/>
+      <c r="G118" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H117" s="4" t="s">
+      <c r="H118" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I117" s="3"/>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="5" t="s">
+      <c r="I118" s="3"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B118" s="5"/>
-      <c r="C118" s="5"/>
-      <c r="D118" s="5"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="5"/>
-      <c r="G118" s="5"/>
-      <c r="H118" s="5"/>
-      <c r="I118" s="5"/>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="G119" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H119" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I119" s="7"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="5"/>
+      <c r="E119" s="5"/>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5"/>
+      <c r="I119" s="5"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>75</v>
@@ -10053,7 +10085,7 @@
         <v>249</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H120" s="7" t="n">
         <v>1</v>
@@ -10062,7 +10094,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>75</v>
@@ -10080,7 +10112,7 @@
         <v>249</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H121" s="7" t="n">
         <v>1</v>
@@ -10089,7 +10121,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>75</v>
@@ -10107,7 +10139,7 @@
         <v>249</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H122" s="7" t="n">
         <v>1</v>
@@ -10116,7 +10148,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>75</v>
@@ -10134,7 +10166,7 @@
         <v>249</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H123" s="7" t="n">
         <v>1</v>
@@ -10143,7 +10175,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>75</v>
@@ -10161,7 +10193,7 @@
         <v>249</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H124" s="7" t="n">
         <v>1</v>
@@ -10170,7 +10202,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>75</v>
@@ -10188,7 +10220,7 @@
         <v>249</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H125" s="7" t="n">
         <v>1</v>
@@ -10197,7 +10229,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>75</v>
@@ -10215,7 +10247,7 @@
         <v>249</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H126" s="7" t="n">
         <v>1</v>
@@ -10224,7 +10256,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>75</v>
@@ -10242,7 +10274,7 @@
         <v>249</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>201</v>
+        <v>8</v>
       </c>
       <c r="H127" s="7" t="n">
         <v>1</v>
@@ -10251,7 +10283,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>75</v>
@@ -10269,7 +10301,7 @@
         <v>249</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H128" s="7" t="n">
         <v>1</v>
@@ -10278,7 +10310,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>75</v>
@@ -10296,7 +10328,7 @@
         <v>249</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="H129" s="7" t="n">
         <v>1</v>
@@ -10305,7 +10337,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>75</v>
@@ -10323,7 +10355,7 @@
         <v>249</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H130" s="7" t="n">
         <v>1</v>
@@ -10332,7 +10364,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>75</v>
@@ -10350,7 +10382,7 @@
         <v>249</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H131" s="7" t="n">
         <v>1</v>
@@ -10359,7 +10391,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>75</v>
@@ -10377,7 +10409,7 @@
         <v>249</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H132" s="7" t="n">
         <v>1</v>
@@ -10386,7 +10418,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>75</v>
@@ -10404,7 +10436,7 @@
         <v>249</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H133" s="7" t="n">
         <v>1</v>
@@ -10413,7 +10445,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>75</v>
@@ -10431,7 +10463,7 @@
         <v>249</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H134" s="7" t="n">
         <v>1</v>
@@ -10440,7 +10472,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>75</v>
@@ -10458,7 +10490,7 @@
         <v>249</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H135" s="7" t="n">
         <v>1</v>
@@ -10467,7 +10499,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>75</v>
@@ -10485,7 +10517,7 @@
         <v>249</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H136" s="7" t="n">
         <v>1</v>
@@ -10494,7 +10526,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>75</v>
@@ -10512,7 +10544,7 @@
         <v>249</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H137" s="7" t="n">
         <v>1</v>
@@ -10521,7 +10553,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>75</v>
@@ -10539,7 +10571,7 @@
         <v>249</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H138" s="7" t="n">
         <v>1</v>
@@ -10548,7 +10580,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>75</v>
@@ -10566,7 +10598,7 @@
         <v>249</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H139" s="7" t="n">
         <v>1</v>
@@ -10575,7 +10607,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>75</v>
@@ -10593,7 +10625,7 @@
         <v>249</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H140" s="7" t="n">
         <v>1</v>
@@ -10602,7 +10634,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>75</v>
@@ -10620,7 +10652,7 @@
         <v>249</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>401</v>
+        <v>312</v>
       </c>
       <c r="H141" s="7" t="n">
         <v>1</v>
@@ -10629,7 +10661,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>272</v>
+        <v>323</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>75</v>
@@ -10647,7 +10679,7 @@
         <v>249</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>402</v>
+        <v>313</v>
       </c>
       <c r="H142" s="7" t="n">
         <v>1</v>
@@ -10656,7 +10688,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>273</v>
+        <v>324</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>75</v>
@@ -10674,7 +10706,7 @@
         <v>249</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>403</v>
+        <v>314</v>
       </c>
       <c r="H143" s="7" t="n">
         <v>1</v>
@@ -10683,7 +10715,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
@@ -10701,7 +10733,7 @@
         <v>249</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>404</v>
+        <v>315</v>
       </c>
       <c r="H144" s="7" t="n">
         <v>1</v>
@@ -10710,7 +10742,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
@@ -10728,7 +10760,7 @@
         <v>249</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>405</v>
+        <v>316</v>
       </c>
       <c r="H145" s="7" t="n">
         <v>1</v>
@@ -10737,7 +10769,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
@@ -10755,7 +10787,7 @@
         <v>249</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>406</v>
+        <v>317</v>
       </c>
       <c r="H146" s="7" t="n">
         <v>1</v>
@@ -10764,7 +10796,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>277</v>
+        <v>328</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
@@ -10782,7 +10814,7 @@
         <v>249</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>601</v>
+        <v>318</v>
       </c>
       <c r="H147" s="7" t="n">
         <v>1</v>
@@ -10791,7 +10823,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
@@ -10809,7 +10841,7 @@
         <v>249</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>602</v>
+        <v>401</v>
       </c>
       <c r="H148" s="7" t="n">
         <v>1</v>
@@ -10818,7 +10850,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
@@ -10836,7 +10868,7 @@
         <v>249</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>603</v>
+        <v>402</v>
       </c>
       <c r="H149" s="7" t="n">
         <v>1</v>
@@ -10845,7 +10877,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
@@ -10863,7 +10895,7 @@
         <v>249</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>604</v>
+        <v>403</v>
       </c>
       <c r="H150" s="7" t="n">
         <v>1</v>
@@ -10872,7 +10904,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
@@ -10890,7 +10922,7 @@
         <v>249</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>605</v>
+        <v>404</v>
       </c>
       <c r="H151" s="7" t="n">
         <v>1</v>
@@ -10899,7 +10931,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
@@ -10917,7 +10949,7 @@
         <v>249</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>606</v>
+        <v>405</v>
       </c>
       <c r="H152" s="7" t="n">
         <v>1</v>
@@ -10926,7 +10958,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
@@ -10944,7 +10976,7 @@
         <v>249</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>607</v>
+        <v>406</v>
       </c>
       <c r="H153" s="7" t="n">
         <v>1</v>
@@ -10953,7 +10985,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
@@ -10971,7 +11003,7 @@
         <v>249</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="H154" s="7" t="n">
         <v>1</v>
@@ -10980,7 +11012,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
@@ -10998,7 +11030,7 @@
         <v>249</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="H155" s="7" t="n">
         <v>1</v>
@@ -11007,7 +11039,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
@@ -11025,7 +11057,7 @@
         <v>249</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="H156" s="7" t="n">
         <v>1</v>
@@ -11034,7 +11066,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
@@ -11052,7 +11084,7 @@
         <v>249</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="H157" s="7" t="n">
         <v>1</v>
@@ -11061,7 +11093,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
@@ -11079,7 +11111,7 @@
         <v>249</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="H158" s="7" t="n">
         <v>1</v>
@@ -11088,7 +11120,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
@@ -11106,7 +11138,7 @@
         <v>249</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>801</v>
+        <v>606</v>
       </c>
       <c r="H159" s="7" t="n">
         <v>1</v>
@@ -11115,7 +11147,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
@@ -11133,7 +11165,7 @@
         <v>249</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>802</v>
+        <v>607</v>
       </c>
       <c r="H160" s="7" t="n">
         <v>1</v>
@@ -11142,7 +11174,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
@@ -11160,7 +11192,7 @@
         <v>249</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>803</v>
+        <v>608</v>
       </c>
       <c r="H161" s="7" t="n">
         <v>1</v>
@@ -11169,7 +11201,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
@@ -11187,7 +11219,7 @@
         <v>249</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>804</v>
+        <v>609</v>
       </c>
       <c r="H162" s="7" t="n">
         <v>1</v>
@@ -11196,7 +11228,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
@@ -11214,7 +11246,7 @@
         <v>249</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>805</v>
+        <v>610</v>
       </c>
       <c r="H163" s="7" t="n">
         <v>1</v>
@@ -11223,7 +11255,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
@@ -11241,7 +11273,7 @@
         <v>249</v>
       </c>
       <c r="G164" s="7" t="n">
-        <v>806</v>
+        <v>611</v>
       </c>
       <c r="H164" s="7" t="n">
         <v>1</v>
@@ -11250,7 +11282,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
@@ -11268,7 +11300,7 @@
         <v>249</v>
       </c>
       <c r="G165" s="7" t="n">
-        <v>807</v>
+        <v>612</v>
       </c>
       <c r="H165" s="7" t="n">
         <v>1</v>
@@ -11277,7 +11309,7 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
@@ -11295,7 +11327,7 @@
         <v>249</v>
       </c>
       <c r="G166" s="7" t="n">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="H166" s="7" t="n">
         <v>1</v>
@@ -11304,7 +11336,7 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>75</v>
@@ -11322,7 +11354,7 @@
         <v>249</v>
       </c>
       <c r="G167" s="7" t="n">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="H167" s="7" t="n">
         <v>1</v>
@@ -11331,7 +11363,7 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>75</v>
@@ -11349,7 +11381,7 @@
         <v>249</v>
       </c>
       <c r="G168" s="7" t="n">
-        <v>901</v>
+        <v>803</v>
       </c>
       <c r="H168" s="7" t="n">
         <v>1</v>
@@ -11358,7 +11390,7 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>75</v>
@@ -11376,7 +11408,7 @@
         <v>249</v>
       </c>
       <c r="G169" s="7" t="n">
-        <v>902</v>
+        <v>804</v>
       </c>
       <c r="H169" s="7" t="n">
         <v>1</v>
@@ -11385,7 +11417,7 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>75</v>
@@ -11403,7 +11435,7 @@
         <v>249</v>
       </c>
       <c r="G170" s="7" t="n">
-        <v>903</v>
+        <v>805</v>
       </c>
       <c r="H170" s="7" t="n">
         <v>1</v>
@@ -11412,7 +11444,7 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>75</v>
@@ -11430,278 +11462,264 @@
         <v>249</v>
       </c>
       <c r="G171" s="7" t="n">
+        <v>806</v>
+      </c>
+      <c r="H171" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" s="7"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G172" s="7" t="n">
+        <v>807</v>
+      </c>
+      <c r="H172" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I172" s="7"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G173" s="7" t="n">
+        <v>808</v>
+      </c>
+      <c r="H173" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" s="7"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G174" s="7" t="n">
+        <v>809</v>
+      </c>
+      <c r="H174" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" s="7"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G175" s="7" t="n">
+        <v>901</v>
+      </c>
+      <c r="H175" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" s="7"/>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G176" s="7" t="n">
+        <v>902</v>
+      </c>
+      <c r="H176" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I176" s="7"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G177" s="7" t="n">
+        <v>903</v>
+      </c>
+      <c r="H177" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I177" s="7"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G178" s="7" t="n">
         <v>904</v>
       </c>
-      <c r="H171" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I171" s="7"/>
-    </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="3" t="s">
+      <c r="H178" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" s="7"/>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A179" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B179" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C172" s="4" t="s">
+      <c r="C179" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D172" s="3" t="s">
+      <c r="D179" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E172" s="4" t="s">
+      <c r="E179" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F172" s="3" t="s">
+      <c r="F179" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G172" s="4" t="s">
+      <c r="G179" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H172" s="4" t="s">
+      <c r="H179" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I172" s="3" t="s">
+      <c r="I179" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="3"/>
-      <c r="B173" s="4" t="s">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="3"/>
+      <c r="B180" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C173" s="4" t="s">
+      <c r="C180" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D173" s="3"/>
-      <c r="E173" s="4" t="s">
+      <c r="D180" s="3"/>
+      <c r="E180" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F173" s="3"/>
-      <c r="G173" s="4" t="s">
+      <c r="F180" s="3"/>
+      <c r="G180" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H173" s="4" t="s">
+      <c r="H180" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I173" s="3"/>
-    </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="B174" s="5"/>
-      <c r="C174" s="5"/>
-      <c r="D174" s="5"/>
-      <c r="E174" s="5"/>
-      <c r="F174" s="5"/>
-      <c r="G174" s="5"/>
-      <c r="H174" s="5"/>
-      <c r="I174" s="5"/>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="B175" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C175" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D175" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E175" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F175" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G175" s="12" t="n">
-        <v>20001</v>
-      </c>
-      <c r="H175" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I175" s="12" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="12" t="s">
-        <v>324</v>
-      </c>
-      <c r="B176" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C176" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E176" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F176" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G176" s="12" t="n">
-        <v>20002</v>
-      </c>
-      <c r="H176" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I176" s="12" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="B177" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C177" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D177" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E177" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F177" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G177" s="12" t="n">
-        <v>20003</v>
-      </c>
-      <c r="H177" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I177" s="12" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="B178" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C178" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D178" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E178" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F178" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G178" s="12" t="n">
-        <v>20004</v>
-      </c>
-      <c r="H178" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I178" s="12" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="B179" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C179" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D179" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E179" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F179" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G179" s="12" t="n">
-        <v>20005</v>
-      </c>
-      <c r="H179" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I179" s="12" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="B180" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C180" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D180" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E180" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F180" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G180" s="12" t="n">
-        <v>20006</v>
-      </c>
-      <c r="H180" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I180" s="12" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="12" t="s">
+      <c r="I180" s="3"/>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A181" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B181" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C181" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D181" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E181" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F181" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G181" s="12" t="n">
-        <v>20007</v>
-      </c>
-      <c r="H181" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I181" s="12" t="s">
-        <v>323</v>
-      </c>
+      <c r="B181" s="5"/>
+      <c r="C181" s="5"/>
+      <c r="D181" s="5"/>
+      <c r="E181" s="5"/>
+      <c r="F181" s="5"/>
+      <c r="G181" s="5"/>
+      <c r="H181" s="5"/>
+      <c r="I181" s="5"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="12" t="s">
@@ -11720,79 +11738,79 @@
         <v>75</v>
       </c>
       <c r="F182" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>20008</v>
+        <v>20001</v>
       </c>
       <c r="H182" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I182" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E183" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F183" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="B183" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C183" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D183" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E183" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F183" s="12" t="s">
-        <v>322</v>
-      </c>
       <c r="G183" s="12" t="n">
-        <v>30001</v>
+        <v>20002</v>
       </c>
       <c r="H183" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I183" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E184" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F184" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>20003</v>
+      </c>
+      <c r="H184" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I184" s="12" t="s">
         <v>332</v>
-      </c>
-      <c r="B184" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C184" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D184" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E184" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F184" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G184" s="12" t="n">
-        <v>30002</v>
-      </c>
-      <c r="H184" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I184" s="12" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B185" s="12" t="s">
         <v>75</v>
@@ -11807,21 +11825,21 @@
         <v>75</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>30003</v>
+        <v>20004</v>
       </c>
       <c r="H185" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I185" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B186" s="12" t="s">
         <v>75</v>
@@ -11836,21 +11854,21 @@
         <v>75</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>30004</v>
+        <v>20005</v>
       </c>
       <c r="H186" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I186" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B187" s="12" t="s">
         <v>75</v>
@@ -11865,21 +11883,21 @@
         <v>75</v>
       </c>
       <c r="F187" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>30005</v>
+        <v>20006</v>
       </c>
       <c r="H187" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I187" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>75</v>
@@ -11894,21 +11912,21 @@
         <v>75</v>
       </c>
       <c r="F188" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>30006</v>
+        <v>20007</v>
       </c>
       <c r="H188" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>75</v>
@@ -11923,21 +11941,21 @@
         <v>75</v>
       </c>
       <c r="F189" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>40001</v>
+        <v>20008</v>
       </c>
       <c r="H189" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>75</v>
@@ -11952,21 +11970,21 @@
         <v>75</v>
       </c>
       <c r="F190" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>60001</v>
+        <v>30001</v>
       </c>
       <c r="H190" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>75</v>
@@ -11981,21 +11999,21 @@
         <v>75</v>
       </c>
       <c r="F191" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>60002</v>
+        <v>30002</v>
       </c>
       <c r="H191" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>75</v>
@@ -12010,21 +12028,21 @@
         <v>75</v>
       </c>
       <c r="F192" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>60003</v>
+        <v>30003</v>
       </c>
       <c r="H192" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B193" s="12" t="s">
         <v>75</v>
@@ -12039,21 +12057,21 @@
         <v>75</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>60004</v>
+        <v>30004</v>
       </c>
       <c r="H193" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>75</v>
@@ -12068,21 +12086,21 @@
         <v>75</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>60005</v>
+        <v>30005</v>
       </c>
       <c r="H194" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>75</v>
@@ -12097,21 +12115,21 @@
         <v>75</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>60006</v>
+        <v>30006</v>
       </c>
       <c r="H195" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>75</v>
@@ -12126,21 +12144,21 @@
         <v>75</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>60007</v>
+        <v>40001</v>
       </c>
       <c r="H196" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>75</v>
@@ -12155,287 +12173,287 @@
         <v>75</v>
       </c>
       <c r="F197" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G197" s="12" t="n">
+        <v>60001</v>
+      </c>
+      <c r="H197" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B198" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D198" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E198" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F198" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G198" s="12" t="n">
+        <v>60002</v>
+      </c>
+      <c r="H198" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I198" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B199" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C199" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D199" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E199" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F199" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G199" s="12" t="n">
+        <v>60003</v>
+      </c>
+      <c r="H199" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I199" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B200" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D200" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E200" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F200" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G200" s="12" t="n">
+        <v>60004</v>
+      </c>
+      <c r="H200" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I200" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C201" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D201" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E201" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F201" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G201" s="12" t="n">
+        <v>60005</v>
+      </c>
+      <c r="H201" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I201" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D202" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E202" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F202" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G202" s="12" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H202" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C203" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D203" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E203" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F203" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G203" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H203" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I203" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D204" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E204" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F204" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G204" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H197" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I197" s="12" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="3" t="s">
+      <c r="H204" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A205" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B205" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C198" s="4" t="s">
+      <c r="C205" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D198" s="3" t="s">
+      <c r="D205" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E198" s="4" t="s">
+      <c r="E205" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F198" s="3" t="s">
+      <c r="F205" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G198" s="4" t="s">
+      <c r="G205" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H198" s="4" t="s">
+      <c r="H205" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I198" s="3" t="s">
+      <c r="I205" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="3"/>
-      <c r="B199" s="4" t="s">
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="3"/>
+      <c r="B206" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C199" s="4" t="s">
+      <c r="C206" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D199" s="3"/>
-      <c r="E199" s="4" t="s">
+      <c r="D206" s="3"/>
+      <c r="E206" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F199" s="3"/>
-      <c r="G199" s="4" t="s">
+      <c r="F206" s="3"/>
+      <c r="G206" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H199" s="4" t="s">
+      <c r="H206" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I199" s="3"/>
-    </row>
-    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="B200" s="5"/>
-      <c r="C200" s="5"/>
-      <c r="D200" s="5"/>
-      <c r="E200" s="5"/>
-      <c r="F200" s="5"/>
-      <c r="G200" s="5"/>
-      <c r="H200" s="5"/>
-      <c r="I200" s="5"/>
-    </row>
-    <row r="201" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="B201" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C201" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D201" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E201" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F201" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G201" s="12" t="n">
-        <v>30001</v>
-      </c>
-      <c r="H201" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I201" s="12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="202" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="B202" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C202" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D202" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E202" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F202" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G202" s="12" t="n">
-        <v>30002</v>
-      </c>
-      <c r="H202" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I202" s="12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="B203" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C203" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D203" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E203" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F203" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G203" s="12" t="n">
-        <v>30003</v>
-      </c>
-      <c r="H203" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I203" s="12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="B204" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C204" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D204" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E204" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F204" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G204" s="12" t="n">
-        <v>30004</v>
-      </c>
-      <c r="H204" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I204" s="12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="B205" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C205" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D205" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E205" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F205" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G205" s="12" t="n">
-        <v>30005</v>
-      </c>
-      <c r="H205" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I205" s="12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="B206" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C206" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D206" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E206" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F206" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G206" s="12" t="n">
-        <v>30006</v>
-      </c>
-      <c r="H206" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I206" s="12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="B207" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C207" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D207" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E207" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F207" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G207" s="12" t="n">
-        <v>40001</v>
-      </c>
-      <c r="H207" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I207" s="12" t="s">
-        <v>323</v>
-      </c>
+      <c r="I206" s="3"/>
+    </row>
+    <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A207" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B207" s="5"/>
+      <c r="C207" s="5"/>
+      <c r="D207" s="5"/>
+      <c r="E207" s="5"/>
+      <c r="F207" s="5"/>
+      <c r="G207" s="5"/>
+      <c r="H207" s="5"/>
+      <c r="I207" s="5"/>
     </row>
     <row r="208" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>75</v>
@@ -12450,21 +12468,21 @@
         <v>75</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>45001</v>
+        <v>30001</v>
       </c>
       <c r="H208" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>75</v>
@@ -12479,21 +12497,21 @@
         <v>75</v>
       </c>
       <c r="F209" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>60001</v>
+        <v>30002</v>
       </c>
       <c r="H209" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="12" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>75</v>
@@ -12508,21 +12526,21 @@
         <v>75</v>
       </c>
       <c r="F210" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G210" s="12" t="n">
-        <v>60002</v>
+        <v>30003</v>
       </c>
       <c r="H210" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="12" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>75</v>
@@ -12537,21 +12555,21 @@
         <v>75</v>
       </c>
       <c r="F211" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G211" s="12" t="n">
-        <v>60003</v>
+        <v>30004</v>
       </c>
       <c r="H211" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I211" s="12" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="12" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B212" s="12" t="s">
         <v>75</v>
@@ -12566,21 +12584,21 @@
         <v>75</v>
       </c>
       <c r="F212" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G212" s="12" t="n">
-        <v>60004</v>
+        <v>30005</v>
       </c>
       <c r="H212" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="12" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B213" s="12" t="s">
         <v>75</v>
@@ -12595,21 +12613,21 @@
         <v>75</v>
       </c>
       <c r="F213" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G213" s="12" t="n">
-        <v>60005</v>
+        <v>30006</v>
       </c>
       <c r="H213" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I213" s="12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="12" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B214" s="12" t="s">
         <v>75</v>
@@ -12624,21 +12642,21 @@
         <v>75</v>
       </c>
       <c r="F214" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G214" s="12" t="n">
-        <v>60006</v>
+        <v>40001</v>
       </c>
       <c r="H214" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I214" s="12" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="12" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B215" s="12" t="s">
         <v>75</v>
@@ -12653,21 +12671,21 @@
         <v>75</v>
       </c>
       <c r="F215" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G215" s="12" t="n">
-        <v>60007</v>
+        <v>45001</v>
       </c>
       <c r="H215" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I215" s="12" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B216" s="12" t="s">
         <v>75</v>
@@ -12682,277 +12700,287 @@
         <v>75</v>
       </c>
       <c r="F216" s="12" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G216" s="12" t="n">
+        <v>60001</v>
+      </c>
+      <c r="H216" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E217" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F217" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G217" s="12" t="n">
+        <v>60002</v>
+      </c>
+      <c r="H217" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B218" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D218" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E218" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F218" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G218" s="12" t="n">
+        <v>60003</v>
+      </c>
+      <c r="H218" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B219" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D219" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E219" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F219" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G219" s="12" t="n">
+        <v>60004</v>
+      </c>
+      <c r="H219" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B220" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D220" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E220" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F220" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G220" s="12" t="n">
+        <v>60005</v>
+      </c>
+      <c r="H220" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I220" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D221" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E221" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F221" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G221" s="12" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H221" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B222" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D222" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E222" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F222" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G222" s="12" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H222" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I222" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E223" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G223" s="12" t="n">
         <v>60008</v>
       </c>
-      <c r="H216" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I216" s="12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="3" t="s">
+      <c r="H223" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A224" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B224" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C217" s="4" t="s">
+      <c r="C224" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D217" s="3" t="s">
+      <c r="D224" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E217" s="4" t="s">
+      <c r="E224" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F217" s="3" t="s">
+      <c r="F224" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G217" s="4" t="s">
+      <c r="G224" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H217" s="4" t="s">
+      <c r="H224" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I217" s="3" t="s">
+      <c r="I224" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="3"/>
-      <c r="B218" s="4" t="s">
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="3"/>
+      <c r="B225" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C218" s="4" t="s">
+      <c r="C225" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D218" s="3"/>
-      <c r="E218" s="4" t="s">
+      <c r="D225" s="3"/>
+      <c r="E225" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F218" s="3"/>
-      <c r="G218" s="4" t="s">
+      <c r="F225" s="3"/>
+      <c r="G225" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H218" s="4" t="s">
+      <c r="H225" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I218" s="3"/>
-    </row>
-    <row r="219" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="5" t="s">
+      <c r="I225" s="3"/>
+    </row>
+    <row r="226" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A226" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B219" s="5"/>
-      <c r="C219" s="5"/>
-      <c r="D219" s="5"/>
-      <c r="E219" s="5"/>
-      <c r="F219" s="5"/>
-      <c r="G219" s="5"/>
-      <c r="H219" s="5"/>
-      <c r="I219" s="5"/>
-    </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B220" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C220" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D220" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E220" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F220" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G220" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="H220" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I220" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="B221" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C221" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D221" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E221" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F221" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G221" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H221" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I221" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B222" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C222" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D222" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E222" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F222" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G222" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="H222" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I222" s="7"/>
-    </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B223" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C223" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D223" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E223" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F223" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G223" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H223" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I223" s="7"/>
-    </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B224" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C224" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D224" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E224" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F224" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G224" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="H224" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I224" s="7"/>
-    </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B225" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C225" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D225" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E225" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F225" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G225" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="H225" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I225" s="7"/>
-    </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="B226" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C226" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D226" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E226" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F226" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G226" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="H226" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I226" s="7"/>
+      <c r="B226" s="5"/>
+      <c r="C226" s="5"/>
+      <c r="D226" s="5"/>
+      <c r="E226" s="5"/>
+      <c r="F226" s="5"/>
+      <c r="G226" s="5"/>
+      <c r="H226" s="5"/>
+      <c r="I226" s="5"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="9" t="s">
-        <v>207</v>
+        <v>108</v>
       </c>
       <c r="B227" s="7" t="s">
         <v>109</v>
@@ -12970,19 +12998,21 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>208</v>
+        <v>303</v>
       </c>
       <c r="H227" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I227" s="7"/>
+      <c r="I227" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="9" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C228" s="7" t="s">
         <v>110</v>
@@ -12997,16 +13027,18 @@
         <v>26</v>
       </c>
       <c r="G228" s="10" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="H228" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I228" s="7"/>
+      <c r="I228" s="7" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B229" s="7" t="s">
         <v>24</v>
@@ -13024,7 +13056,7 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="H229" s="7" t="n">
         <v>2</v>
@@ -13033,7 +13065,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="9" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B230" s="7" t="s">
         <v>24</v>
@@ -13051,7 +13083,7 @@
         <v>26</v>
       </c>
       <c r="G230" s="10" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H230" s="7" t="n">
         <v>2</v>
@@ -13060,7 +13092,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="9" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B231" s="7" t="s">
         <v>24</v>
@@ -13078,7 +13110,7 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="H231" s="7" t="n">
         <v>2</v>
@@ -13087,10 +13119,10 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="9" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C232" s="7" t="s">
         <v>110</v>
@@ -13105,7 +13137,7 @@
         <v>26</v>
       </c>
       <c r="G232" s="10" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="H232" s="7" t="n">
         <v>2</v>
@@ -13114,7 +13146,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="9" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>109</v>
@@ -13132,7 +13164,7 @@
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H233" s="7" t="n">
         <v>2</v>
@@ -13141,10 +13173,10 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="9" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>222</v>
+        <v>109</v>
       </c>
       <c r="C234" s="7" t="s">
         <v>110</v>
@@ -13159,7 +13191,7 @@
         <v>26</v>
       </c>
       <c r="G234" s="10" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="H234" s="7" t="n">
         <v>2</v>
@@ -13168,10 +13200,10 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="9" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>222</v>
+        <v>24</v>
       </c>
       <c r="C235" s="7" t="s">
         <v>110</v>
@@ -13186,7 +13218,7 @@
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="H235" s="7" t="n">
         <v>2</v>
@@ -13195,10 +13227,10 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="9" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="C236" s="7" t="s">
         <v>110</v>
@@ -13213,7 +13245,7 @@
         <v>26</v>
       </c>
       <c r="G236" s="10" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H236" s="7" t="n">
         <v>2</v>
@@ -13222,10 +13254,10 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="9" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="C237" s="7" t="s">
         <v>110</v>
@@ -13240,7 +13272,7 @@
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="H237" s="7" t="n">
         <v>2</v>
@@ -13249,10 +13281,10 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B238" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C238" s="7" t="s">
         <v>110</v>
@@ -13267,7 +13299,7 @@
         <v>26</v>
       </c>
       <c r="G238" s="10" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="H238" s="7" t="n">
         <v>2</v>
@@ -13276,7 +13308,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="9" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="B239" s="7" t="s">
         <v>109</v>
@@ -13294,7 +13326,7 @@
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="H239" s="7" t="n">
         <v>2</v>
@@ -13302,11 +13334,11 @@
       <c r="I239" s="7"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="7" t="s">
-        <v>304</v>
+      <c r="A240" s="9" t="s">
+        <v>219</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C240" s="7" t="s">
         <v>110</v>
@@ -13321,21 +13353,19 @@
         <v>26</v>
       </c>
       <c r="G240" s="10" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="H240" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I240" s="7" t="s">
-        <v>236</v>
-      </c>
+      <c r="I240" s="7"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="7" t="s">
-        <v>237</v>
+      <c r="A241" s="9" t="s">
+        <v>221</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="C241" s="7" t="s">
         <v>110</v>
@@ -13350,197 +13380,409 @@
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H241" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I241" s="7"/>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B242" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C242" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D242" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E242" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F242" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G242" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H242" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I242" s="7"/>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B243" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C243" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D243" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E243" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F243" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G243" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="H243" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I243" s="7"/>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B244" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C244" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D244" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E244" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G244" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H244" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I244" s="7"/>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B245" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C245" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D245" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E245" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F245" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G245" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H245" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I245" s="7"/>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B246" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C246" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D246" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E246" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F246" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G246" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="H246" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I246" s="7"/>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B247" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C247" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D247" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E247" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F247" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G247" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H247" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I247" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B248" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C248" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D248" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E248" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G248" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="H241" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I241" s="7" t="s">
+      <c r="H248" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I248" s="7" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="12" t="s">
+    <row r="249" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B249" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C249" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D249" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E249" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G249" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="H249" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I249" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="B242" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C242" s="12" t="s">
+      <c r="B250" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C250" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D242" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E242" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F242" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G242" s="12" t="s">
+      <c r="D250" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E250" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G250" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="H242" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I242" s="12" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="12" t="s">
+      <c r="H250" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I250" s="12" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="B243" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C243" s="12" t="s">
+      <c r="B251" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C251" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D243" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E243" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F243" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G243" s="12" t="s">
+      <c r="D251" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E251" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G251" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="H243" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I243" s="12" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="244" customFormat="false" ht="45.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="B244" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C244" s="12" t="s">
+      <c r="H251" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I251" s="12" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B252" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C252" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D244" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E244" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F244" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G244" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="H244" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I244" s="12" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="245" customFormat="false" ht="36.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="B245" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C245" s="12" t="s">
+      <c r="D252" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E252" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F252" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G252" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="H252" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I252" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="B253" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C253" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D245" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E245" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F245" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G245" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="H245" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I245" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="246" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="B246" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C246" s="12" t="s">
+      <c r="D253" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E253" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F253" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G253" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="H253" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I253" s="12" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B254" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C254" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D246" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E246" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F246" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G246" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="H246" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I246" s="12" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="247" customFormat="false" ht="28.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B247" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C247" s="12" t="s">
+      <c r="D254" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E254" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G254" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="H254" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I254" s="12" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="B255" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C255" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D247" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E247" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F247" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G247" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="H247" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I247" s="12" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D255" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E255" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F255" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G255" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="H255" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
     <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -13559,26 +13801,26 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="F116:F117"/>
-    <mergeCell ref="I116:I117"/>
-    <mergeCell ref="A118:I118"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="D172:D173"/>
-    <mergeCell ref="F172:F173"/>
-    <mergeCell ref="I172:I173"/>
-    <mergeCell ref="A174:I174"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="D198:D199"/>
-    <mergeCell ref="F198:F199"/>
-    <mergeCell ref="I198:I199"/>
-    <mergeCell ref="A200:I200"/>
-    <mergeCell ref="A217:A218"/>
-    <mergeCell ref="D217:D218"/>
-    <mergeCell ref="F217:F218"/>
-    <mergeCell ref="I217:I218"/>
-    <mergeCell ref="A219:I219"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="D117:D118"/>
+    <mergeCell ref="F117:F118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="A119:I119"/>
+    <mergeCell ref="A179:A180"/>
+    <mergeCell ref="D179:D180"/>
+    <mergeCell ref="F179:F180"/>
+    <mergeCell ref="I179:I180"/>
+    <mergeCell ref="A181:I181"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="D205:D206"/>
+    <mergeCell ref="F205:F206"/>
+    <mergeCell ref="I205:I206"/>
+    <mergeCell ref="A207:I207"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="A226:I226"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13614,7 +13856,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13622,7 +13864,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13643,10 +13885,10 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13701,7 +13943,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -13714,7 +13956,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>195</v>
@@ -13732,18 +13974,18 @@
         <v>26</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>195</v>
@@ -13761,18 +14003,18 @@
         <v>26</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>24</v>
@@ -13790,18 +14032,18 @@
         <v>26</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>75</v>
@@ -13819,18 +14061,18 @@
         <v>26</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>75</v>
@@ -13848,18 +14090,18 @@
         <v>26</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>75</v>
@@ -13877,18 +14119,18 @@
         <v>26</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>75</v>
@@ -13906,18 +14148,18 @@
         <v>26</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>75</v>
@@ -13935,18 +14177,18 @@
         <v>26</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -13959,7 +14201,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -13972,7 +14214,7 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -13985,7 +14227,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -13998,7 +14240,7 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -14011,7 +14253,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -14024,7 +14266,7 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -14037,7 +14279,7 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -14050,7 +14292,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -14063,7 +14305,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Modbus Table" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2498" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2546" uniqueCount="397">
   <si>
     <t xml:space="preserve">Controller:</t>
   </si>
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Firmware</t>
   </si>
   <si>
-    <t xml:space="preserve">V2.12</t>
+    <t xml:space="preserve">V2.15</t>
   </si>
   <si>
     <t xml:space="preserve">Protocol</t>
@@ -744,6 +744,15 @@
     <t xml:space="preserve">0: OFF (Fans Enabled), 1: ON (Fans Disabled)</t>
   </si>
   <si>
+    <t xml:space="preserve">Firmware Upgrade Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: No Firmware Upgrade Ongoing/Firmware Upgrade completed, 1:Firmware Uploading Ongoing, 2: Firmware Updating Ongoing, 127: Error Occured</t>
+  </si>
+  <si>
     <t xml:space="preserve">Serial Number Lower Half</t>
   </si>
   <si>
@@ -837,22 +846,40 @@
     <t xml:space="preserve">Solar B Phase Over Voltage</t>
   </si>
   <si>
-    <t xml:space="preserve">Grid R Phase Contactor Coil Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Contactor Coil Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Contactor Coil Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Solar Contactor Coil Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load On Grid Contactor &amp; Solar Neutral Earth Contactor Coil Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fans Output</t>
+    <t xml:space="preserve">Grid R Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Y Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar R Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar Y Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar B Phase Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relay 1 Energized (Grid R Phase Contactor Coil Deenergized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relay 2 Energized (Grid Y Phase Contactor Coil Deenergized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relay 3 Energized (Grid B Phase Contactor Coil Deenergized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relay 4 Energized (Load On Solar Contactor Coil Energized &amp; Solar Neutral To Earth Contactor Coil Energized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relay 5 Energized (Load On Grid Contactor Coil Deenergized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relay 6 Energized (Fans Output Deenergized)</t>
   </si>
   <si>
     <t xml:space="preserve">Grid R Phase Contactor Stuck Open Error Suspected</t>
@@ -939,13 +966,7 @@
     <t xml:space="preserve">DG Detection Enable/Disable Setting</t>
   </si>
   <si>
-    <t xml:space="preserve">Firmware Upgrade Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0: No Firmware Upgrade Ongoing/Firmware Upgrade completed, 1:Firmware Uploading Ongoing, 2: Firmware Updating Ongoing, 127: Error Occured</t>
+    <t xml:space="preserve">0: No Action, 1:Signals start of Firmware Uploading, 2: Signals end of Firmware Uploading</t>
   </si>
   <si>
     <t xml:space="preserve">Switch Pressed</t>
@@ -1012,24 +1033,6 @@
 Used to store a temporarily value. Resets when SOCO restarts on POR.</t>
   </si>
   <si>
-    <t xml:space="preserve">Grid R Phase Loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Y Phase Loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid B Phase Loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar R Phase Loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Y Phase Loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar B Phase Loss</t>
-  </si>
-  <si>
     <t xml:space="preserve">READ COIL STATUS (Function Code: 0x01)</t>
   </si>
   <si>
@@ -1116,9 +1119,6 @@
   </si>
   <si>
     <t xml:space="preserve">Restart Controller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0: No Action, 1:Signals start of Firmware Uploading, 2: Signals end of Firmware Uploading</t>
   </si>
   <si>
     <t xml:space="preserve">Internal Only. Not visible to customer. 
@@ -1767,7 +1767,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.15"/>
@@ -4595,7 +4595,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
         <v>240</v>
       </c>
@@ -4614,17 +4614,19 @@
       <c r="F108" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G108" s="7" t="s">
+      <c r="G108" s="10" t="s">
         <v>241</v>
       </c>
       <c r="H108" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I108" s="7"/>
+      <c r="I108" s="7" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>75</v>
@@ -4642,7 +4644,7 @@
         <v>26</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>2</v>
@@ -4651,7 +4653,7 @@
     </row>
     <row r="110" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>75</v>
@@ -4663,108 +4665,108 @@
         <v>4</v>
       </c>
       <c r="E110" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="H110" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" s="7"/>
+    </row>
+    <row r="111" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E111" s="7" t="n">
         <v>0.01</v>
       </c>
-      <c r="F110" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="H110" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I110" s="7"/>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="3" t="s">
+      <c r="F111" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="7"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B112" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C112" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D112" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E111" s="4" t="s">
+      <c r="E112" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="F112" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="G112" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H111" s="4" t="s">
+      <c r="H112" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I111" s="3" t="s">
+      <c r="I112" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="3"/>
-      <c r="B112" s="4" t="s">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="3"/>
+      <c r="B113" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C113" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D112" s="3"/>
-      <c r="E112" s="4" t="s">
+      <c r="D113" s="3"/>
+      <c r="E113" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F112" s="3"/>
-      <c r="G112" s="4" t="s">
+      <c r="F113" s="3"/>
+      <c r="G113" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H112" s="4" t="s">
+      <c r="H113" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I112" s="3"/>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
-      <c r="G113" s="5"/>
-      <c r="H113" s="5"/>
-      <c r="I113" s="5"/>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F114" s="7" t="s">
+      <c r="I113" s="3"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="G114" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H114" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I114" s="7"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="5"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5"/>
+      <c r="I114" s="5"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
@@ -4774,7 +4776,7 @@
         <v>75</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>75</v>
@@ -4783,10 +4785,10 @@
         <v>75</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115" s="7" t="n">
         <v>1</v>
@@ -4795,13 +4797,13 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>75</v>
@@ -4810,10 +4812,10 @@
         <v>75</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G116" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H116" s="7" t="n">
         <v>1</v>
@@ -4822,25 +4824,25 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F117" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B117" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>249</v>
-      </c>
       <c r="G117" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>1</v>
@@ -4849,13 +4851,13 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>75</v>
@@ -4864,10 +4866,10 @@
         <v>75</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H118" s="7" t="n">
         <v>1</v>
@@ -4876,13 +4878,13 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>75</v>
@@ -4891,10 +4893,10 @@
         <v>75</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H119" s="7" t="n">
         <v>1</v>
@@ -4903,13 +4905,13 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>75</v>
@@ -4918,10 +4920,10 @@
         <v>75</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H120" s="7" t="n">
         <v>1</v>
@@ -4930,13 +4932,13 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>75</v>
@@ -4945,10 +4947,10 @@
         <v>75</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H121" s="7" t="n">
         <v>1</v>
@@ -4957,13 +4959,13 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>75</v>
@@ -4972,10 +4974,10 @@
         <v>75</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>201</v>
+        <v>8</v>
       </c>
       <c r="H122" s="7" t="n">
         <v>1</v>
@@ -4984,13 +4986,13 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>75</v>
@@ -4999,10 +5001,10 @@
         <v>75</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H123" s="7" t="n">
         <v>1</v>
@@ -5011,13 +5013,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>75</v>
@@ -5026,10 +5028,10 @@
         <v>75</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="H124" s="7" t="n">
         <v>1</v>
@@ -5038,13 +5040,13 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>75</v>
@@ -5053,10 +5055,10 @@
         <v>75</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H125" s="7" t="n">
         <v>1</v>
@@ -5065,13 +5067,13 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>75</v>
@@ -5080,10 +5082,10 @@
         <v>75</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H126" s="7" t="n">
         <v>1</v>
@@ -5092,13 +5094,13 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>75</v>
@@ -5107,10 +5109,10 @@
         <v>75</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H127" s="7" t="n">
         <v>1</v>
@@ -5119,13 +5121,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>75</v>
@@ -5134,10 +5136,10 @@
         <v>75</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H128" s="7" t="n">
         <v>1</v>
@@ -5146,13 +5148,13 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>75</v>
@@ -5161,10 +5163,10 @@
         <v>75</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H129" s="7" t="n">
         <v>1</v>
@@ -5173,13 +5175,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>75</v>
@@ -5188,10 +5190,10 @@
         <v>75</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H130" s="7" t="n">
         <v>1</v>
@@ -5200,13 +5202,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>75</v>
@@ -5215,10 +5217,10 @@
         <v>75</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H131" s="7" t="n">
         <v>1</v>
@@ -5227,13 +5229,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>75</v>
@@ -5242,10 +5244,10 @@
         <v>75</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H132" s="7" t="n">
         <v>1</v>
@@ -5254,13 +5256,13 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D133" s="7" t="s">
         <v>75</v>
@@ -5269,10 +5271,10 @@
         <v>75</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H133" s="7" t="n">
         <v>1</v>
@@ -5281,13 +5283,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>75</v>
@@ -5296,10 +5298,10 @@
         <v>75</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H134" s="7" t="n">
         <v>1</v>
@@ -5308,13 +5310,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>75</v>
@@ -5323,10 +5325,10 @@
         <v>75</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H135" s="7" t="n">
         <v>1</v>
@@ -5335,13 +5337,13 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D136" s="7" t="s">
         <v>75</v>
@@ -5350,10 +5352,10 @@
         <v>75</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>401</v>
+        <v>312</v>
       </c>
       <c r="H136" s="7" t="n">
         <v>1</v>
@@ -5362,13 +5364,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D137" s="7" t="s">
         <v>75</v>
@@ -5377,10 +5379,10 @@
         <v>75</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>402</v>
+        <v>313</v>
       </c>
       <c r="H137" s="7" t="n">
         <v>1</v>
@@ -5389,13 +5391,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D138" s="7" t="s">
         <v>75</v>
@@ -5404,10 +5406,10 @@
         <v>75</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>403</v>
+        <v>314</v>
       </c>
       <c r="H138" s="7" t="n">
         <v>1</v>
@@ -5416,13 +5418,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>75</v>
@@ -5431,10 +5433,10 @@
         <v>75</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>404</v>
+        <v>315</v>
       </c>
       <c r="H139" s="7" t="n">
         <v>1</v>
@@ -5443,13 +5445,13 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D140" s="7" t="s">
         <v>75</v>
@@ -5458,10 +5460,10 @@
         <v>75</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>405</v>
+        <v>316</v>
       </c>
       <c r="H140" s="7" t="n">
         <v>1</v>
@@ -5470,13 +5472,13 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>75</v>
@@ -5485,10 +5487,10 @@
         <v>75</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>406</v>
+        <v>317</v>
       </c>
       <c r="H141" s="7" t="n">
         <v>1</v>
@@ -5497,13 +5499,13 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D142" s="7" t="s">
         <v>75</v>
@@ -5512,10 +5514,10 @@
         <v>75</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>601</v>
+        <v>318</v>
       </c>
       <c r="H142" s="7" t="n">
         <v>1</v>
@@ -5524,13 +5526,13 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>75</v>
@@ -5539,10 +5541,10 @@
         <v>75</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>602</v>
+        <v>401</v>
       </c>
       <c r="H143" s="7" t="n">
         <v>1</v>
@@ -5551,13 +5553,13 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>75</v>
@@ -5566,10 +5568,10 @@
         <v>75</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>603</v>
+        <v>402</v>
       </c>
       <c r="H144" s="7" t="n">
         <v>1</v>
@@ -5578,13 +5580,13 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>75</v>
@@ -5593,25 +5595,25 @@
         <v>75</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>604</v>
+        <v>403</v>
       </c>
       <c r="H145" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I145" s="7"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>75</v>
@@ -5620,10 +5622,10 @@
         <v>75</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>605</v>
+        <v>404</v>
       </c>
       <c r="H146" s="7" t="n">
         <v>1</v>
@@ -5632,13 +5634,13 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D147" s="7" t="s">
         <v>75</v>
@@ -5647,10 +5649,10 @@
         <v>75</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>606</v>
+        <v>405</v>
       </c>
       <c r="H147" s="7" t="n">
         <v>1</v>
@@ -5659,13 +5661,13 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D148" s="7" t="s">
         <v>75</v>
@@ -5674,10 +5676,10 @@
         <v>75</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>607</v>
+        <v>406</v>
       </c>
       <c r="H148" s="7" t="n">
         <v>1</v>
@@ -5686,13 +5688,13 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D149" s="7" t="s">
         <v>75</v>
@@ -5701,10 +5703,10 @@
         <v>75</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="H149" s="7" t="n">
         <v>1</v>
@@ -5713,13 +5715,13 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D150" s="7" t="s">
         <v>75</v>
@@ -5728,10 +5730,10 @@
         <v>75</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="H150" s="7" t="n">
         <v>1</v>
@@ -5740,13 +5742,13 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D151" s="7" t="s">
         <v>75</v>
@@ -5755,10 +5757,10 @@
         <v>75</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="H151" s="7" t="n">
         <v>1</v>
@@ -5767,13 +5769,13 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>75</v>
@@ -5782,10 +5784,10 @@
         <v>75</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="H152" s="7" t="n">
         <v>1</v>
@@ -5794,13 +5796,13 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>75</v>
@@ -5809,10 +5811,10 @@
         <v>75</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="H153" s="7" t="n">
         <v>1</v>
@@ -5821,13 +5823,13 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>75</v>
@@ -5836,10 +5838,10 @@
         <v>75</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>801</v>
+        <v>606</v>
       </c>
       <c r="H154" s="7" t="n">
         <v>1</v>
@@ -5848,13 +5850,13 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D155" s="7" t="s">
         <v>75</v>
@@ -5863,10 +5865,10 @@
         <v>75</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>802</v>
+        <v>607</v>
       </c>
       <c r="H155" s="7" t="n">
         <v>1</v>
@@ -5875,13 +5877,13 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>75</v>
@@ -5890,10 +5892,10 @@
         <v>75</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>803</v>
+        <v>608</v>
       </c>
       <c r="H156" s="7" t="n">
         <v>1</v>
@@ -5902,13 +5904,13 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D157" s="7" t="s">
         <v>75</v>
@@ -5917,10 +5919,10 @@
         <v>75</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>804</v>
+        <v>609</v>
       </c>
       <c r="H157" s="7" t="n">
         <v>1</v>
@@ -5929,13 +5931,13 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D158" s="7" t="s">
         <v>75</v>
@@ -5944,10 +5946,10 @@
         <v>75</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>805</v>
+        <v>610</v>
       </c>
       <c r="H158" s="7" t="n">
         <v>1</v>
@@ -5956,13 +5958,13 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D159" s="7" t="s">
         <v>75</v>
@@ -5971,10 +5973,10 @@
         <v>75</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>806</v>
+        <v>611</v>
       </c>
       <c r="H159" s="7" t="n">
         <v>1</v>
@@ -5983,13 +5985,13 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D160" s="7" t="s">
         <v>75</v>
@@ -5998,10 +6000,10 @@
         <v>75</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>807</v>
+        <v>612</v>
       </c>
       <c r="H160" s="7" t="n">
         <v>1</v>
@@ -6010,13 +6012,13 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D161" s="7" t="s">
         <v>75</v>
@@ -6025,10 +6027,10 @@
         <v>75</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="H161" s="7" t="n">
         <v>1</v>
@@ -6037,13 +6039,13 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D162" s="7" t="s">
         <v>75</v>
@@ -6052,10 +6054,10 @@
         <v>75</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="H162" s="7" t="n">
         <v>1</v>
@@ -6064,13 +6066,13 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D163" s="7" t="s">
         <v>75</v>
@@ -6079,10 +6081,10 @@
         <v>75</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>901</v>
+        <v>803</v>
       </c>
       <c r="H163" s="7" t="n">
         <v>1</v>
@@ -6091,13 +6093,13 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D164" s="7" t="s">
         <v>75</v>
@@ -6106,10 +6108,10 @@
         <v>75</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G164" s="7" t="n">
-        <v>902</v>
+        <v>804</v>
       </c>
       <c r="H164" s="7" t="n">
         <v>1</v>
@@ -6118,13 +6120,13 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>75</v>
@@ -6133,10 +6135,10 @@
         <v>75</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G165" s="7" t="n">
-        <v>903</v>
+        <v>805</v>
       </c>
       <c r="H165" s="7" t="n">
         <v>1</v>
@@ -6145,13 +6147,13 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D166" s="7" t="s">
         <v>75</v>
@@ -6160,275 +6162,271 @@
         <v>75</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G166" s="7" t="n">
+        <v>806</v>
+      </c>
+      <c r="H166" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" s="7"/>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F167" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G167" s="7" t="n">
+        <v>807</v>
+      </c>
+      <c r="H167" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" s="7"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G168" s="7" t="n">
+        <v>808</v>
+      </c>
+      <c r="H168" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" s="7"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G169" s="7" t="n">
+        <v>809</v>
+      </c>
+      <c r="H169" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" s="7"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G170" s="7" t="n">
+        <v>901</v>
+      </c>
+      <c r="H170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="7"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F171" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G171" s="7" t="n">
+        <v>902</v>
+      </c>
+      <c r="H171" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" s="7"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G172" s="7" t="n">
+        <v>903</v>
+      </c>
+      <c r="H172" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I172" s="7"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G173" s="7" t="n">
         <v>904</v>
       </c>
-      <c r="H166" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I166" s="7"/>
-    </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="3" t="s">
+      <c r="H173" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" s="7"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A174" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B174" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C174" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D167" s="3" t="s">
+      <c r="D174" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E167" s="4" t="s">
+      <c r="E174" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F167" s="3" t="s">
+      <c r="F174" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G167" s="4" t="s">
+      <c r="G174" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H167" s="4" t="s">
+      <c r="H174" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I167" s="3" t="s">
+      <c r="I174" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="3"/>
-      <c r="B168" s="4" t="s">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="3"/>
+      <c r="B175" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C175" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D168" s="3"/>
-      <c r="E168" s="4" t="s">
+      <c r="D175" s="3"/>
+      <c r="E175" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F168" s="3"/>
-      <c r="G168" s="4" t="s">
+      <c r="F175" s="3"/>
+      <c r="G175" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H168" s="4" t="s">
+      <c r="H175" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I168" s="3"/>
-    </row>
-    <row r="169" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B169" s="5"/>
-      <c r="C169" s="5"/>
-      <c r="D169" s="5"/>
-      <c r="E169" s="5"/>
-      <c r="F169" s="5"/>
-      <c r="G169" s="5"/>
-      <c r="H169" s="5"/>
-      <c r="I169" s="5"/>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C170" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D170" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E170" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F170" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G170" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="H170" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I170" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="B171" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C171" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D171" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E171" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G171" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H171" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I171" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B172" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C172" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D172" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E172" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G172" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="H172" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I172" s="7"/>
-    </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B173" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C173" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D173" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E173" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F173" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G173" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H173" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I173" s="7"/>
-    </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C174" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D174" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E174" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F174" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G174" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="H174" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I174" s="7"/>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B175" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C175" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D175" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E175" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F175" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G175" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="H175" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I175" s="7"/>
-    </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="B176" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C176" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D176" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E176" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F176" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G176" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="H176" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I176" s="7"/>
+      <c r="I175" s="3"/>
+    </row>
+    <row r="176" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A176" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B176" s="5"/>
+      <c r="C176" s="5"/>
+      <c r="D176" s="5"/>
+      <c r="E176" s="5"/>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
+      <c r="H176" s="5"/>
+      <c r="I176" s="5"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="9" t="s">
-        <v>207</v>
+        <v>108</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>109</v>
@@ -6446,19 +6444,21 @@
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="H177" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I177" s="7"/>
+      <c r="I177" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="9" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C178" s="7" t="s">
         <v>110</v>
@@ -6473,16 +6473,18 @@
         <v>26</v>
       </c>
       <c r="G178" s="10" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="H178" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I178" s="7"/>
+      <c r="I178" s="7" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>24</v>
@@ -6500,7 +6502,7 @@
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="H179" s="7" t="n">
         <v>2</v>
@@ -6509,7 +6511,7 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="9" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>24</v>
@@ -6527,7 +6529,7 @@
         <v>26</v>
       </c>
       <c r="G180" s="10" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H180" s="7" t="n">
         <v>2</v>
@@ -6536,7 +6538,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="9" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B181" s="7" t="s">
         <v>24</v>
@@ -6554,7 +6556,7 @@
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="H181" s="7" t="n">
         <v>2</v>
@@ -6563,10 +6565,10 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="9" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C182" s="7" t="s">
         <v>110</v>
@@ -6581,7 +6583,7 @@
         <v>26</v>
       </c>
       <c r="G182" s="10" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="H182" s="7" t="n">
         <v>2</v>
@@ -6590,7 +6592,7 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="9" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>109</v>
@@ -6608,7 +6610,7 @@
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H183" s="7" t="n">
         <v>2</v>
@@ -6617,10 +6619,10 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="9" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>222</v>
+        <v>109</v>
       </c>
       <c r="C184" s="7" t="s">
         <v>110</v>
@@ -6635,7 +6637,7 @@
         <v>26</v>
       </c>
       <c r="G184" s="10" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="H184" s="7" t="n">
         <v>2</v>
@@ -6644,10 +6646,10 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="9" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>222</v>
+        <v>24</v>
       </c>
       <c r="C185" s="7" t="s">
         <v>110</v>
@@ -6662,7 +6664,7 @@
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="H185" s="7" t="n">
         <v>2</v>
@@ -6671,10 +6673,10 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="9" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="C186" s="7" t="s">
         <v>110</v>
@@ -6689,7 +6691,7 @@
         <v>26</v>
       </c>
       <c r="G186" s="10" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H186" s="7" t="n">
         <v>2</v>
@@ -6698,10 +6700,10 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="9" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="C187" s="7" t="s">
         <v>110</v>
@@ -6716,7 +6718,7 @@
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="H187" s="7" t="n">
         <v>2</v>
@@ -6725,10 +6727,10 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C188" s="7" t="s">
         <v>110</v>
@@ -6743,7 +6745,7 @@
         <v>26</v>
       </c>
       <c r="G188" s="10" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="H188" s="7" t="n">
         <v>2</v>
@@ -6752,7 +6754,7 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="9" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>109</v>
@@ -6770,7 +6772,7 @@
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="H189" s="7" t="n">
         <v>2</v>
@@ -6778,11 +6780,11 @@
       <c r="I189" s="7"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="7" t="s">
-        <v>304</v>
+      <c r="A190" s="9" t="s">
+        <v>219</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C190" s="7" t="s">
         <v>110</v>
@@ -6797,21 +6799,19 @@
         <v>26</v>
       </c>
       <c r="G190" s="10" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="H190" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I190" s="7" t="s">
-        <v>236</v>
-      </c>
+      <c r="I190" s="7"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="7" t="s">
-        <v>237</v>
+      <c r="A191" s="9" t="s">
+        <v>221</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="C191" s="7" t="s">
         <v>110</v>
@@ -6826,15 +6826,241 @@
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H191" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I191" s="7"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D192" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E192" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F192" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G192" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H192" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I192" s="7"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D193" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E193" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F193" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G193" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="H193" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I193" s="7"/>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D194" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E194" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G194" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H194" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I194" s="7"/>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D195" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E195" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G195" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H195" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I195" s="7"/>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D196" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E196" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G196" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="H196" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I196" s="7"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D197" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E197" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G197" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H197" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I197" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D198" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E198" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G198" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="H191" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I191" s="7" t="s">
+      <c r="H198" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I198" s="7" t="s">
         <v>239</v>
       </c>
     </row>
+    <row r="199" customFormat="false" ht="19.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D199" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E199" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G199" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="H199" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I199" s="7" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -6892,16 +7118,16 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="D111:D112"/>
-    <mergeCell ref="F111:F112"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="A113:I113"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="I167:I168"/>
-    <mergeCell ref="A169:I169"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="D112:D113"/>
+    <mergeCell ref="F112:F113"/>
+    <mergeCell ref="I112:I113"/>
+    <mergeCell ref="A114:I114"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A176:I176"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9749,7 +9975,7 @@
     </row>
     <row r="108" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>305</v>
+        <v>240</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>75</v>
@@ -9767,18 +9993,18 @@
         <v>26</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>306</v>
+        <v>241</v>
       </c>
       <c r="H108" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>307</v>
+        <v>242</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="86.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="11" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B109" s="12" t="s">
         <v>75</v>
@@ -9796,18 +10022,18 @@
         <v>26</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="H109" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I109" s="12" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>75</v>
@@ -9825,7 +10051,7 @@
         <v>26</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H110" s="7" t="n">
         <v>2</v>
@@ -9834,7 +10060,7 @@
     </row>
     <row r="111" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>75</v>
@@ -9852,7 +10078,7 @@
         <v>26</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H111" s="7" t="n">
         <v>2</v>
@@ -9861,7 +10087,7 @@
     </row>
     <row r="112" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>75</v>
@@ -9879,7 +10105,7 @@
         <v>26</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H112" s="7" t="n">
         <v>2</v>
@@ -9888,7 +10114,7 @@
     </row>
     <row r="113" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="11" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B113" s="12" t="s">
         <v>75</v>
@@ -9906,18 +10132,18 @@
         <v>26</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="H113" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="11" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B114" s="12" t="s">
         <v>75</v>
@@ -9935,18 +10161,18 @@
         <v>26</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="H114" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I114" s="12" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="236.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="11" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B115" s="12" t="s">
         <v>75</v>
@@ -9964,18 +10190,18 @@
         <v>26</v>
       </c>
       <c r="G115" s="13" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="H115" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="36.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="11" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B116" s="12" t="s">
         <v>75</v>
@@ -9993,13 +10219,13 @@
         <v>26</v>
       </c>
       <c r="G116" s="13" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="H116" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10054,7 +10280,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -10067,13 +10293,13 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>75</v>
@@ -10082,7 +10308,7 @@
         <v>75</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>1</v>
@@ -10094,13 +10320,13 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>75</v>
@@ -10109,7 +10335,7 @@
         <v>75</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>2</v>
@@ -10121,13 +10347,13 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>75</v>
@@ -10136,7 +10362,7 @@
         <v>75</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>3</v>
@@ -10148,22 +10374,22 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F123" s="7" t="s">
         <v>252</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>249</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>4</v>
@@ -10175,13 +10401,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>75</v>
@@ -10190,7 +10416,7 @@
         <v>75</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>5</v>
@@ -10202,13 +10428,13 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>75</v>
@@ -10217,7 +10443,7 @@
         <v>75</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>6</v>
@@ -10229,13 +10455,13 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>75</v>
@@ -10244,7 +10470,7 @@
         <v>75</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>7</v>
@@ -10256,13 +10482,13 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>75</v>
@@ -10271,7 +10497,7 @@
         <v>75</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>8</v>
@@ -10283,13 +10509,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>75</v>
@@ -10298,7 +10524,7 @@
         <v>75</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>201</v>
@@ -10310,13 +10536,13 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>75</v>
@@ -10325,7 +10551,7 @@
         <v>75</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>202</v>
@@ -10337,13 +10563,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>75</v>
@@ -10352,7 +10578,7 @@
         <v>75</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G130" s="7" t="n">
         <v>301</v>
@@ -10364,13 +10590,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>75</v>
@@ -10379,7 +10605,7 @@
         <v>75</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G131" s="7" t="n">
         <v>302</v>
@@ -10391,13 +10617,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>75</v>
@@ -10406,7 +10632,7 @@
         <v>75</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>303</v>
@@ -10418,13 +10644,13 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D133" s="7" t="s">
         <v>75</v>
@@ -10433,7 +10659,7 @@
         <v>75</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G133" s="7" t="n">
         <v>304</v>
@@ -10445,13 +10671,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>75</v>
@@ -10460,7 +10686,7 @@
         <v>75</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>305</v>
@@ -10472,13 +10698,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>75</v>
@@ -10487,7 +10713,7 @@
         <v>75</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G135" s="7" t="n">
         <v>306</v>
@@ -10499,13 +10725,13 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D136" s="7" t="s">
         <v>75</v>
@@ -10514,7 +10740,7 @@
         <v>75</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>307</v>
@@ -10526,13 +10752,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D137" s="7" t="s">
         <v>75</v>
@@ -10541,7 +10767,7 @@
         <v>75</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G137" s="7" t="n">
         <v>308</v>
@@ -10553,13 +10779,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D138" s="7" t="s">
         <v>75</v>
@@ -10568,7 +10794,7 @@
         <v>75</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>309</v>
@@ -10580,13 +10806,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>75</v>
@@ -10595,7 +10821,7 @@
         <v>75</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G139" s="7" t="n">
         <v>310</v>
@@ -10607,13 +10833,13 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D140" s="7" t="s">
         <v>75</v>
@@ -10622,7 +10848,7 @@
         <v>75</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>311</v>
@@ -10634,13 +10860,13 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>75</v>
@@ -10649,7 +10875,7 @@
         <v>75</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G141" s="7" t="n">
         <v>312</v>
@@ -10661,13 +10887,13 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D142" s="7" t="s">
         <v>75</v>
@@ -10676,7 +10902,7 @@
         <v>75</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G142" s="7" t="n">
         <v>313</v>
@@ -10688,13 +10914,13 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>75</v>
@@ -10703,7 +10929,7 @@
         <v>75</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G143" s="7" t="n">
         <v>314</v>
@@ -10715,13 +10941,13 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>75</v>
@@ -10730,7 +10956,7 @@
         <v>75</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G144" s="7" t="n">
         <v>315</v>
@@ -10742,13 +10968,13 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>75</v>
@@ -10757,7 +10983,7 @@
         <v>75</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G145" s="7" t="n">
         <v>316</v>
@@ -10769,13 +10995,13 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>75</v>
@@ -10784,7 +11010,7 @@
         <v>75</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>317</v>
@@ -10796,13 +11022,13 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D147" s="7" t="s">
         <v>75</v>
@@ -10811,7 +11037,7 @@
         <v>75</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G147" s="7" t="n">
         <v>318</v>
@@ -10823,13 +11049,13 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D148" s="7" t="s">
         <v>75</v>
@@ -10838,7 +11064,7 @@
         <v>75</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>401</v>
@@ -10850,13 +11076,13 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D149" s="7" t="s">
         <v>75</v>
@@ -10865,7 +11091,7 @@
         <v>75</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G149" s="7" t="n">
         <v>402</v>
@@ -10877,13 +11103,13 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D150" s="7" t="s">
         <v>75</v>
@@ -10892,7 +11118,7 @@
         <v>75</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G150" s="7" t="n">
         <v>403</v>
@@ -10902,15 +11128,15 @@
       </c>
       <c r="I150" s="7"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D151" s="7" t="s">
         <v>75</v>
@@ -10919,7 +11145,7 @@
         <v>75</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G151" s="7" t="n">
         <v>404</v>
@@ -10929,15 +11155,15 @@
       </c>
       <c r="I151" s="7"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>75</v>
@@ -10946,7 +11172,7 @@
         <v>75</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G152" s="7" t="n">
         <v>405</v>
@@ -10958,13 +11184,13 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>75</v>
@@ -10973,7 +11199,7 @@
         <v>75</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G153" s="7" t="n">
         <v>406</v>
@@ -10985,13 +11211,13 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>75</v>
@@ -11000,7 +11226,7 @@
         <v>75</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>601</v>
@@ -11012,13 +11238,13 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D155" s="7" t="s">
         <v>75</v>
@@ -11027,7 +11253,7 @@
         <v>75</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G155" s="7" t="n">
         <v>602</v>
@@ -11039,13 +11265,13 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>75</v>
@@ -11054,7 +11280,7 @@
         <v>75</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>603</v>
@@ -11066,13 +11292,13 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D157" s="7" t="s">
         <v>75</v>
@@ -11081,7 +11307,7 @@
         <v>75</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G157" s="7" t="n">
         <v>604</v>
@@ -11093,13 +11319,13 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D158" s="7" t="s">
         <v>75</v>
@@ -11108,7 +11334,7 @@
         <v>75</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>605</v>
@@ -11120,13 +11346,13 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D159" s="7" t="s">
         <v>75</v>
@@ -11135,7 +11361,7 @@
         <v>75</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G159" s="7" t="n">
         <v>606</v>
@@ -11147,13 +11373,13 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D160" s="7" t="s">
         <v>75</v>
@@ -11162,7 +11388,7 @@
         <v>75</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>607</v>
@@ -11174,13 +11400,13 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D161" s="7" t="s">
         <v>75</v>
@@ -11189,7 +11415,7 @@
         <v>75</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G161" s="7" t="n">
         <v>608</v>
@@ -11201,13 +11427,13 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D162" s="7" t="s">
         <v>75</v>
@@ -11216,7 +11442,7 @@
         <v>75</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>609</v>
@@ -11228,13 +11454,13 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D163" s="7" t="s">
         <v>75</v>
@@ -11243,7 +11469,7 @@
         <v>75</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G163" s="7" t="n">
         <v>610</v>
@@ -11255,13 +11481,13 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D164" s="7" t="s">
         <v>75</v>
@@ -11270,7 +11496,7 @@
         <v>75</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G164" s="7" t="n">
         <v>611</v>
@@ -11282,13 +11508,13 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>75</v>
@@ -11297,7 +11523,7 @@
         <v>75</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G165" s="7" t="n">
         <v>612</v>
@@ -11309,13 +11535,13 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D166" s="7" t="s">
         <v>75</v>
@@ -11324,7 +11550,7 @@
         <v>75</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G166" s="7" t="n">
         <v>801</v>
@@ -11336,13 +11562,13 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D167" s="7" t="s">
         <v>75</v>
@@ -11351,7 +11577,7 @@
         <v>75</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G167" s="7" t="n">
         <v>802</v>
@@ -11363,13 +11589,13 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D168" s="7" t="s">
         <v>75</v>
@@ -11378,7 +11604,7 @@
         <v>75</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G168" s="7" t="n">
         <v>803</v>
@@ -11390,13 +11616,13 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D169" s="7" t="s">
         <v>75</v>
@@ -11405,7 +11631,7 @@
         <v>75</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G169" s="7" t="n">
         <v>804</v>
@@ -11417,13 +11643,13 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D170" s="7" t="s">
         <v>75</v>
@@ -11432,7 +11658,7 @@
         <v>75</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G170" s="7" t="n">
         <v>805</v>
@@ -11444,13 +11670,13 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D171" s="7" t="s">
         <v>75</v>
@@ -11459,7 +11685,7 @@
         <v>75</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G171" s="7" t="n">
         <v>806</v>
@@ -11471,13 +11697,13 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D172" s="7" t="s">
         <v>75</v>
@@ -11486,7 +11712,7 @@
         <v>75</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>807</v>
@@ -11498,13 +11724,13 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D173" s="7" t="s">
         <v>75</v>
@@ -11513,7 +11739,7 @@
         <v>75</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G173" s="7" t="n">
         <v>808</v>
@@ -11525,13 +11751,13 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D174" s="7" t="s">
         <v>75</v>
@@ -11540,7 +11766,7 @@
         <v>75</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>809</v>
@@ -11552,13 +11778,13 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D175" s="7" t="s">
         <v>75</v>
@@ -11567,7 +11793,7 @@
         <v>75</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G175" s="7" t="n">
         <v>901</v>
@@ -11579,13 +11805,13 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D176" s="7" t="s">
         <v>75</v>
@@ -11594,7 +11820,7 @@
         <v>75</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>902</v>
@@ -11606,13 +11832,13 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D177" s="7" t="s">
         <v>75</v>
@@ -11621,7 +11847,7 @@
         <v>75</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G177" s="7" t="n">
         <v>903</v>
@@ -11633,13 +11859,13 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D178" s="7" t="s">
         <v>75</v>
@@ -11648,7 +11874,7 @@
         <v>75</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>904</v>
@@ -11710,7 +11936,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -11723,13 +11949,13 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B182" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D182" s="12" t="s">
         <v>75</v>
@@ -11738,7 +11964,7 @@
         <v>75</v>
       </c>
       <c r="F182" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G182" s="12" t="n">
         <v>20001</v>
@@ -11747,18 +11973,18 @@
         <v>1</v>
       </c>
       <c r="I182" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B183" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D183" s="12" t="s">
         <v>75</v>
@@ -11767,7 +11993,7 @@
         <v>75</v>
       </c>
       <c r="F183" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G183" s="12" t="n">
         <v>20002</v>
@@ -11776,18 +12002,18 @@
         <v>1</v>
       </c>
       <c r="I183" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B184" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D184" s="12" t="s">
         <v>75</v>
@@ -11796,7 +12022,7 @@
         <v>75</v>
       </c>
       <c r="F184" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G184" s="12" t="n">
         <v>20003</v>
@@ -11805,18 +12031,18 @@
         <v>1</v>
       </c>
       <c r="I184" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B185" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D185" s="12" t="s">
         <v>75</v>
@@ -11825,7 +12051,7 @@
         <v>75</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G185" s="12" t="n">
         <v>20004</v>
@@ -11834,18 +12060,18 @@
         <v>1</v>
       </c>
       <c r="I185" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B186" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D186" s="12" t="s">
         <v>75</v>
@@ -11854,7 +12080,7 @@
         <v>75</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G186" s="12" t="n">
         <v>20005</v>
@@ -11863,18 +12089,18 @@
         <v>1</v>
       </c>
       <c r="I186" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B187" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D187" s="12" t="s">
         <v>75</v>
@@ -11883,7 +12109,7 @@
         <v>75</v>
       </c>
       <c r="F187" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G187" s="12" t="n">
         <v>20006</v>
@@ -11892,18 +12118,18 @@
         <v>1</v>
       </c>
       <c r="I187" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D188" s="12" t="s">
         <v>75</v>
@@ -11912,7 +12138,7 @@
         <v>75</v>
       </c>
       <c r="F188" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G188" s="12" t="n">
         <v>20007</v>
@@ -11921,18 +12147,18 @@
         <v>1</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D189" s="12" t="s">
         <v>75</v>
@@ -11941,7 +12167,7 @@
         <v>75</v>
       </c>
       <c r="F189" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G189" s="12" t="n">
         <v>20008</v>
@@ -11950,18 +12176,18 @@
         <v>1</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D190" s="12" t="s">
         <v>75</v>
@@ -11970,7 +12196,7 @@
         <v>75</v>
       </c>
       <c r="F190" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G190" s="12" t="n">
         <v>30001</v>
@@ -11979,18 +12205,18 @@
         <v>1</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D191" s="12" t="s">
         <v>75</v>
@@ -11999,7 +12225,7 @@
         <v>75</v>
       </c>
       <c r="F191" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G191" s="12" t="n">
         <v>30002</v>
@@ -12008,18 +12234,18 @@
         <v>1</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D192" s="12" t="s">
         <v>75</v>
@@ -12028,7 +12254,7 @@
         <v>75</v>
       </c>
       <c r="F192" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G192" s="12" t="n">
         <v>30003</v>
@@ -12037,18 +12263,18 @@
         <v>1</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B193" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D193" s="12" t="s">
         <v>75</v>
@@ -12057,7 +12283,7 @@
         <v>75</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G193" s="12" t="n">
         <v>30004</v>
@@ -12066,18 +12292,18 @@
         <v>1</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D194" s="12" t="s">
         <v>75</v>
@@ -12086,7 +12312,7 @@
         <v>75</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G194" s="12" t="n">
         <v>30005</v>
@@ -12095,18 +12321,18 @@
         <v>1</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D195" s="12" t="s">
         <v>75</v>
@@ -12115,7 +12341,7 @@
         <v>75</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G195" s="12" t="n">
         <v>30006</v>
@@ -12124,18 +12350,18 @@
         <v>1</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D196" s="12" t="s">
         <v>75</v>
@@ -12144,7 +12370,7 @@
         <v>75</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G196" s="12" t="n">
         <v>40001</v>
@@ -12153,18 +12379,18 @@
         <v>1</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D197" s="12" t="s">
         <v>75</v>
@@ -12173,7 +12399,7 @@
         <v>75</v>
       </c>
       <c r="F197" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G197" s="12" t="n">
         <v>60001</v>
@@ -12182,18 +12408,18 @@
         <v>1</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D198" s="12" t="s">
         <v>75</v>
@@ -12202,7 +12428,7 @@
         <v>75</v>
       </c>
       <c r="F198" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G198" s="12" t="n">
         <v>60002</v>
@@ -12211,18 +12437,18 @@
         <v>1</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B199" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D199" s="12" t="s">
         <v>75</v>
@@ -12231,7 +12457,7 @@
         <v>75</v>
       </c>
       <c r="F199" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G199" s="12" t="n">
         <v>60003</v>
@@ -12240,18 +12466,18 @@
         <v>1</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D200" s="12" t="s">
         <v>75</v>
@@ -12260,7 +12486,7 @@
         <v>75</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G200" s="12" t="n">
         <v>60004</v>
@@ -12269,18 +12495,18 @@
         <v>1</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D201" s="12" t="s">
         <v>75</v>
@@ -12289,7 +12515,7 @@
         <v>75</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G201" s="12" t="n">
         <v>60005</v>
@@ -12298,18 +12524,18 @@
         <v>1</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D202" s="12" t="s">
         <v>75</v>
@@ -12318,7 +12544,7 @@
         <v>75</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G202" s="12" t="n">
         <v>60006</v>
@@ -12327,18 +12553,18 @@
         <v>1</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D203" s="12" t="s">
         <v>75</v>
@@ -12347,7 +12573,7 @@
         <v>75</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G203" s="12" t="n">
         <v>60007</v>
@@ -12356,18 +12582,18 @@
         <v>1</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D204" s="12" t="s">
         <v>75</v>
@@ -12376,7 +12602,7 @@
         <v>75</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G204" s="12" t="n">
         <v>60008</v>
@@ -12385,7 +12611,7 @@
         <v>1</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12440,7 +12666,7 @@
     </row>
     <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -12453,13 +12679,13 @@
     </row>
     <row r="208" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D208" s="12" t="s">
         <v>75</v>
@@ -12468,7 +12694,7 @@
         <v>75</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G208" s="12" t="n">
         <v>30001</v>
@@ -12477,18 +12703,18 @@
         <v>1</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D209" s="12" t="s">
         <v>75</v>
@@ -12497,7 +12723,7 @@
         <v>75</v>
       </c>
       <c r="F209" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G209" s="12" t="n">
         <v>30002</v>
@@ -12506,18 +12732,18 @@
         <v>1</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D210" s="12" t="s">
         <v>75</v>
@@ -12526,7 +12752,7 @@
         <v>75</v>
       </c>
       <c r="F210" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G210" s="12" t="n">
         <v>30003</v>
@@ -12535,18 +12761,18 @@
         <v>1</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D211" s="12" t="s">
         <v>75</v>
@@ -12555,7 +12781,7 @@
         <v>75</v>
       </c>
       <c r="F211" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G211" s="12" t="n">
         <v>30004</v>
@@ -12564,18 +12790,18 @@
         <v>1</v>
       </c>
       <c r="I211" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B212" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D212" s="12" t="s">
         <v>75</v>
@@ -12584,7 +12810,7 @@
         <v>75</v>
       </c>
       <c r="F212" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G212" s="12" t="n">
         <v>30005</v>
@@ -12593,18 +12819,18 @@
         <v>1</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B213" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D213" s="12" t="s">
         <v>75</v>
@@ -12613,7 +12839,7 @@
         <v>75</v>
       </c>
       <c r="F213" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G213" s="12" t="n">
         <v>30006</v>
@@ -12622,18 +12848,18 @@
         <v>1</v>
       </c>
       <c r="I213" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B214" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D214" s="12" t="s">
         <v>75</v>
@@ -12642,7 +12868,7 @@
         <v>75</v>
       </c>
       <c r="F214" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G214" s="12" t="n">
         <v>40001</v>
@@ -12651,18 +12877,18 @@
         <v>1</v>
       </c>
       <c r="I214" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B215" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D215" s="12" t="s">
         <v>75</v>
@@ -12671,7 +12897,7 @@
         <v>75</v>
       </c>
       <c r="F215" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G215" s="12" t="n">
         <v>45001</v>
@@ -12680,18 +12906,18 @@
         <v>1</v>
       </c>
       <c r="I215" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B216" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D216" s="12" t="s">
         <v>75</v>
@@ -12700,7 +12926,7 @@
         <v>75</v>
       </c>
       <c r="F216" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G216" s="12" t="n">
         <v>60001</v>
@@ -12709,18 +12935,18 @@
         <v>1</v>
       </c>
       <c r="I216" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B217" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D217" s="12" t="s">
         <v>75</v>
@@ -12729,7 +12955,7 @@
         <v>75</v>
       </c>
       <c r="F217" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G217" s="12" t="n">
         <v>60002</v>
@@ -12738,18 +12964,18 @@
         <v>1</v>
       </c>
       <c r="I217" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B218" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D218" s="12" t="s">
         <v>75</v>
@@ -12758,7 +12984,7 @@
         <v>75</v>
       </c>
       <c r="F218" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G218" s="12" t="n">
         <v>60003</v>
@@ -12767,18 +12993,18 @@
         <v>1</v>
       </c>
       <c r="I218" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B219" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D219" s="12" t="s">
         <v>75</v>
@@ -12787,7 +13013,7 @@
         <v>75</v>
       </c>
       <c r="F219" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G219" s="12" t="n">
         <v>60004</v>
@@ -12796,18 +13022,18 @@
         <v>1</v>
       </c>
       <c r="I219" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B220" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D220" s="12" t="s">
         <v>75</v>
@@ -12816,7 +13042,7 @@
         <v>75</v>
       </c>
       <c r="F220" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G220" s="12" t="n">
         <v>60005</v>
@@ -12825,18 +13051,18 @@
         <v>1</v>
       </c>
       <c r="I220" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B221" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D221" s="12" t="s">
         <v>75</v>
@@ -12845,7 +13071,7 @@
         <v>75</v>
       </c>
       <c r="F221" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G221" s="12" t="n">
         <v>60006</v>
@@ -12854,18 +13080,18 @@
         <v>1</v>
       </c>
       <c r="I221" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B222" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D222" s="12" t="s">
         <v>75</v>
@@ -12874,7 +13100,7 @@
         <v>75</v>
       </c>
       <c r="F222" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G222" s="12" t="n">
         <v>60007</v>
@@ -12883,18 +13109,18 @@
         <v>1</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B223" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D223" s="12" t="s">
         <v>75</v>
@@ -12903,7 +13129,7 @@
         <v>75</v>
       </c>
       <c r="F223" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G223" s="12" t="n">
         <v>60008</v>
@@ -12912,7 +13138,7 @@
         <v>1</v>
       </c>
       <c r="I223" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12967,7 +13193,7 @@
     </row>
     <row r="226" customFormat="false" ht="10.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="5" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -12998,7 +13224,7 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="H227" s="7" t="n">
         <v>2</v>
@@ -13524,7 +13750,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B247" s="7" t="s">
         <v>75</v>
@@ -13582,7 +13808,7 @@
     </row>
     <row r="249" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="7" t="s">
-        <v>305</v>
+        <v>240</v>
       </c>
       <c r="B249" s="7" t="s">
         <v>75</v>
@@ -13600,18 +13826,18 @@
         <v>26</v>
       </c>
       <c r="G249" s="10" t="s">
-        <v>306</v>
+        <v>241</v>
       </c>
       <c r="H249" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I249" s="7" t="s">
-        <v>358</v>
+        <v>314</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B250" s="12" t="s">
         <v>75</v>
@@ -13629,7 +13855,7 @@
         <v>26</v>
       </c>
       <c r="G250" s="12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H250" s="12" t="n">
         <v>2</v>
@@ -13640,7 +13866,7 @@
     </row>
     <row r="251" customFormat="false" ht="27.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B251" s="12" t="s">
         <v>75</v>
@@ -13658,7 +13884,7 @@
         <v>26</v>
       </c>
       <c r="G251" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H251" s="12" t="n">
         <v>2</v>
@@ -13669,7 +13895,7 @@
     </row>
     <row r="252" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="11" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B252" s="12" t="s">
         <v>75</v>
@@ -13687,7 +13913,7 @@
         <v>26</v>
       </c>
       <c r="G252" s="13" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="H252" s="12" t="n">
         <v>2</v>
@@ -13698,7 +13924,7 @@
     </row>
     <row r="253" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="11" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B253" s="12" t="s">
         <v>75</v>
@@ -13716,7 +13942,7 @@
         <v>26</v>
       </c>
       <c r="G253" s="13" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="H253" s="12" t="n">
         <v>2</v>
@@ -13745,7 +13971,7 @@
         <v>26</v>
       </c>
       <c r="G254" s="13" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="H254" s="12" t="n">
         <v>2</v>
@@ -13756,7 +13982,7 @@
     </row>
     <row r="255" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="11" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B255" s="12" t="s">
         <v>75</v>
@@ -13774,13 +14000,13 @@
         <v>26</v>
       </c>
       <c r="G255" s="13" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="H255" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I255" s="12" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -14072,7 +14298,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>75</v>
@@ -14101,7 +14327,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>75</v>
@@ -14130,7 +14356,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>75</v>
@@ -14159,7 +14385,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>75</v>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -8054,6 +8054,7 @@
     <mergeCell ref="D174:D175"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="F174:F175"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="I174:I175"/>
     <mergeCell ref="D112:D113"/>
     <mergeCell ref="I6:I7"/>
@@ -8062,9 +8063,8 @@
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="A176:I176"/>
     <mergeCell ref="A114:I114"/>
+    <mergeCell ref="A112:A113"/>
     <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12274,14 +12274,16 @@
         <is>
           <t>Internal Only. Not visible to customer. 
 Indicates the state machine of calibration
-0: Calibration Not Initiated. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 20A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
-17,18,19,20: High Point Calibration In Progress
-21: High Point Calibration Done. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 4A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
-22,23,24: Mid Point Calibration In Progress
-25: Mid Point Calibration Done. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 0.4A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
-26,27,28: Low Point Calibration In Progress
-29: Low Point Calibration Done. Set Fan 1 Current and Fan 2 Current to 0.1A each. And then set Advance Calibration Flag.
-30: Fan Calibration In Progress
+0: Calibration Not Initiated. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 100A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
+17,18,19,20: Extra-High Point Calibration In Progress (V/I + PF at 100A)
+21: Extra-High Point Calibration Done. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 20A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
+22,23,24: High Point Calibration In Progress
+25: High Point Calibration Done. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 4A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
+26,27,28: Mid Point Calibration In Progress
+29: Mid Point Calibration Done. Set Grid R/Y/B and Solar R/Y/B Voltages to 240V. Set Grid R/Y/B and Solar R/Y/B current to 0.4A. Set Grid R/Y/B and Solar R/Y/B Power Factor to 0.5. And then set Advance Calibration Flag.
+30,31,32: Low Point Calibration In Progress
+33: Low Point Calibration Done. Set Fan 1 Current and Fan 2 Current to 0.1A each. And then set Advance Calibration Flag.
+34: Fan Calibration In Progress
 127: Calibration Completed Successfully
 126: Error occured during calibration. Please restart controller</t>
         </is>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -8078,7 +8078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I255"/>
+  <dimension ref="A1:I258"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="46.94" customWidth="1" style="18" min="1" max="1"/>
@@ -12331,220 +12331,229 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1" s="19">
-      <c r="A117" s="21" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="31" t="inlineStr">
+        <is>
+          <t>Switch Increment - Press Counter</t>
+        </is>
+      </c>
+      <c r="B117" s="32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C117" s="32" t="inlineStr">
+        <is>
+          <t>Unsigned Integer</t>
+        </is>
+      </c>
+      <c r="D117" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="32" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G117" s="33" t="inlineStr">
+        <is>
+          <t>50017</t>
+        </is>
+      </c>
+      <c r="H117" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" s="32" t="inlineStr">
+        <is>
+          <t>Internal Only. Not visible to customer.
+Increments once each time the Increment switch transitions from released to pressed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="31" t="inlineStr">
+        <is>
+          <t>Switch Decrement - Press Counter</t>
+        </is>
+      </c>
+      <c r="B118" s="32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C118" s="32" t="inlineStr">
+        <is>
+          <t>Unsigned Integer</t>
+        </is>
+      </c>
+      <c r="D118" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="32" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G118" s="33" t="inlineStr">
+        <is>
+          <t>50019</t>
+        </is>
+      </c>
+      <c r="H118" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I118" s="32" t="inlineStr">
+        <is>
+          <t>Internal Only. Not visible to customer.
+Increments once each time the Decrement switch transitions from released to pressed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="31" t="inlineStr">
+        <is>
+          <t>Switch Next - Press Counter</t>
+        </is>
+      </c>
+      <c r="B119" s="32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C119" s="32" t="inlineStr">
+        <is>
+          <t>Unsigned Integer</t>
+        </is>
+      </c>
+      <c r="D119" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E119" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="32" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G119" s="33" t="inlineStr">
+        <is>
+          <t>50021</t>
+        </is>
+      </c>
+      <c r="H119" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I119" s="32" t="inlineStr">
+        <is>
+          <t>Internal Only. Not visible to customer.
+Increments once each time the Next switch transitions from released to pressed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1" s="19">
+      <c r="A120" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Parameters </t>
         </is>
       </c>
-      <c r="B117" s="22" t="inlineStr">
+      <c r="B120" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Units of </t>
         </is>
       </c>
-      <c r="C117" s="22" t="inlineStr">
+      <c r="C120" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Data Type </t>
         </is>
       </c>
-      <c r="D117" s="21" t="inlineStr">
+      <c r="D120" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Size in byte </t>
         </is>
       </c>
-      <c r="E117" s="22" t="inlineStr">
+      <c r="E120" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversion </t>
         </is>
       </c>
-      <c r="F117" s="21" t="inlineStr">
+      <c r="F120" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Type of Register </t>
         </is>
       </c>
-      <c r="G117" s="22" t="inlineStr">
+      <c r="G120" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Modbus </t>
         </is>
       </c>
-      <c r="H117" s="22" t="inlineStr">
+      <c r="H120" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">No. of </t>
         </is>
       </c>
-      <c r="I117" s="21" t="inlineStr">
+      <c r="I120" s="21" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1" s="19">
-      <c r="A118" s="23" t="n"/>
-      <c r="B118" s="22" t="inlineStr">
+    <row r="121" ht="15" customHeight="1" s="19">
+      <c r="A121" s="23" t="n"/>
+      <c r="B121" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Measurement </t>
         </is>
       </c>
-      <c r="C118" s="22" t="inlineStr">
+      <c r="C121" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">(Float/Hex etc.) </t>
         </is>
       </c>
-      <c r="D118" s="23" t="n"/>
-      <c r="E118" s="22" t="inlineStr">
+      <c r="D121" s="23" t="n"/>
+      <c r="E121" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Multiplier to read the data </t>
         </is>
       </c>
-      <c r="F118" s="23" t="n"/>
-      <c r="G118" s="22" t="inlineStr">
+      <c r="F121" s="23" t="n"/>
+      <c r="G121" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Register Address </t>
         </is>
       </c>
-      <c r="H118" s="22" t="inlineStr">
+      <c r="H121" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Registers required </t>
         </is>
       </c>
-      <c r="I118" s="23" t="n"/>
-    </row>
-    <row r="119" ht="15" customHeight="1" s="19">
-      <c r="A119" s="24" t="inlineStr">
+      <c r="I121" s="23" t="n"/>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="19">
+      <c r="A122" s="24" t="inlineStr">
         <is>
           <t>READ INPUT STATUS (Function Code: 0x02)</t>
         </is>
       </c>
-      <c r="B119" s="25" t="n"/>
-      <c r="C119" s="25" t="n"/>
-      <c r="D119" s="25" t="n"/>
-      <c r="E119" s="25" t="n"/>
-      <c r="F119" s="25" t="n"/>
-      <c r="G119" s="25" t="n"/>
-      <c r="H119" s="25" t="n"/>
-      <c r="I119" s="25" t="n"/>
-    </row>
-    <row r="120" ht="15" customHeight="1" s="19">
-      <c r="A120" s="27" t="inlineStr">
-        <is>
-          <t>Grid Phase 1 Contactor On Feedback</t>
-        </is>
-      </c>
-      <c r="B120" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C120" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIT </t>
-        </is>
-      </c>
-      <c r="D120" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E120" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F120" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Input Status </t>
-        </is>
-      </c>
-      <c r="G120" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I120" s="27" t="n"/>
-    </row>
-    <row r="121" ht="15" customHeight="1" s="19">
-      <c r="A121" s="27" t="inlineStr">
-        <is>
-          <t>Grid Phase 2 Contactor On Feedback</t>
-        </is>
-      </c>
-      <c r="B121" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C121" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIT </t>
-        </is>
-      </c>
-      <c r="D121" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E121" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F121" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Input Status </t>
-        </is>
-      </c>
-      <c r="G121" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H121" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I121" s="27" t="n"/>
-    </row>
-    <row r="122" ht="15" customHeight="1" s="19">
-      <c r="A122" s="27" t="inlineStr">
-        <is>
-          <t>Grid Phase 3 Contactor On Feedback</t>
-        </is>
-      </c>
-      <c r="B122" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C122" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIT </t>
-        </is>
-      </c>
-      <c r="D122" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E122" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F122" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Input Status </t>
-        </is>
-      </c>
-      <c r="G122" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="H122" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I122" s="27" t="n"/>
+      <c r="B122" s="25" t="n"/>
+      <c r="C122" s="25" t="n"/>
+      <c r="D122" s="25" t="n"/>
+      <c r="E122" s="25" t="n"/>
+      <c r="F122" s="25" t="n"/>
+      <c r="G122" s="25" t="n"/>
+      <c r="H122" s="25" t="n"/>
+      <c r="I122" s="25" t="n"/>
     </row>
     <row r="123" ht="15" customHeight="1" s="19">
       <c r="A123" s="27" t="inlineStr">
         <is>
-          <t>Load On Solar Contactor On Feedback</t>
+          <t>Grid Phase 1 Contactor On Feedback</t>
         </is>
       </c>
       <c r="B123" s="27" t="inlineStr">
@@ -12573,7 +12582,7 @@
         </is>
       </c>
       <c r="G123" s="27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H123" s="27" t="n">
         <v>1</v>
@@ -12583,7 +12592,7 @@
     <row r="124" ht="15" customHeight="1" s="19">
       <c r="A124" s="27" t="inlineStr">
         <is>
-          <t>Load On Grid  Contactor On Feedback</t>
+          <t>Grid Phase 2 Contactor On Feedback</t>
         </is>
       </c>
       <c r="B124" s="27" t="inlineStr">
@@ -12612,7 +12621,7 @@
         </is>
       </c>
       <c r="G124" s="27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H124" s="27" t="n">
         <v>1</v>
@@ -12622,7 +12631,7 @@
     <row r="125" ht="15" customHeight="1" s="19">
       <c r="A125" s="27" t="inlineStr">
         <is>
-          <t>Solar Neutral Earth Contactor On Feedback</t>
+          <t>Grid Phase 3 Contactor On Feedback</t>
         </is>
       </c>
       <c r="B125" s="27" t="inlineStr">
@@ -12651,7 +12660,7 @@
         </is>
       </c>
       <c r="G125" s="27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H125" s="27" t="n">
         <v>1</v>
@@ -12661,7 +12670,7 @@
     <row r="126" ht="15" customHeight="1" s="19">
       <c r="A126" s="27" t="inlineStr">
         <is>
-          <t>DG Off</t>
+          <t>Load On Solar Contactor On Feedback</t>
         </is>
       </c>
       <c r="B126" s="27" t="inlineStr">
@@ -12690,7 +12699,7 @@
         </is>
       </c>
       <c r="G126" s="27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H126" s="27" t="n">
         <v>1</v>
@@ -12700,7 +12709,7 @@
     <row r="127" ht="15" customHeight="1" s="19">
       <c r="A127" s="27" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Load On Grid  Contactor On Feedback</t>
         </is>
       </c>
       <c r="B127" s="27" t="inlineStr">
@@ -12729,7 +12738,7 @@
         </is>
       </c>
       <c r="G127" s="27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H127" s="27" t="n">
         <v>1</v>
@@ -12739,7 +12748,7 @@
     <row r="128" ht="15" customHeight="1" s="19">
       <c r="A128" s="27" t="inlineStr">
         <is>
-          <t>DC Aux Power Available</t>
+          <t>Solar Neutral Earth Contactor On Feedback</t>
         </is>
       </c>
       <c r="B128" s="27" t="inlineStr">
@@ -12768,7 +12777,7 @@
         </is>
       </c>
       <c r="G128" s="27" t="n">
-        <v>201</v>
+        <v>6</v>
       </c>
       <c r="H128" s="27" t="n">
         <v>1</v>
@@ -12778,7 +12787,7 @@
     <row r="129" ht="15" customHeight="1" s="19">
       <c r="A129" s="27" t="inlineStr">
         <is>
-          <t>AC Aux Power Available</t>
+          <t>DG Off</t>
         </is>
       </c>
       <c r="B129" s="27" t="inlineStr">
@@ -12807,7 +12816,7 @@
         </is>
       </c>
       <c r="G129" s="27" t="n">
-        <v>202</v>
+        <v>7</v>
       </c>
       <c r="H129" s="27" t="n">
         <v>1</v>
@@ -12817,7 +12826,7 @@
     <row r="130" ht="15" customHeight="1" s="19">
       <c r="A130" s="27" t="inlineStr">
         <is>
-          <t>Grid R Phase Under Voltage</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="B130" s="27" t="inlineStr">
@@ -12846,7 +12855,7 @@
         </is>
       </c>
       <c r="G130" s="27" t="n">
-        <v>301</v>
+        <v>8</v>
       </c>
       <c r="H130" s="27" t="n">
         <v>1</v>
@@ -12856,7 +12865,7 @@
     <row r="131" ht="15" customHeight="1" s="19">
       <c r="A131" s="27" t="inlineStr">
         <is>
-          <t>Grid R Phase Over Voltage</t>
+          <t>DC Aux Power Available</t>
         </is>
       </c>
       <c r="B131" s="27" t="inlineStr">
@@ -12885,7 +12894,7 @@
         </is>
       </c>
       <c r="G131" s="27" t="n">
-        <v>302</v>
+        <v>201</v>
       </c>
       <c r="H131" s="27" t="n">
         <v>1</v>
@@ -12895,7 +12904,7 @@
     <row r="132" ht="15" customHeight="1" s="19">
       <c r="A132" s="27" t="inlineStr">
         <is>
-          <t>Grid Y Phase Under Voltage</t>
+          <t>AC Aux Power Available</t>
         </is>
       </c>
       <c r="B132" s="27" t="inlineStr">
@@ -12924,7 +12933,7 @@
         </is>
       </c>
       <c r="G132" s="27" t="n">
-        <v>303</v>
+        <v>202</v>
       </c>
       <c r="H132" s="27" t="n">
         <v>1</v>
@@ -12934,7 +12943,7 @@
     <row r="133" ht="15" customHeight="1" s="19">
       <c r="A133" s="27" t="inlineStr">
         <is>
-          <t>Grid Y Phase Over Voltage</t>
+          <t>Grid R Phase Under Voltage</t>
         </is>
       </c>
       <c r="B133" s="27" t="inlineStr">
@@ -12963,7 +12972,7 @@
         </is>
       </c>
       <c r="G133" s="27" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H133" s="27" t="n">
         <v>1</v>
@@ -12973,7 +12982,7 @@
     <row r="134" ht="15" customHeight="1" s="19">
       <c r="A134" s="27" t="inlineStr">
         <is>
-          <t>Grid B Phase Under Voltage</t>
+          <t>Grid R Phase Over Voltage</t>
         </is>
       </c>
       <c r="B134" s="27" t="inlineStr">
@@ -13002,7 +13011,7 @@
         </is>
       </c>
       <c r="G134" s="27" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H134" s="27" t="n">
         <v>1</v>
@@ -13012,7 +13021,7 @@
     <row r="135" ht="15" customHeight="1" s="19">
       <c r="A135" s="27" t="inlineStr">
         <is>
-          <t>Grid B Phase Over Voltage</t>
+          <t>Grid Y Phase Under Voltage</t>
         </is>
       </c>
       <c r="B135" s="27" t="inlineStr">
@@ -13041,7 +13050,7 @@
         </is>
       </c>
       <c r="G135" s="27" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H135" s="27" t="n">
         <v>1</v>
@@ -13051,7 +13060,7 @@
     <row r="136" ht="15" customHeight="1" s="19">
       <c r="A136" s="27" t="inlineStr">
         <is>
-          <t>Solar R Phase Under Voltage</t>
+          <t>Grid Y Phase Over Voltage</t>
         </is>
       </c>
       <c r="B136" s="27" t="inlineStr">
@@ -13080,7 +13089,7 @@
         </is>
       </c>
       <c r="G136" s="27" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H136" s="27" t="n">
         <v>1</v>
@@ -13090,7 +13099,7 @@
     <row r="137" ht="15" customHeight="1" s="19">
       <c r="A137" s="27" t="inlineStr">
         <is>
-          <t>Solar R Phase Over Voltage</t>
+          <t>Grid B Phase Under Voltage</t>
         </is>
       </c>
       <c r="B137" s="27" t="inlineStr">
@@ -13119,7 +13128,7 @@
         </is>
       </c>
       <c r="G137" s="27" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H137" s="27" t="n">
         <v>1</v>
@@ -13129,7 +13138,7 @@
     <row r="138" ht="15" customHeight="1" s="19">
       <c r="A138" s="27" t="inlineStr">
         <is>
-          <t>Solar Y Phase Under Voltage</t>
+          <t>Grid B Phase Over Voltage</t>
         </is>
       </c>
       <c r="B138" s="27" t="inlineStr">
@@ -13158,7 +13167,7 @@
         </is>
       </c>
       <c r="G138" s="27" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H138" s="27" t="n">
         <v>1</v>
@@ -13168,7 +13177,7 @@
     <row r="139" ht="15" customHeight="1" s="19">
       <c r="A139" s="27" t="inlineStr">
         <is>
-          <t>Solar Y Phase Over Voltage</t>
+          <t>Solar R Phase Under Voltage</t>
         </is>
       </c>
       <c r="B139" s="27" t="inlineStr">
@@ -13197,7 +13206,7 @@
         </is>
       </c>
       <c r="G139" s="27" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H139" s="27" t="n">
         <v>1</v>
@@ -13207,7 +13216,7 @@
     <row r="140" ht="15" customHeight="1" s="19">
       <c r="A140" s="27" t="inlineStr">
         <is>
-          <t>Solar B Phase Under Voltage</t>
+          <t>Solar R Phase Over Voltage</t>
         </is>
       </c>
       <c r="B140" s="27" t="inlineStr">
@@ -13236,7 +13245,7 @@
         </is>
       </c>
       <c r="G140" s="27" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H140" s="27" t="n">
         <v>1</v>
@@ -13246,7 +13255,7 @@
     <row r="141" ht="15" customHeight="1" s="19">
       <c r="A141" s="27" t="inlineStr">
         <is>
-          <t>Solar B Phase Over Voltage</t>
+          <t>Solar Y Phase Under Voltage</t>
         </is>
       </c>
       <c r="B141" s="27" t="inlineStr">
@@ -13275,7 +13284,7 @@
         </is>
       </c>
       <c r="G141" s="27" t="n">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H141" s="27" t="n">
         <v>1</v>
@@ -13285,7 +13294,7 @@
     <row r="142" ht="15" customHeight="1" s="19">
       <c r="A142" s="27" t="inlineStr">
         <is>
-          <t>Grid R Phase Loss</t>
+          <t>Solar Y Phase Over Voltage</t>
         </is>
       </c>
       <c r="B142" s="27" t="inlineStr">
@@ -13314,7 +13323,7 @@
         </is>
       </c>
       <c r="G142" s="27" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H142" s="27" t="n">
         <v>1</v>
@@ -13324,7 +13333,7 @@
     <row r="143" ht="15" customHeight="1" s="19">
       <c r="A143" s="27" t="inlineStr">
         <is>
-          <t>Grid Y Phase Loss</t>
+          <t>Solar B Phase Under Voltage</t>
         </is>
       </c>
       <c r="B143" s="27" t="inlineStr">
@@ -13353,7 +13362,7 @@
         </is>
       </c>
       <c r="G143" s="27" t="n">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H143" s="27" t="n">
         <v>1</v>
@@ -13363,7 +13372,7 @@
     <row r="144" ht="15" customHeight="1" s="19">
       <c r="A144" s="27" t="inlineStr">
         <is>
-          <t>Grid B Phase Loss</t>
+          <t>Solar B Phase Over Voltage</t>
         </is>
       </c>
       <c r="B144" s="27" t="inlineStr">
@@ -13392,7 +13401,7 @@
         </is>
       </c>
       <c r="G144" s="27" t="n">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H144" s="27" t="n">
         <v>1</v>
@@ -13402,7 +13411,7 @@
     <row r="145" ht="15" customHeight="1" s="19">
       <c r="A145" s="27" t="inlineStr">
         <is>
-          <t>Solar R Phase Loss</t>
+          <t>Grid R Phase Loss</t>
         </is>
       </c>
       <c r="B145" s="27" t="inlineStr">
@@ -13431,7 +13440,7 @@
         </is>
       </c>
       <c r="G145" s="27" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H145" s="27" t="n">
         <v>1</v>
@@ -13441,7 +13450,7 @@
     <row r="146" ht="15" customHeight="1" s="19">
       <c r="A146" s="27" t="inlineStr">
         <is>
-          <t>Solar Y Phase Loss</t>
+          <t>Grid Y Phase Loss</t>
         </is>
       </c>
       <c r="B146" s="27" t="inlineStr">
@@ -13470,7 +13479,7 @@
         </is>
       </c>
       <c r="G146" s="27" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H146" s="27" t="n">
         <v>1</v>
@@ -13480,7 +13489,7 @@
     <row r="147" ht="15" customHeight="1" s="19">
       <c r="A147" s="27" t="inlineStr">
         <is>
-          <t>Solar B Phase Loss</t>
+          <t>Grid B Phase Loss</t>
         </is>
       </c>
       <c r="B147" s="27" t="inlineStr">
@@ -13509,7 +13518,7 @@
         </is>
       </c>
       <c r="G147" s="27" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="H147" s="27" t="n">
         <v>1</v>
@@ -13519,7 +13528,7 @@
     <row r="148" ht="15" customHeight="1" s="19">
       <c r="A148" s="27" t="inlineStr">
         <is>
-          <t>Relay 1 Energized (Grid R Phase Contactor Coil Deenergized)</t>
+          <t>Solar R Phase Loss</t>
         </is>
       </c>
       <c r="B148" s="27" t="inlineStr">
@@ -13548,7 +13557,7 @@
         </is>
       </c>
       <c r="G148" s="27" t="n">
-        <v>401</v>
+        <v>316</v>
       </c>
       <c r="H148" s="27" t="n">
         <v>1</v>
@@ -13558,7 +13567,7 @@
     <row r="149" ht="15" customHeight="1" s="19">
       <c r="A149" s="27" t="inlineStr">
         <is>
-          <t>Relay 2 Energized (Grid Y Phase Contactor Coil Deenergized)</t>
+          <t>Solar Y Phase Loss</t>
         </is>
       </c>
       <c r="B149" s="27" t="inlineStr">
@@ -13587,7 +13596,7 @@
         </is>
       </c>
       <c r="G149" s="27" t="n">
-        <v>402</v>
+        <v>317</v>
       </c>
       <c r="H149" s="27" t="n">
         <v>1</v>
@@ -13597,7 +13606,7 @@
     <row r="150" ht="15" customHeight="1" s="19">
       <c r="A150" s="27" t="inlineStr">
         <is>
-          <t>Relay 3 Energized (Grid B Phase Contactor Coil Deenergized)</t>
+          <t>Solar B Phase Loss</t>
         </is>
       </c>
       <c r="B150" s="27" t="inlineStr">
@@ -13626,17 +13635,17 @@
         </is>
       </c>
       <c r="G150" s="27" t="n">
-        <v>403</v>
+        <v>318</v>
       </c>
       <c r="H150" s="27" t="n">
         <v>1</v>
       </c>
       <c r="I150" s="27" t="n"/>
     </row>
-    <row r="151" ht="19.4" customHeight="1" s="19">
+    <row r="151" ht="15" customHeight="1" s="19">
       <c r="A151" s="27" t="inlineStr">
         <is>
-          <t>Relay 4 Energized (Load On Solar Contactor Coil Energized &amp; Solar Neutral To Earth Contactor Coil Energized)</t>
+          <t>Relay 1 Energized (Grid R Phase Contactor Coil Deenergized)</t>
         </is>
       </c>
       <c r="B151" s="27" t="inlineStr">
@@ -13665,17 +13674,17 @@
         </is>
       </c>
       <c r="G151" s="27" t="n">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H151" s="27" t="n">
         <v>1</v>
       </c>
       <c r="I151" s="27" t="n"/>
     </row>
-    <row r="152" ht="19.4" customHeight="1" s="19">
+    <row r="152" ht="15" customHeight="1" s="19">
       <c r="A152" s="27" t="inlineStr">
         <is>
-          <t>Relay 5 Energized (Load On Grid Contactor Coil Deenergized)</t>
+          <t>Relay 2 Energized (Grid Y Phase Contactor Coil Deenergized)</t>
         </is>
       </c>
       <c r="B152" s="27" t="inlineStr">
@@ -13704,7 +13713,7 @@
         </is>
       </c>
       <c r="G152" s="27" t="n">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H152" s="27" t="n">
         <v>1</v>
@@ -13714,7 +13723,7 @@
     <row r="153" ht="15" customHeight="1" s="19">
       <c r="A153" s="27" t="inlineStr">
         <is>
-          <t>Relay 6 Energized (Fans Output Deenergized)</t>
+          <t>Relay 3 Energized (Grid B Phase Contactor Coil Deenergized)</t>
         </is>
       </c>
       <c r="B153" s="27" t="inlineStr">
@@ -13743,17 +13752,17 @@
         </is>
       </c>
       <c r="G153" s="27" t="n">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H153" s="27" t="n">
         <v>1</v>
       </c>
       <c r="I153" s="27" t="n"/>
     </row>
-    <row r="154" ht="15" customHeight="1" s="19">
+    <row r="154" ht="19.4" customHeight="1" s="19">
       <c r="A154" s="27" t="inlineStr">
         <is>
-          <t>Grid R Phase Contactor Stuck Open Error Suspected</t>
+          <t>Relay 4 Energized (Load On Solar Contactor Coil Energized &amp; Solar Neutral To Earth Contactor Coil Energized)</t>
         </is>
       </c>
       <c r="B154" s="27" t="inlineStr">
@@ -13782,17 +13791,17 @@
         </is>
       </c>
       <c r="G154" s="27" t="n">
-        <v>601</v>
+        <v>404</v>
       </c>
       <c r="H154" s="27" t="n">
         <v>1</v>
       </c>
       <c r="I154" s="27" t="n"/>
     </row>
-    <row r="155" ht="15" customHeight="1" s="19">
+    <row r="155" ht="19.4" customHeight="1" s="19">
       <c r="A155" s="27" t="inlineStr">
         <is>
-          <t>Grid R Phase Contactor Stuck Closed Error Suspected</t>
+          <t>Relay 5 Energized (Load On Grid Contactor Coil Deenergized)</t>
         </is>
       </c>
       <c r="B155" s="27" t="inlineStr">
@@ -13821,7 +13830,7 @@
         </is>
       </c>
       <c r="G155" s="27" t="n">
-        <v>602</v>
+        <v>405</v>
       </c>
       <c r="H155" s="27" t="n">
         <v>1</v>
@@ -13831,7 +13840,7 @@
     <row r="156" ht="15" customHeight="1" s="19">
       <c r="A156" s="27" t="inlineStr">
         <is>
-          <t>Grid Y Phase Contactor Stuck Open Error Suspected</t>
+          <t>Relay 6 Energized (Fans Output Deenergized)</t>
         </is>
       </c>
       <c r="B156" s="27" t="inlineStr">
@@ -13860,7 +13869,7 @@
         </is>
       </c>
       <c r="G156" s="27" t="n">
-        <v>603</v>
+        <v>406</v>
       </c>
       <c r="H156" s="27" t="n">
         <v>1</v>
@@ -13870,7 +13879,7 @@
     <row r="157" ht="15" customHeight="1" s="19">
       <c r="A157" s="27" t="inlineStr">
         <is>
-          <t>Grid Y Phase Contactor Stuck Closed Error Suspected</t>
+          <t>Grid R Phase Contactor Stuck Open Error Suspected</t>
         </is>
       </c>
       <c r="B157" s="27" t="inlineStr">
@@ -13899,7 +13908,7 @@
         </is>
       </c>
       <c r="G157" s="27" t="n">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="H157" s="27" t="n">
         <v>1</v>
@@ -13909,7 +13918,7 @@
     <row r="158" ht="15" customHeight="1" s="19">
       <c r="A158" s="27" t="inlineStr">
         <is>
-          <t>Grid B Phase Contactor Stuck Open Error Suspected</t>
+          <t>Grid R Phase Contactor Stuck Closed Error Suspected</t>
         </is>
       </c>
       <c r="B158" s="27" t="inlineStr">
@@ -13938,7 +13947,7 @@
         </is>
       </c>
       <c r="G158" s="27" t="n">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="H158" s="27" t="n">
         <v>1</v>
@@ -13948,7 +13957,7 @@
     <row r="159" ht="15" customHeight="1" s="19">
       <c r="A159" s="27" t="inlineStr">
         <is>
-          <t>Grid B Phase Contactor Stuck Closed Error Suspected</t>
+          <t>Grid Y Phase Contactor Stuck Open Error Suspected</t>
         </is>
       </c>
       <c r="B159" s="27" t="inlineStr">
@@ -13977,7 +13986,7 @@
         </is>
       </c>
       <c r="G159" s="27" t="n">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="H159" s="27" t="n">
         <v>1</v>
@@ -13987,7 +13996,7 @@
     <row r="160" ht="15" customHeight="1" s="19">
       <c r="A160" s="27" t="inlineStr">
         <is>
-          <t>Load On Solar Contactor Stuck Open Error Suspected</t>
+          <t>Grid Y Phase Contactor Stuck Closed Error Suspected</t>
         </is>
       </c>
       <c r="B160" s="27" t="inlineStr">
@@ -14016,7 +14025,7 @@
         </is>
       </c>
       <c r="G160" s="27" t="n">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="H160" s="27" t="n">
         <v>1</v>
@@ -14026,7 +14035,7 @@
     <row r="161" ht="15" customHeight="1" s="19">
       <c r="A161" s="27" t="inlineStr">
         <is>
-          <t>Load On Solar Contactor Stuck Closed Error Suspected</t>
+          <t>Grid B Phase Contactor Stuck Open Error Suspected</t>
         </is>
       </c>
       <c r="B161" s="27" t="inlineStr">
@@ -14055,7 +14064,7 @@
         </is>
       </c>
       <c r="G161" s="27" t="n">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="H161" s="27" t="n">
         <v>1</v>
@@ -14065,7 +14074,7 @@
     <row r="162" ht="15" customHeight="1" s="19">
       <c r="A162" s="27" t="inlineStr">
         <is>
-          <t>Load On Grid Contactor Stuck Open Error Suspected</t>
+          <t>Grid B Phase Contactor Stuck Closed Error Suspected</t>
         </is>
       </c>
       <c r="B162" s="27" t="inlineStr">
@@ -14094,7 +14103,7 @@
         </is>
       </c>
       <c r="G162" s="27" t="n">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="H162" s="27" t="n">
         <v>1</v>
@@ -14104,7 +14113,7 @@
     <row r="163" ht="15" customHeight="1" s="19">
       <c r="A163" s="27" t="inlineStr">
         <is>
-          <t>Load On Grid Contactor Stuck Closed Error Suspected</t>
+          <t>Load On Solar Contactor Stuck Open Error Suspected</t>
         </is>
       </c>
       <c r="B163" s="27" t="inlineStr">
@@ -14133,7 +14142,7 @@
         </is>
       </c>
       <c r="G163" s="27" t="n">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H163" s="27" t="n">
         <v>1</v>
@@ -14143,7 +14152,7 @@
     <row r="164" ht="15" customHeight="1" s="19">
       <c r="A164" s="27" t="inlineStr">
         <is>
-          <t>Solar Neutral Earth Contactor Stuck Open Error Suspected</t>
+          <t>Load On Solar Contactor Stuck Closed Error Suspected</t>
         </is>
       </c>
       <c r="B164" s="27" t="inlineStr">
@@ -14172,7 +14181,7 @@
         </is>
       </c>
       <c r="G164" s="27" t="n">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="H164" s="27" t="n">
         <v>1</v>
@@ -14182,7 +14191,7 @@
     <row r="165" ht="15" customHeight="1" s="19">
       <c r="A165" s="27" t="inlineStr">
         <is>
-          <t>Solar Neutral Earth Contactor Stuck Closed Error Suspected</t>
+          <t>Load On Grid Contactor Stuck Open Error Suspected</t>
         </is>
       </c>
       <c r="B165" s="27" t="inlineStr">
@@ -14211,7 +14220,7 @@
         </is>
       </c>
       <c r="G165" s="27" t="n">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="H165" s="27" t="n">
         <v>1</v>
@@ -14221,7 +14230,7 @@
     <row r="166" ht="15" customHeight="1" s="19">
       <c r="A166" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load On Grid </t>
+          <t>Load On Grid Contactor Stuck Closed Error Suspected</t>
         </is>
       </c>
       <c r="B166" s="27" t="inlineStr">
@@ -14250,7 +14259,7 @@
         </is>
       </c>
       <c r="G166" s="27" t="n">
-        <v>801</v>
+        <v>610</v>
       </c>
       <c r="H166" s="27" t="n">
         <v>1</v>
@@ -14260,7 +14269,7 @@
     <row r="167" ht="15" customHeight="1" s="19">
       <c r="A167" s="27" t="inlineStr">
         <is>
-          <t>Load Not On Grid  As User Disabled</t>
+          <t>Solar Neutral Earth Contactor Stuck Open Error Suspected</t>
         </is>
       </c>
       <c r="B167" s="27" t="inlineStr">
@@ -14289,7 +14298,7 @@
         </is>
       </c>
       <c r="G167" s="27" t="n">
-        <v>802</v>
+        <v>611</v>
       </c>
       <c r="H167" s="27" t="n">
         <v>1</v>
@@ -14299,7 +14308,7 @@
     <row r="168" ht="15" customHeight="1" s="19">
       <c r="A168" s="27" t="inlineStr">
         <is>
-          <t>Load Not On Grid As Grid R Phase Unhealthy</t>
+          <t>Solar Neutral Earth Contactor Stuck Closed Error Suspected</t>
         </is>
       </c>
       <c r="B168" s="27" t="inlineStr">
@@ -14328,7 +14337,7 @@
         </is>
       </c>
       <c r="G168" s="27" t="n">
-        <v>803</v>
+        <v>612</v>
       </c>
       <c r="H168" s="27" t="n">
         <v>1</v>
@@ -14338,7 +14347,7 @@
     <row r="169" ht="15" customHeight="1" s="19">
       <c r="A169" s="27" t="inlineStr">
         <is>
-          <t>Load Not On Grid As Solar Contactors On</t>
+          <t xml:space="preserve">Load On Grid </t>
         </is>
       </c>
       <c r="B169" s="27" t="inlineStr">
@@ -14367,7 +14376,7 @@
         </is>
       </c>
       <c r="G169" s="27" t="n">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="H169" s="27" t="n">
         <v>1</v>
@@ -14377,7 +14386,7 @@
     <row r="170" ht="15" customHeight="1" s="19">
       <c r="A170" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load On Solar </t>
+          <t>Load Not On Grid  As User Disabled</t>
         </is>
       </c>
       <c r="B170" s="27" t="inlineStr">
@@ -14406,7 +14415,7 @@
         </is>
       </c>
       <c r="G170" s="27" t="n">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="H170" s="27" t="n">
         <v>1</v>
@@ -14416,7 +14425,7 @@
     <row r="171" ht="15" customHeight="1" s="19">
       <c r="A171" s="27" t="inlineStr">
         <is>
-          <t>Load Not On Solar As User Disabled</t>
+          <t>Load Not On Grid As Grid R Phase Unhealthy</t>
         </is>
       </c>
       <c r="B171" s="27" t="inlineStr">
@@ -14445,7 +14454,7 @@
         </is>
       </c>
       <c r="G171" s="27" t="n">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="H171" s="27" t="n">
         <v>1</v>
@@ -14455,7 +14464,7 @@
     <row r="172" ht="15" customHeight="1" s="19">
       <c r="A172" s="27" t="inlineStr">
         <is>
-          <t>Load Not On Solar As Solar R Phase Unhealthy</t>
+          <t>Load Not On Grid As Solar Contactors On</t>
         </is>
       </c>
       <c r="B172" s="27" t="inlineStr">
@@ -14484,7 +14493,7 @@
         </is>
       </c>
       <c r="G172" s="27" t="n">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="H172" s="27" t="n">
         <v>1</v>
@@ -14494,7 +14503,7 @@
     <row r="173" ht="15" customHeight="1" s="19">
       <c r="A173" s="27" t="inlineStr">
         <is>
-          <t>Load Not On Solar As Grid Contactors On</t>
+          <t xml:space="preserve">Load On Solar </t>
         </is>
       </c>
       <c r="B173" s="27" t="inlineStr">
@@ -14523,7 +14532,7 @@
         </is>
       </c>
       <c r="G173" s="27" t="n">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="H173" s="27" t="n">
         <v>1</v>
@@ -14533,7 +14542,7 @@
     <row r="174" ht="15" customHeight="1" s="19">
       <c r="A174" s="27" t="inlineStr">
         <is>
-          <t>Load Not On Solar As DG Running</t>
+          <t>Load Not On Solar As User Disabled</t>
         </is>
       </c>
       <c r="B174" s="27" t="inlineStr">
@@ -14562,7 +14571,7 @@
         </is>
       </c>
       <c r="G174" s="27" t="n">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="H174" s="27" t="n">
         <v>1</v>
@@ -14572,7 +14581,7 @@
     <row r="175" ht="15" customHeight="1" s="19">
       <c r="A175" s="27" t="inlineStr">
         <is>
-          <t>Fan 1 Short Circuit</t>
+          <t>Load Not On Solar As Solar R Phase Unhealthy</t>
         </is>
       </c>
       <c r="B175" s="27" t="inlineStr">
@@ -14601,7 +14610,7 @@
         </is>
       </c>
       <c r="G175" s="27" t="n">
-        <v>901</v>
+        <v>807</v>
       </c>
       <c r="H175" s="27" t="n">
         <v>1</v>
@@ -14611,7 +14620,7 @@
     <row r="176" ht="15" customHeight="1" s="19">
       <c r="A176" s="27" t="inlineStr">
         <is>
-          <t>Fan 1 Open Circuit</t>
+          <t>Load Not On Solar As Grid Contactors On</t>
         </is>
       </c>
       <c r="B176" s="27" t="inlineStr">
@@ -14640,7 +14649,7 @@
         </is>
       </c>
       <c r="G176" s="27" t="n">
-        <v>902</v>
+        <v>808</v>
       </c>
       <c r="H176" s="27" t="n">
         <v>1</v>
@@ -14650,7 +14659,7 @@
     <row r="177" ht="15" customHeight="1" s="19">
       <c r="A177" s="27" t="inlineStr">
         <is>
-          <t>Fan 2 Short Circuit</t>
+          <t>Load Not On Solar As DG Running</t>
         </is>
       </c>
       <c r="B177" s="27" t="inlineStr">
@@ -14679,7 +14688,7 @@
         </is>
       </c>
       <c r="G177" s="27" t="n">
-        <v>903</v>
+        <v>809</v>
       </c>
       <c r="H177" s="27" t="n">
         <v>1</v>
@@ -14689,268 +14698,256 @@
     <row r="178" ht="15" customHeight="1" s="19">
       <c r="A178" s="27" t="inlineStr">
         <is>
+          <t>Fan 1 Short Circuit</t>
+        </is>
+      </c>
+      <c r="B178" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C178" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIT </t>
+        </is>
+      </c>
+      <c r="D178" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E178" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F178" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input Status </t>
+        </is>
+      </c>
+      <c r="G178" s="27" t="n">
+        <v>901</v>
+      </c>
+      <c r="H178" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" s="27" t="n"/>
+    </row>
+    <row r="179" ht="15" customHeight="1" s="19">
+      <c r="A179" s="27" t="inlineStr">
+        <is>
+          <t>Fan 1 Open Circuit</t>
+        </is>
+      </c>
+      <c r="B179" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C179" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIT </t>
+        </is>
+      </c>
+      <c r="D179" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E179" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F179" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input Status </t>
+        </is>
+      </c>
+      <c r="G179" s="27" t="n">
+        <v>902</v>
+      </c>
+      <c r="H179" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" s="27" t="n"/>
+    </row>
+    <row r="180" ht="15" customHeight="1" s="19">
+      <c r="A180" s="27" t="inlineStr">
+        <is>
+          <t>Fan 2 Short Circuit</t>
+        </is>
+      </c>
+      <c r="B180" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C180" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIT </t>
+        </is>
+      </c>
+      <c r="D180" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E180" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F180" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input Status </t>
+        </is>
+      </c>
+      <c r="G180" s="27" t="n">
+        <v>903</v>
+      </c>
+      <c r="H180" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I180" s="27" t="n"/>
+    </row>
+    <row r="181" ht="15" customHeight="1" s="19">
+      <c r="A181" s="27" t="inlineStr">
+        <is>
           <t>Fan 2 Open Circuit</t>
         </is>
       </c>
-      <c r="B178" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C178" s="27" t="inlineStr">
+      <c r="B181" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C181" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D178" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E178" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F178" s="27" t="inlineStr">
+      <c r="D181" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E181" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F181" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Input Status </t>
         </is>
       </c>
-      <c r="G178" s="27" t="n">
+      <c r="G181" s="27" t="n">
         <v>904</v>
       </c>
-      <c r="H178" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I178" s="27" t="n"/>
-    </row>
-    <row r="179" ht="15" customHeight="1" s="19">
-      <c r="A179" s="21" t="inlineStr">
+      <c r="H181" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" s="27" t="n"/>
+    </row>
+    <row r="182" ht="15" customHeight="1" s="19">
+      <c r="A182" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Parameters </t>
         </is>
       </c>
-      <c r="B179" s="22" t="inlineStr">
+      <c r="B182" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Units of </t>
         </is>
       </c>
-      <c r="C179" s="22" t="inlineStr">
+      <c r="C182" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Data Type </t>
         </is>
       </c>
-      <c r="D179" s="21" t="inlineStr">
+      <c r="D182" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Size in byte </t>
         </is>
       </c>
-      <c r="E179" s="22" t="inlineStr">
+      <c r="E182" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversion </t>
         </is>
       </c>
-      <c r="F179" s="21" t="inlineStr">
+      <c r="F182" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Type of Register </t>
         </is>
       </c>
-      <c r="G179" s="22" t="inlineStr">
+      <c r="G182" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Modbus </t>
         </is>
       </c>
-      <c r="H179" s="22" t="inlineStr">
+      <c r="H182" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">No. of </t>
         </is>
       </c>
-      <c r="I179" s="21" t="inlineStr">
+      <c r="I182" s="21" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="15" customHeight="1" s="19">
-      <c r="A180" s="23" t="n"/>
-      <c r="B180" s="22" t="inlineStr">
+    <row r="183" ht="15" customHeight="1" s="19">
+      <c r="A183" s="23" t="n"/>
+      <c r="B183" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Measurement </t>
         </is>
       </c>
-      <c r="C180" s="22" t="inlineStr">
+      <c r="C183" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">(Float/Hex etc.) </t>
         </is>
       </c>
-      <c r="D180" s="23" t="n"/>
-      <c r="E180" s="22" t="inlineStr">
+      <c r="D183" s="23" t="n"/>
+      <c r="E183" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Multiplier to read the data </t>
         </is>
       </c>
-      <c r="F180" s="23" t="n"/>
-      <c r="G180" s="22" t="inlineStr">
+      <c r="F183" s="23" t="n"/>
+      <c r="G183" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Register Address </t>
         </is>
       </c>
-      <c r="H180" s="22" t="inlineStr">
+      <c r="H183" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Registers required </t>
         </is>
       </c>
-      <c r="I180" s="23" t="n"/>
-    </row>
-    <row r="181" ht="15" customHeight="1" s="19">
-      <c r="A181" s="24" t="inlineStr">
+      <c r="I183" s="23" t="n"/>
+    </row>
+    <row r="184" ht="15" customHeight="1" s="19">
+      <c r="A184" s="24" t="inlineStr">
         <is>
           <t>READ COIL STATUS (Function Code: 0x01)</t>
         </is>
       </c>
-      <c r="B181" s="25" t="n"/>
-      <c r="C181" s="25" t="n"/>
-      <c r="D181" s="25" t="n"/>
-      <c r="E181" s="25" t="n"/>
-      <c r="F181" s="25" t="n"/>
-      <c r="G181" s="25" t="n"/>
-      <c r="H181" s="25" t="n"/>
-      <c r="I181" s="25" t="n"/>
-    </row>
-    <row r="182" ht="15" customHeight="1" s="19">
-      <c r="A182" s="32" t="inlineStr">
-        <is>
-          <t>Digital Input 1</t>
-        </is>
-      </c>
-      <c r="B182" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C182" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIT </t>
-        </is>
-      </c>
-      <c r="D182" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E182" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F182" s="32" t="inlineStr">
-        <is>
-          <t>Coil Status</t>
-        </is>
-      </c>
-      <c r="G182" s="32" t="n">
-        <v>20001</v>
-      </c>
-      <c r="H182" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I182" s="32" t="inlineStr">
-        <is>
-          <t>Internal Only. Not visible to customer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="15" customHeight="1" s="19">
-      <c r="A183" s="32" t="inlineStr">
-        <is>
-          <t>Digital Input 2</t>
-        </is>
-      </c>
-      <c r="B183" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C183" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIT </t>
-        </is>
-      </c>
-      <c r="D183" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E183" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F183" s="32" t="inlineStr">
-        <is>
-          <t>Coil Status</t>
-        </is>
-      </c>
-      <c r="G183" s="32" t="n">
-        <v>20002</v>
-      </c>
-      <c r="H183" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I183" s="32" t="inlineStr">
-        <is>
-          <t>Internal Only. Not visible to customer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="15" customHeight="1" s="19">
-      <c r="A184" s="32" t="inlineStr">
-        <is>
-          <t>Digital Input 3</t>
-        </is>
-      </c>
-      <c r="B184" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C184" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIT </t>
-        </is>
-      </c>
-      <c r="D184" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E184" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F184" s="32" t="inlineStr">
-        <is>
-          <t>Coil Status</t>
-        </is>
-      </c>
-      <c r="G184" s="32" t="n">
-        <v>20003</v>
-      </c>
-      <c r="H184" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I184" s="32" t="inlineStr">
-        <is>
-          <t>Internal Only. Not visible to customer.</t>
-        </is>
-      </c>
+      <c r="B184" s="25" t="n"/>
+      <c r="C184" s="25" t="n"/>
+      <c r="D184" s="25" t="n"/>
+      <c r="E184" s="25" t="n"/>
+      <c r="F184" s="25" t="n"/>
+      <c r="G184" s="25" t="n"/>
+      <c r="H184" s="25" t="n"/>
+      <c r="I184" s="25" t="n"/>
     </row>
     <row r="185" ht="15" customHeight="1" s="19">
       <c r="A185" s="32" t="inlineStr">
         <is>
-          <t>Digital Input 4</t>
+          <t>Digital Input 1</t>
         </is>
       </c>
       <c r="B185" s="32" t="inlineStr">
@@ -14979,7 +14976,7 @@
         </is>
       </c>
       <c r="G185" s="32" t="n">
-        <v>20004</v>
+        <v>20001</v>
       </c>
       <c r="H185" s="32" t="n">
         <v>1</v>
@@ -14993,7 +14990,7 @@
     <row r="186" ht="15" customHeight="1" s="19">
       <c r="A186" s="32" t="inlineStr">
         <is>
-          <t>Digital Input 5</t>
+          <t>Digital Input 2</t>
         </is>
       </c>
       <c r="B186" s="32" t="inlineStr">
@@ -15022,7 +15019,7 @@
         </is>
       </c>
       <c r="G186" s="32" t="n">
-        <v>20005</v>
+        <v>20002</v>
       </c>
       <c r="H186" s="32" t="n">
         <v>1</v>
@@ -15036,7 +15033,7 @@
     <row r="187" ht="15" customHeight="1" s="19">
       <c r="A187" s="32" t="inlineStr">
         <is>
-          <t>Digital Input 6</t>
+          <t>Digital Input 3</t>
         </is>
       </c>
       <c r="B187" s="32" t="inlineStr">
@@ -15065,7 +15062,7 @@
         </is>
       </c>
       <c r="G187" s="32" t="n">
-        <v>20006</v>
+        <v>20003</v>
       </c>
       <c r="H187" s="32" t="n">
         <v>1</v>
@@ -15079,7 +15076,7 @@
     <row r="188" ht="15" customHeight="1" s="19">
       <c r="A188" s="32" t="inlineStr">
         <is>
-          <t>Digital Input 7</t>
+          <t>Digital Input 4</t>
         </is>
       </c>
       <c r="B188" s="32" t="inlineStr">
@@ -15108,7 +15105,7 @@
         </is>
       </c>
       <c r="G188" s="32" t="n">
-        <v>20007</v>
+        <v>20004</v>
       </c>
       <c r="H188" s="32" t="n">
         <v>1</v>
@@ -15122,7 +15119,7 @@
     <row r="189" ht="15" customHeight="1" s="19">
       <c r="A189" s="32" t="inlineStr">
         <is>
-          <t>Digital Input 8</t>
+          <t>Digital Input 5</t>
         </is>
       </c>
       <c r="B189" s="32" t="inlineStr">
@@ -15151,7 +15148,7 @@
         </is>
       </c>
       <c r="G189" s="32" t="n">
-        <v>20008</v>
+        <v>20005</v>
       </c>
       <c r="H189" s="32" t="n">
         <v>1</v>
@@ -15165,7 +15162,7 @@
     <row r="190" ht="15" customHeight="1" s="19">
       <c r="A190" s="32" t="inlineStr">
         <is>
-          <t>Digital Output 1</t>
+          <t>Digital Input 6</t>
         </is>
       </c>
       <c r="B190" s="32" t="inlineStr">
@@ -15194,7 +15191,7 @@
         </is>
       </c>
       <c r="G190" s="32" t="n">
-        <v>30001</v>
+        <v>20006</v>
       </c>
       <c r="H190" s="32" t="n">
         <v>1</v>
@@ -15208,7 +15205,7 @@
     <row r="191" ht="15" customHeight="1" s="19">
       <c r="A191" s="32" t="inlineStr">
         <is>
-          <t>Digital Output 2</t>
+          <t>Digital Input 7</t>
         </is>
       </c>
       <c r="B191" s="32" t="inlineStr">
@@ -15237,7 +15234,7 @@
         </is>
       </c>
       <c r="G191" s="32" t="n">
-        <v>30002</v>
+        <v>20007</v>
       </c>
       <c r="H191" s="32" t="n">
         <v>1</v>
@@ -15251,7 +15248,7 @@
     <row r="192" ht="15" customHeight="1" s="19">
       <c r="A192" s="32" t="inlineStr">
         <is>
-          <t>Digital Output 3</t>
+          <t>Digital Input 8</t>
         </is>
       </c>
       <c r="B192" s="32" t="inlineStr">
@@ -15280,7 +15277,7 @@
         </is>
       </c>
       <c r="G192" s="32" t="n">
-        <v>30003</v>
+        <v>20008</v>
       </c>
       <c r="H192" s="32" t="n">
         <v>1</v>
@@ -15294,7 +15291,7 @@
     <row r="193" ht="15" customHeight="1" s="19">
       <c r="A193" s="32" t="inlineStr">
         <is>
-          <t>Digital Output 4</t>
+          <t>Digital Output 1</t>
         </is>
       </c>
       <c r="B193" s="32" t="inlineStr">
@@ -15323,7 +15320,7 @@
         </is>
       </c>
       <c r="G193" s="32" t="n">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="H193" s="32" t="n">
         <v>1</v>
@@ -15337,7 +15334,7 @@
     <row r="194" ht="15" customHeight="1" s="19">
       <c r="A194" s="32" t="inlineStr">
         <is>
-          <t>Digital Output 5</t>
+          <t>Digital Output 2</t>
         </is>
       </c>
       <c r="B194" s="32" t="inlineStr">
@@ -15366,7 +15363,7 @@
         </is>
       </c>
       <c r="G194" s="32" t="n">
-        <v>30005</v>
+        <v>30002</v>
       </c>
       <c r="H194" s="32" t="n">
         <v>1</v>
@@ -15380,7 +15377,7 @@
     <row r="195" ht="15" customHeight="1" s="19">
       <c r="A195" s="32" t="inlineStr">
         <is>
-          <t>Digital Output 6</t>
+          <t>Digital Output 3</t>
         </is>
       </c>
       <c r="B195" s="32" t="inlineStr">
@@ -15409,7 +15406,7 @@
         </is>
       </c>
       <c r="G195" s="32" t="n">
-        <v>30006</v>
+        <v>30003</v>
       </c>
       <c r="H195" s="32" t="n">
         <v>1</v>
@@ -15423,7 +15420,7 @@
     <row r="196" ht="15" customHeight="1" s="19">
       <c r="A196" s="32" t="inlineStr">
         <is>
-          <t>Test Mode</t>
+          <t>Digital Output 4</t>
         </is>
       </c>
       <c r="B196" s="32" t="inlineStr">
@@ -15452,7 +15449,7 @@
         </is>
       </c>
       <c r="G196" s="32" t="n">
-        <v>40001</v>
+        <v>30004</v>
       </c>
       <c r="H196" s="32" t="n">
         <v>1</v>
@@ -15466,7 +15463,7 @@
     <row r="197" ht="15" customHeight="1" s="19">
       <c r="A197" s="32" t="inlineStr">
         <is>
-          <t>LED 1</t>
+          <t>Digital Output 5</t>
         </is>
       </c>
       <c r="B197" s="32" t="inlineStr">
@@ -15495,7 +15492,7 @@
         </is>
       </c>
       <c r="G197" s="32" t="n">
-        <v>60001</v>
+        <v>30005</v>
       </c>
       <c r="H197" s="32" t="n">
         <v>1</v>
@@ -15509,7 +15506,7 @@
     <row r="198" ht="15" customHeight="1" s="19">
       <c r="A198" s="32" t="inlineStr">
         <is>
-          <t>LED 2</t>
+          <t>Digital Output 6</t>
         </is>
       </c>
       <c r="B198" s="32" t="inlineStr">
@@ -15538,7 +15535,7 @@
         </is>
       </c>
       <c r="G198" s="32" t="n">
-        <v>60002</v>
+        <v>30006</v>
       </c>
       <c r="H198" s="32" t="n">
         <v>1</v>
@@ -15552,7 +15549,7 @@
     <row r="199" ht="15" customHeight="1" s="19">
       <c r="A199" s="32" t="inlineStr">
         <is>
-          <t>LED 3</t>
+          <t>Test Mode</t>
         </is>
       </c>
       <c r="B199" s="32" t="inlineStr">
@@ -15581,7 +15578,7 @@
         </is>
       </c>
       <c r="G199" s="32" t="n">
-        <v>60003</v>
+        <v>40001</v>
       </c>
       <c r="H199" s="32" t="n">
         <v>1</v>
@@ -15595,7 +15592,7 @@
     <row r="200" ht="15" customHeight="1" s="19">
       <c r="A200" s="32" t="inlineStr">
         <is>
-          <t>LED 4</t>
+          <t>LED 1</t>
         </is>
       </c>
       <c r="B200" s="32" t="inlineStr">
@@ -15624,7 +15621,7 @@
         </is>
       </c>
       <c r="G200" s="32" t="n">
-        <v>60004</v>
+        <v>60001</v>
       </c>
       <c r="H200" s="32" t="n">
         <v>1</v>
@@ -15638,7 +15635,7 @@
     <row r="201" ht="15" customHeight="1" s="19">
       <c r="A201" s="32" t="inlineStr">
         <is>
-          <t>LED 5</t>
+          <t>LED 2</t>
         </is>
       </c>
       <c r="B201" s="32" t="inlineStr">
@@ -15667,7 +15664,7 @@
         </is>
       </c>
       <c r="G201" s="32" t="n">
-        <v>60005</v>
+        <v>60002</v>
       </c>
       <c r="H201" s="32" t="n">
         <v>1</v>
@@ -15681,7 +15678,7 @@
     <row r="202" ht="15" customHeight="1" s="19">
       <c r="A202" s="32" t="inlineStr">
         <is>
-          <t>LED 6</t>
+          <t>LED 3</t>
         </is>
       </c>
       <c r="B202" s="32" t="inlineStr">
@@ -15710,7 +15707,7 @@
         </is>
       </c>
       <c r="G202" s="32" t="n">
-        <v>60006</v>
+        <v>60003</v>
       </c>
       <c r="H202" s="32" t="n">
         <v>1</v>
@@ -15724,7 +15721,7 @@
     <row r="203" ht="15" customHeight="1" s="19">
       <c r="A203" s="32" t="inlineStr">
         <is>
-          <t>LED 7</t>
+          <t>LED 4</t>
         </is>
       </c>
       <c r="B203" s="32" t="inlineStr">
@@ -15753,7 +15750,7 @@
         </is>
       </c>
       <c r="G203" s="32" t="n">
-        <v>60007</v>
+        <v>60004</v>
       </c>
       <c r="H203" s="32" t="n">
         <v>1</v>
@@ -15767,1063 +15764,1073 @@
     <row r="204" ht="15" customHeight="1" s="19">
       <c r="A204" s="32" t="inlineStr">
         <is>
+          <t>LED 5</t>
+        </is>
+      </c>
+      <c r="B204" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C204" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIT </t>
+        </is>
+      </c>
+      <c r="D204" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E204" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F204" s="32" t="inlineStr">
+        <is>
+          <t>Coil Status</t>
+        </is>
+      </c>
+      <c r="G204" s="32" t="n">
+        <v>60005</v>
+      </c>
+      <c r="H204" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" s="32" t="inlineStr">
+        <is>
+          <t>Internal Only. Not visible to customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="15" customHeight="1" s="19">
+      <c r="A205" s="32" t="inlineStr">
+        <is>
+          <t>LED 6</t>
+        </is>
+      </c>
+      <c r="B205" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C205" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIT </t>
+        </is>
+      </c>
+      <c r="D205" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E205" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F205" s="32" t="inlineStr">
+        <is>
+          <t>Coil Status</t>
+        </is>
+      </c>
+      <c r="G205" s="32" t="n">
+        <v>60006</v>
+      </c>
+      <c r="H205" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" s="32" t="inlineStr">
+        <is>
+          <t>Internal Only. Not visible to customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="15" customHeight="1" s="19">
+      <c r="A206" s="32" t="inlineStr">
+        <is>
+          <t>LED 7</t>
+        </is>
+      </c>
+      <c r="B206" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C206" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIT </t>
+        </is>
+      </c>
+      <c r="D206" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E206" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F206" s="32" t="inlineStr">
+        <is>
+          <t>Coil Status</t>
+        </is>
+      </c>
+      <c r="G206" s="32" t="n">
+        <v>60007</v>
+      </c>
+      <c r="H206" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" s="32" t="inlineStr">
+        <is>
+          <t>Internal Only. Not visible to customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="15" customHeight="1" s="19">
+      <c r="A207" s="32" t="inlineStr">
+        <is>
           <t>LED 8</t>
         </is>
       </c>
-      <c r="B204" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C204" s="32" t="inlineStr">
+      <c r="B207" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C207" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D204" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E204" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F204" s="32" t="inlineStr">
+      <c r="D207" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E207" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F207" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G204" s="32" t="n">
+      <c r="G207" s="32" t="n">
         <v>60008</v>
       </c>
-      <c r="H204" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I204" s="32" t="inlineStr">
+      <c r="H207" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I207" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="13.8" customHeight="1" s="19">
-      <c r="A205" s="21" t="inlineStr">
+    <row r="208" ht="13.8" customHeight="1" s="19">
+      <c r="A208" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Parameters </t>
         </is>
       </c>
-      <c r="B205" s="22" t="inlineStr">
+      <c r="B208" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Units of </t>
         </is>
       </c>
-      <c r="C205" s="22" t="inlineStr">
+      <c r="C208" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Data Type </t>
         </is>
       </c>
-      <c r="D205" s="21" t="inlineStr">
+      <c r="D208" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Size in byte </t>
         </is>
       </c>
-      <c r="E205" s="22" t="inlineStr">
+      <c r="E208" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversion </t>
         </is>
       </c>
-      <c r="F205" s="21" t="inlineStr">
+      <c r="F208" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Type of Register </t>
         </is>
       </c>
-      <c r="G205" s="22" t="inlineStr">
+      <c r="G208" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Modbus </t>
         </is>
       </c>
-      <c r="H205" s="22" t="inlineStr">
+      <c r="H208" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">No. of </t>
         </is>
       </c>
-      <c r="I205" s="21" t="inlineStr">
+      <c r="I208" s="21" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="15" customHeight="1" s="19">
-      <c r="A206" s="23" t="n"/>
-      <c r="B206" s="22" t="inlineStr">
+    <row r="209" ht="15" customHeight="1" s="19">
+      <c r="A209" s="23" t="n"/>
+      <c r="B209" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Measurement </t>
         </is>
       </c>
-      <c r="C206" s="22" t="inlineStr">
+      <c r="C209" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">(Float/Hex etc.) </t>
         </is>
       </c>
-      <c r="D206" s="23" t="n"/>
-      <c r="E206" s="22" t="inlineStr">
+      <c r="D209" s="23" t="n"/>
+      <c r="E209" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Multiplier to read the data </t>
         </is>
       </c>
-      <c r="F206" s="23" t="n"/>
-      <c r="G206" s="22" t="inlineStr">
+      <c r="F209" s="23" t="n"/>
+      <c r="G209" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Register Address </t>
         </is>
       </c>
-      <c r="H206" s="22" t="inlineStr">
+      <c r="H209" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Registers required </t>
         </is>
       </c>
-      <c r="I206" s="23" t="n"/>
-    </row>
-    <row r="207" ht="13.8" customHeight="1" s="19">
-      <c r="A207" s="24" t="inlineStr">
+      <c r="I209" s="23" t="n"/>
+    </row>
+    <row r="210" ht="13.8" customHeight="1" s="19">
+      <c r="A210" s="24" t="inlineStr">
         <is>
           <t>WRITE SINGLE COIL STATUS (Function Code: 0x05)</t>
         </is>
       </c>
-      <c r="B207" s="25" t="n"/>
-      <c r="C207" s="25" t="n"/>
-      <c r="D207" s="25" t="n"/>
-      <c r="E207" s="25" t="n"/>
-      <c r="F207" s="25" t="n"/>
-      <c r="G207" s="25" t="n"/>
-      <c r="H207" s="25" t="n"/>
-      <c r="I207" s="25" t="n"/>
-    </row>
-    <row r="208" ht="19.1" customHeight="1" s="19">
-      <c r="A208" s="32" t="inlineStr">
+      <c r="B210" s="25" t="n"/>
+      <c r="C210" s="25" t="n"/>
+      <c r="D210" s="25" t="n"/>
+      <c r="E210" s="25" t="n"/>
+      <c r="F210" s="25" t="n"/>
+      <c r="G210" s="25" t="n"/>
+      <c r="H210" s="25" t="n"/>
+      <c r="I210" s="25" t="n"/>
+    </row>
+    <row r="211" ht="19.1" customHeight="1" s="19">
+      <c r="A211" s="32" t="inlineStr">
         <is>
           <t>Digital Output 1</t>
         </is>
       </c>
-      <c r="B208" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C208" s="32" t="inlineStr">
+      <c r="B211" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C211" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D208" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E208" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F208" s="32" t="inlineStr">
+      <c r="D211" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E211" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F211" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G208" s="32" t="n">
+      <c r="G211" s="32" t="n">
         <v>30001</v>
       </c>
-      <c r="H208" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I208" s="32" t="inlineStr">
+      <c r="H211" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="19.1" customHeight="1" s="19">
-      <c r="A209" s="32" t="inlineStr">
+    <row r="212" ht="19.1" customHeight="1" s="19">
+      <c r="A212" s="32" t="inlineStr">
         <is>
           <t>Digital Output 2</t>
         </is>
       </c>
-      <c r="B209" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C209" s="32" t="inlineStr">
+      <c r="B212" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C212" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D209" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E209" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F209" s="32" t="inlineStr">
+      <c r="D212" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E212" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F212" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G209" s="32" t="n">
+      <c r="G212" s="32" t="n">
         <v>30002</v>
       </c>
-      <c r="H209" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I209" s="32" t="inlineStr">
+      <c r="H212" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I212" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="19.1" customHeight="1" s="19">
-      <c r="A210" s="32" t="inlineStr">
+    <row r="213" ht="19.1" customHeight="1" s="19">
+      <c r="A213" s="32" t="inlineStr">
         <is>
           <t>Digital Output 3</t>
         </is>
       </c>
-      <c r="B210" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C210" s="32" t="inlineStr">
+      <c r="B213" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C213" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D210" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E210" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F210" s="32" t="inlineStr">
+      <c r="D213" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E213" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F213" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G210" s="32" t="n">
+      <c r="G213" s="32" t="n">
         <v>30003</v>
       </c>
-      <c r="H210" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I210" s="32" t="inlineStr">
+      <c r="H213" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="19.1" customHeight="1" s="19">
-      <c r="A211" s="32" t="inlineStr">
+    <row r="214" ht="19.1" customHeight="1" s="19">
+      <c r="A214" s="32" t="inlineStr">
         <is>
           <t>Digital Output 4</t>
         </is>
       </c>
-      <c r="B211" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C211" s="32" t="inlineStr">
+      <c r="B214" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C214" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D211" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E211" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F211" s="32" t="inlineStr">
+      <c r="D214" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E214" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F214" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G211" s="32" t="n">
+      <c r="G214" s="32" t="n">
         <v>30004</v>
       </c>
-      <c r="H211" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I211" s="32" t="inlineStr">
+      <c r="H214" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="19.1" customHeight="1" s="19">
-      <c r="A212" s="32" t="inlineStr">
+    <row r="215" ht="19.1" customHeight="1" s="19">
+      <c r="A215" s="32" t="inlineStr">
         <is>
           <t>Digital Output 5</t>
         </is>
       </c>
-      <c r="B212" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C212" s="32" t="inlineStr">
+      <c r="B215" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C215" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D212" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E212" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F212" s="32" t="inlineStr">
+      <c r="D215" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E215" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F215" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G212" s="32" t="n">
+      <c r="G215" s="32" t="n">
         <v>30005</v>
       </c>
-      <c r="H212" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I212" s="32" t="inlineStr">
+      <c r="H215" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="19.1" customHeight="1" s="19">
-      <c r="A213" s="32" t="inlineStr">
+    <row r="216" ht="19.1" customHeight="1" s="19">
+      <c r="A216" s="32" t="inlineStr">
         <is>
           <t>Digital Output 6</t>
         </is>
       </c>
-      <c r="B213" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C213" s="32" t="inlineStr">
+      <c r="B216" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C216" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D213" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E213" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F213" s="32" t="inlineStr">
+      <c r="D216" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E216" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F216" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G213" s="32" t="n">
+      <c r="G216" s="32" t="n">
         <v>30006</v>
       </c>
-      <c r="H213" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I213" s="32" t="inlineStr">
+      <c r="H216" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="15" customHeight="1" s="19">
-      <c r="A214" s="32" t="inlineStr">
+    <row r="217" ht="15" customHeight="1" s="19">
+      <c r="A217" s="32" t="inlineStr">
         <is>
           <t>Test Mode</t>
         </is>
       </c>
-      <c r="B214" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C214" s="32" t="inlineStr">
+      <c r="B217" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C217" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D214" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E214" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F214" s="32" t="inlineStr">
+      <c r="D217" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E217" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F217" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G214" s="32" t="n">
+      <c r="G217" s="32" t="n">
         <v>40001</v>
       </c>
-      <c r="H214" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I214" s="32" t="inlineStr">
+      <c r="H217" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="19.1" customHeight="1" s="19">
-      <c r="A215" s="32" t="inlineStr">
+    <row r="218" ht="19.1" customHeight="1" s="19">
+      <c r="A218" s="32" t="inlineStr">
         <is>
           <t>Restart Controller</t>
         </is>
       </c>
-      <c r="B215" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C215" s="32" t="inlineStr">
+      <c r="B218" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C218" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D215" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E215" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F215" s="32" t="inlineStr">
+      <c r="D218" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E218" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F218" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G215" s="32" t="n">
+      <c r="G218" s="32" t="n">
         <v>45001</v>
       </c>
-      <c r="H215" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I215" s="32" t="inlineStr">
+      <c r="H218" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="19.1" customHeight="1" s="19">
-      <c r="A216" s="32" t="inlineStr">
+    <row r="219" ht="19.1" customHeight="1" s="19">
+      <c r="A219" s="32" t="inlineStr">
         <is>
           <t>LED 1</t>
         </is>
       </c>
-      <c r="B216" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C216" s="32" t="inlineStr">
+      <c r="B219" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C219" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D216" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E216" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F216" s="32" t="inlineStr">
+      <c r="D219" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E219" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F219" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G216" s="32" t="n">
+      <c r="G219" s="32" t="n">
         <v>60001</v>
       </c>
-      <c r="H216" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I216" s="32" t="inlineStr">
+      <c r="H219" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="19.1" customHeight="1" s="19">
-      <c r="A217" s="32" t="inlineStr">
+    <row r="220" ht="19.1" customHeight="1" s="19">
+      <c r="A220" s="32" t="inlineStr">
         <is>
           <t>LED 2</t>
         </is>
       </c>
-      <c r="B217" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C217" s="32" t="inlineStr">
+      <c r="B220" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C220" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D217" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E217" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F217" s="32" t="inlineStr">
+      <c r="D220" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E220" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F220" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G217" s="32" t="n">
+      <c r="G220" s="32" t="n">
         <v>60002</v>
       </c>
-      <c r="H217" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I217" s="32" t="inlineStr">
+      <c r="H220" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I220" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="19.1" customHeight="1" s="19">
-      <c r="A218" s="32" t="inlineStr">
+    <row r="221" ht="19.1" customHeight="1" s="19">
+      <c r="A221" s="32" t="inlineStr">
         <is>
           <t>LED 3</t>
         </is>
       </c>
-      <c r="B218" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C218" s="32" t="inlineStr">
+      <c r="B221" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C221" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D218" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E218" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F218" s="32" t="inlineStr">
+      <c r="D221" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E221" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F221" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G218" s="32" t="n">
+      <c r="G221" s="32" t="n">
         <v>60003</v>
       </c>
-      <c r="H218" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I218" s="32" t="inlineStr">
+      <c r="H221" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="19.1" customHeight="1" s="19">
-      <c r="A219" s="32" t="inlineStr">
+    <row r="222" ht="19.1" customHeight="1" s="19">
+      <c r="A222" s="32" t="inlineStr">
         <is>
           <t>LED 4</t>
         </is>
       </c>
-      <c r="B219" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C219" s="32" t="inlineStr">
+      <c r="B222" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C222" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D219" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E219" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F219" s="32" t="inlineStr">
+      <c r="D222" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E222" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F222" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G219" s="32" t="n">
+      <c r="G222" s="32" t="n">
         <v>60004</v>
       </c>
-      <c r="H219" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I219" s="32" t="inlineStr">
+      <c r="H222" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I222" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="19.1" customHeight="1" s="19">
-      <c r="A220" s="32" t="inlineStr">
+    <row r="223" ht="19.1" customHeight="1" s="19">
+      <c r="A223" s="32" t="inlineStr">
         <is>
           <t>LED 5</t>
         </is>
       </c>
-      <c r="B220" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C220" s="32" t="inlineStr">
+      <c r="B223" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C223" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D220" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E220" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F220" s="32" t="inlineStr">
+      <c r="D223" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E223" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F223" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G220" s="32" t="n">
+      <c r="G223" s="32" t="n">
         <v>60005</v>
       </c>
-      <c r="H220" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I220" s="32" t="inlineStr">
+      <c r="H223" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="19.1" customHeight="1" s="19">
-      <c r="A221" s="32" t="inlineStr">
+    <row r="224" ht="19.1" customHeight="1" s="19">
+      <c r="A224" s="32" t="inlineStr">
         <is>
           <t>LED 6</t>
         </is>
       </c>
-      <c r="B221" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C221" s="32" t="inlineStr">
+      <c r="B224" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C224" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D221" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E221" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F221" s="32" t="inlineStr">
+      <c r="D224" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E224" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F224" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G221" s="32" t="n">
+      <c r="G224" s="32" t="n">
         <v>60006</v>
       </c>
-      <c r="H221" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I221" s="32" t="inlineStr">
+      <c r="H224" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="19.1" customHeight="1" s="19">
-      <c r="A222" s="32" t="inlineStr">
+    <row r="225" ht="19.1" customHeight="1" s="19">
+      <c r="A225" s="32" t="inlineStr">
         <is>
           <t>LED 7</t>
         </is>
       </c>
-      <c r="B222" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C222" s="32" t="inlineStr">
+      <c r="B225" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C225" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D222" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E222" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F222" s="32" t="inlineStr">
+      <c r="D225" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E225" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F225" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G222" s="32" t="n">
+      <c r="G225" s="32" t="n">
         <v>60007</v>
       </c>
-      <c r="H222" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I222" s="32" t="inlineStr">
+      <c r="H225" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I225" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="19.1" customHeight="1" s="19">
-      <c r="A223" s="32" t="inlineStr">
+    <row r="226" ht="19.1" customHeight="1" s="19">
+      <c r="A226" s="32" t="inlineStr">
         <is>
           <t>LED 8</t>
         </is>
       </c>
-      <c r="B223" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C223" s="32" t="inlineStr">
+      <c r="B226" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C226" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">BIT </t>
         </is>
       </c>
-      <c r="D223" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="E223" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="F223" s="32" t="inlineStr">
+      <c r="D226" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="E226" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="F226" s="32" t="inlineStr">
         <is>
           <t>Coil Status</t>
         </is>
       </c>
-      <c r="G223" s="32" t="n">
+      <c r="G226" s="32" t="n">
         <v>60008</v>
       </c>
-      <c r="H223" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I223" s="32" t="inlineStr">
+      <c r="H226" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer.
 Only settable when test mode enabled</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="15" customHeight="1" s="19">
-      <c r="A224" s="21" t="inlineStr">
+    <row r="227" ht="15" customHeight="1" s="19">
+      <c r="A227" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Parameters </t>
         </is>
       </c>
-      <c r="B224" s="22" t="inlineStr">
+      <c r="B227" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Units of </t>
         </is>
       </c>
-      <c r="C224" s="22" t="inlineStr">
+      <c r="C227" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Data Type </t>
         </is>
       </c>
-      <c r="D224" s="21" t="inlineStr">
+      <c r="D227" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Size in byte </t>
         </is>
       </c>
-      <c r="E224" s="22" t="inlineStr">
+      <c r="E227" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversion </t>
         </is>
       </c>
-      <c r="F224" s="21" t="inlineStr">
+      <c r="F227" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Type of Register </t>
         </is>
       </c>
-      <c r="G224" s="22" t="inlineStr">
+      <c r="G227" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Modbus </t>
         </is>
       </c>
-      <c r="H224" s="22" t="inlineStr">
+      <c r="H227" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">No. of </t>
         </is>
       </c>
-      <c r="I224" s="21" t="inlineStr">
+      <c r="I227" s="21" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="15" customHeight="1" s="19">
-      <c r="A225" s="23" t="n"/>
-      <c r="B225" s="22" t="inlineStr">
+    <row r="228" ht="15" customHeight="1" s="19">
+      <c r="A228" s="23" t="n"/>
+      <c r="B228" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Measurement </t>
         </is>
       </c>
-      <c r="C225" s="22" t="inlineStr">
+      <c r="C228" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">(Float/Hex etc.) </t>
         </is>
       </c>
-      <c r="D225" s="23" t="n"/>
-      <c r="E225" s="22" t="inlineStr">
+      <c r="D228" s="23" t="n"/>
+      <c r="E228" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Multiplier to read the data </t>
         </is>
       </c>
-      <c r="F225" s="23" t="n"/>
-      <c r="G225" s="22" t="inlineStr">
+      <c r="F228" s="23" t="n"/>
+      <c r="G228" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Register Address </t>
         </is>
       </c>
-      <c r="H225" s="22" t="inlineStr">
+      <c r="H228" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Registers required </t>
         </is>
       </c>
-      <c r="I225" s="23" t="n"/>
-    </row>
-    <row r="226" ht="10.4" customHeight="1" s="19">
-      <c r="A226" s="24" t="inlineStr">
+      <c r="I228" s="23" t="n"/>
+    </row>
+    <row r="229" ht="10.4" customHeight="1" s="19">
+      <c r="A229" s="24" t="inlineStr">
         <is>
           <t>WRITE MULTIPLE  HOLDING REGISTERS (0x10)</t>
         </is>
       </c>
-      <c r="B226" s="25" t="n"/>
-      <c r="C226" s="25" t="n"/>
-      <c r="D226" s="25" t="n"/>
-      <c r="E226" s="25" t="n"/>
-      <c r="F226" s="25" t="n"/>
-      <c r="G226" s="25" t="n"/>
-      <c r="H226" s="25" t="n"/>
-      <c r="I226" s="25" t="n"/>
-    </row>
-    <row r="227" ht="15" customHeight="1" s="19">
-      <c r="A227" s="29" t="inlineStr">
-        <is>
-          <t>Disable Load On Grid Duration Remaining</t>
-        </is>
-      </c>
-      <c r="B227" s="27" t="inlineStr">
-        <is>
-          <t>Seconds</t>
-        </is>
-      </c>
-      <c r="C227" s="27" t="inlineStr">
-        <is>
-          <t>Unsigned Integer</t>
-        </is>
-      </c>
-      <c r="D227" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E227" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F227" s="27" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G227" s="30" t="inlineStr">
-        <is>
-          <t>6001</t>
-        </is>
-      </c>
-      <c r="H227" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I227" s="27" t="inlineStr">
-        <is>
-          <t>Number of seconds till Load Can't be put on Grid</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="15" customHeight="1" s="19">
-      <c r="A228" s="29" t="inlineStr">
-        <is>
-          <t>Disable Load On Solar Duration Remaining</t>
-        </is>
-      </c>
-      <c r="B228" s="27" t="inlineStr">
-        <is>
-          <t>Seconds</t>
-        </is>
-      </c>
-      <c r="C228" s="27" t="inlineStr">
-        <is>
-          <t>Unsigned Integer</t>
-        </is>
-      </c>
-      <c r="D228" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E228" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F228" s="27" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G228" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16001 </t>
-        </is>
-      </c>
-      <c r="H228" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I228" s="27" t="inlineStr">
-        <is>
-          <t>Number of seconds till Load Can't be put on Solar</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="15" customHeight="1" s="19">
-      <c r="A229" s="29" t="inlineStr">
-        <is>
-          <t>Mains Under Voltage Setting</t>
-        </is>
-      </c>
-      <c r="B229" s="27" t="inlineStr">
-        <is>
-          <t>Volts</t>
-        </is>
-      </c>
-      <c r="C229" s="27" t="inlineStr">
-        <is>
-          <t>Unsigned Integer</t>
-        </is>
-      </c>
-      <c r="D229" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E229" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F229" s="27" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G229" s="30" t="inlineStr">
-        <is>
-          <t>30001</t>
-        </is>
-      </c>
-      <c r="H229" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I229" s="27" t="n"/>
+      <c r="B229" s="25" t="n"/>
+      <c r="C229" s="25" t="n"/>
+      <c r="D229" s="25" t="n"/>
+      <c r="E229" s="25" t="n"/>
+      <c r="F229" s="25" t="n"/>
+      <c r="G229" s="25" t="n"/>
+      <c r="H229" s="25" t="n"/>
+      <c r="I229" s="25" t="n"/>
     </row>
     <row r="230" ht="15" customHeight="1" s="19">
       <c r="A230" s="29" t="inlineStr">
         <is>
-          <t>Mains Over Voltage Setting</t>
+          <t>Disable Load On Grid Duration Remaining</t>
         </is>
       </c>
       <c r="B230" s="27" t="inlineStr">
         <is>
-          <t>Volts</t>
+          <t>Seconds</t>
         </is>
       </c>
       <c r="C230" s="27" t="inlineStr">
@@ -16844,23 +16851,27 @@
       </c>
       <c r="G230" s="30" t="inlineStr">
         <is>
-          <t>30003</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="H230" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="I230" s="27" t="n"/>
+      <c r="I230" s="27" t="inlineStr">
+        <is>
+          <t>Number of seconds till Load Can't be put on Grid</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="15" customHeight="1" s="19">
       <c r="A231" s="29" t="inlineStr">
         <is>
-          <t>Mains Under Voltage Reset Setting</t>
+          <t>Disable Load On Solar Duration Remaining</t>
         </is>
       </c>
       <c r="B231" s="27" t="inlineStr">
         <is>
-          <t>Volts</t>
+          <t>Seconds</t>
         </is>
       </c>
       <c r="C231" s="27" t="inlineStr">
@@ -16881,18 +16892,22 @@
       </c>
       <c r="G231" s="30" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t xml:space="preserve">16001 </t>
         </is>
       </c>
       <c r="H231" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="I231" s="27" t="n"/>
+      <c r="I231" s="27" t="inlineStr">
+        <is>
+          <t>Number of seconds till Load Can't be put on Solar</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="15" customHeight="1" s="19">
       <c r="A232" s="29" t="inlineStr">
         <is>
-          <t>Mains Over Voltage Reset Setting</t>
+          <t>Mains Under Voltage Setting</t>
         </is>
       </c>
       <c r="B232" s="27" t="inlineStr">
@@ -16918,7 +16933,7 @@
       </c>
       <c r="G232" s="30" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>30001</t>
         </is>
       </c>
       <c r="H232" s="27" t="n">
@@ -16929,12 +16944,12 @@
     <row r="233" ht="15" customHeight="1" s="19">
       <c r="A233" s="29" t="inlineStr">
         <is>
-          <t>Mains Fail Delay Setting</t>
+          <t>Mains Over Voltage Setting</t>
         </is>
       </c>
       <c r="B233" s="27" t="inlineStr">
         <is>
-          <t>Seconds</t>
+          <t>Volts</t>
         </is>
       </c>
       <c r="C233" s="27" t="inlineStr">
@@ -16955,7 +16970,7 @@
       </c>
       <c r="G233" s="30" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30003</t>
         </is>
       </c>
       <c r="H233" s="27" t="n">
@@ -16966,12 +16981,12 @@
     <row r="234" ht="15" customHeight="1" s="19">
       <c r="A234" s="29" t="inlineStr">
         <is>
-          <t>Mains Return Delay Setting</t>
+          <t>Mains Under Voltage Reset Setting</t>
         </is>
       </c>
       <c r="B234" s="27" t="inlineStr">
         <is>
-          <t>Seconds</t>
+          <t>Volts</t>
         </is>
       </c>
       <c r="C234" s="27" t="inlineStr">
@@ -16992,7 +17007,7 @@
       </c>
       <c r="G234" s="30" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>30005</t>
         </is>
       </c>
       <c r="H234" s="27" t="n">
@@ -17003,7 +17018,7 @@
     <row r="235" ht="15" customHeight="1" s="19">
       <c r="A235" s="29" t="inlineStr">
         <is>
-          <t>Solar Under Voltage Setting</t>
+          <t>Mains Over Voltage Reset Setting</t>
         </is>
       </c>
       <c r="B235" s="27" t="inlineStr">
@@ -17029,7 +17044,7 @@
       </c>
       <c r="G235" s="30" t="inlineStr">
         <is>
-          <t>30013</t>
+          <t>30007</t>
         </is>
       </c>
       <c r="H235" s="27" t="n">
@@ -17040,12 +17055,12 @@
     <row r="236" ht="15" customHeight="1" s="19">
       <c r="A236" s="29" t="inlineStr">
         <is>
-          <t>Solar Over Voltage Setting</t>
+          <t>Mains Fail Delay Setting</t>
         </is>
       </c>
       <c r="B236" s="27" t="inlineStr">
         <is>
-          <t>Volts</t>
+          <t>Seconds</t>
         </is>
       </c>
       <c r="C236" s="27" t="inlineStr">
@@ -17066,7 +17081,7 @@
       </c>
       <c r="G236" s="30" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="H236" s="27" t="n">
@@ -17077,12 +17092,12 @@
     <row r="237" ht="15" customHeight="1" s="19">
       <c r="A237" s="29" t="inlineStr">
         <is>
-          <t>Solar Under Voltage Reset Setting</t>
+          <t>Mains Return Delay Setting</t>
         </is>
       </c>
       <c r="B237" s="27" t="inlineStr">
         <is>
-          <t>Volts</t>
+          <t>Seconds</t>
         </is>
       </c>
       <c r="C237" s="27" t="inlineStr">
@@ -17103,7 +17118,7 @@
       </c>
       <c r="G237" s="30" t="inlineStr">
         <is>
-          <t>30017</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="H237" s="27" t="n">
@@ -17114,7 +17129,7 @@
     <row r="238" ht="15" customHeight="1" s="19">
       <c r="A238" s="29" t="inlineStr">
         <is>
-          <t>Solar Over Voltage Reset Setting</t>
+          <t>Solar Under Voltage Setting</t>
         </is>
       </c>
       <c r="B238" s="27" t="inlineStr">
@@ -17140,7 +17155,7 @@
       </c>
       <c r="G238" s="30" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="H238" s="27" t="n">
@@ -17151,12 +17166,12 @@
     <row r="239" ht="15" customHeight="1" s="19">
       <c r="A239" s="29" t="inlineStr">
         <is>
-          <t>Solar Fail Delay Setting</t>
+          <t>Solar Over Voltage Setting</t>
         </is>
       </c>
       <c r="B239" s="27" t="inlineStr">
         <is>
-          <t>Seconds</t>
+          <t>Volts</t>
         </is>
       </c>
       <c r="C239" s="27" t="inlineStr">
@@ -17177,7 +17192,7 @@
       </c>
       <c r="G239" s="30" t="inlineStr">
         <is>
-          <t>30021</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="H239" s="27" t="n">
@@ -17188,12 +17203,12 @@
     <row r="240" ht="15" customHeight="1" s="19">
       <c r="A240" s="29" t="inlineStr">
         <is>
-          <t>Solar Return Delay Setting</t>
+          <t>Solar Under Voltage Reset Setting</t>
         </is>
       </c>
       <c r="B240" s="27" t="inlineStr">
         <is>
-          <t>Seconds</t>
+          <t>Volts</t>
         </is>
       </c>
       <c r="C240" s="27" t="inlineStr">
@@ -17214,7 +17229,7 @@
       </c>
       <c r="G240" s="30" t="inlineStr">
         <is>
-          <t>30023</t>
+          <t>30017</t>
         </is>
       </c>
       <c r="H240" s="27" t="n">
@@ -17225,12 +17240,12 @@
     <row r="241" ht="15" customHeight="1" s="19">
       <c r="A241" s="29" t="inlineStr">
         <is>
-          <t>Fan Under Current Setting</t>
+          <t>Solar Over Voltage Reset Setting</t>
         </is>
       </c>
       <c r="B241" s="27" t="inlineStr">
         <is>
-          <t>Milli Ampere</t>
+          <t>Volts</t>
         </is>
       </c>
       <c r="C241" s="27" t="inlineStr">
@@ -17251,7 +17266,7 @@
       </c>
       <c r="G241" s="30" t="inlineStr">
         <is>
-          <t>30025</t>
+          <t>30019</t>
         </is>
       </c>
       <c r="H241" s="27" t="n">
@@ -17262,12 +17277,12 @@
     <row r="242" ht="15" customHeight="1" s="19">
       <c r="A242" s="29" t="inlineStr">
         <is>
-          <t>Fan Over Current Setting</t>
+          <t>Solar Fail Delay Setting</t>
         </is>
       </c>
       <c r="B242" s="27" t="inlineStr">
         <is>
-          <t>Milli Ampere</t>
+          <t>Seconds</t>
         </is>
       </c>
       <c r="C242" s="27" t="inlineStr">
@@ -17288,7 +17303,7 @@
       </c>
       <c r="G242" s="30" t="inlineStr">
         <is>
-          <t>30027</t>
+          <t>30021</t>
         </is>
       </c>
       <c r="H242" s="27" t="n">
@@ -17299,12 +17314,12 @@
     <row r="243" ht="15" customHeight="1" s="19">
       <c r="A243" s="29" t="inlineStr">
         <is>
-          <t>Over Temperature Setting</t>
+          <t>Solar Return Delay Setting</t>
         </is>
       </c>
       <c r="B243" s="27" t="inlineStr">
         <is>
-          <t>Celsius</t>
+          <t>Seconds</t>
         </is>
       </c>
       <c r="C243" s="27" t="inlineStr">
@@ -17325,7 +17340,7 @@
       </c>
       <c r="G243" s="30" t="inlineStr">
         <is>
-          <t>30029</t>
+          <t>30023</t>
         </is>
       </c>
       <c r="H243" s="27" t="n">
@@ -17336,12 +17351,12 @@
     <row r="244" ht="15" customHeight="1" s="19">
       <c r="A244" s="29" t="inlineStr">
         <is>
-          <t>Under Temperature Setting</t>
+          <t>Fan Under Current Setting</t>
         </is>
       </c>
       <c r="B244" s="27" t="inlineStr">
         <is>
-          <t>Celsius</t>
+          <t>Milli Ampere</t>
         </is>
       </c>
       <c r="C244" s="27" t="inlineStr">
@@ -17362,7 +17377,7 @@
       </c>
       <c r="G244" s="30" t="inlineStr">
         <is>
-          <t>30031</t>
+          <t>30025</t>
         </is>
       </c>
       <c r="H244" s="27" t="n">
@@ -17373,12 +17388,12 @@
     <row r="245" ht="15" customHeight="1" s="19">
       <c r="A245" s="29" t="inlineStr">
         <is>
-          <t>Over Temperature Delay Setting</t>
+          <t>Fan Over Current Setting</t>
         </is>
       </c>
       <c r="B245" s="27" t="inlineStr">
         <is>
-          <t>Seconds</t>
+          <t>Milli Ampere</t>
         </is>
       </c>
       <c r="C245" s="27" t="inlineStr">
@@ -17399,7 +17414,7 @@
       </c>
       <c r="G245" s="30" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>30027</t>
         </is>
       </c>
       <c r="H245" s="27" t="n">
@@ -17410,199 +17425,310 @@
     <row r="246" ht="15" customHeight="1" s="19">
       <c r="A246" s="29" t="inlineStr">
         <is>
+          <t>Over Temperature Setting</t>
+        </is>
+      </c>
+      <c r="B246" s="27" t="inlineStr">
+        <is>
+          <t>Celsius</t>
+        </is>
+      </c>
+      <c r="C246" s="27" t="inlineStr">
+        <is>
+          <t>Unsigned Integer</t>
+        </is>
+      </c>
+      <c r="D246" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E246" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F246" s="27" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G246" s="30" t="inlineStr">
+        <is>
+          <t>30029</t>
+        </is>
+      </c>
+      <c r="H246" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I246" s="27" t="n"/>
+    </row>
+    <row r="247" ht="15" customHeight="1" s="19">
+      <c r="A247" s="29" t="inlineStr">
+        <is>
+          <t>Under Temperature Setting</t>
+        </is>
+      </c>
+      <c r="B247" s="27" t="inlineStr">
+        <is>
+          <t>Celsius</t>
+        </is>
+      </c>
+      <c r="C247" s="27" t="inlineStr">
+        <is>
+          <t>Unsigned Integer</t>
+        </is>
+      </c>
+      <c r="D247" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E247" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F247" s="27" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G247" s="30" t="inlineStr">
+        <is>
+          <t>30031</t>
+        </is>
+      </c>
+      <c r="H247" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I247" s="27" t="n"/>
+    </row>
+    <row r="248" ht="15" customHeight="1" s="19">
+      <c r="A248" s="29" t="inlineStr">
+        <is>
+          <t>Over Temperature Delay Setting</t>
+        </is>
+      </c>
+      <c r="B248" s="27" t="inlineStr">
+        <is>
+          <t>Seconds</t>
+        </is>
+      </c>
+      <c r="C248" s="27" t="inlineStr">
+        <is>
+          <t>Unsigned Integer</t>
+        </is>
+      </c>
+      <c r="D248" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E248" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" s="27" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G248" s="30" t="inlineStr">
+        <is>
+          <t>30033</t>
+        </is>
+      </c>
+      <c r="H248" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I248" s="27" t="n"/>
+    </row>
+    <row r="249" ht="15" customHeight="1" s="19">
+      <c r="A249" s="29" t="inlineStr">
+        <is>
           <t>Under Temperature Delay Setting</t>
         </is>
       </c>
-      <c r="B246" s="27" t="inlineStr">
+      <c r="B249" s="27" t="inlineStr">
         <is>
           <t>Seconds</t>
         </is>
       </c>
-      <c r="C246" s="27" t="inlineStr">
+      <c r="C249" s="27" t="inlineStr">
         <is>
           <t>Unsigned Integer</t>
         </is>
       </c>
-      <c r="D246" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E246" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F246" s="27" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G246" s="30" t="inlineStr">
+      <c r="D249" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E249" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" s="27" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G249" s="30" t="inlineStr">
         <is>
           <t>30035</t>
         </is>
       </c>
-      <c r="H246" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I246" s="27" t="n"/>
-    </row>
-    <row r="247" ht="15" customHeight="1" s="19">
-      <c r="A247" s="27" t="inlineStr">
+      <c r="H249" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I249" s="27" t="n"/>
+    </row>
+    <row r="250" ht="15" customHeight="1" s="19">
+      <c r="A250" s="27" t="inlineStr">
         <is>
           <t>DG Detection Enable/Disable Setting</t>
         </is>
       </c>
-      <c r="B247" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C247" s="27" t="inlineStr">
+      <c r="B250" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C250" s="27" t="inlineStr">
         <is>
           <t>Unsigned Integer</t>
         </is>
       </c>
-      <c r="D247" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E247" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F247" s="27" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G247" s="30" t="inlineStr">
+      <c r="D250" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E250" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" s="27" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G250" s="30" t="inlineStr">
         <is>
           <t>30037</t>
         </is>
       </c>
-      <c r="H247" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I247" s="27" t="inlineStr">
+      <c r="H250" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I250" s="27" t="inlineStr">
         <is>
           <t>0: OFF (DG Detection Enabled), 1: ON (DG Detection Disabled)</t>
         </is>
       </c>
     </row>
-    <row r="248" ht="15" customHeight="1" s="19">
-      <c r="A248" s="27" t="inlineStr">
+    <row r="251" ht="15" customHeight="1" s="19">
+      <c r="A251" s="27" t="inlineStr">
         <is>
           <t>Fan Disable Setting</t>
         </is>
       </c>
-      <c r="B248" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C248" s="27" t="inlineStr">
+      <c r="B251" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C251" s="27" t="inlineStr">
         <is>
           <t>Unsigned Integer</t>
         </is>
       </c>
-      <c r="D248" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E248" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F248" s="27" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G248" s="30" t="inlineStr">
+      <c r="D251" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E251" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" s="27" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G251" s="30" t="inlineStr">
         <is>
           <t>30039</t>
         </is>
       </c>
-      <c r="H248" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I248" s="27" t="inlineStr">
+      <c r="H251" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I251" s="27" t="inlineStr">
         <is>
           <t>0: OFF (Fans Enabled), 1: ON (Fans Disabled)</t>
         </is>
       </c>
     </row>
-    <row r="249" ht="29.2" customHeight="1" s="19">
-      <c r="A249" s="27" t="inlineStr">
+    <row r="252" ht="29.2" customHeight="1" s="19">
+      <c r="A252" s="27" t="inlineStr">
         <is>
           <t>Firmware Upgrade Status</t>
         </is>
       </c>
-      <c r="B249" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C249" s="27" t="inlineStr">
+      <c r="B252" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C252" s="27" t="inlineStr">
         <is>
           <t>Unsigned Integer</t>
         </is>
       </c>
-      <c r="D249" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E249" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F249" s="27" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G249" s="30" t="inlineStr">
+      <c r="D252" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E252" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F252" s="27" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G252" s="30" t="inlineStr">
         <is>
           <t>40001</t>
         </is>
       </c>
-      <c r="H249" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I249" s="27" t="inlineStr">
+      <c r="H252" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I252" s="27" t="inlineStr">
         <is>
           <t>0: No Action, 1:Signals start of Firmware Uploading, 2: Signals end of Firmware Uploading</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="27.9" customHeight="1" s="19">
-      <c r="A250" s="32" t="inlineStr">
+    <row r="253" ht="27.9" customHeight="1" s="19">
+      <c r="A253" s="32" t="inlineStr">
         <is>
           <t>Serial Number Lower Half</t>
         </is>
       </c>
-      <c r="B250" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C250" s="32" t="inlineStr">
+      <c r="B253" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C253" s="32" t="inlineStr">
         <is>
           <t>Unsigned Integer</t>
         </is>
       </c>
-      <c r="D250" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E250" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F250" s="32" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G250" s="32" t="inlineStr">
+      <c r="D253" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E253" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F253" s="32" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G253" s="32" t="inlineStr">
         <is>
           <t>50003</t>
         </is>
       </c>
-      <c r="H250" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I250" s="32" t="inlineStr">
+      <c r="H253" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I253" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer. 
 Only writtable when test mode enabled.
@@ -17610,42 +17736,42 @@
         </is>
       </c>
     </row>
-    <row r="251" ht="27.9" customHeight="1" s="19">
-      <c r="A251" s="32" t="inlineStr">
+    <row r="254" ht="27.9" customHeight="1" s="19">
+      <c r="A254" s="32" t="inlineStr">
         <is>
           <t>Serial Number Upper Half</t>
         </is>
       </c>
-      <c r="B251" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C251" s="32" t="inlineStr">
+      <c r="B254" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C254" s="32" t="inlineStr">
         <is>
           <t>Unsigned Integer</t>
         </is>
       </c>
-      <c r="D251" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E251" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F251" s="32" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G251" s="32" t="inlineStr">
+      <c r="D254" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E254" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" s="32" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G254" s="32" t="inlineStr">
         <is>
           <t>50005</t>
         </is>
       </c>
-      <c r="H251" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I251" s="32" t="inlineStr">
+      <c r="H254" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I254" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer. 
 Only writtable when test mode enabled.
@@ -17653,177 +17779,174 @@
         </is>
       </c>
     </row>
-    <row r="252" ht="46.25" customHeight="1" s="19">
-      <c r="A252" s="31" t="inlineStr">
+    <row r="255" ht="46.25" customHeight="1" s="19">
+      <c r="A255" s="31" t="inlineStr">
         <is>
           <t>Functionally Tested</t>
         </is>
       </c>
-      <c r="B252" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C252" s="32" t="inlineStr">
+      <c r="B255" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C255" s="32" t="inlineStr">
         <is>
           <t>Unsigned Integer</t>
         </is>
       </c>
-      <c r="D252" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E252" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F252" s="32" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G252" s="33" t="inlineStr">
+      <c r="D255" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E255" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F255" s="32" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G255" s="33" t="inlineStr">
         <is>
           <t>50009</t>
         </is>
       </c>
-      <c r="H252" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I252" s="32" t="inlineStr">
+      <c r="H255" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer. 
 If set to non-zero, indicates product was tested functionally during production. Only writtable when test mode enabled. Suggested to write the Unix Timestamp for the time when the product was functionally tested.</t>
         </is>
       </c>
     </row>
-    <row r="253" ht="46.25" customHeight="1" s="19">
-      <c r="A253" s="31" t="inlineStr">
+    <row r="256" ht="46.25" customHeight="1" s="19">
+      <c r="A256" s="31" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="B253" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C253" s="32" t="inlineStr">
+      <c r="B256" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C256" s="32" t="inlineStr">
         <is>
           <t>Unsigned Integer</t>
         </is>
       </c>
-      <c r="D253" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E253" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F253" s="32" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G253" s="33" t="inlineStr">
+      <c r="D256" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E256" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" s="32" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G256" s="33" t="inlineStr">
         <is>
           <t>50011</t>
         </is>
       </c>
-      <c r="H253" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I253" s="32" t="inlineStr">
+      <c r="H256" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I256" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer. 
 If set to non-zero, indicates product was calibrated during production. Only writtable when test mode enabled. Suggested to write Unix Epoch Timestamp of the time when calibration took place</t>
         </is>
       </c>
     </row>
-    <row r="254" ht="37.3" customHeight="1" s="19">
-      <c r="A254" s="31" t="inlineStr">
+    <row r="257" ht="37.3" customHeight="1" s="19">
+      <c r="A257" s="31" t="inlineStr">
         <is>
           <t>Advance Calibration State</t>
         </is>
       </c>
-      <c r="B254" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C254" s="32" t="inlineStr">
+      <c r="B257" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C257" s="32" t="inlineStr">
         <is>
           <t>Unsigned Integer</t>
         </is>
       </c>
-      <c r="D254" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E254" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F254" s="32" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G254" s="33" t="inlineStr">
+      <c r="D257" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E257" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F257" s="32" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G257" s="33" t="inlineStr">
         <is>
           <t>50013</t>
         </is>
       </c>
-      <c r="H254" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I254" s="32" t="inlineStr">
+      <c r="H257" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I257" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer. 
 If set to non-zero, it advances the calibration state machine when it is waiting for external input. Only writtable when test mode enabled.</t>
         </is>
       </c>
     </row>
-    <row r="255" ht="28.35" customHeight="1" s="19">
-      <c r="A255" s="31" t="inlineStr">
+    <row r="258" ht="28.35" customHeight="1" s="19">
+      <c r="A258" s="31" t="inlineStr">
         <is>
           <t>Scratch Pad</t>
         </is>
       </c>
-      <c r="B255" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NA </t>
-        </is>
-      </c>
-      <c r="C255" s="32" t="inlineStr">
+      <c r="B258" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA </t>
+        </is>
+      </c>
+      <c r="C258" s="32" t="inlineStr">
         <is>
           <t>Unsigned Integer</t>
         </is>
       </c>
-      <c r="D255" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E255" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F255" s="32" t="inlineStr">
-        <is>
-          <t>Holding Register</t>
-        </is>
-      </c>
-      <c r="G255" s="33" t="inlineStr">
+      <c r="D258" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E258" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F258" s="32" t="inlineStr">
+        <is>
+          <t>Holding Register</t>
+        </is>
+      </c>
+      <c r="G258" s="33" t="inlineStr">
         <is>
           <t>50015</t>
         </is>
       </c>
-      <c r="H255" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I255" s="32" t="inlineStr">
+      <c r="H258" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I258" s="32" t="inlineStr">
         <is>
           <t>Internal Only. Not visible to customer. 
 Used to store a temporarily value. Resets when SOCO restarts on POR.</t>
         </is>
       </c>
     </row>
-    <row r="1048566" ht="12.8" customHeight="1" s="19"/>
-    <row r="1048567" ht="12.8" customHeight="1" s="19"/>
-    <row r="1048568" ht="12.8" customHeight="1" s="19"/>
     <row r="1048569" ht="12.8" customHeight="1" s="19"/>
     <row r="1048570" ht="12.8" customHeight="1" s="19"/>
     <row r="1048571" ht="12.8" customHeight="1" s="19"/>
@@ -17832,31 +17955,34 @@
     <row r="1048574" ht="12.8" customHeight="1" s="19"/>
     <row r="1048575" ht="12.8" customHeight="1" s="19"/>
     <row r="1048576" ht="12.8" customHeight="1" s="19"/>
+    <row r="1048577" ht="12.8" customHeight="1" s="19"/>
+    <row r="1048578" ht="12.8" customHeight="1" s="19"/>
+    <row r="1048579" ht="12.8" customHeight="1" s="19"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I179:I180"/>
-    <mergeCell ref="F205:F206"/>
-    <mergeCell ref="D179:D180"/>
+    <mergeCell ref="I182:I183"/>
+    <mergeCell ref="F208:F209"/>
+    <mergeCell ref="D182:D183"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="A181:I181"/>
-    <mergeCell ref="I205:I206"/>
+    <mergeCell ref="I227:I228"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:I184"/>
+    <mergeCell ref="I208:I209"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="D205:D206"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="F179:F180"/>
-    <mergeCell ref="D117:D118"/>
-    <mergeCell ref="F117:F118"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="A226:I226"/>
-    <mergeCell ref="A207:I207"/>
+    <mergeCell ref="D208:D209"/>
+    <mergeCell ref="D227:D228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="I120:I121"/>
+    <mergeCell ref="F182:F183"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="F120:F121"/>
+    <mergeCell ref="A227:A228"/>
+    <mergeCell ref="A229:I229"/>
+    <mergeCell ref="A210:I210"/>
     <mergeCell ref="I6:I7"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A119:I119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:I122"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="F6:F7"/>
   </mergeCells>

--- a/Document/SOCOModbusTable.xlsx
+++ b/Document/SOCOModbusTable.xlsx
@@ -4403,7 +4403,7 @@
     <row r="106" ht="15" customHeight="1" s="19">
       <c r="A106" s="27" t="inlineStr">
         <is>
-          <t>DG Detection Disable Setting</t>
+          <t>DG Detection Enable/Disable Setting</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
@@ -11872,7 +11872,7 @@
     <row r="106" ht="15" customHeight="1" s="19">
       <c r="A106" s="27" t="inlineStr">
         <is>
-          <t>DG Detection Disable Setting</t>
+          <t>DG Detection Enable/Disable Setting</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
